--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -650,10 +650,10 @@
         <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>74676.65579999999</v>
+        <v>74676.655510204</v>
       </c>
       <c r="O6" t="n">
-        <v>1493533.116</v>
+        <v>1493533.11020408</v>
       </c>
       <c r="P6" t="n">
         <v>144900</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -727,19 +727,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N8" t="n">
-        <v>1811.303568532</v>
+        <v>1811.3036050799</v>
       </c>
       <c r="O8" t="n">
-        <v>74263.446309812</v>
+        <v>67018.23338795631</v>
       </c>
       <c r="P8" t="n">
         <v>2600</v>
       </c>
       <c r="Q8" t="n">
-        <v>106600</v>
+        <v>96200</v>
       </c>
     </row>
     <row r="9">
@@ -808,10 +808,10 @@
         <v>476</v>
       </c>
       <c r="N10" t="n">
-        <v>3376.7465268817</v>
+        <v>3376.7465222073</v>
       </c>
       <c r="O10" t="n">
-        <v>1607331.346795689</v>
+        <v>1607331.344570675</v>
       </c>
       <c r="P10" t="n">
         <v>4500</v>
@@ -1326,10 +1326,10 @@
         <v>180</v>
       </c>
       <c r="N23" t="n">
-        <v>3926.8371355499</v>
+        <v>3926.8371340839</v>
       </c>
       <c r="O23" t="n">
-        <v>706830.684398982</v>
+        <v>706830.684135102</v>
       </c>
       <c r="P23" t="n">
         <v>4800</v>
@@ -1560,10 +1560,10 @@
         <v>17</v>
       </c>
       <c r="N29" t="n">
-        <v>15403.520437158</v>
+        <v>15403.520494505</v>
       </c>
       <c r="O29" t="n">
-        <v>261859.847431686</v>
+        <v>261859.848406585</v>
       </c>
       <c r="P29" t="n">
         <v>33500</v>
@@ -1893,10 +1893,10 @@
         <v>7</v>
       </c>
       <c r="N37" t="n">
-        <v>62349.661025641</v>
+        <v>62349.660526316</v>
       </c>
       <c r="O37" t="n">
-        <v>436447.627179487</v>
+        <v>436447.623684212</v>
       </c>
       <c r="P37" t="n">
         <v>109900</v>
@@ -1987,10 +1987,10 @@
         <v>71</v>
       </c>
       <c r="N39" t="n">
-        <v>141416.88438871</v>
+        <v>141416.8844164</v>
       </c>
       <c r="O39" t="n">
-        <v>10040598.79159841</v>
+        <v>10040598.7935644</v>
       </c>
       <c r="P39" t="n">
         <v>251900</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2026,19 +2026,19 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N40" t="n">
-        <v>200072.19883562</v>
+        <v>200072.19889655</v>
       </c>
       <c r="O40" t="n">
-        <v>9003248.9476029</v>
+        <v>8002887.955862</v>
       </c>
       <c r="P40" t="n">
         <v>312000</v>
       </c>
       <c r="Q40" t="n">
-        <v>14040000</v>
+        <v>12480000</v>
       </c>
     </row>
     <row r="41">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2117,19 +2117,19 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N42" t="n">
         <v>344599.17885246</v>
       </c>
       <c r="O42" t="n">
-        <v>3790590.96737706</v>
+        <v>3101392.60967214</v>
       </c>
       <c r="P42" t="n">
         <v>532900</v>
       </c>
       <c r="Q42" t="n">
-        <v>5861900</v>
+        <v>4796100</v>
       </c>
     </row>
     <row r="43">
@@ -2167,10 +2167,10 @@
         <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>263530.18090909</v>
+        <v>263530.18</v>
       </c>
       <c r="O43" t="n">
-        <v>527060.36181818</v>
+        <v>527060.36</v>
       </c>
       <c r="P43" t="n">
         <v>402900</v>
@@ -3498,10 +3498,10 @@
         <v>2592</v>
       </c>
       <c r="N74" t="n">
-        <v>3158.8608104732</v>
+        <v>3158.8608123465</v>
       </c>
       <c r="O74" t="n">
-        <v>8187767.220746535</v>
+        <v>8187767.225602129</v>
       </c>
       <c r="P74" t="n">
         <v>5600</v>
@@ -3861,10 +3861,10 @@
         <v>396</v>
       </c>
       <c r="N82" t="n">
-        <v>4890.9300453258</v>
+        <v>4890.9300453515</v>
       </c>
       <c r="O82" t="n">
-        <v>1936808.297949017</v>
+        <v>1936808.297959194</v>
       </c>
       <c r="P82" t="n">
         <v>8200</v>
@@ -4181,10 +4181,10 @@
         <v>288</v>
       </c>
       <c r="N89" t="n">
-        <v>3594.2542925089</v>
+        <v>3594.2542686567</v>
       </c>
       <c r="O89" t="n">
-        <v>1035145.236242563</v>
+        <v>1035145.22937313</v>
       </c>
       <c r="P89" t="n">
         <v>6500</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4773,19 +4773,19 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N102" t="n">
         <v>3655.96</v>
       </c>
       <c r="O102" t="n">
-        <v>179142.04</v>
+        <v>149894.36</v>
       </c>
       <c r="P102" t="n">
         <v>5500</v>
       </c>
       <c r="Q102" t="n">
-        <v>269500</v>
+        <v>225500</v>
       </c>
     </row>
     <row r="103">
@@ -6273,10 +6273,10 @@
         <v>576</v>
       </c>
       <c r="N135" t="n">
-        <v>2029.8734883721</v>
+        <v>2029.8735277516</v>
       </c>
       <c r="O135" t="n">
-        <v>1169207.12930233</v>
+        <v>1169207.151984922</v>
       </c>
       <c r="P135" t="n">
         <v>3600</v>
@@ -6486,10 +6486,10 @@
         <v>310</v>
       </c>
       <c r="N140" t="n">
-        <v>2680.7397012195</v>
+        <v>2680.739700672</v>
       </c>
       <c r="O140" t="n">
-        <v>831029.3073780451</v>
+        <v>831029.3072083199</v>
       </c>
       <c r="P140" t="n">
         <v>4900</v>
@@ -6670,10 +6670,10 @@
         <v>799</v>
       </c>
       <c r="N144" t="n">
-        <v>998.76124730022</v>
+        <v>998.76125748503</v>
       </c>
       <c r="O144" t="n">
-        <v>798010.2365928758</v>
+        <v>798010.2447305389</v>
       </c>
       <c r="P144" t="n">
         <v>1600</v>
@@ -6765,10 +6765,10 @@
         <v>36</v>
       </c>
       <c r="N146" t="n">
-        <v>4285.1951158107</v>
+        <v>4285.1951469098</v>
       </c>
       <c r="O146" t="n">
-        <v>154267.0241691852</v>
+        <v>154267.0252887528</v>
       </c>
       <c r="P146" t="n">
         <v>6900</v>
@@ -6893,10 +6893,10 @@
         <v>55</v>
       </c>
       <c r="N149" t="n">
-        <v>30244.600034602</v>
+        <v>30244.600034662</v>
       </c>
       <c r="O149" t="n">
-        <v>1663453.00190311</v>
+        <v>1663453.00190641</v>
       </c>
       <c r="P149" t="n">
         <v>48900</v>
@@ -7573,10 +7573,10 @@
         <v>714</v>
       </c>
       <c r="N164" t="n">
-        <v>1560.9979018405</v>
+        <v>1560.9980701754</v>
       </c>
       <c r="O164" t="n">
-        <v>1114552.501914117</v>
+        <v>1114552.622105236</v>
       </c>
       <c r="P164" t="n">
         <v>2900</v>
@@ -8568,10 +8568,10 @@
         <v>680</v>
       </c>
       <c r="N186" t="n">
-        <v>1778.4724932172</v>
+        <v>1778.4724989266</v>
       </c>
       <c r="O186" t="n">
-        <v>1209361.295387696</v>
+        <v>1209361.299270088</v>
       </c>
       <c r="P186" t="n">
         <v>4900</v>
@@ -9905,10 +9905,10 @@
         <v>162</v>
       </c>
       <c r="N215" t="n">
-        <v>4907.8218731563</v>
+        <v>4907.821884273</v>
       </c>
       <c r="O215" t="n">
-        <v>795067.1434513206</v>
+        <v>795067.145252226</v>
       </c>
       <c r="P215" t="n">
         <v>8200</v>
@@ -10135,10 +10135,10 @@
         <v>280</v>
       </c>
       <c r="N220" t="n">
-        <v>3903.7357803468</v>
+        <v>3903.7358031838</v>
       </c>
       <c r="O220" t="n">
-        <v>1093046.018497104</v>
+        <v>1093046.024891464</v>
       </c>
       <c r="P220" t="n">
         <v>7500</v>
@@ -10539,10 +10539,10 @@
         <v>144</v>
       </c>
       <c r="N229" t="n">
-        <v>5869.1728472222</v>
+        <v>5869.1728258706</v>
       </c>
       <c r="O229" t="n">
-        <v>845160.8899999969</v>
+        <v>845160.8869253664</v>
       </c>
       <c r="P229" t="n">
         <v>9500</v>
@@ -11551,10 +11551,10 @@
         <v>192</v>
       </c>
       <c r="N251" t="n">
-        <v>17075.989526424</v>
+        <v>17075.98952512</v>
       </c>
       <c r="O251" t="n">
-        <v>3278589.989073408</v>
+        <v>3278589.98882304</v>
       </c>
       <c r="P251" t="n">
         <v>27500</v>
@@ -12416,7 +12416,7 @@
         </is>
       </c>
       <c r="J270" t="n">
-        <v>2181</v>
+        <v>2081</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -12425,19 +12425,19 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>2181</v>
+        <v>2081</v>
       </c>
       <c r="N270" t="n">
         <v>1326</v>
       </c>
       <c r="O270" t="n">
-        <v>2892006</v>
+        <v>2759406</v>
       </c>
       <c r="P270" t="n">
         <v>2500</v>
       </c>
       <c r="Q270" t="n">
-        <v>5452500</v>
+        <v>5202500</v>
       </c>
     </row>
     <row r="271">
@@ -13072,10 +13072,10 @@
         <v>1152</v>
       </c>
       <c r="N284" t="n">
-        <v>1516.0388206553</v>
+        <v>1516.0388192979</v>
       </c>
       <c r="O284" t="n">
-        <v>1746476.721394906</v>
+        <v>1746476.719831181</v>
       </c>
       <c r="P284" t="n">
         <v>2300</v>
@@ -13439,10 +13439,10 @@
         <v>121</v>
       </c>
       <c r="N292" t="n">
-        <v>2857.22</v>
+        <v>2861.1357880311</v>
       </c>
       <c r="O292" t="n">
-        <v>345723.62</v>
+        <v>346197.4303517631</v>
       </c>
       <c r="P292" t="n">
         <v>4900</v>
@@ -13763,10 +13763,10 @@
         <v>1440</v>
       </c>
       <c r="N299" t="n">
-        <v>1690.8700087222</v>
+        <v>1690.8700087336</v>
       </c>
       <c r="O299" t="n">
-        <v>2434852.812559968</v>
+        <v>2434852.812576384</v>
       </c>
       <c r="P299" t="n">
         <v>3000</v>
@@ -13944,10 +13944,10 @@
         <v>1436</v>
       </c>
       <c r="N303" t="n">
-        <v>345.55838654429</v>
+        <v>345.55838640256</v>
       </c>
       <c r="O303" t="n">
-        <v>496221.8430776004</v>
+        <v>496221.8428740762</v>
       </c>
       <c r="P303" t="n">
         <v>600</v>
@@ -14322,10 +14322,10 @@
         <v>252</v>
       </c>
       <c r="N311" t="n">
-        <v>3110.8438819661</v>
+        <v>3110.8436976288</v>
       </c>
       <c r="O311" t="n">
-        <v>783932.6582554572</v>
+        <v>783932.6118024576</v>
       </c>
       <c r="P311" t="n">
         <v>4500</v>
@@ -14366,10 +14366,10 @@
         <v>17172</v>
       </c>
       <c r="N312" t="n">
-        <v>703.79553851454</v>
+        <v>703.79553051727</v>
       </c>
       <c r="O312" t="n">
-        <v>12085576.98737168</v>
+        <v>12085576.85004256</v>
       </c>
       <c r="P312" t="n">
         <v>900</v>
@@ -15802,10 +15802,10 @@
         <v>120</v>
       </c>
       <c r="N342" t="n">
-        <v>4159.0002826855</v>
+        <v>4159.0002836879</v>
       </c>
       <c r="O342" t="n">
-        <v>499080.03392226</v>
+        <v>499080.034042548</v>
       </c>
       <c r="P342" t="n">
         <v>8900</v>
@@ -16276,10 +16276,10 @@
         <v>699</v>
       </c>
       <c r="N352" t="n">
-        <v>7046.9398310097</v>
+        <v>7046.9398308668</v>
       </c>
       <c r="O352" t="n">
-        <v>4925810.941875781</v>
+        <v>4925810.941775893</v>
       </c>
       <c r="P352" t="n">
         <v>9900</v>
@@ -16783,10 +16783,10 @@
         <v>324</v>
       </c>
       <c r="N363" t="n">
-        <v>1008.8197488922</v>
+        <v>1008.8186415712</v>
       </c>
       <c r="O363" t="n">
-        <v>326857.5986410728</v>
+        <v>326857.2398690688</v>
       </c>
       <c r="P363" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -13439,10 +13439,10 @@
         <v>121</v>
       </c>
       <c r="N292" t="n">
-        <v>2861.1357880311</v>
+        <v>2857.22</v>
       </c>
       <c r="O292" t="n">
-        <v>346197.4303517631</v>
+        <v>345723.62</v>
       </c>
       <c r="P292" t="n">
         <v>4900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -650,10 +650,10 @@
         <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>74676.655510204</v>
+        <v>74676.654222222</v>
       </c>
       <c r="O6" t="n">
-        <v>1493533.11020408</v>
+        <v>1493533.08444444</v>
       </c>
       <c r="P6" t="n">
         <v>144900</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -727,19 +727,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N8" t="n">
-        <v>1811.3036050799</v>
+        <v>1811.3037351443</v>
       </c>
       <c r="O8" t="n">
-        <v>67018.23338795631</v>
+        <v>63395.6307300505</v>
       </c>
       <c r="P8" t="n">
         <v>2600</v>
       </c>
       <c r="Q8" t="n">
-        <v>96200</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="9">
@@ -808,10 +808,10 @@
         <v>476</v>
       </c>
       <c r="N10" t="n">
-        <v>3376.7465222073</v>
+        <v>3376.746520334</v>
       </c>
       <c r="O10" t="n">
-        <v>1607331.344570675</v>
+        <v>1607331.343678984</v>
       </c>
       <c r="P10" t="n">
         <v>4500</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1984,19 +1984,19 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="N39" t="n">
-        <v>141416.8844164</v>
+        <v>141416.8844586</v>
       </c>
       <c r="O39" t="n">
-        <v>10040598.7935644</v>
+        <v>9192097.489808999</v>
       </c>
       <c r="P39" t="n">
         <v>251900</v>
       </c>
       <c r="Q39" t="n">
-        <v>17884900</v>
+        <v>16373500</v>
       </c>
     </row>
     <row r="40">
@@ -2029,10 +2029,10 @@
         <v>40</v>
       </c>
       <c r="N40" t="n">
-        <v>200072.19889655</v>
+        <v>200072.19902098</v>
       </c>
       <c r="O40" t="n">
-        <v>8002887.955862</v>
+        <v>8002887.960839201</v>
       </c>
       <c r="P40" t="n">
         <v>312000</v>
@@ -2167,10 +2167,10 @@
         <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>263530.18</v>
+        <v>263530.179</v>
       </c>
       <c r="O43" t="n">
-        <v>527060.36</v>
+        <v>527060.358</v>
       </c>
       <c r="P43" t="n">
         <v>402900</v>
@@ -2370,10 +2370,10 @@
         <v>86</v>
       </c>
       <c r="N48" t="n">
-        <v>61666.873832487</v>
+        <v>61666.873842239</v>
       </c>
       <c r="O48" t="n">
-        <v>5303351.149593882</v>
+        <v>5303351.150432554</v>
       </c>
       <c r="P48" t="n">
         <v>98900</v>
@@ -3498,10 +3498,10 @@
         <v>2592</v>
       </c>
       <c r="N74" t="n">
-        <v>3158.8608123465</v>
+        <v>3158.860813208</v>
       </c>
       <c r="O74" t="n">
-        <v>8187767.225602129</v>
+        <v>8187767.227835136</v>
       </c>
       <c r="P74" t="n">
         <v>5600</v>
@@ -3544,10 +3544,10 @@
         <v>79</v>
       </c>
       <c r="N75" t="n">
-        <v>3841.6246596357</v>
+        <v>3841.6246641075</v>
       </c>
       <c r="O75" t="n">
-        <v>303488.3481112203</v>
+        <v>303488.3484644925</v>
       </c>
       <c r="P75" t="n">
         <v>6900</v>
@@ -3682,10 +3682,10 @@
         <v>648</v>
       </c>
       <c r="N78" t="n">
-        <v>3795.7100070286</v>
+        <v>3795.7100070299</v>
       </c>
       <c r="O78" t="n">
-        <v>2459620.084554533</v>
+        <v>2459620.084555375</v>
       </c>
       <c r="P78" t="n">
         <v>6200</v>
@@ -4181,10 +4181,10 @@
         <v>288</v>
       </c>
       <c r="N89" t="n">
-        <v>3594.2542686567</v>
+        <v>3594.2542583732</v>
       </c>
       <c r="O89" t="n">
-        <v>1035145.22937313</v>
+        <v>1035145.226411482</v>
       </c>
       <c r="P89" t="n">
         <v>6500</v>
@@ -4594,10 +4594,10 @@
         <v>5516</v>
       </c>
       <c r="N98" t="n">
-        <v>19098.750004659</v>
+        <v>19098.75000466</v>
       </c>
       <c r="O98" t="n">
-        <v>105348705.025699</v>
+        <v>105348705.0257046</v>
       </c>
       <c r="P98" t="n">
         <v>15000</v>
@@ -6314,10 +6314,10 @@
         <v>528</v>
       </c>
       <c r="N136" t="n">
-        <v>22485.695964126</v>
+        <v>22485.695955056</v>
       </c>
       <c r="O136" t="n">
-        <v>11872447.46905853</v>
+        <v>11872447.46426957</v>
       </c>
       <c r="P136" t="n">
         <v>36500</v>
@@ -6486,10 +6486,10 @@
         <v>310</v>
       </c>
       <c r="N140" t="n">
-        <v>2680.739700672</v>
+        <v>2680.739700489</v>
       </c>
       <c r="O140" t="n">
-        <v>831029.3072083199</v>
+        <v>831029.30715159</v>
       </c>
       <c r="P140" t="n">
         <v>4900</v>
@@ -6670,10 +6670,10 @@
         <v>799</v>
       </c>
       <c r="N144" t="n">
-        <v>998.76125748503</v>
+        <v>998.76125816993</v>
       </c>
       <c r="O144" t="n">
-        <v>798010.2447305389</v>
+        <v>798010.2452777741</v>
       </c>
       <c r="P144" t="n">
         <v>1600</v>
@@ -6765,10 +6765,10 @@
         <v>36</v>
       </c>
       <c r="N146" t="n">
-        <v>4285.1951469098</v>
+        <v>4285.1951678535</v>
       </c>
       <c r="O146" t="n">
-        <v>154267.0252887528</v>
+        <v>154267.026042726</v>
       </c>
       <c r="P146" t="n">
         <v>6900</v>
@@ -7389,10 +7389,10 @@
         <v>144</v>
       </c>
       <c r="N160" t="n">
-        <v>27123.765285451</v>
+        <v>27123.765268022</v>
       </c>
       <c r="O160" t="n">
-        <v>3905822.201104944</v>
+        <v>3905822.198595168</v>
       </c>
       <c r="P160" t="n">
         <v>44500</v>
@@ -7573,10 +7573,10 @@
         <v>714</v>
       </c>
       <c r="N164" t="n">
-        <v>1560.9980701754</v>
+        <v>1560.9982458387</v>
       </c>
       <c r="O164" t="n">
-        <v>1114552.622105236</v>
+        <v>1114552.747528832</v>
       </c>
       <c r="P164" t="n">
         <v>2900</v>
@@ -8568,10 +8568,10 @@
         <v>680</v>
       </c>
       <c r="N186" t="n">
-        <v>1778.4724989266</v>
+        <v>1778.4725014327</v>
       </c>
       <c r="O186" t="n">
-        <v>1209361.299270088</v>
+        <v>1209361.300974236</v>
       </c>
       <c r="P186" t="n">
         <v>4900</v>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -9258,19 +9258,19 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="N201" t="n">
         <v>10411</v>
       </c>
       <c r="O201" t="n">
-        <v>2498640</v>
+        <v>2186310</v>
       </c>
       <c r="P201" t="n">
         <v>16900</v>
       </c>
       <c r="Q201" t="n">
-        <v>4056000</v>
+        <v>3549000</v>
       </c>
     </row>
     <row r="202">
@@ -9905,10 +9905,10 @@
         <v>162</v>
       </c>
       <c r="N215" t="n">
-        <v>4907.821884273</v>
+        <v>4907.8218926975</v>
       </c>
       <c r="O215" t="n">
-        <v>795067.145252226</v>
+        <v>795067.146616995</v>
       </c>
       <c r="P215" t="n">
         <v>8200</v>
@@ -10539,10 +10539,10 @@
         <v>144</v>
       </c>
       <c r="N229" t="n">
-        <v>5869.1728258706</v>
+        <v>5869.1727972028</v>
       </c>
       <c r="O229" t="n">
-        <v>845160.8869253664</v>
+        <v>845160.8827972033</v>
       </c>
       <c r="P229" t="n">
         <v>9500</v>
@@ -11493,7 +11493,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -11502,19 +11502,19 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="N250" t="n">
         <v>11348</v>
       </c>
       <c r="O250" t="n">
-        <v>3551924</v>
+        <v>3290920</v>
       </c>
       <c r="P250" t="n">
         <v>19900</v>
       </c>
       <c r="Q250" t="n">
-        <v>6228700</v>
+        <v>5771000</v>
       </c>
     </row>
     <row r="251">
@@ -13072,10 +13072,10 @@
         <v>1152</v>
       </c>
       <c r="N284" t="n">
-        <v>1516.0388192979</v>
+        <v>1516.038818618</v>
       </c>
       <c r="O284" t="n">
-        <v>1746476.719831181</v>
+        <v>1746476.719047936</v>
       </c>
       <c r="P284" t="n">
         <v>2300</v>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>5472</v>
+        <v>5328</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13297,19 +13297,19 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>5472</v>
+        <v>5328</v>
       </c>
       <c r="N289" t="n">
         <v>1801</v>
       </c>
       <c r="O289" t="n">
-        <v>9855072</v>
+        <v>9595728</v>
       </c>
       <c r="P289" t="n">
         <v>2900</v>
       </c>
       <c r="Q289" t="n">
-        <v>15868800</v>
+        <v>15451200</v>
       </c>
     </row>
     <row r="290">
@@ -13763,10 +13763,10 @@
         <v>1440</v>
       </c>
       <c r="N299" t="n">
-        <v>1690.8700087336</v>
+        <v>1690.8700087796</v>
       </c>
       <c r="O299" t="n">
-        <v>2434852.812576384</v>
+        <v>2434852.812642624</v>
       </c>
       <c r="P299" t="n">
         <v>3000</v>
@@ -13988,10 +13988,10 @@
         <v>11416</v>
       </c>
       <c r="N304" t="n">
-        <v>711.33665018328</v>
+        <v>711.33665006743</v>
       </c>
       <c r="O304" t="n">
-        <v>8120619.198492324</v>
+        <v>8120619.197169781</v>
       </c>
       <c r="P304" t="n">
         <v>900</v>
@@ -14322,10 +14322,10 @@
         <v>252</v>
       </c>
       <c r="N311" t="n">
-        <v>3110.8436976288</v>
+        <v>3110.8435374771</v>
       </c>
       <c r="O311" t="n">
-        <v>783932.6118024576</v>
+        <v>783932.5714442292</v>
       </c>
       <c r="P311" t="n">
         <v>4500</v>
@@ -14366,10 +14366,10 @@
         <v>17172</v>
       </c>
       <c r="N312" t="n">
-        <v>703.79553051727</v>
+        <v>703.79547499887</v>
       </c>
       <c r="O312" t="n">
-        <v>12085576.85004256</v>
+        <v>12085575.8966806</v>
       </c>
       <c r="P312" t="n">
         <v>900</v>
@@ -15802,10 +15802,10 @@
         <v>120</v>
       </c>
       <c r="N342" t="n">
-        <v>4159.0002836879</v>
+        <v>4159.0002846975</v>
       </c>
       <c r="O342" t="n">
-        <v>499080.034042548</v>
+        <v>499080.0341637001</v>
       </c>
       <c r="P342" t="n">
         <v>8900</v>
@@ -16276,10 +16276,10 @@
         <v>699</v>
       </c>
       <c r="N352" t="n">
-        <v>7046.9398308668</v>
+        <v>7046.939830831</v>
       </c>
       <c r="O352" t="n">
-        <v>4925810.941775893</v>
+        <v>4925810.941750869</v>
       </c>
       <c r="P352" t="n">
         <v>9900</v>
@@ -16500,7 +16500,7 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>396</v>
+        <v>276</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -16509,19 +16509,19 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>396</v>
+        <v>276</v>
       </c>
       <c r="N357" t="n">
         <v>7811.9</v>
       </c>
       <c r="O357" t="n">
-        <v>3093512.4</v>
+        <v>2156084.4</v>
       </c>
       <c r="P357" t="n">
         <v>13900</v>
       </c>
       <c r="Q357" t="n">
-        <v>5504400</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="358">
@@ -16771,7 +16771,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -16780,19 +16780,19 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="N363" t="n">
-        <v>1008.8186415712</v>
+        <v>1008.8185289256</v>
       </c>
       <c r="O363" t="n">
-        <v>326857.2398690688</v>
+        <v>320804.2921983408</v>
       </c>
       <c r="P363" t="n">
         <v>1500</v>
       </c>
       <c r="Q363" t="n">
-        <v>486000</v>
+        <v>477000</v>
       </c>
     </row>
     <row r="364">

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -769,10 +769,10 @@
         <v>63</v>
       </c>
       <c r="N9" t="n">
-        <v>27225.941422594</v>
+        <v>27000</v>
       </c>
       <c r="O9" t="n">
-        <v>1715234.309623422</v>
+        <v>1701000</v>
       </c>
       <c r="P9" t="n">
         <v>30000</v>
@@ -886,10 +886,10 @@
         <v>96</v>
       </c>
       <c r="N12" t="n">
-        <v>5784.4419026549</v>
+        <v>5758.9597787611</v>
       </c>
       <c r="O12" t="n">
-        <v>555306.4226548704</v>
+        <v>552860.1387610657</v>
       </c>
       <c r="P12" t="n">
         <v>16900</v>
@@ -1521,10 +1521,10 @@
         <v>74</v>
       </c>
       <c r="N28" t="n">
-        <v>21510.733070539</v>
+        <v>21333.69</v>
       </c>
       <c r="O28" t="n">
-        <v>1591794.247219886</v>
+        <v>1578693.06</v>
       </c>
       <c r="P28" t="n">
         <v>30000</v>
@@ -1646,10 +1646,10 @@
         <v>20</v>
       </c>
       <c r="N31" t="n">
-        <v>9642.5297333333</v>
+        <v>9392.0745333333</v>
       </c>
       <c r="O31" t="n">
-        <v>192850.594666666</v>
+        <v>187841.490666666</v>
       </c>
       <c r="P31" t="n">
         <v>18500</v>
@@ -2414,10 +2414,10 @@
         <v>48</v>
       </c>
       <c r="N49" t="n">
-        <v>27232.75862069</v>
+        <v>27000</v>
       </c>
       <c r="O49" t="n">
-        <v>1307172.41379312</v>
+        <v>1296000</v>
       </c>
       <c r="P49" t="n">
         <v>20000</v>
@@ -2570,10 +2570,10 @@
         <v>208</v>
       </c>
       <c r="N53" t="n">
-        <v>8104.9092</v>
+        <v>8046.39</v>
       </c>
       <c r="O53" t="n">
-        <v>1685821.1136</v>
+        <v>1673649.12</v>
       </c>
       <c r="P53" t="n">
         <v>20900</v>
@@ -2795,10 +2795,10 @@
         <v>10</v>
       </c>
       <c r="N58" t="n">
-        <v>7477.1013333333</v>
+        <v>7394.9354444444</v>
       </c>
       <c r="O58" t="n">
-        <v>74771.013333333</v>
+        <v>73949.354444444</v>
       </c>
       <c r="P58" t="n">
         <v>17900</v>
@@ -2878,10 +2878,10 @@
         <v>96</v>
       </c>
       <c r="N60" t="n">
-        <v>2576.9026455026</v>
+        <v>2563.34</v>
       </c>
       <c r="O60" t="n">
-        <v>247382.6539682496</v>
+        <v>246080.64</v>
       </c>
       <c r="P60" t="n">
         <v>4700</v>
@@ -3321,10 +3321,10 @@
         <v>268</v>
       </c>
       <c r="N70" t="n">
-        <v>13624.59908046</v>
+        <v>13593.35</v>
       </c>
       <c r="O70" t="n">
-        <v>3651392.55356328</v>
+        <v>3643017.8</v>
       </c>
       <c r="P70" t="n">
         <v>25500</v>
@@ -4181,10 +4181,10 @@
         <v>424</v>
       </c>
       <c r="N89" t="n">
-        <v>4898.3218562874</v>
+        <v>4891</v>
       </c>
       <c r="O89" t="n">
-        <v>2076888.467065857</v>
+        <v>2073784</v>
       </c>
       <c r="P89" t="n">
         <v>8200</v>
@@ -7481,10 +7481,10 @@
         <v>148</v>
       </c>
       <c r="N162" t="n">
-        <v>5453.6557676349</v>
+        <v>5431.12</v>
       </c>
       <c r="O162" t="n">
-        <v>807141.0536099653</v>
+        <v>803805.76</v>
       </c>
       <c r="P162" t="n">
         <v>8900</v>
@@ -7573,10 +7573,10 @@
         <v>144</v>
       </c>
       <c r="N164" t="n">
-        <v>27226.972222222</v>
+        <v>26854</v>
       </c>
       <c r="O164" t="n">
-        <v>3920683.999999968</v>
+        <v>3866976</v>
       </c>
       <c r="P164" t="n">
         <v>43900</v>
@@ -7747,10 +7747,10 @@
         <v>85</v>
       </c>
       <c r="N168" t="n">
-        <v>13971.496466667</v>
+        <v>13878.97</v>
       </c>
       <c r="O168" t="n">
-        <v>1187577.199666695</v>
+        <v>1179712.45</v>
       </c>
       <c r="P168" t="n">
         <v>21900</v>
@@ -8338,10 +8338,10 @@
         <v>19</v>
       </c>
       <c r="N181" t="n">
-        <v>44124.685714286</v>
+        <v>42899</v>
       </c>
       <c r="O181" t="n">
-        <v>838369.0285714341</v>
+        <v>815081</v>
       </c>
       <c r="P181" t="n">
         <v>70900</v>
@@ -8522,10 +8522,10 @@
         <v>240</v>
       </c>
       <c r="N185" t="n">
-        <v>22795.894912427</v>
+        <v>22739</v>
       </c>
       <c r="O185" t="n">
-        <v>5471014.77898248</v>
+        <v>5457360</v>
       </c>
       <c r="P185" t="n">
         <v>36900</v>
@@ -8614,10 +8614,10 @@
         <v>160</v>
       </c>
       <c r="N187" t="n">
-        <v>16092.045229682</v>
+        <v>16058</v>
       </c>
       <c r="O187" t="n">
-        <v>2574727.23674912</v>
+        <v>2569280</v>
       </c>
       <c r="P187" t="n">
         <v>25900</v>
@@ -9353,10 +9353,10 @@
         <v>136</v>
       </c>
       <c r="N203" t="n">
-        <v>21748.414253898</v>
+        <v>21676</v>
       </c>
       <c r="O203" t="n">
-        <v>2957784.338530128</v>
+        <v>2947936</v>
       </c>
       <c r="P203" t="n">
         <v>34900</v>
@@ -10631,10 +10631,10 @@
         <v>132</v>
       </c>
       <c r="N231" t="n">
-        <v>27422.4</v>
+        <v>27186</v>
       </c>
       <c r="O231" t="n">
-        <v>3619756.8</v>
+        <v>3588552</v>
       </c>
       <c r="P231" t="n">
         <v>43900</v>
@@ -10769,10 +10769,10 @@
         <v>144</v>
       </c>
       <c r="N234" t="n">
-        <v>3903.9739463602</v>
+        <v>3898</v>
       </c>
       <c r="O234" t="n">
-        <v>562172.2482758688</v>
+        <v>561312</v>
       </c>
       <c r="P234" t="n">
         <v>6900</v>
@@ -10815,10 +10815,10 @@
         <v>245</v>
       </c>
       <c r="N235" t="n">
-        <v>13585.460030166</v>
+        <v>13565</v>
       </c>
       <c r="O235" t="n">
-        <v>3328437.70739067</v>
+        <v>3323425</v>
       </c>
       <c r="P235" t="n">
         <v>22500</v>
@@ -11091,10 +11091,10 @@
         <v>560</v>
       </c>
       <c r="N241" t="n">
-        <v>8836.1575342466</v>
+        <v>8806</v>
       </c>
       <c r="O241" t="n">
-        <v>4948248.219178096</v>
+        <v>4931360</v>
       </c>
       <c r="P241" t="n">
         <v>14900</v>
@@ -12244,10 +12244,10 @@
         <v>447</v>
       </c>
       <c r="N266" t="n">
-        <v>3647.235915493</v>
+        <v>3639.35</v>
       </c>
       <c r="O266" t="n">
-        <v>1630314.454225371</v>
+        <v>1626789.45</v>
       </c>
       <c r="P266" t="n">
         <v>7500</v>
@@ -12382,10 +12382,10 @@
         <v>279</v>
       </c>
       <c r="N269" t="n">
-        <v>10816.221634615</v>
+        <v>10713.21</v>
       </c>
       <c r="O269" t="n">
-        <v>3017725.836057585</v>
+        <v>2988985.59</v>
       </c>
       <c r="P269" t="n">
         <v>20900</v>
@@ -12474,10 +12474,10 @@
         <v>117</v>
       </c>
       <c r="N271" t="n">
-        <v>12664.079439252</v>
+        <v>12489</v>
       </c>
       <c r="O271" t="n">
-        <v>1481697.294392484</v>
+        <v>1461213</v>
       </c>
       <c r="P271" t="n">
         <v>20900</v>
@@ -12520,10 +12520,10 @@
         <v>181</v>
       </c>
       <c r="N272" t="n">
-        <v>21937.5</v>
+        <v>21762</v>
       </c>
       <c r="O272" t="n">
-        <v>3970687.5</v>
+        <v>3938922</v>
       </c>
       <c r="P272" t="n">
         <v>35900</v>
@@ -14886,10 +14886,10 @@
         <v>57</v>
       </c>
       <c r="N323" t="n">
-        <v>10459.349677419</v>
+        <v>10348.08</v>
       </c>
       <c r="O323" t="n">
-        <v>596182.931612883</v>
+        <v>589840.5599999999</v>
       </c>
       <c r="P323" t="n">
         <v>16900</v>
@@ -14935,10 +14935,10 @@
         <v>48</v>
       </c>
       <c r="N324" t="n">
-        <v>10020.157196262</v>
+        <v>9746.8801869159</v>
       </c>
       <c r="O324" t="n">
-        <v>480967.545420576</v>
+        <v>467850.2489719632</v>
       </c>
       <c r="P324" t="n">
         <v>18500</v>
@@ -15180,10 +15180,10 @@
         <v>60</v>
       </c>
       <c r="N329" t="n">
-        <v>4388.3371764706</v>
+        <v>4337.31</v>
       </c>
       <c r="O329" t="n">
-        <v>263300.230588236</v>
+        <v>260238.6</v>
       </c>
       <c r="P329" t="n">
         <v>12900</v>
@@ -15324,10 +15324,10 @@
         <v>19</v>
       </c>
       <c r="N332" t="n">
-        <v>4360.6660810811</v>
+        <v>4190.77</v>
       </c>
       <c r="O332" t="n">
-        <v>82852.6555405409</v>
+        <v>79624.63</v>
       </c>
       <c r="P332" t="n">
         <v>5900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -730,10 +730,10 @@
         <v>16</v>
       </c>
       <c r="N8" t="n">
-        <v>1815.9962867012</v>
+        <v>1811.3037996546</v>
       </c>
       <c r="O8" t="n">
-        <v>29055.9405872192</v>
+        <v>28980.8607944736</v>
       </c>
       <c r="P8" t="n">
         <v>2600</v>
@@ -2492,10 +2492,10 @@
         <v>60</v>
       </c>
       <c r="N51" t="n">
-        <v>3872.3234767642</v>
+        <v>3865.67</v>
       </c>
       <c r="O51" t="n">
-        <v>232339.408605852</v>
+        <v>231940.2</v>
       </c>
       <c r="P51" t="n">
         <v>5500</v>
@@ -2662,10 +2662,10 @@
         <v>120</v>
       </c>
       <c r="N55" t="n">
-        <v>2589.9594489247</v>
+        <v>2572.67</v>
       </c>
       <c r="O55" t="n">
-        <v>310795.133870964</v>
+        <v>308720.4</v>
       </c>
       <c r="P55" t="n">
         <v>4700</v>
@@ -2708,10 +2708,10 @@
         <v>96</v>
       </c>
       <c r="N56" t="n">
-        <v>2597.4440764331</v>
+        <v>2570.16</v>
       </c>
       <c r="O56" t="n">
-        <v>249354.6313375776</v>
+        <v>246735.36</v>
       </c>
       <c r="P56" t="n">
         <v>4700</v>
@@ -2878,10 +2878,10 @@
         <v>96</v>
       </c>
       <c r="N60" t="n">
-        <v>2597.7011260054</v>
+        <v>2563.34</v>
       </c>
       <c r="O60" t="n">
-        <v>249379.3080965184</v>
+        <v>246080.64</v>
       </c>
       <c r="P60" t="n">
         <v>4700</v>
@@ -3682,10 +3682,10 @@
         <v>648</v>
       </c>
       <c r="N78" t="n">
-        <v>3801.7317574476</v>
+        <v>3795.7100070509</v>
       </c>
       <c r="O78" t="n">
-        <v>2463522.178826045</v>
+        <v>2459620.084568983</v>
       </c>
       <c r="P78" t="n">
         <v>6200</v>
@@ -3728,10 +3728,10 @@
         <v>504</v>
       </c>
       <c r="N79" t="n">
-        <v>3695.2967632027</v>
+        <v>3684</v>
       </c>
       <c r="O79" t="n">
-        <v>1862429.568654161</v>
+        <v>1856736</v>
       </c>
       <c r="P79" t="n">
         <v>6200</v>
@@ -4227,10 +4227,10 @@
         <v>242</v>
       </c>
       <c r="N90" t="n">
-        <v>8209.849315068501</v>
+        <v>8154</v>
       </c>
       <c r="O90" t="n">
-        <v>1986783.534246577</v>
+        <v>1973268</v>
       </c>
       <c r="P90" t="n">
         <v>13500</v>
@@ -4317,10 +4317,10 @@
         <v>3200</v>
       </c>
       <c r="N92" t="n">
-        <v>616.28176305926</v>
+        <v>616.01871898278</v>
       </c>
       <c r="O92" t="n">
-        <v>1972101.641789632</v>
+        <v>1971259.900744896</v>
       </c>
       <c r="P92" t="n">
         <v>800</v>
@@ -5786,10 +5786,10 @@
         <v>440</v>
       </c>
       <c r="N124" t="n">
-        <v>2678.0253782895</v>
+        <v>2651.8557072368</v>
       </c>
       <c r="O124" t="n">
-        <v>1178331.16644738</v>
+        <v>1166816.511184192</v>
       </c>
       <c r="P124" t="n">
         <v>3800</v>
@@ -6094,10 +6094,10 @@
         <v>352</v>
       </c>
       <c r="N131" t="n">
-        <v>8818.9498942682</v>
+        <v>8794.48</v>
       </c>
       <c r="O131" t="n">
-        <v>3104270.362782407</v>
+        <v>3095656.96</v>
       </c>
       <c r="P131" t="n">
         <v>14500</v>
@@ -6181,10 +6181,10 @@
         <v>576</v>
       </c>
       <c r="N133" t="n">
-        <v>2035.7801454898</v>
+        <v>2029.8736372454</v>
       </c>
       <c r="O133" t="n">
-        <v>1172609.363802125</v>
+        <v>1169207.21505335</v>
       </c>
       <c r="P133" t="n">
         <v>3600</v>
@@ -6222,10 +6222,10 @@
         <v>528</v>
       </c>
       <c r="N134" t="n">
-        <v>22561.918644068</v>
+        <v>22485.695932203</v>
       </c>
       <c r="O134" t="n">
-        <v>11912693.0440679</v>
+        <v>11872447.45220318</v>
       </c>
       <c r="P134" t="n">
         <v>36500</v>
@@ -6304,10 +6304,10 @@
         <v>116</v>
       </c>
       <c r="N136" t="n">
-        <v>7136.7702060222</v>
+        <v>7103</v>
       </c>
       <c r="O136" t="n">
-        <v>827865.3438985752</v>
+        <v>823948</v>
       </c>
       <c r="P136" t="n">
         <v>10700</v>
@@ -7205,10 +7205,10 @@
         <v>273</v>
       </c>
       <c r="N156" t="n">
-        <v>22817.681329923</v>
+        <v>22730.48</v>
       </c>
       <c r="O156" t="n">
-        <v>6229227.00306898</v>
+        <v>6205421.04</v>
       </c>
       <c r="P156" t="n">
         <v>36900</v>
@@ -9583,10 +9583,10 @@
         <v>124</v>
       </c>
       <c r="N208" t="n">
-        <v>9045.4669811321</v>
+        <v>9003</v>
       </c>
       <c r="O208" t="n">
-        <v>1121637.90566038</v>
+        <v>1116372</v>
       </c>
       <c r="P208" t="n">
         <v>14900</v>
@@ -10171,10 +10171,10 @@
         <v>118</v>
       </c>
       <c r="N221" t="n">
-        <v>4223.6597938144</v>
+        <v>4202</v>
       </c>
       <c r="O221" t="n">
-        <v>498391.8556700991</v>
+        <v>495836</v>
       </c>
       <c r="P221" t="n">
         <v>7900</v>
@@ -13024,10 +13024,10 @@
         <v>79</v>
       </c>
       <c r="N283" t="n">
-        <v>5414.576625</v>
+        <v>5347.73</v>
       </c>
       <c r="O283" t="n">
-        <v>427751.553375</v>
+        <v>422470.67</v>
       </c>
       <c r="P283" t="n">
         <v>9500</v>
@@ -14084,10 +14084,10 @@
         <v>17172</v>
       </c>
       <c r="N306" t="n">
-        <v>704.1779547101401</v>
+        <v>703.79545471015</v>
       </c>
       <c r="O306" t="n">
-        <v>12092143.83828253</v>
+        <v>12085575.5482827</v>
       </c>
       <c r="P306" t="n">
         <v>900</v>
@@ -16372,10 +16372,10 @@
         <v>1450</v>
       </c>
       <c r="N354" t="n">
-        <v>714.37850499616</v>
+        <v>704.8968946963899</v>
       </c>
       <c r="O354" t="n">
-        <v>1035848.832244432</v>
+        <v>1022100.497309765</v>
       </c>
       <c r="P354" t="n">
         <v>900</v>
@@ -16685,10 +16685,10 @@
         <v>186</v>
       </c>
       <c r="N361" t="n">
-        <v>707.12182981928</v>
+        <v>705.52801204819</v>
       </c>
       <c r="O361" t="n">
-        <v>131524.6603463861</v>
+        <v>131228.2102409634</v>
       </c>
       <c r="P361" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -650,10 +650,10 @@
         <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>74676.654222222</v>
+        <v>74676.65386363601</v>
       </c>
       <c r="O6" t="n">
-        <v>1493533.08444444</v>
+        <v>1493533.07727272</v>
       </c>
       <c r="P6" t="n">
         <v>144900</v>
@@ -730,10 +730,10 @@
         <v>16</v>
       </c>
       <c r="N8" t="n">
-        <v>1811.3037996546</v>
+        <v>1811.3039621792</v>
       </c>
       <c r="O8" t="n">
-        <v>28980.8607944736</v>
+        <v>28980.8633948672</v>
       </c>
       <c r="P8" t="n">
         <v>2600</v>
@@ -1326,10 +1326,10 @@
         <v>180</v>
       </c>
       <c r="N23" t="n">
-        <v>3926.8371326165</v>
+        <v>3926.8371296771</v>
       </c>
       <c r="O23" t="n">
-        <v>706830.68387097</v>
+        <v>706830.683341878</v>
       </c>
       <c r="P23" t="n">
         <v>4800</v>
@@ -1404,10 +1404,10 @@
         <v>40</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.330188383</v>
+        <v>3716.3301889764</v>
       </c>
       <c r="O25" t="n">
-        <v>148653.20753532</v>
+        <v>148653.207559056</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -1934,22 +1934,22 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>77455.73771929801</v>
+        <v>77455.737927928</v>
       </c>
       <c r="O38" t="n">
-        <v>154911.475438596</v>
+        <v>77455.737927928</v>
       </c>
       <c r="P38" t="n">
         <v>122900</v>
       </c>
       <c r="Q38" t="n">
-        <v>245800</v>
+        <v>122900</v>
       </c>
     </row>
     <row r="39">
@@ -1987,10 +1987,10 @@
         <v>65</v>
       </c>
       <c r="N39" t="n">
-        <v>141416.88447284</v>
+        <v>141416.88453074</v>
       </c>
       <c r="O39" t="n">
-        <v>9192097.4907346</v>
+        <v>9192097.4944981</v>
       </c>
       <c r="P39" t="n">
         <v>251900</v>
@@ -2120,10 +2120,10 @@
         <v>9</v>
       </c>
       <c r="N42" t="n">
-        <v>344599.17881356</v>
+        <v>344599.1787931</v>
       </c>
       <c r="O42" t="n">
-        <v>3101392.60932204</v>
+        <v>3101392.6091379</v>
       </c>
       <c r="P42" t="n">
         <v>532900</v>
@@ -2370,10 +2370,10 @@
         <v>86</v>
       </c>
       <c r="N48" t="n">
-        <v>61666.873842239</v>
+        <v>61666.873852041</v>
       </c>
       <c r="O48" t="n">
-        <v>5303351.150432554</v>
+        <v>5303351.151275526</v>
       </c>
       <c r="P48" t="n">
         <v>98900</v>
@@ -3861,10 +3861,10 @@
         <v>396</v>
       </c>
       <c r="N82" t="n">
-        <v>4890.930045977</v>
+        <v>4890.9300460299</v>
       </c>
       <c r="O82" t="n">
-        <v>1936808.298206892</v>
+        <v>1936808.29822784</v>
       </c>
       <c r="P82" t="n">
         <v>8200</v>
@@ -4080,22 +4080,22 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M87" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
         <v>8012</v>
       </c>
       <c r="O87" t="n">
-        <v>512768</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
         <v>13200</v>
       </c>
       <c r="Q87" t="n">
-        <v>844800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4135,10 +4135,10 @@
         <v>288</v>
       </c>
       <c r="N88" t="n">
-        <v>3594.2542480527</v>
+        <v>3594.2542307692</v>
       </c>
       <c r="O88" t="n">
-        <v>1035145.223439178</v>
+        <v>1035145.21846153</v>
       </c>
       <c r="P88" t="n">
         <v>6500</v>
@@ -4684,10 +4684,10 @@
         <v>1406</v>
       </c>
       <c r="N100" t="n">
-        <v>4372.2107862617</v>
+        <v>4372.2107863175</v>
       </c>
       <c r="O100" t="n">
-        <v>6147328.365483951</v>
+        <v>6147328.365562405</v>
       </c>
       <c r="P100" t="n">
         <v>7500</v>
@@ -6175,22 +6175,22 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M133" t="n">
-        <v>576</v>
+        <v>432</v>
       </c>
       <c r="N133" t="n">
         <v>2029.8736372454</v>
       </c>
       <c r="O133" t="n">
-        <v>1169207.21505335</v>
+        <v>876905.4112900128</v>
       </c>
       <c r="P133" t="n">
         <v>3600</v>
       </c>
       <c r="Q133" t="n">
-        <v>2073600</v>
+        <v>1555200</v>
       </c>
     </row>
     <row r="134">
@@ -6222,10 +6222,10 @@
         <v>528</v>
       </c>
       <c r="N134" t="n">
-        <v>22485.695932203</v>
+        <v>22485.695927602</v>
       </c>
       <c r="O134" t="n">
-        <v>11872447.45220318</v>
+        <v>11872447.44977386</v>
       </c>
       <c r="P134" t="n">
         <v>36500</v>
@@ -6394,10 +6394,10 @@
         <v>310</v>
       </c>
       <c r="N138" t="n">
-        <v>2680.739700489</v>
+        <v>2680.7396999388</v>
       </c>
       <c r="O138" t="n">
-        <v>831029.30715159</v>
+        <v>831029.3069810281</v>
       </c>
       <c r="P138" t="n">
         <v>4900</v>
@@ -6434,22 +6434,22 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M139" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="N139" t="n">
         <v>14060.64</v>
       </c>
       <c r="O139" t="n">
-        <v>1012366.08</v>
+        <v>674910.72</v>
       </c>
       <c r="P139" t="n">
         <v>22900</v>
       </c>
       <c r="Q139" t="n">
-        <v>1648800</v>
+        <v>1099200</v>
       </c>
     </row>
     <row r="140">
@@ -6673,10 +6673,10 @@
         <v>36</v>
       </c>
       <c r="N144" t="n">
-        <v>4285.1952263374</v>
+        <v>4285.1952479339</v>
       </c>
       <c r="O144" t="n">
-        <v>154267.0281481464</v>
+        <v>154267.0289256204</v>
       </c>
       <c r="P144" t="n">
         <v>6900</v>
@@ -6801,10 +6801,10 @@
         <v>55</v>
       </c>
       <c r="N147" t="n">
-        <v>30244.600034662</v>
+        <v>30244.600034682</v>
       </c>
       <c r="O147" t="n">
-        <v>1663453.00190641</v>
+        <v>1663453.00190751</v>
       </c>
       <c r="P147" t="n">
         <v>48900</v>
@@ -7297,10 +7297,10 @@
         <v>144</v>
       </c>
       <c r="N158" t="n">
-        <v>27123.765259259</v>
+        <v>27123.765250464</v>
       </c>
       <c r="O158" t="n">
-        <v>3905822.197333296</v>
+        <v>3905822.196066816</v>
       </c>
       <c r="P158" t="n">
         <v>44500</v>
@@ -7481,10 +7481,10 @@
         <v>714</v>
       </c>
       <c r="N162" t="n">
-        <v>1560.9985110132</v>
+        <v>1560.9988178914</v>
       </c>
       <c r="O162" t="n">
-        <v>1114552.936863425</v>
+        <v>1114553.15597446</v>
       </c>
       <c r="P162" t="n">
         <v>2900</v>
@@ -8430,10 +8430,10 @@
         <v>680</v>
       </c>
       <c r="N183" t="n">
-        <v>1778.4725093418</v>
+        <v>1778.4725198441</v>
       </c>
       <c r="O183" t="n">
-        <v>1209361.306352424</v>
+        <v>1209361.313493988</v>
       </c>
       <c r="P183" t="n">
         <v>4900</v>
@@ -9767,10 +9767,10 @@
         <v>162</v>
       </c>
       <c r="N212" t="n">
-        <v>4907.821904048</v>
+        <v>4907.8219155354</v>
       </c>
       <c r="O212" t="n">
-        <v>795067.1484557759</v>
+        <v>795067.1503167348</v>
       </c>
       <c r="P212" t="n">
         <v>8200</v>
@@ -9997,10 +9997,10 @@
         <v>280</v>
       </c>
       <c r="N217" t="n">
-        <v>3903.7358605664</v>
+        <v>3903.7358951965</v>
       </c>
       <c r="O217" t="n">
-        <v>1093046.040958592</v>
+        <v>1093046.05065502</v>
       </c>
       <c r="P217" t="n">
         <v>7500</v>
@@ -10355,10 +10355,10 @@
         <v>144</v>
       </c>
       <c r="N225" t="n">
-        <v>5869.1727610442</v>
+        <v>5869.1727464789</v>
       </c>
       <c r="O225" t="n">
-        <v>845160.8775903649</v>
+        <v>845160.8754929616</v>
       </c>
       <c r="P225" t="n">
         <v>9500</v>
@@ -12146,22 +12146,22 @@
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M264" t="n">
-        <v>321</v>
+        <v>285</v>
       </c>
       <c r="N264" t="n">
         <v>8700</v>
       </c>
       <c r="O264" t="n">
-        <v>2792700</v>
+        <v>2479500</v>
       </c>
       <c r="P264" t="n">
         <v>14900</v>
       </c>
       <c r="Q264" t="n">
-        <v>4782900</v>
+        <v>4246500</v>
       </c>
     </row>
     <row r="265">
@@ -12888,10 +12888,10 @@
         <v>1152</v>
       </c>
       <c r="N280" t="n">
-        <v>1516.0388166875</v>
+        <v>1516.0388137227</v>
       </c>
       <c r="O280" t="n">
-        <v>1746476.716824</v>
+        <v>1746476.71340855</v>
       </c>
       <c r="P280" t="n">
         <v>2300</v>
@@ -13110,22 +13110,22 @@
         <v>0</v>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="M285" t="n">
-        <v>5328</v>
+        <v>4896</v>
       </c>
       <c r="N285" t="n">
         <v>1801</v>
       </c>
       <c r="O285" t="n">
-        <v>9595728</v>
+        <v>8817696</v>
       </c>
       <c r="P285" t="n">
         <v>2900</v>
       </c>
       <c r="Q285" t="n">
-        <v>15451200</v>
+        <v>14198400</v>
       </c>
     </row>
     <row r="286">
@@ -13298,22 +13298,22 @@
         <v>0</v>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M289" t="n">
-        <v>696</v>
+        <v>600</v>
       </c>
       <c r="N289" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O289" t="n">
-        <v>6225984.48</v>
+        <v>5367227.999999999</v>
       </c>
       <c r="P289" t="n">
         <v>14900</v>
       </c>
       <c r="Q289" t="n">
-        <v>10370400</v>
+        <v>8940000</v>
       </c>
     </row>
     <row r="290">
@@ -13574,10 +13574,10 @@
         <v>2556</v>
       </c>
       <c r="N295" t="n">
-        <v>481.48791484103</v>
+        <v>481.48791460674</v>
       </c>
       <c r="O295" t="n">
-        <v>1230683.110333673</v>
+        <v>1230683.109734827</v>
       </c>
       <c r="P295" t="n">
         <v>650</v>
@@ -14078,22 +14078,22 @@
         <v>0</v>
       </c>
       <c r="L306" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="M306" t="n">
-        <v>17172</v>
+        <v>16596</v>
       </c>
       <c r="N306" t="n">
-        <v>703.79545471015</v>
+        <v>703.79543678174</v>
       </c>
       <c r="O306" t="n">
-        <v>12085575.5482827</v>
+        <v>11680189.06882976</v>
       </c>
       <c r="P306" t="n">
         <v>900</v>
       </c>
       <c r="Q306" t="n">
-        <v>15454800</v>
+        <v>14936400</v>
       </c>
     </row>
     <row r="307">
@@ -15994,10 +15994,10 @@
         <v>699</v>
       </c>
       <c r="N346" t="n">
-        <v>7046.9398305803</v>
+        <v>7046.9398302567</v>
       </c>
       <c r="O346" t="n">
-        <v>4925810.94157563</v>
+        <v>4925810.941349433</v>
       </c>
       <c r="P346" t="n">
         <v>9900</v>
@@ -16639,10 +16639,10 @@
         <v>169</v>
       </c>
       <c r="N360" t="n">
-        <v>1213.6821153846</v>
+        <v>1213.6821194605</v>
       </c>
       <c r="O360" t="n">
-        <v>205112.2774999974</v>
+        <v>205112.2781888245</v>
       </c>
       <c r="P360" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -650,10 +650,10 @@
         <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>74676.65386363601</v>
+        <v>74676.651315789</v>
       </c>
       <c r="O6" t="n">
-        <v>1493533.07727272</v>
+        <v>1493533.02631578</v>
       </c>
       <c r="P6" t="n">
         <v>144900</v>
@@ -730,10 +730,10 @@
         <v>16</v>
       </c>
       <c r="N8" t="n">
-        <v>1811.3039621792</v>
+        <v>1811.3040256176</v>
       </c>
       <c r="O8" t="n">
-        <v>28980.8633948672</v>
+        <v>28980.8644098816</v>
       </c>
       <c r="P8" t="n">
         <v>2600</v>
@@ -808,10 +808,10 @@
         <v>476</v>
       </c>
       <c r="N10" t="n">
-        <v>3376.7465175202</v>
+        <v>3376.746511879</v>
       </c>
       <c r="O10" t="n">
-        <v>1607331.342339615</v>
+        <v>1607331.339654404</v>
       </c>
       <c r="P10" t="n">
         <v>4500</v>
@@ -1006,10 +1006,10 @@
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>27815.961111111</v>
+        <v>27815.961126761</v>
       </c>
       <c r="O15" t="n">
-        <v>834478.83333333</v>
+        <v>834478.8338028301</v>
       </c>
       <c r="P15" t="n">
         <v>58600</v>
@@ -1646,10 +1646,10 @@
         <v>20</v>
       </c>
       <c r="N31" t="n">
-        <v>9392.0745333333</v>
+        <v>9392.0745945946</v>
       </c>
       <c r="O31" t="n">
-        <v>187841.490666666</v>
+        <v>187841.491891892</v>
       </c>
       <c r="P31" t="n">
         <v>18500</v>
@@ -2029,10 +2029,10 @@
         <v>40</v>
       </c>
       <c r="N40" t="n">
-        <v>200072.19914894</v>
+        <v>200072.19977273</v>
       </c>
       <c r="O40" t="n">
-        <v>8002887.965957601</v>
+        <v>8002887.9909092</v>
       </c>
       <c r="P40" t="n">
         <v>312000</v>
@@ -4227,10 +4227,10 @@
         <v>48</v>
       </c>
       <c r="N90" t="n">
-        <v>14822.378867925</v>
+        <v>14822.378867257</v>
       </c>
       <c r="O90" t="n">
-        <v>711474.1856604</v>
+        <v>711474.185628336</v>
       </c>
       <c r="P90" t="n">
         <v>24900</v>
@@ -6135,10 +6135,10 @@
         <v>432</v>
       </c>
       <c r="N132" t="n">
-        <v>2029.8736372454</v>
+        <v>2029.8736443149</v>
       </c>
       <c r="O132" t="n">
-        <v>876905.4112900128</v>
+        <v>876905.4143440368</v>
       </c>
       <c r="P132" t="n">
         <v>3600</v>
@@ -6801,10 +6801,10 @@
         <v>228</v>
       </c>
       <c r="N147" t="n">
-        <v>4605.2146231618</v>
+        <v>4605.2146487985</v>
       </c>
       <c r="O147" t="n">
-        <v>1049988.93408089</v>
+        <v>1049988.939926058</v>
       </c>
       <c r="P147" t="n">
         <v>7600</v>
@@ -7435,10 +7435,10 @@
         <v>714</v>
       </c>
       <c r="N161" t="n">
-        <v>1560.9988178914</v>
+        <v>1560.9988868445</v>
       </c>
       <c r="O161" t="n">
-        <v>1114553.15597446</v>
+        <v>1114553.205206973</v>
       </c>
       <c r="P161" t="n">
         <v>2900</v>
@@ -8292,10 +8292,10 @@
         <v>11</v>
       </c>
       <c r="N180" t="n">
-        <v>23521.624852941</v>
+        <v>23521.624776119</v>
       </c>
       <c r="O180" t="n">
-        <v>258737.873382351</v>
+        <v>258737.872537309</v>
       </c>
       <c r="P180" t="n">
         <v>39000</v>
@@ -8384,10 +8384,10 @@
         <v>680</v>
       </c>
       <c r="N182" t="n">
-        <v>1778.4725198441</v>
+        <v>1778.4725231214</v>
       </c>
       <c r="O182" t="n">
-        <v>1209361.313493988</v>
+        <v>1209361.315722552</v>
       </c>
       <c r="P182" t="n">
         <v>4900</v>
@@ -9721,10 +9721,10 @@
         <v>162</v>
       </c>
       <c r="N211" t="n">
-        <v>4907.8219155354</v>
+        <v>4907.8219300912</v>
       </c>
       <c r="O211" t="n">
-        <v>795067.1503167348</v>
+        <v>795067.1526747743</v>
       </c>
       <c r="P211" t="n">
         <v>8200</v>
@@ -9951,10 +9951,10 @@
         <v>280</v>
       </c>
       <c r="N216" t="n">
-        <v>3903.7358951965</v>
+        <v>3903.7359183673</v>
       </c>
       <c r="O216" t="n">
-        <v>1093046.05065502</v>
+        <v>1093046.057142844</v>
       </c>
       <c r="P216" t="n">
         <v>7500</v>
@@ -11321,10 +11321,10 @@
         <v>192</v>
       </c>
       <c r="N246" t="n">
-        <v>17075.98952512</v>
+        <v>17075.989524793</v>
       </c>
       <c r="O246" t="n">
-        <v>3278589.98882304</v>
+        <v>3278589.988760256</v>
       </c>
       <c r="P246" t="n">
         <v>27500</v>
@@ -12842,10 +12842,10 @@
         <v>1152</v>
       </c>
       <c r="N279" t="n">
-        <v>1516.0388137227</v>
+        <v>1516.0388131508</v>
       </c>
       <c r="O279" t="n">
-        <v>1746476.71340855</v>
+        <v>1746476.712749722</v>
       </c>
       <c r="P279" t="n">
         <v>2300</v>
@@ -13484,10 +13484,10 @@
         <v>1440</v>
       </c>
       <c r="N293" t="n">
-        <v>1690.8700088067</v>
+        <v>1690.8700088574</v>
       </c>
       <c r="O293" t="n">
-        <v>2434852.812681648</v>
+        <v>2434852.812754656</v>
       </c>
       <c r="P293" t="n">
         <v>3000</v>
@@ -14038,10 +14038,10 @@
         <v>16596</v>
       </c>
       <c r="N305" t="n">
-        <v>703.79543678174</v>
+        <v>703.79542528945</v>
       </c>
       <c r="O305" t="n">
-        <v>11680189.06882976</v>
+        <v>11680188.87810371</v>
       </c>
       <c r="P305" t="n">
         <v>900</v>
@@ -14843,10 +14843,10 @@
         <v>48</v>
       </c>
       <c r="N322" t="n">
-        <v>9746.8801869159</v>
+        <v>9746.880188679201</v>
       </c>
       <c r="O322" t="n">
-        <v>467850.2489719632</v>
+        <v>467850.2490566017</v>
       </c>
       <c r="P322" t="n">
         <v>18500</v>
@@ -15615,10 +15615,10 @@
         <v>11</v>
       </c>
       <c r="N338" t="n">
-        <v>14751.8203125</v>
+        <v>14751.82031746</v>
       </c>
       <c r="O338" t="n">
-        <v>162270.0234375</v>
+        <v>162270.02349206</v>
       </c>
       <c r="P338" t="n">
         <v>37100</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-11</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -556,10 +556,10 @@
         <v>330</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27043.062200957</v>
       </c>
       <c r="O4" t="n">
-        <v>8910000</v>
+        <v>8924210.52631581</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -730,10 +730,10 @@
         <v>16</v>
       </c>
       <c r="N8" t="n">
-        <v>1811.3040256176</v>
+        <v>1811.3041548631</v>
       </c>
       <c r="O8" t="n">
-        <v>28980.8644098816</v>
+        <v>28980.8664778096</v>
       </c>
       <c r="P8" t="n">
         <v>2600</v>
@@ -808,10 +808,10 @@
         <v>476</v>
       </c>
       <c r="N10" t="n">
-        <v>3376.746511879</v>
+        <v>3376.7465109371</v>
       </c>
       <c r="O10" t="n">
-        <v>1607331.339654404</v>
+        <v>1607331.33920606</v>
       </c>
       <c r="P10" t="n">
         <v>4500</v>
@@ -1092,10 +1092,10 @@
         <v>142</v>
       </c>
       <c r="N17" t="n">
-        <v>27000</v>
+        <v>27064.133016627</v>
       </c>
       <c r="O17" t="n">
-        <v>3834000</v>
+        <v>3843106.888361034</v>
       </c>
       <c r="P17" t="n">
         <v>20000</v>
@@ -1326,10 +1326,10 @@
         <v>180</v>
       </c>
       <c r="N23" t="n">
-        <v>3926.8371296771</v>
+        <v>3926.8371267317</v>
       </c>
       <c r="O23" t="n">
-        <v>706830.683341878</v>
+        <v>706830.6828117061</v>
       </c>
       <c r="P23" t="n">
         <v>4800</v>
@@ -1404,10 +1404,10 @@
         <v>40</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.3301889764</v>
+        <v>3716.3301892744</v>
       </c>
       <c r="O25" t="n">
-        <v>148653.207559056</v>
+        <v>148653.207570976</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -1521,10 +1521,10 @@
         <v>74</v>
       </c>
       <c r="N28" t="n">
-        <v>21333.69</v>
+        <v>21423.327352941</v>
       </c>
       <c r="O28" t="n">
-        <v>1578693.06</v>
+        <v>1585326.224117634</v>
       </c>
       <c r="P28" t="n">
         <v>30000</v>
@@ -1802,10 +1802,10 @@
         <v>24</v>
       </c>
       <c r="N35" t="n">
-        <v>14708.815789474</v>
+        <v>14708.815744681</v>
       </c>
       <c r="O35" t="n">
-        <v>353011.578947376</v>
+        <v>353011.577872344</v>
       </c>
       <c r="P35" t="n">
         <v>16900</v>
@@ -2120,10 +2120,10 @@
         <v>9</v>
       </c>
       <c r="N42" t="n">
-        <v>344599.1787931</v>
+        <v>344599.17865385</v>
       </c>
       <c r="O42" t="n">
-        <v>3101392.6091379</v>
+        <v>3101392.60788465</v>
       </c>
       <c r="P42" t="n">
         <v>532900</v>
@@ -2370,10 +2370,10 @@
         <v>86</v>
       </c>
       <c r="N48" t="n">
-        <v>61666.873852041</v>
+        <v>61666.873861893</v>
       </c>
       <c r="O48" t="n">
-        <v>5303351.151275526</v>
+        <v>5303351.152122798</v>
       </c>
       <c r="P48" t="n">
         <v>98900</v>
@@ -3498,10 +3498,10 @@
         <v>2592</v>
       </c>
       <c r="N74" t="n">
-        <v>3158.8608137572</v>
+        <v>3158.860813875</v>
       </c>
       <c r="O74" t="n">
-        <v>8187767.229258662</v>
+        <v>8187767.229564</v>
       </c>
       <c r="P74" t="n">
         <v>5600</v>
@@ -3544,10 +3544,10 @@
         <v>77</v>
       </c>
       <c r="N75" t="n">
-        <v>3841.6246911197</v>
+        <v>3841.6247184466</v>
       </c>
       <c r="O75" t="n">
-        <v>295805.1012162169</v>
+        <v>295805.1033203882</v>
       </c>
       <c r="P75" t="n">
         <v>6900</v>
@@ -3682,10 +3682,10 @@
         <v>648</v>
       </c>
       <c r="N78" t="n">
-        <v>3795.7100070509</v>
+        <v>3795.7100070547</v>
       </c>
       <c r="O78" t="n">
-        <v>2459620.084568983</v>
+        <v>2459620.084571445</v>
       </c>
       <c r="P78" t="n">
         <v>6200</v>
@@ -3861,10 +3861,10 @@
         <v>396</v>
       </c>
       <c r="N82" t="n">
-        <v>4890.9300460299</v>
+        <v>4890.9300461095</v>
       </c>
       <c r="O82" t="n">
-        <v>1936808.29822784</v>
+        <v>1936808.298259362</v>
       </c>
       <c r="P82" t="n">
         <v>8200</v>
@@ -4040,10 +4040,10 @@
         <v>723</v>
       </c>
       <c r="N86" t="n">
-        <v>5667.94</v>
+        <v>5672.995244381</v>
       </c>
       <c r="O86" t="n">
-        <v>4097920.62</v>
+        <v>4101575.561687463</v>
       </c>
       <c r="P86" t="n">
         <v>9500</v>
@@ -4089,10 +4089,10 @@
         <v>288</v>
       </c>
       <c r="N87" t="n">
-        <v>3594.2542307692</v>
+        <v>3594.254188862</v>
       </c>
       <c r="O87" t="n">
-        <v>1035145.21846153</v>
+        <v>1035145.206392256</v>
       </c>
       <c r="P87" t="n">
         <v>6500</v>
@@ -4638,10 +4638,10 @@
         <v>1406</v>
       </c>
       <c r="N99" t="n">
-        <v>4372.2107863175</v>
+        <v>4372.2107866525</v>
       </c>
       <c r="O99" t="n">
-        <v>6147328.365562405</v>
+        <v>6147328.366033415</v>
       </c>
       <c r="P99" t="n">
         <v>7500</v>
@@ -6135,10 +6135,10 @@
         <v>432</v>
       </c>
       <c r="N132" t="n">
-        <v>2029.8736443149</v>
+        <v>2029.8736460865</v>
       </c>
       <c r="O132" t="n">
-        <v>876905.4143440368</v>
+        <v>876905.415109368</v>
       </c>
       <c r="P132" t="n">
         <v>3600</v>
@@ -6176,10 +6176,10 @@
         <v>528</v>
       </c>
       <c r="N133" t="n">
-        <v>22485.695927602</v>
+        <v>22485.695904437</v>
       </c>
       <c r="O133" t="n">
-        <v>11872447.44977386</v>
+        <v>11872447.43754274</v>
       </c>
       <c r="P133" t="n">
         <v>36500</v>
@@ -6532,10 +6532,10 @@
         <v>799</v>
       </c>
       <c r="N141" t="n">
-        <v>998.76125816993</v>
+        <v>998.76125988546</v>
       </c>
       <c r="O141" t="n">
-        <v>798010.2452777741</v>
+        <v>798010.2466484826</v>
       </c>
       <c r="P141" t="n">
         <v>1600</v>
@@ -6755,10 +6755,10 @@
         <v>55</v>
       </c>
       <c r="N146" t="n">
-        <v>30244.600034682</v>
+        <v>30262.092573742</v>
       </c>
       <c r="O146" t="n">
-        <v>1663453.00190751</v>
+        <v>1664415.09155581</v>
       </c>
       <c r="P146" t="n">
         <v>48900</v>
@@ -6842,10 +6842,10 @@
         <v>1278</v>
       </c>
       <c r="N148" t="n">
-        <v>3591.13</v>
+        <v>3592.9712903777</v>
       </c>
       <c r="O148" t="n">
-        <v>4589464.140000001</v>
+        <v>4591817.3091027</v>
       </c>
       <c r="P148" t="n">
         <v>6300</v>
@@ -6980,10 +6980,10 @@
         <v>60</v>
       </c>
       <c r="N151" t="n">
-        <v>21418.04</v>
+        <v>21897.548358209</v>
       </c>
       <c r="O151" t="n">
-        <v>1285082.4</v>
+        <v>1313852.90149254</v>
       </c>
       <c r="P151" t="n">
         <v>34900</v>
@@ -7435,10 +7435,10 @@
         <v>714</v>
       </c>
       <c r="N161" t="n">
-        <v>1560.9988868445</v>
+        <v>1560.9989986027</v>
       </c>
       <c r="O161" t="n">
-        <v>1114553.205206973</v>
+        <v>1114553.285002328</v>
       </c>
       <c r="P161" t="n">
         <v>2900</v>
@@ -7609,10 +7609,10 @@
         <v>31</v>
       </c>
       <c r="N165" t="n">
-        <v>12981.59</v>
+        <v>13028.454945848</v>
       </c>
       <c r="O165" t="n">
-        <v>402429.29</v>
+        <v>403882.103321288</v>
       </c>
       <c r="P165" t="n">
         <v>21900</v>
@@ -7655,10 +7655,10 @@
         <v>85</v>
       </c>
       <c r="N166" t="n">
-        <v>13878.97</v>
+        <v>13925.387959866</v>
       </c>
       <c r="O166" t="n">
-        <v>1179712.45</v>
+        <v>1183657.97658861</v>
       </c>
       <c r="P166" t="n">
         <v>21900</v>
@@ -8384,10 +8384,10 @@
         <v>680</v>
       </c>
       <c r="N182" t="n">
-        <v>1778.4725231214</v>
+        <v>1778.4725400058</v>
       </c>
       <c r="O182" t="n">
-        <v>1209361.315722552</v>
+        <v>1209361.327203944</v>
       </c>
       <c r="P182" t="n">
         <v>4900</v>
@@ -8522,10 +8522,10 @@
         <v>160</v>
       </c>
       <c r="N185" t="n">
-        <v>16058</v>
+        <v>16069.364472753</v>
       </c>
       <c r="O185" t="n">
-        <v>2569280</v>
+        <v>2571098.31564048</v>
       </c>
       <c r="P185" t="n">
         <v>25900</v>
@@ -9583,10 +9583,10 @@
         <v>216</v>
       </c>
       <c r="N208" t="n">
-        <v>9178</v>
+        <v>9197.9305103149</v>
       </c>
       <c r="O208" t="n">
-        <v>1982448</v>
+        <v>1986752.990228018</v>
       </c>
       <c r="P208" t="n">
         <v>14900</v>
@@ -9629,10 +9629,10 @@
         <v>147</v>
       </c>
       <c r="N209" t="n">
-        <v>13922</v>
+        <v>13973.183823529</v>
       </c>
       <c r="O209" t="n">
-        <v>2046534</v>
+        <v>2054058.022058763</v>
       </c>
       <c r="P209" t="n">
         <v>22900</v>
@@ -9721,10 +9721,10 @@
         <v>162</v>
       </c>
       <c r="N211" t="n">
-        <v>4907.8219300912</v>
+        <v>4907.8219330289</v>
       </c>
       <c r="O211" t="n">
-        <v>795067.1526747743</v>
+        <v>795067.1531506819</v>
       </c>
       <c r="P211" t="n">
         <v>8200</v>
@@ -9951,10 +9951,10 @@
         <v>280</v>
       </c>
       <c r="N216" t="n">
-        <v>3903.7359183673</v>
+        <v>3903.7359649123</v>
       </c>
       <c r="O216" t="n">
-        <v>1093046.057142844</v>
+        <v>1093046.070175444</v>
       </c>
       <c r="P216" t="n">
         <v>7500</v>
@@ -10631,10 +10631,10 @@
         <v>153</v>
       </c>
       <c r="N231" t="n">
-        <v>7562</v>
+        <v>7649.2538461538</v>
       </c>
       <c r="O231" t="n">
-        <v>1156986</v>
+        <v>1170335.838461531</v>
       </c>
       <c r="P231" t="n">
         <v>12900</v>
@@ -11137,10 +11137,10 @@
         <v>180</v>
       </c>
       <c r="N242" t="n">
-        <v>17992</v>
+        <v>18015.037131882</v>
       </c>
       <c r="O242" t="n">
-        <v>3238560</v>
+        <v>3242706.68373876</v>
       </c>
       <c r="P242" t="n">
         <v>28900</v>
@@ -11321,10 +11321,10 @@
         <v>192</v>
       </c>
       <c r="N246" t="n">
-        <v>17075.989524793</v>
+        <v>17075.989524138</v>
       </c>
       <c r="O246" t="n">
-        <v>3278589.988760256</v>
+        <v>3278589.988634496</v>
       </c>
       <c r="P246" t="n">
         <v>27500</v>
@@ -12014,10 +12014,10 @@
         <v>45</v>
       </c>
       <c r="N261" t="n">
-        <v>16282</v>
+        <v>16694.202531646</v>
       </c>
       <c r="O261" t="n">
-        <v>732690</v>
+        <v>751239.1139240699</v>
       </c>
       <c r="P261" t="n">
         <v>27900</v>
@@ -12106,10 +12106,10 @@
         <v>285</v>
       </c>
       <c r="N263" t="n">
-        <v>8700</v>
+        <v>8709.5604395604</v>
       </c>
       <c r="O263" t="n">
-        <v>2479500</v>
+        <v>2482224.725274714</v>
       </c>
       <c r="P263" t="n">
         <v>14900</v>
@@ -12842,10 +12842,10 @@
         <v>1152</v>
       </c>
       <c r="N279" t="n">
-        <v>1516.0388131508</v>
+        <v>1516.0388129219</v>
       </c>
       <c r="O279" t="n">
-        <v>1746476.712749722</v>
+        <v>1746476.712486029</v>
       </c>
       <c r="P279" t="n">
         <v>2300</v>
@@ -13484,10 +13484,10 @@
         <v>1440</v>
       </c>
       <c r="N293" t="n">
-        <v>1690.8700088574</v>
+        <v>1690.8700089286</v>
       </c>
       <c r="O293" t="n">
-        <v>2434852.812754656</v>
+        <v>2434852.812857184</v>
       </c>
       <c r="P293" t="n">
         <v>3000</v>
@@ -14038,10 +14038,10 @@
         <v>16596</v>
       </c>
       <c r="N305" t="n">
-        <v>703.79542528945</v>
+        <v>703.79541200942</v>
       </c>
       <c r="O305" t="n">
-        <v>11680188.87810371</v>
+        <v>11680188.65770834</v>
       </c>
       <c r="P305" t="n">
         <v>900</v>
@@ -15039,10 +15039,10 @@
         <v>21</v>
       </c>
       <c r="N326" t="n">
-        <v>2992.5684269663</v>
+        <v>2992.5687209302</v>
       </c>
       <c r="O326" t="n">
-        <v>62843.93696629231</v>
+        <v>62843.9431395342</v>
       </c>
       <c r="P326" t="n">
         <v>6000</v>
@@ -15474,10 +15474,10 @@
         <v>120</v>
       </c>
       <c r="N335" t="n">
-        <v>4159.0002867384</v>
+        <v>4173.9607194245</v>
       </c>
       <c r="O335" t="n">
-        <v>499080.034408608</v>
+        <v>500875.28633094</v>
       </c>
       <c r="P335" t="n">
         <v>8900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-11</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-12</t>
         </is>
       </c>
     </row>
@@ -556,10 +556,10 @@
         <v>330</v>
       </c>
       <c r="N4" t="n">
-        <v>27043.062200957</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>8924210.52631581</v>
+        <v>8910000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -1092,10 +1092,10 @@
         <v>142</v>
       </c>
       <c r="N17" t="n">
-        <v>27064.133016627</v>
+        <v>27000</v>
       </c>
       <c r="O17" t="n">
-        <v>3843106.888361034</v>
+        <v>3834000</v>
       </c>
       <c r="P17" t="n">
         <v>20000</v>
@@ -1521,10 +1521,10 @@
         <v>74</v>
       </c>
       <c r="N28" t="n">
-        <v>21423.327352941</v>
+        <v>21333.69</v>
       </c>
       <c r="O28" t="n">
-        <v>1585326.224117634</v>
+        <v>1578693.06</v>
       </c>
       <c r="P28" t="n">
         <v>30000</v>
@@ -4040,10 +4040,10 @@
         <v>723</v>
       </c>
       <c r="N86" t="n">
-        <v>5672.995244381</v>
+        <v>5667.94</v>
       </c>
       <c r="O86" t="n">
-        <v>4101575.561687463</v>
+        <v>4097920.62</v>
       </c>
       <c r="P86" t="n">
         <v>9500</v>
@@ -6755,10 +6755,10 @@
         <v>55</v>
       </c>
       <c r="N146" t="n">
-        <v>30262.092573742</v>
+        <v>30244.600034702</v>
       </c>
       <c r="O146" t="n">
-        <v>1664415.09155581</v>
+        <v>1663453.00190861</v>
       </c>
       <c r="P146" t="n">
         <v>48900</v>
@@ -6842,10 +6842,10 @@
         <v>1278</v>
       </c>
       <c r="N148" t="n">
-        <v>3592.9712903777</v>
+        <v>3591.13</v>
       </c>
       <c r="O148" t="n">
-        <v>4591817.3091027</v>
+        <v>4589464.140000001</v>
       </c>
       <c r="P148" t="n">
         <v>6300</v>
@@ -6980,10 +6980,10 @@
         <v>60</v>
       </c>
       <c r="N151" t="n">
-        <v>21897.548358209</v>
+        <v>21418.04</v>
       </c>
       <c r="O151" t="n">
-        <v>1313852.90149254</v>
+        <v>1285082.4</v>
       </c>
       <c r="P151" t="n">
         <v>34900</v>
@@ -7609,10 +7609,10 @@
         <v>31</v>
       </c>
       <c r="N165" t="n">
-        <v>13028.454945848</v>
+        <v>12981.59</v>
       </c>
       <c r="O165" t="n">
-        <v>403882.103321288</v>
+        <v>402429.29</v>
       </c>
       <c r="P165" t="n">
         <v>21900</v>
@@ -7655,10 +7655,10 @@
         <v>85</v>
       </c>
       <c r="N166" t="n">
-        <v>13925.387959866</v>
+        <v>13878.97</v>
       </c>
       <c r="O166" t="n">
-        <v>1183657.97658861</v>
+        <v>1179712.45</v>
       </c>
       <c r="P166" t="n">
         <v>21900</v>
@@ -8522,10 +8522,10 @@
         <v>160</v>
       </c>
       <c r="N185" t="n">
-        <v>16069.364472753</v>
+        <v>16058</v>
       </c>
       <c r="O185" t="n">
-        <v>2571098.31564048</v>
+        <v>2569280</v>
       </c>
       <c r="P185" t="n">
         <v>25900</v>
@@ -9583,10 +9583,10 @@
         <v>216</v>
       </c>
       <c r="N208" t="n">
-        <v>9197.9305103149</v>
+        <v>9178</v>
       </c>
       <c r="O208" t="n">
-        <v>1986752.990228018</v>
+        <v>1982448</v>
       </c>
       <c r="P208" t="n">
         <v>14900</v>
@@ -9629,10 +9629,10 @@
         <v>147</v>
       </c>
       <c r="N209" t="n">
-        <v>13973.183823529</v>
+        <v>13922</v>
       </c>
       <c r="O209" t="n">
-        <v>2054058.022058763</v>
+        <v>2046534</v>
       </c>
       <c r="P209" t="n">
         <v>22900</v>
@@ -10631,10 +10631,10 @@
         <v>153</v>
       </c>
       <c r="N231" t="n">
-        <v>7649.2538461538</v>
+        <v>7562</v>
       </c>
       <c r="O231" t="n">
-        <v>1170335.838461531</v>
+        <v>1156986</v>
       </c>
       <c r="P231" t="n">
         <v>12900</v>
@@ -11137,10 +11137,10 @@
         <v>180</v>
       </c>
       <c r="N242" t="n">
-        <v>18015.037131882</v>
+        <v>17992</v>
       </c>
       <c r="O242" t="n">
-        <v>3242706.68373876</v>
+        <v>3238560</v>
       </c>
       <c r="P242" t="n">
         <v>28900</v>
@@ -12014,10 +12014,10 @@
         <v>45</v>
       </c>
       <c r="N261" t="n">
-        <v>16694.202531646</v>
+        <v>16282</v>
       </c>
       <c r="O261" t="n">
-        <v>751239.1139240699</v>
+        <v>732690</v>
       </c>
       <c r="P261" t="n">
         <v>27900</v>
@@ -12106,10 +12106,10 @@
         <v>285</v>
       </c>
       <c r="N263" t="n">
-        <v>8709.5604395604</v>
+        <v>8700</v>
       </c>
       <c r="O263" t="n">
-        <v>2482224.725274714</v>
+        <v>2479500</v>
       </c>
       <c r="P263" t="n">
         <v>14900</v>
@@ -15474,10 +15474,10 @@
         <v>120</v>
       </c>
       <c r="N335" t="n">
-        <v>4173.9607194245</v>
+        <v>4159.0002877698</v>
       </c>
       <c r="O335" t="n">
-        <v>500875.28633094</v>
+        <v>499080.034532376</v>
       </c>
       <c r="P335" t="n">
         <v>8900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -650,10 +650,10 @@
         <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>74676.651315789</v>
+        <v>74676.651794872</v>
       </c>
       <c r="O6" t="n">
-        <v>1493533.02631578</v>
+        <v>1493533.03589744</v>
       </c>
       <c r="P6" t="n">
         <v>144900</v>
@@ -724,22 +724,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N8" t="n">
-        <v>1811.3041548631</v>
+        <v>1811.3043052838</v>
       </c>
       <c r="O8" t="n">
-        <v>28980.8664778096</v>
+        <v>27169.564579257</v>
       </c>
       <c r="P8" t="n">
         <v>2600</v>
       </c>
       <c r="Q8" t="n">
-        <v>41600</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="9">
@@ -808,10 +808,10 @@
         <v>476</v>
       </c>
       <c r="N10" t="n">
-        <v>3376.7465109371</v>
+        <v>3376.7465014893</v>
       </c>
       <c r="O10" t="n">
-        <v>1607331.33920606</v>
+        <v>1607331.334708907</v>
       </c>
       <c r="P10" t="n">
         <v>4500</v>
@@ -1599,10 +1599,10 @@
         <v>120</v>
       </c>
       <c r="N30" t="n">
-        <v>3910.628245614</v>
+        <v>3910.6282352941</v>
       </c>
       <c r="O30" t="n">
-        <v>469275.38947368</v>
+        <v>469275.388235292</v>
       </c>
       <c r="P30" t="n">
         <v>9100</v>
@@ -1646,10 +1646,10 @@
         <v>20</v>
       </c>
       <c r="N31" t="n">
-        <v>9392.0745945946</v>
+        <v>9392.0746575342</v>
       </c>
       <c r="O31" t="n">
-        <v>187841.491891892</v>
+        <v>187841.493150684</v>
       </c>
       <c r="P31" t="n">
         <v>18500</v>
@@ -1987,10 +1987,10 @@
         <v>65</v>
       </c>
       <c r="N39" t="n">
-        <v>141416.88453074</v>
+        <v>141416.88454545</v>
       </c>
       <c r="O39" t="n">
-        <v>9192097.4944981</v>
+        <v>9192097.49545425</v>
       </c>
       <c r="P39" t="n">
         <v>251900</v>
@@ -2370,10 +2370,10 @@
         <v>86</v>
       </c>
       <c r="N48" t="n">
-        <v>61666.873861893</v>
+        <v>61666.873932292</v>
       </c>
       <c r="O48" t="n">
-        <v>5303351.152122798</v>
+        <v>5303351.158177112</v>
       </c>
       <c r="P48" t="n">
         <v>98900</v>
@@ -3498,10 +3498,10 @@
         <v>2592</v>
       </c>
       <c r="N74" t="n">
-        <v>3158.860813875</v>
+        <v>3158.8608143857</v>
       </c>
       <c r="O74" t="n">
-        <v>8187767.229564</v>
+        <v>8187767.230887734</v>
       </c>
       <c r="P74" t="n">
         <v>5600</v>
@@ -3861,10 +3861,10 @@
         <v>396</v>
       </c>
       <c r="N82" t="n">
-        <v>4890.9300461095</v>
+        <v>4890.9300462963</v>
       </c>
       <c r="O82" t="n">
-        <v>1936808.298259362</v>
+        <v>1936808.298333335</v>
       </c>
       <c r="P82" t="n">
         <v>8200</v>
@@ -4089,10 +4089,10 @@
         <v>288</v>
       </c>
       <c r="N87" t="n">
-        <v>3594.254188862</v>
+        <v>3594.2541747573</v>
       </c>
       <c r="O87" t="n">
-        <v>1035145.206392256</v>
+        <v>1035145.202330102</v>
       </c>
       <c r="P87" t="n">
         <v>6500</v>
@@ -4227,10 +4227,10 @@
         <v>48</v>
       </c>
       <c r="N90" t="n">
-        <v>14822.378867257</v>
+        <v>14822.378864577</v>
       </c>
       <c r="O90" t="n">
-        <v>711474.185628336</v>
+        <v>711474.1854996961</v>
       </c>
       <c r="P90" t="n">
         <v>24900</v>
@@ -4638,10 +4638,10 @@
         <v>1406</v>
       </c>
       <c r="N99" t="n">
-        <v>4372.2107866525</v>
+        <v>4372.2107869318</v>
       </c>
       <c r="O99" t="n">
-        <v>6147328.366033415</v>
+        <v>6147328.36642611</v>
       </c>
       <c r="P99" t="n">
         <v>7500</v>
@@ -4823,10 +4823,10 @@
         <v>4733</v>
       </c>
       <c r="N103" t="n">
-        <v>17472.91</v>
+        <v>17476.031091396</v>
       </c>
       <c r="O103" t="n">
-        <v>82699283.03</v>
+        <v>82714055.15557726</v>
       </c>
       <c r="P103" t="n">
         <v>2900</v>
@@ -5234,10 +5234,10 @@
         <v>42</v>
       </c>
       <c r="N112" t="n">
-        <v>8341.030000000001</v>
+        <v>8367.5094603175</v>
       </c>
       <c r="O112" t="n">
-        <v>350323.26</v>
+        <v>351435.397333335</v>
       </c>
       <c r="P112" t="n">
         <v>13900</v>
@@ -5463,10 +5463,10 @@
         <v>853</v>
       </c>
       <c r="N117" t="n">
-        <v>1151.3923550423</v>
+        <v>1151.3923553227</v>
       </c>
       <c r="O117" t="n">
-        <v>982137.678851082</v>
+        <v>982137.6790902631</v>
       </c>
       <c r="P117" t="n">
         <v>1500</v>
@@ -6135,10 +6135,10 @@
         <v>432</v>
       </c>
       <c r="N132" t="n">
-        <v>2029.8736460865</v>
+        <v>2029.8736549708</v>
       </c>
       <c r="O132" t="n">
-        <v>876905.415109368</v>
+        <v>876905.4189473856</v>
       </c>
       <c r="P132" t="n">
         <v>3600</v>
@@ -6627,10 +6627,10 @@
         <v>36</v>
       </c>
       <c r="N143" t="n">
-        <v>4285.1952479339</v>
+        <v>4285.1952751817</v>
       </c>
       <c r="O143" t="n">
-        <v>154267.0289256204</v>
+        <v>154267.0299065412</v>
       </c>
       <c r="P143" t="n">
         <v>6900</v>
@@ -6801,10 +6801,10 @@
         <v>228</v>
       </c>
       <c r="N147" t="n">
-        <v>4605.2146487985</v>
+        <v>4605.2146574074</v>
       </c>
       <c r="O147" t="n">
-        <v>1049988.939926058</v>
+        <v>1049988.941888887</v>
       </c>
       <c r="P147" t="n">
         <v>7600</v>
@@ -7251,10 +7251,10 @@
         <v>144</v>
       </c>
       <c r="N157" t="n">
-        <v>27123.765250464</v>
+        <v>27123.765241636</v>
       </c>
       <c r="O157" t="n">
-        <v>3905822.196066816</v>
+        <v>3905822.194795584</v>
       </c>
       <c r="P157" t="n">
         <v>44500</v>
@@ -7343,10 +7343,10 @@
         <v>221</v>
       </c>
       <c r="N159" t="n">
-        <v>8332.779624999999</v>
+        <v>8332.7796240601</v>
       </c>
       <c r="O159" t="n">
-        <v>1841544.297125</v>
+        <v>1841544.296917282</v>
       </c>
       <c r="P159" t="n">
         <v>14900</v>
@@ -7435,10 +7435,10 @@
         <v>714</v>
       </c>
       <c r="N161" t="n">
-        <v>1560.9989986027</v>
+        <v>1560.9991607397</v>
       </c>
       <c r="O161" t="n">
-        <v>1114553.285002328</v>
+        <v>1114553.400768146</v>
       </c>
       <c r="P161" t="n">
         <v>2900</v>
@@ -8384,10 +8384,10 @@
         <v>680</v>
       </c>
       <c r="N182" t="n">
-        <v>1778.4725400058</v>
+        <v>1778.4725489051</v>
       </c>
       <c r="O182" t="n">
-        <v>1209361.327203944</v>
+        <v>1209361.333255468</v>
       </c>
       <c r="P182" t="n">
         <v>4900</v>
@@ -9169,10 +9169,10 @@
         <v>36</v>
       </c>
       <c r="N199" t="n">
-        <v>17644.653166667</v>
+        <v>17644.653275862</v>
       </c>
       <c r="O199" t="n">
-        <v>635207.5140000121</v>
+        <v>635207.517931032</v>
       </c>
       <c r="P199" t="n">
         <v>28200</v>
@@ -9951,10 +9951,10 @@
         <v>280</v>
       </c>
       <c r="N216" t="n">
-        <v>3903.7359649123</v>
+        <v>3903.7361538462</v>
       </c>
       <c r="O216" t="n">
-        <v>1093046.070175444</v>
+        <v>1093046.123076936</v>
       </c>
       <c r="P216" t="n">
         <v>7500</v>
@@ -10125,10 +10125,10 @@
         <v>118</v>
       </c>
       <c r="N220" t="n">
-        <v>4202</v>
+        <v>4213.1164021164</v>
       </c>
       <c r="O220" t="n">
-        <v>495836</v>
+        <v>497147.7354497352</v>
       </c>
       <c r="P220" t="n">
         <v>7900</v>
@@ -11321,10 +11321,10 @@
         <v>192</v>
       </c>
       <c r="N246" t="n">
-        <v>17075.989524138</v>
+        <v>17075.98952381</v>
       </c>
       <c r="O246" t="n">
-        <v>3278589.988634496</v>
+        <v>3278589.98857152</v>
       </c>
       <c r="P246" t="n">
         <v>27500</v>
@@ -12978,10 +12978,10 @@
         <v>79</v>
       </c>
       <c r="N282" t="n">
-        <v>5347.73</v>
+        <v>5370.4862978723</v>
       </c>
       <c r="O282" t="n">
-        <v>422470.67</v>
+        <v>424268.4175319117</v>
       </c>
       <c r="P282" t="n">
         <v>9500</v>
@@ -14038,10 +14038,10 @@
         <v>16596</v>
       </c>
       <c r="N305" t="n">
-        <v>703.79541200942</v>
+        <v>703.79538564105</v>
       </c>
       <c r="O305" t="n">
-        <v>11680188.65770834</v>
+        <v>11680188.22009886</v>
       </c>
       <c r="P305" t="n">
         <v>900</v>
@@ -15137,10 +15137,10 @@
         <v>45</v>
       </c>
       <c r="N328" t="n">
-        <v>3067.0905341246</v>
+        <v>3067.0905389222</v>
       </c>
       <c r="O328" t="n">
-        <v>138019.074035607</v>
+        <v>138019.074251499</v>
       </c>
       <c r="P328" t="n">
         <v>7200</v>
@@ -15232,10 +15232,10 @@
         <v>19</v>
       </c>
       <c r="N330" t="n">
-        <v>4190.77</v>
+        <v>4205.0243197279</v>
       </c>
       <c r="O330" t="n">
-        <v>79624.63</v>
+        <v>79895.46207483009</v>
       </c>
       <c r="P330" t="n">
         <v>5900</v>
@@ -15281,10 +15281,10 @@
         <v>200</v>
       </c>
       <c r="N331" t="n">
-        <v>3499.72</v>
+        <v>3508.0033609467</v>
       </c>
       <c r="O331" t="n">
-        <v>699944</v>
+        <v>701600.67218934</v>
       </c>
       <c r="P331" t="n">
         <v>6900</v>
@@ -15474,10 +15474,10 @@
         <v>120</v>
       </c>
       <c r="N335" t="n">
-        <v>4159.0002877698</v>
+        <v>4159.0002919708</v>
       </c>
       <c r="O335" t="n">
-        <v>499080.034532376</v>
+        <v>499080.0350364961</v>
       </c>
       <c r="P335" t="n">
         <v>8900</v>
@@ -15948,10 +15948,10 @@
         <v>699</v>
       </c>
       <c r="N345" t="n">
-        <v>7046.9398302567</v>
+        <v>7046.9398299681</v>
       </c>
       <c r="O345" t="n">
-        <v>4925810.941349433</v>
+        <v>4925810.941147702</v>
       </c>
       <c r="P345" t="n">
         <v>9900</v>
@@ -16135,10 +16135,10 @@
         <v>1432</v>
       </c>
       <c r="N349" t="n">
-        <v>641.78</v>
+        <v>642.25894029851</v>
       </c>
       <c r="O349" t="n">
-        <v>919028.96</v>
+        <v>919714.8025074663</v>
       </c>
       <c r="P349" t="n">
         <v>2500</v>
@@ -16455,10 +16455,10 @@
         <v>282</v>
       </c>
       <c r="N356" t="n">
-        <v>1008.8176731794</v>
+        <v>1019.6846499102</v>
       </c>
       <c r="O356" t="n">
-        <v>284486.5838365908</v>
+        <v>287551.0712746764</v>
       </c>
       <c r="P356" t="n">
         <v>1500</v>
@@ -16593,10 +16593,10 @@
         <v>169</v>
       </c>
       <c r="N359" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821442495</v>
       </c>
       <c r="O359" t="n">
-        <v>205112.2781888245</v>
+        <v>205112.2823781655</v>
       </c>
       <c r="P359" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-12</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>15</v>
@@ -4823,10 +4823,10 @@
         <v>4733</v>
       </c>
       <c r="N103" t="n">
-        <v>17476.031091396</v>
+        <v>17472.91</v>
       </c>
       <c r="O103" t="n">
-        <v>82714055.15557726</v>
+        <v>82699283.03</v>
       </c>
       <c r="P103" t="n">
         <v>2900</v>
@@ -5234,10 +5234,10 @@
         <v>42</v>
       </c>
       <c r="N112" t="n">
-        <v>8367.5094603175</v>
+        <v>8341.030000000001</v>
       </c>
       <c r="O112" t="n">
-        <v>351435.397333335</v>
+        <v>350323.26</v>
       </c>
       <c r="P112" t="n">
         <v>13900</v>
@@ -10125,10 +10125,10 @@
         <v>118</v>
       </c>
       <c r="N220" t="n">
-        <v>4213.1164021164</v>
+        <v>4202</v>
       </c>
       <c r="O220" t="n">
-        <v>497147.7354497352</v>
+        <v>495836</v>
       </c>
       <c r="P220" t="n">
         <v>7900</v>
@@ -12978,10 +12978,10 @@
         <v>79</v>
       </c>
       <c r="N282" t="n">
-        <v>5370.4862978723</v>
+        <v>5347.73</v>
       </c>
       <c r="O282" t="n">
-        <v>424268.4175319117</v>
+        <v>422470.67</v>
       </c>
       <c r="P282" t="n">
         <v>9500</v>
@@ -15232,10 +15232,10 @@
         <v>19</v>
       </c>
       <c r="N330" t="n">
-        <v>4205.0243197279</v>
+        <v>4190.77</v>
       </c>
       <c r="O330" t="n">
-        <v>79895.46207483009</v>
+        <v>79624.63</v>
       </c>
       <c r="P330" t="n">
         <v>5900</v>
@@ -15281,10 +15281,10 @@
         <v>200</v>
       </c>
       <c r="N331" t="n">
-        <v>3508.0033609467</v>
+        <v>3499.72</v>
       </c>
       <c r="O331" t="n">
-        <v>701600.67218934</v>
+        <v>699944</v>
       </c>
       <c r="P331" t="n">
         <v>6900</v>
@@ -16135,10 +16135,10 @@
         <v>1432</v>
       </c>
       <c r="N349" t="n">
-        <v>642.25894029851</v>
+        <v>641.78</v>
       </c>
       <c r="O349" t="n">
-        <v>919714.8025074663</v>
+        <v>919028.96</v>
       </c>
       <c r="P349" t="n">
         <v>2500</v>
@@ -16455,10 +16455,10 @@
         <v>282</v>
       </c>
       <c r="N356" t="n">
-        <v>1019.6846499102</v>
+        <v>1008.817540395</v>
       </c>
       <c r="O356" t="n">
-        <v>287551.0712746764</v>
+        <v>284486.54639139</v>
       </c>
       <c r="P356" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -724,22 +724,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>1811.3043052838</v>
+        <v>1811.3044243338</v>
       </c>
       <c r="O8" t="n">
-        <v>27169.564579257</v>
+        <v>16301.7398190042</v>
       </c>
       <c r="P8" t="n">
         <v>2600</v>
       </c>
       <c r="Q8" t="n">
-        <v>39000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="9">
@@ -1326,10 +1326,10 @@
         <v>180</v>
       </c>
       <c r="N23" t="n">
-        <v>3926.8371267317</v>
+        <v>3926.8371237802</v>
       </c>
       <c r="O23" t="n">
-        <v>706830.6828117061</v>
+        <v>706830.6822804359</v>
       </c>
       <c r="P23" t="n">
         <v>4800</v>
@@ -1599,10 +1599,10 @@
         <v>120</v>
       </c>
       <c r="N30" t="n">
-        <v>3910.6282352941</v>
+        <v>3933.7680473373</v>
       </c>
       <c r="O30" t="n">
-        <v>469275.388235292</v>
+        <v>472052.165680476</v>
       </c>
       <c r="P30" t="n">
         <v>9100</v>
@@ -2029,10 +2029,10 @@
         <v>40</v>
       </c>
       <c r="N40" t="n">
-        <v>200072.19977273</v>
+        <v>200072.19992308</v>
       </c>
       <c r="O40" t="n">
-        <v>8002887.9909092</v>
+        <v>8002887.996923201</v>
       </c>
       <c r="P40" t="n">
         <v>312000</v>
@@ -2067,22 +2067,22 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>288344.10333333</v>
+        <v>288344.57</v>
       </c>
       <c r="O41" t="n">
-        <v>288344.10333333</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>450000</v>
       </c>
       <c r="Q41" t="n">
-        <v>450000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2114,22 +2114,22 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N42" t="n">
-        <v>344599.17865385</v>
+        <v>344599.17862745</v>
       </c>
       <c r="O42" t="n">
-        <v>3101392.60788465</v>
+        <v>2756793.4290196</v>
       </c>
       <c r="P42" t="n">
         <v>532900</v>
       </c>
       <c r="Q42" t="n">
-        <v>4796100</v>
+        <v>4263200</v>
       </c>
     </row>
     <row r="43">
@@ -2167,10 +2167,10 @@
         <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>263530.179</v>
+        <v>263530.17666667</v>
       </c>
       <c r="O43" t="n">
-        <v>263530.179</v>
+        <v>263530.17666667</v>
       </c>
       <c r="P43" t="n">
         <v>402900</v>
@@ -2253,10 +2253,10 @@
         <v>84</v>
       </c>
       <c r="N45" t="n">
-        <v>20961.76</v>
+        <v>21291.002303665</v>
       </c>
       <c r="O45" t="n">
-        <v>1760787.84</v>
+        <v>1788444.19350786</v>
       </c>
       <c r="P45" t="n">
         <v>38300</v>
@@ -2370,10 +2370,10 @@
         <v>86</v>
       </c>
       <c r="N48" t="n">
-        <v>61666.873932292</v>
+        <v>61666.873994709</v>
       </c>
       <c r="O48" t="n">
-        <v>5303351.158177112</v>
+        <v>5303351.163544974</v>
       </c>
       <c r="P48" t="n">
         <v>98900</v>
@@ -3144,10 +3144,10 @@
         <v>73</v>
       </c>
       <c r="N66" t="n">
-        <v>3775.99</v>
+        <v>3826.6744295302</v>
       </c>
       <c r="O66" t="n">
-        <v>275647.27</v>
+        <v>279347.2333557046</v>
       </c>
       <c r="P66" t="n">
         <v>7300</v>
@@ -3275,10 +3275,10 @@
         <v>60</v>
       </c>
       <c r="N69" t="n">
-        <v>7569</v>
+        <v>7632.3389121339</v>
       </c>
       <c r="O69" t="n">
-        <v>454140</v>
+        <v>457940.334728034</v>
       </c>
       <c r="P69" t="n">
         <v>12900</v>
@@ -3498,10 +3498,10 @@
         <v>2592</v>
       </c>
       <c r="N74" t="n">
-        <v>3158.8608143857</v>
+        <v>3158.8608147003</v>
       </c>
       <c r="O74" t="n">
-        <v>8187767.230887734</v>
+        <v>8187767.231703178</v>
       </c>
       <c r="P74" t="n">
         <v>5600</v>
@@ -3682,10 +3682,10 @@
         <v>648</v>
       </c>
       <c r="N78" t="n">
-        <v>3795.7100070547</v>
+        <v>3795.7100070621</v>
       </c>
       <c r="O78" t="n">
-        <v>2459620.084571445</v>
+        <v>2459620.084576241</v>
       </c>
       <c r="P78" t="n">
         <v>6200</v>
@@ -3861,10 +3861,10 @@
         <v>396</v>
       </c>
       <c r="N82" t="n">
-        <v>4890.9300462963</v>
+        <v>4890.9300463499</v>
       </c>
       <c r="O82" t="n">
-        <v>1936808.298333335</v>
+        <v>1936808.298354561</v>
       </c>
       <c r="P82" t="n">
         <v>8200</v>
@@ -4089,10 +4089,10 @@
         <v>288</v>
       </c>
       <c r="N87" t="n">
-        <v>3594.2541747573</v>
+        <v>3594.25414277</v>
       </c>
       <c r="O87" t="n">
-        <v>1035145.202330102</v>
+        <v>1035145.19311776</v>
       </c>
       <c r="P87" t="n">
         <v>6500</v>
@@ -4227,10 +4227,10 @@
         <v>48</v>
       </c>
       <c r="N90" t="n">
-        <v>14822.378864577</v>
+        <v>14822.378863905</v>
       </c>
       <c r="O90" t="n">
-        <v>711474.1854996961</v>
+        <v>711474.1854674399</v>
       </c>
       <c r="P90" t="n">
         <v>24900</v>
@@ -4638,10 +4638,10 @@
         <v>1406</v>
       </c>
       <c r="N99" t="n">
-        <v>4372.2107869318</v>
+        <v>4372.2107876031</v>
       </c>
       <c r="O99" t="n">
-        <v>6147328.36642611</v>
+        <v>6147328.367369958</v>
       </c>
       <c r="P99" t="n">
         <v>7500</v>
@@ -5190,10 +5190,10 @@
         <v>23</v>
       </c>
       <c r="N111" t="n">
-        <v>16897</v>
+        <v>17010.976391231</v>
       </c>
       <c r="O111" t="n">
-        <v>388631</v>
+        <v>391252.456998313</v>
       </c>
       <c r="P111" t="n">
         <v>27900</v>
@@ -6135,10 +6135,10 @@
         <v>432</v>
       </c>
       <c r="N132" t="n">
-        <v>2029.8736549708</v>
+        <v>2029.8736782737</v>
       </c>
       <c r="O132" t="n">
-        <v>876905.4189473856</v>
+        <v>876905.4290142384</v>
       </c>
       <c r="P132" t="n">
         <v>3600</v>
@@ -6176,10 +6176,10 @@
         <v>528</v>
       </c>
       <c r="N133" t="n">
-        <v>22485.695904437</v>
+        <v>22511.306036446</v>
       </c>
       <c r="O133" t="n">
-        <v>11872447.43754274</v>
+        <v>11885969.58724349</v>
       </c>
       <c r="P133" t="n">
         <v>36500</v>
@@ -7251,10 +7251,10 @@
         <v>144</v>
       </c>
       <c r="N157" t="n">
-        <v>27123.765241636</v>
+        <v>27123.765232775</v>
       </c>
       <c r="O157" t="n">
-        <v>3905822.194795584</v>
+        <v>3905822.1935196</v>
       </c>
       <c r="P157" t="n">
         <v>44500</v>
@@ -7389,10 +7389,10 @@
         <v>148</v>
       </c>
       <c r="N160" t="n">
-        <v>5431.12</v>
+        <v>5465.2779874214</v>
       </c>
       <c r="O160" t="n">
-        <v>803805.76</v>
+        <v>808861.1421383673</v>
       </c>
       <c r="P160" t="n">
         <v>8900</v>
@@ -7435,10 +7435,10 @@
         <v>714</v>
       </c>
       <c r="N161" t="n">
-        <v>1560.9991607397</v>
+        <v>1560.999261745</v>
       </c>
       <c r="O161" t="n">
-        <v>1114553.400768146</v>
+        <v>1114553.47288593</v>
       </c>
       <c r="P161" t="n">
         <v>2900</v>
@@ -7563,10 +7563,10 @@
         <v>60</v>
       </c>
       <c r="N164" t="n">
-        <v>11662.4</v>
+        <v>12042.695652174</v>
       </c>
       <c r="O164" t="n">
-        <v>699744</v>
+        <v>722561.7391304399</v>
       </c>
       <c r="P164" t="n">
         <v>19900</v>
@@ -7924,10 +7924,10 @@
         <v>16</v>
       </c>
       <c r="N172" t="n">
-        <v>10174</v>
+        <v>10716.613333333</v>
       </c>
       <c r="O172" t="n">
-        <v>162784</v>
+        <v>171465.813333328</v>
       </c>
       <c r="P172" t="n">
         <v>16900</v>
@@ -8108,10 +8108,10 @@
         <v>126</v>
       </c>
       <c r="N176" t="n">
-        <v>15824</v>
+        <v>15908.394666667</v>
       </c>
       <c r="O176" t="n">
-        <v>1993824</v>
+        <v>2004457.728000042</v>
       </c>
       <c r="P176" t="n">
         <v>26900</v>
@@ -8292,10 +8292,10 @@
         <v>11</v>
       </c>
       <c r="N180" t="n">
-        <v>23521.624776119</v>
+        <v>23878.013030303</v>
       </c>
       <c r="O180" t="n">
-        <v>258737.872537309</v>
+        <v>262658.143333333</v>
       </c>
       <c r="P180" t="n">
         <v>39000</v>
@@ -8332,22 +8332,22 @@
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M181" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="N181" t="n">
-        <v>3486</v>
+        <v>3502.5901249256</v>
       </c>
       <c r="O181" t="n">
-        <v>446208</v>
+        <v>420310.814991072</v>
       </c>
       <c r="P181" t="n">
         <v>6900</v>
       </c>
       <c r="Q181" t="n">
-        <v>883200</v>
+        <v>828000</v>
       </c>
     </row>
     <row r="182">
@@ -8384,10 +8384,10 @@
         <v>680</v>
       </c>
       <c r="N182" t="n">
-        <v>1778.4725489051</v>
+        <v>1786.8332290289</v>
       </c>
       <c r="O182" t="n">
-        <v>1209361.333255468</v>
+        <v>1215046.595739652</v>
       </c>
       <c r="P182" t="n">
         <v>4900</v>
@@ -8706,10 +8706,10 @@
         <v>126</v>
       </c>
       <c r="N189" t="n">
-        <v>4917</v>
+        <v>5030.2949308756</v>
       </c>
       <c r="O189" t="n">
-        <v>619542</v>
+        <v>633817.1612903256</v>
       </c>
       <c r="P189" t="n">
         <v>8600</v>
@@ -8939,10 +8939,10 @@
         <v>96</v>
       </c>
       <c r="N194" t="n">
-        <v>7713</v>
+        <v>7735.3565217391</v>
       </c>
       <c r="O194" t="n">
-        <v>740448</v>
+        <v>742594.2260869535</v>
       </c>
       <c r="P194" t="n">
         <v>12500</v>
@@ -9123,10 +9123,10 @@
         <v>12</v>
       </c>
       <c r="N198" t="n">
-        <v>13019</v>
+        <v>13090.336986301</v>
       </c>
       <c r="O198" t="n">
-        <v>156228</v>
+        <v>157084.043835612</v>
       </c>
       <c r="P198" t="n">
         <v>20900</v>
@@ -9169,10 +9169,10 @@
         <v>36</v>
       </c>
       <c r="N199" t="n">
-        <v>17644.653275862</v>
+        <v>17644.653166667</v>
       </c>
       <c r="O199" t="n">
-        <v>635207.517931032</v>
+        <v>635207.5140000121</v>
       </c>
       <c r="P199" t="n">
         <v>28200</v>
@@ -9721,10 +9721,10 @@
         <v>162</v>
       </c>
       <c r="N211" t="n">
-        <v>4907.8219330289</v>
+        <v>4907.821941896</v>
       </c>
       <c r="O211" t="n">
-        <v>795067.1531506819</v>
+        <v>795067.1545871519</v>
       </c>
       <c r="P211" t="n">
         <v>8200</v>
@@ -9767,10 +9767,10 @@
         <v>252</v>
       </c>
       <c r="N212" t="n">
-        <v>6414</v>
+        <v>6426.7641791045</v>
       </c>
       <c r="O212" t="n">
-        <v>1616328</v>
+        <v>1619544.573134334</v>
       </c>
       <c r="P212" t="n">
         <v>10900</v>
@@ -9951,10 +9951,10 @@
         <v>280</v>
       </c>
       <c r="N216" t="n">
-        <v>3903.7361538462</v>
+        <v>3903.7361658031</v>
       </c>
       <c r="O216" t="n">
-        <v>1093046.123076936</v>
+        <v>1093046.126424868</v>
       </c>
       <c r="P216" t="n">
         <v>7500</v>
@@ -10125,10 +10125,10 @@
         <v>118</v>
       </c>
       <c r="N220" t="n">
-        <v>4202</v>
+        <v>4235.616</v>
       </c>
       <c r="O220" t="n">
-        <v>495836</v>
+        <v>499802.688</v>
       </c>
       <c r="P220" t="n">
         <v>7900</v>
@@ -10401,10 +10401,10 @@
         <v>792</v>
       </c>
       <c r="N226" t="n">
-        <v>5772</v>
+        <v>5789.4673839946</v>
       </c>
       <c r="O226" t="n">
-        <v>4571424</v>
+        <v>4585258.168123723</v>
       </c>
       <c r="P226" t="n">
         <v>9900</v>
@@ -10447,10 +10447,10 @@
         <v>552</v>
       </c>
       <c r="N227" t="n">
-        <v>6645</v>
+        <v>6663.0865541644</v>
       </c>
       <c r="O227" t="n">
-        <v>3668040</v>
+        <v>3678023.777898749</v>
       </c>
       <c r="P227" t="n">
         <v>10900</v>
@@ -10493,10 +10493,10 @@
         <v>256</v>
       </c>
       <c r="N228" t="n">
-        <v>13098</v>
+        <v>13167.485411141</v>
       </c>
       <c r="O228" t="n">
-        <v>3353088</v>
+        <v>3370876.265252096</v>
       </c>
       <c r="P228" t="n">
         <v>21200</v>
@@ -10677,10 +10677,10 @@
         <v>144</v>
       </c>
       <c r="N232" t="n">
-        <v>3898</v>
+        <v>3913.1437451437</v>
       </c>
       <c r="O232" t="n">
-        <v>561312</v>
+        <v>563492.6993006928</v>
       </c>
       <c r="P232" t="n">
         <v>6900</v>
@@ -11551,10 +11551,10 @@
         <v>68</v>
       </c>
       <c r="N251" t="n">
-        <v>10219</v>
+        <v>10293.773170732</v>
       </c>
       <c r="O251" t="n">
-        <v>694892</v>
+        <v>699976.575609776</v>
       </c>
       <c r="P251" t="n">
         <v>16900</v>
@@ -11738,10 +11738,10 @@
         <v>132</v>
       </c>
       <c r="N255" t="n">
-        <v>27254</v>
+        <v>27323.703324808</v>
       </c>
       <c r="O255" t="n">
-        <v>3597528</v>
+        <v>3606728.838874656</v>
       </c>
       <c r="P255" t="n">
         <v>43900</v>
@@ -12152,10 +12152,10 @@
         <v>447</v>
       </c>
       <c r="N264" t="n">
-        <v>3639.35</v>
+        <v>3659.324478595</v>
       </c>
       <c r="O264" t="n">
-        <v>1626789.45</v>
+        <v>1635718.041931965</v>
       </c>
       <c r="P264" t="n">
         <v>7500</v>
@@ -12244,10 +12244,10 @@
         <v>196</v>
       </c>
       <c r="N266" t="n">
-        <v>5640</v>
+        <v>5732.1568627451</v>
       </c>
       <c r="O266" t="n">
-        <v>1105440</v>
+        <v>1123502.74509804</v>
       </c>
       <c r="P266" t="n">
         <v>9900</v>
@@ -12474,10 +12474,10 @@
         <v>934</v>
       </c>
       <c r="N271" t="n">
-        <v>3821</v>
+        <v>3828.7583756345</v>
       </c>
       <c r="O271" t="n">
-        <v>3568814</v>
+        <v>3576060.322842623</v>
       </c>
       <c r="P271" t="n">
         <v>5900</v>
@@ -12704,10 +12704,10 @@
         <v>240</v>
       </c>
       <c r="N276" t="n">
-        <v>5476</v>
+        <v>5504.4467532468</v>
       </c>
       <c r="O276" t="n">
-        <v>1314240</v>
+        <v>1321067.220779232</v>
       </c>
       <c r="P276" t="n">
         <v>8900</v>
@@ -12842,10 +12842,10 @@
         <v>1152</v>
       </c>
       <c r="N279" t="n">
-        <v>1516.0388129219</v>
+        <v>1517.7951815022</v>
       </c>
       <c r="O279" t="n">
-        <v>1746476.712486029</v>
+        <v>1748500.049090534</v>
       </c>
       <c r="P279" t="n">
         <v>2300</v>
@@ -12978,10 +12978,10 @@
         <v>79</v>
       </c>
       <c r="N282" t="n">
-        <v>5347.73</v>
+        <v>5393.6332618026</v>
       </c>
       <c r="O282" t="n">
-        <v>422470.67</v>
+        <v>426097.0276824054</v>
       </c>
       <c r="P282" t="n">
         <v>9500</v>
@@ -13070,10 +13070,10 @@
         <v>4896</v>
       </c>
       <c r="N284" t="n">
-        <v>1801</v>
+        <v>1803.2544202785</v>
       </c>
       <c r="O284" t="n">
-        <v>8817696</v>
+        <v>8828733.641683536</v>
       </c>
       <c r="P284" t="n">
         <v>2900</v>
@@ -13209,10 +13209,10 @@
         <v>121</v>
       </c>
       <c r="N287" t="n">
-        <v>2857.22</v>
+        <v>2865.3179310345</v>
       </c>
       <c r="O287" t="n">
-        <v>345723.62</v>
+        <v>346703.4696551745</v>
       </c>
       <c r="P287" t="n">
         <v>4900</v>
@@ -13258,10 +13258,10 @@
         <v>600</v>
       </c>
       <c r="N288" t="n">
-        <v>8945.379999999999</v>
+        <v>8947.9898847557</v>
       </c>
       <c r="O288" t="n">
-        <v>5367227.999999999</v>
+        <v>5368793.93085342</v>
       </c>
       <c r="P288" t="n">
         <v>14900</v>
@@ -13484,10 +13484,10 @@
         <v>1440</v>
       </c>
       <c r="N293" t="n">
-        <v>1690.8700089286</v>
+        <v>1690.8700089526</v>
       </c>
       <c r="O293" t="n">
-        <v>2434852.812857184</v>
+        <v>2434852.812891744</v>
       </c>
       <c r="P293" t="n">
         <v>3000</v>
@@ -14038,10 +14038,10 @@
         <v>16596</v>
       </c>
       <c r="N305" t="n">
-        <v>703.79538564105</v>
+        <v>703.79534416571</v>
       </c>
       <c r="O305" t="n">
-        <v>11680188.22009886</v>
+        <v>11680187.53177412</v>
       </c>
       <c r="P305" t="n">
         <v>900</v>
@@ -14892,10 +14892,10 @@
         <v>15</v>
       </c>
       <c r="N323" t="n">
-        <v>13623.91</v>
+        <v>14147.906538462</v>
       </c>
       <c r="O323" t="n">
-        <v>204358.65</v>
+        <v>212218.59807693</v>
       </c>
       <c r="P323" t="n">
         <v>26900</v>
@@ -15039,10 +15039,10 @@
         <v>21</v>
       </c>
       <c r="N326" t="n">
-        <v>2992.5687209302</v>
+        <v>2992.5688235294</v>
       </c>
       <c r="O326" t="n">
-        <v>62843.9431395342</v>
+        <v>62843.9452941174</v>
       </c>
       <c r="P326" t="n">
         <v>6000</v>
@@ -15281,10 +15281,10 @@
         <v>200</v>
       </c>
       <c r="N331" t="n">
-        <v>3499.72</v>
+        <v>3516.3655172414</v>
       </c>
       <c r="O331" t="n">
-        <v>699944</v>
+        <v>703273.10344828</v>
       </c>
       <c r="P331" t="n">
         <v>6900</v>
@@ -15330,10 +15330,10 @@
         <v>208</v>
       </c>
       <c r="N332" t="n">
-        <v>4578.04</v>
+        <v>4597.9229098806</v>
       </c>
       <c r="O332" t="n">
-        <v>952232.3199999999</v>
+        <v>956367.9652551648</v>
       </c>
       <c r="P332" t="n">
         <v>7500</v>
@@ -16593,10 +16593,10 @@
         <v>169</v>
       </c>
       <c r="N359" t="n">
-        <v>1213.6821442495</v>
+        <v>1213.6821194605</v>
       </c>
       <c r="O359" t="n">
-        <v>205112.2823781655</v>
+        <v>205112.2781888245</v>
       </c>
       <c r="P359" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -603,10 +603,10 @@
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>66707.97725</v>
+        <v>66707.977837838</v>
       </c>
       <c r="O5" t="n">
-        <v>333539.88625</v>
+        <v>333539.88918919</v>
       </c>
       <c r="P5" t="n">
         <v>125900</v>
@@ -724,22 +724,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>1811.3044243338</v>
+        <v>1811.3044829343</v>
       </c>
       <c r="O8" t="n">
-        <v>16301.7398190042</v>
+        <v>14490.4358634744</v>
       </c>
       <c r="P8" t="n">
         <v>2600</v>
       </c>
       <c r="Q8" t="n">
-        <v>23400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="9">
@@ -808,10 +808,10 @@
         <v>476</v>
       </c>
       <c r="N10" t="n">
-        <v>3376.7465014893</v>
+        <v>3376.746498645</v>
       </c>
       <c r="O10" t="n">
-        <v>1607331.334708907</v>
+        <v>1607331.33335502</v>
       </c>
       <c r="P10" t="n">
         <v>4500</v>
@@ -1599,10 +1599,10 @@
         <v>120</v>
       </c>
       <c r="N30" t="n">
-        <v>3910.6282248521</v>
+        <v>3910.6281963928</v>
       </c>
       <c r="O30" t="n">
-        <v>469275.386982252</v>
+        <v>469275.383567136</v>
       </c>
       <c r="P30" t="n">
         <v>9100</v>
@@ -2029,10 +2029,10 @@
         <v>40</v>
       </c>
       <c r="N40" t="n">
-        <v>200072.19992308</v>
+        <v>200072.2</v>
       </c>
       <c r="O40" t="n">
-        <v>8002887.996923201</v>
+        <v>8002888</v>
       </c>
       <c r="P40" t="n">
         <v>312000</v>
@@ -2164,22 +2164,22 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N43" t="n">
         <v>27000</v>
       </c>
       <c r="O43" t="n">
-        <v>1782000</v>
+        <v>1674000</v>
       </c>
       <c r="P43" t="n">
         <v>20000</v>
       </c>
       <c r="Q43" t="n">
-        <v>1320000</v>
+        <v>1240000</v>
       </c>
     </row>
     <row r="44">
@@ -3454,10 +3454,10 @@
         <v>2592</v>
       </c>
       <c r="N73" t="n">
-        <v>3158.8608147003</v>
+        <v>3158.860814779</v>
       </c>
       <c r="O73" t="n">
-        <v>8187767.231703178</v>
+        <v>8187767.231907168</v>
       </c>
       <c r="P73" t="n">
         <v>5600</v>
@@ -3500,10 +3500,10 @@
         <v>77</v>
       </c>
       <c r="N74" t="n">
-        <v>3841.6247184466</v>
+        <v>3841.6247414634</v>
       </c>
       <c r="O74" t="n">
-        <v>295805.1033203882</v>
+        <v>295805.1050926818</v>
       </c>
       <c r="P74" t="n">
         <v>6900</v>
@@ -3817,10 +3817,10 @@
         <v>396</v>
       </c>
       <c r="N81" t="n">
-        <v>4890.9300463499</v>
+        <v>4890.9300464306</v>
       </c>
       <c r="O81" t="n">
-        <v>1936808.298354561</v>
+        <v>1936808.298386517</v>
       </c>
       <c r="P81" t="n">
         <v>8200</v>
@@ -4045,10 +4045,10 @@
         <v>288</v>
       </c>
       <c r="N86" t="n">
-        <v>3594.25414277</v>
+        <v>3594.2541391941</v>
       </c>
       <c r="O86" t="n">
-        <v>1035145.19311776</v>
+        <v>1035145.192087901</v>
       </c>
       <c r="P86" t="n">
         <v>6500</v>
@@ -4183,10 +4183,10 @@
         <v>48</v>
       </c>
       <c r="N89" t="n">
-        <v>14822.378863905</v>
+        <v>14822.378862559</v>
       </c>
       <c r="O89" t="n">
-        <v>711474.1854674399</v>
+        <v>711474.185402832</v>
       </c>
       <c r="P89" t="n">
         <v>24900</v>
@@ -4594,10 +4594,10 @@
         <v>1406</v>
       </c>
       <c r="N98" t="n">
-        <v>4372.2107876031</v>
+        <v>4372.2107877711</v>
       </c>
       <c r="O98" t="n">
-        <v>6147328.367369958</v>
+        <v>6147328.367606166</v>
       </c>
       <c r="P98" t="n">
         <v>7500</v>
@@ -6091,10 +6091,10 @@
         <v>432</v>
       </c>
       <c r="N131" t="n">
-        <v>2029.8736782737</v>
+        <v>2029.8737073653</v>
       </c>
       <c r="O131" t="n">
-        <v>876905.4290142384</v>
+        <v>876905.4415818097</v>
       </c>
       <c r="P131" t="n">
         <v>3600</v>
@@ -7391,10 +7391,10 @@
         <v>714</v>
       </c>
       <c r="N160" t="n">
-        <v>1560.999261745</v>
+        <v>1560.9993877551</v>
       </c>
       <c r="O160" t="n">
-        <v>1114553.47288593</v>
+        <v>1114553.562857141</v>
       </c>
       <c r="P160" t="n">
         <v>2900</v>
@@ -8248,10 +8248,10 @@
         <v>11</v>
       </c>
       <c r="N179" t="n">
-        <v>23521.62469697</v>
+        <v>23521.62453125</v>
       </c>
       <c r="O179" t="n">
-        <v>258737.87166667</v>
+        <v>258737.86984375</v>
       </c>
       <c r="P179" t="n">
         <v>39000</v>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -8291,19 +8291,19 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="N180" t="n">
         <v>3486</v>
       </c>
       <c r="O180" t="n">
-        <v>418320</v>
+        <v>446208</v>
       </c>
       <c r="P180" t="n">
         <v>6900</v>
       </c>
       <c r="Q180" t="n">
-        <v>828000</v>
+        <v>883200</v>
       </c>
     </row>
     <row r="181">
@@ -8340,10 +8340,10 @@
         <v>680</v>
       </c>
       <c r="N181" t="n">
-        <v>1778.4725650066</v>
+        <v>1778.4725680247</v>
       </c>
       <c r="O181" t="n">
-        <v>1209361.344204488</v>
+        <v>1209361.346256796</v>
       </c>
       <c r="P181" t="n">
         <v>4900</v>
@@ -9677,10 +9677,10 @@
         <v>162</v>
       </c>
       <c r="N210" t="n">
-        <v>4907.821941896</v>
+        <v>4907.8219448698</v>
       </c>
       <c r="O210" t="n">
-        <v>795067.1545871519</v>
+        <v>795067.1550689077</v>
       </c>
       <c r="P210" t="n">
         <v>8200</v>
@@ -9907,10 +9907,10 @@
         <v>280</v>
       </c>
       <c r="N215" t="n">
-        <v>3903.7361658031</v>
+        <v>3903.7362017804</v>
       </c>
       <c r="O215" t="n">
-        <v>1093046.126424868</v>
+        <v>1093046.136498512</v>
       </c>
       <c r="P215" t="n">
         <v>7500</v>
@@ -12798,10 +12798,10 @@
         <v>1152</v>
       </c>
       <c r="N278" t="n">
-        <v>1516.0388115466</v>
+        <v>1516.0388110875</v>
       </c>
       <c r="O278" t="n">
-        <v>1746476.710901683</v>
+        <v>1746476.7103728</v>
       </c>
       <c r="P278" t="n">
         <v>2300</v>
@@ -13621,10 +13621,10 @@
         <v>1436</v>
       </c>
       <c r="N296" t="n">
-        <v>345.55838640256</v>
+        <v>345.55838633169</v>
       </c>
       <c r="O296" t="n">
-        <v>496221.8428740762</v>
+        <v>496221.8427723068</v>
       </c>
       <c r="P296" t="n">
         <v>600</v>
@@ -13994,10 +13994,10 @@
         <v>16596</v>
       </c>
       <c r="N304" t="n">
-        <v>703.79534416571</v>
+        <v>703.79533220158</v>
       </c>
       <c r="O304" t="n">
-        <v>11680187.53177412</v>
+        <v>11680187.33321742</v>
       </c>
       <c r="P304" t="n">
         <v>900</v>
@@ -15904,10 +15904,10 @@
         <v>699</v>
       </c>
       <c r="N344" t="n">
-        <v>7046.9398299681</v>
+        <v>7046.939829932</v>
       </c>
       <c r="O344" t="n">
-        <v>4925810.941147702</v>
+        <v>4925810.941122468</v>
       </c>
       <c r="P344" t="n">
         <v>9900</v>
@@ -16589,22 +16589,22 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="M359" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="N359" t="n">
         <v>705.52801204819</v>
       </c>
       <c r="O359" t="n">
-        <v>131228.2102409634</v>
+        <v>0</v>
       </c>
       <c r="P359" t="n">
         <v>1500</v>
       </c>
       <c r="Q359" t="n">
-        <v>279000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -16641,10 +16641,10 @@
         <v>179</v>
       </c>
       <c r="N360" t="n">
-        <v>13493.858313253</v>
+        <v>13493.858308157</v>
       </c>
       <c r="O360" t="n">
-        <v>2415400.638072287</v>
+        <v>2415400.637160103</v>
       </c>
       <c r="P360" t="n">
         <v>16900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q366"/>
+  <dimension ref="A1:Q365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
         </is>
       </c>
     </row>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>8</v>
@@ -2158,13 +2158,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>62</v>
@@ -16564,58 +16564,58 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>C984</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>CG2016531</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>TANGRAM</t>
+          <t>SNORKEL 66046A</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J359" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="K359" t="n">
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="M359" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="N359" t="n">
-        <v>705.52801204819</v>
+        <v>13493.858308157</v>
       </c>
       <c r="O359" t="n">
-        <v>0</v>
+        <v>2415400.637160103</v>
       </c>
       <c r="P359" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="Q359" t="n">
-        <v>0</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -16629,7 +16629,7 @@
         </is>
       </c>
       <c r="J360" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
@@ -16638,35 +16638,40 @@
         <v>0</v>
       </c>
       <c r="M360" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="N360" t="n">
-        <v>13493.858308157</v>
+        <v>2644.9</v>
       </c>
       <c r="O360" t="n">
-        <v>2415400.637160103</v>
+        <v>917780.3</v>
       </c>
       <c r="P360" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q360" t="n">
-        <v>3025100</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -16675,7 +16680,7 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -16684,35 +16689,30 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="N361" t="n">
-        <v>2644.9</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O361" t="n">
-        <v>917780.3</v>
+        <v>33759.88</v>
       </c>
       <c r="P361" t="n">
-        <v>3900</v>
+        <v>29500</v>
       </c>
       <c r="Q361" t="n">
-        <v>1353300</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -16726,7 +16726,7 @@
         </is>
       </c>
       <c r="J362" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K362" t="n">
         <v>0</v>
@@ -16735,35 +16735,40 @@
         <v>0</v>
       </c>
       <c r="M362" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N362" t="n">
-        <v>8439.969999999999</v>
+        <v>12189.832</v>
       </c>
       <c r="O362" t="n">
-        <v>33759.88</v>
+        <v>219416.976</v>
       </c>
       <c r="P362" t="n">
-        <v>29500</v>
+        <v>30900</v>
       </c>
       <c r="Q362" t="n">
-        <v>118000</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -16772,7 +16777,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -16781,35 +16786,30 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="N363" t="n">
-        <v>12189.832</v>
+        <v>15452.21</v>
       </c>
       <c r="O363" t="n">
-        <v>219416.976</v>
+        <v>741706.08</v>
       </c>
       <c r="P363" t="n">
-        <v>30900</v>
+        <v>36500</v>
       </c>
       <c r="Q363" t="n">
-        <v>556200</v>
+        <v>1752000</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>MG30151</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -16823,7 +16823,7 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>48</v>
+        <v>420</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
@@ -16832,35 +16832,40 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>48</v>
+        <v>420</v>
       </c>
       <c r="N364" t="n">
-        <v>15452.21</v>
+        <v>571.87</v>
       </c>
       <c r="O364" t="n">
-        <v>741706.08</v>
+        <v>240185.4</v>
       </c>
       <c r="P364" t="n">
-        <v>36500</v>
+        <v>2500</v>
       </c>
       <c r="Q364" t="n">
-        <v>1752000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -16869,7 +16874,7 @@
         </is>
       </c>
       <c r="J365" t="n">
-        <v>420</v>
+        <v>64</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
@@ -16878,69 +16883,18 @@
         <v>0</v>
       </c>
       <c r="M365" t="n">
-        <v>420</v>
+        <v>64</v>
       </c>
       <c r="N365" t="n">
-        <v>571.87</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O365" t="n">
-        <v>240185.4</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P365" t="n">
-        <v>2500</v>
+        <v>15900</v>
       </c>
       <c r="Q365" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J366" t="n">
-        <v>64</v>
-      </c>
-      <c r="K366" t="n">
-        <v>0</v>
-      </c>
-      <c r="L366" t="n">
-        <v>0</v>
-      </c>
-      <c r="M366" t="n">
-        <v>64</v>
-      </c>
-      <c r="N366" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O366" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P366" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q366" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -724,22 +724,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1811.3044829343</v>
+        <v>1811.3047800109</v>
       </c>
       <c r="O8" t="n">
-        <v>14490.4358634744</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>2600</v>
       </c>
       <c r="Q8" t="n">
-        <v>20800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -808,10 +808,10 @@
         <v>476</v>
       </c>
       <c r="N10" t="n">
-        <v>3376.746498645</v>
+        <v>3376.7464976959</v>
       </c>
       <c r="O10" t="n">
-        <v>1607331.33335502</v>
+        <v>1607331.332903248</v>
       </c>
       <c r="P10" t="n">
         <v>4500</v>
@@ -1599,10 +1599,10 @@
         <v>120</v>
       </c>
       <c r="N30" t="n">
-        <v>3910.6281963928</v>
+        <v>3910.6281927711</v>
       </c>
       <c r="O30" t="n">
-        <v>469275.383567136</v>
+        <v>469275.383132532</v>
       </c>
       <c r="P30" t="n">
         <v>9100</v>
@@ -1802,10 +1802,10 @@
         <v>24</v>
       </c>
       <c r="N35" t="n">
-        <v>14708.815744681</v>
+        <v>14708.815698925</v>
       </c>
       <c r="O35" t="n">
-        <v>353011.577872344</v>
+        <v>353011.5767742</v>
       </c>
       <c r="P35" t="n">
         <v>16900</v>
@@ -2029,10 +2029,10 @@
         <v>40</v>
       </c>
       <c r="N40" t="n">
-        <v>200072.2</v>
+        <v>200072.20007812</v>
       </c>
       <c r="O40" t="n">
-        <v>8002888</v>
+        <v>8002888.0031248</v>
       </c>
       <c r="P40" t="n">
         <v>312000</v>
@@ -2326,10 +2326,10 @@
         <v>86</v>
       </c>
       <c r="N47" t="n">
-        <v>61666.873994709</v>
+        <v>61666.874005305</v>
       </c>
       <c r="O47" t="n">
-        <v>5303351.163544974</v>
+        <v>5303351.16445623</v>
       </c>
       <c r="P47" t="n">
         <v>98900</v>
@@ -3454,10 +3454,10 @@
         <v>2592</v>
       </c>
       <c r="N73" t="n">
-        <v>3158.860814779</v>
+        <v>3158.8608154486</v>
       </c>
       <c r="O73" t="n">
-        <v>8187767.231907168</v>
+        <v>8187767.233642772</v>
       </c>
       <c r="P73" t="n">
         <v>5600</v>
@@ -3638,10 +3638,10 @@
         <v>648</v>
       </c>
       <c r="N77" t="n">
-        <v>3795.7100070621</v>
+        <v>3795.7100070671</v>
       </c>
       <c r="O77" t="n">
-        <v>2459620.084576241</v>
+        <v>2459620.084579481</v>
       </c>
       <c r="P77" t="n">
         <v>6200</v>
@@ -3817,10 +3817,10 @@
         <v>396</v>
       </c>
       <c r="N81" t="n">
-        <v>4890.9300464306</v>
+        <v>4890.9300465929</v>
       </c>
       <c r="O81" t="n">
-        <v>1936808.298386517</v>
+        <v>1936808.298450788</v>
       </c>
       <c r="P81" t="n">
         <v>8200</v>
@@ -4045,10 +4045,10 @@
         <v>288</v>
       </c>
       <c r="N86" t="n">
-        <v>3594.2541391941</v>
+        <v>3594.254124847</v>
       </c>
       <c r="O86" t="n">
-        <v>1035145.192087901</v>
+        <v>1035145.187955936</v>
       </c>
       <c r="P86" t="n">
         <v>6500</v>
@@ -4183,10 +4183,10 @@
         <v>48</v>
       </c>
       <c r="N89" t="n">
-        <v>14822.378862559</v>
+        <v>14822.378861885</v>
       </c>
       <c r="O89" t="n">
-        <v>711474.185402832</v>
+        <v>711474.1853704799</v>
       </c>
       <c r="P89" t="n">
         <v>24900</v>
@@ -6091,10 +6091,10 @@
         <v>432</v>
       </c>
       <c r="N131" t="n">
-        <v>2029.8737073653</v>
+        <v>2029.8737091988</v>
       </c>
       <c r="O131" t="n">
-        <v>876905.4415818097</v>
+        <v>876905.4423738816</v>
       </c>
       <c r="P131" t="n">
         <v>3600</v>
@@ -6488,10 +6488,10 @@
         <v>799</v>
       </c>
       <c r="N140" t="n">
-        <v>998.76125988546</v>
+        <v>998.76126091703</v>
       </c>
       <c r="O140" t="n">
-        <v>798010.2466484826</v>
+        <v>798010.2474727069</v>
       </c>
       <c r="P140" t="n">
         <v>1600</v>
@@ -6583,10 +6583,10 @@
         <v>36</v>
       </c>
       <c r="N142" t="n">
-        <v>4285.1952751817</v>
+        <v>4285.1952806653</v>
       </c>
       <c r="O142" t="n">
-        <v>154267.0299065412</v>
+        <v>154267.0301039508</v>
       </c>
       <c r="P142" t="n">
         <v>6900</v>
@@ -7391,10 +7391,10 @@
         <v>714</v>
       </c>
       <c r="N160" t="n">
-        <v>1560.9993877551</v>
+        <v>1560.9994428152</v>
       </c>
       <c r="O160" t="n">
-        <v>1114553.562857141</v>
+        <v>1114553.602170053</v>
       </c>
       <c r="P160" t="n">
         <v>2900</v>
@@ -9677,10 +9677,10 @@
         <v>162</v>
       </c>
       <c r="N210" t="n">
-        <v>4907.8219448698</v>
+        <v>4907.8219751166</v>
       </c>
       <c r="O210" t="n">
-        <v>795067.1550689077</v>
+        <v>795067.1599688892</v>
       </c>
       <c r="P210" t="n">
         <v>8200</v>
@@ -12798,10 +12798,10 @@
         <v>1152</v>
       </c>
       <c r="N278" t="n">
-        <v>1516.0388110875</v>
+        <v>1516.0388102832</v>
       </c>
       <c r="O278" t="n">
-        <v>1746476.7103728</v>
+        <v>1746476.709446247</v>
       </c>
       <c r="P278" t="n">
         <v>2300</v>
@@ -13440,10 +13440,10 @@
         <v>1440</v>
       </c>
       <c r="N292" t="n">
-        <v>1690.8700089526</v>
+        <v>1690.8700089606</v>
       </c>
       <c r="O292" t="n">
-        <v>2434852.812891744</v>
+        <v>2434852.812903264</v>
       </c>
       <c r="P292" t="n">
         <v>3000</v>
@@ -13994,10 +13994,10 @@
         <v>16596</v>
       </c>
       <c r="N304" t="n">
-        <v>703.79533220158</v>
+        <v>703.7953201758</v>
       </c>
       <c r="O304" t="n">
-        <v>11680187.33321742</v>
+        <v>11680187.13363758</v>
       </c>
       <c r="P304" t="n">
         <v>900</v>
@@ -15093,10 +15093,10 @@
         <v>45</v>
       </c>
       <c r="N327" t="n">
-        <v>3067.0905389222</v>
+        <v>3067.0905454545</v>
       </c>
       <c r="O327" t="n">
-        <v>138019.074251499</v>
+        <v>138019.0745454525</v>
       </c>
       <c r="P327" t="n">
         <v>7200</v>
@@ -15904,10 +15904,10 @@
         <v>699</v>
       </c>
       <c r="N344" t="n">
-        <v>7046.939829932</v>
+        <v>7046.9398298958</v>
       </c>
       <c r="O344" t="n">
-        <v>4925810.941122468</v>
+        <v>4925810.941097165</v>
       </c>
       <c r="P344" t="n">
         <v>9900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>220</v>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>52</v>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>4</v>
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>6</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>66</v>
@@ -2273,13 +2273,13 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>77</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>6</v>
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>108</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="K72" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="K73" t="n">
-        <v>1440</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -3897,13 +3897,13 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>2750</v>
+        <v>250</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>250</v>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>48</v>
+        <v>336</v>
       </c>
       <c r="K90" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -1363,10 +1363,10 @@
         <v>40</v>
       </c>
       <c r="N24" t="n">
-        <v>3716.3301923077</v>
+        <v>3716.3301935484</v>
       </c>
       <c r="O24" t="n">
-        <v>148653.207692308</v>
+        <v>148653.207741936</v>
       </c>
       <c r="P24" t="n">
         <v>9500</v>
@@ -1946,10 +1946,10 @@
         <v>65</v>
       </c>
       <c r="N38" t="n">
-        <v>141416.88454545</v>
+        <v>141416.88456026</v>
       </c>
       <c r="O38" t="n">
-        <v>9192097.49545425</v>
+        <v>9192097.4964169</v>
       </c>
       <c r="P38" t="n">
         <v>251900</v>
@@ -3413,10 +3413,10 @@
         <v>720</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2559749444</v>
+        <v>2582.255965161</v>
       </c>
       <c r="O72" t="n">
-        <v>1859224.301959968</v>
+        <v>1859224.29491592</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3505,10 +3505,10 @@
         <v>2592</v>
       </c>
       <c r="N74" t="n">
-        <v>3158.8608230874</v>
+        <v>3158.86082365</v>
       </c>
       <c r="O74" t="n">
-        <v>8187767.253442541</v>
+        <v>8187767.2549008</v>
       </c>
       <c r="P74" t="n">
         <v>5600</v>
@@ -3551,10 +3551,10 @@
         <v>77</v>
       </c>
       <c r="N75" t="n">
-        <v>3841.6247414634</v>
+        <v>3841.6247693817</v>
       </c>
       <c r="O75" t="n">
-        <v>295805.1050926818</v>
+        <v>295805.1072423909</v>
       </c>
       <c r="P75" t="n">
         <v>6900</v>
@@ -3689,10 +3689,10 @@
         <v>648</v>
       </c>
       <c r="N78" t="n">
-        <v>3795.7100070822</v>
+        <v>3795.7100070872</v>
       </c>
       <c r="O78" t="n">
-        <v>2459620.084589265</v>
+        <v>2459620.084592506</v>
       </c>
       <c r="P78" t="n">
         <v>6200</v>
@@ -3868,10 +3868,10 @@
         <v>396</v>
       </c>
       <c r="N82" t="n">
-        <v>4890.9300467563</v>
+        <v>4890.9300468384</v>
       </c>
       <c r="O82" t="n">
-        <v>1936808.298515495</v>
+        <v>1936808.298548006</v>
       </c>
       <c r="P82" t="n">
         <v>8200</v>
@@ -4234,10 +4234,10 @@
         <v>336</v>
       </c>
       <c r="N90" t="n">
-        <v>14822.378861885</v>
+        <v>14822.378858502</v>
       </c>
       <c r="O90" t="n">
-        <v>4980319.29759336</v>
+        <v>4980319.296456671</v>
       </c>
       <c r="P90" t="n">
         <v>24900</v>
@@ -6142,10 +6142,10 @@
         <v>432</v>
       </c>
       <c r="N132" t="n">
-        <v>2029.8737091988</v>
+        <v>2029.8737110341</v>
       </c>
       <c r="O132" t="n">
-        <v>876905.4423738816</v>
+        <v>876905.4431667313</v>
       </c>
       <c r="P132" t="n">
         <v>3600</v>
@@ -7442,10 +7442,10 @@
         <v>714</v>
       </c>
       <c r="N161" t="n">
-        <v>1560.9995548961</v>
+        <v>1560.9996939288</v>
       </c>
       <c r="O161" t="n">
-        <v>1114553.682195815</v>
+        <v>1114553.781465163</v>
       </c>
       <c r="P161" t="n">
         <v>2900</v>
@@ -7925,22 +7925,22 @@
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M172" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N172" t="n">
         <v>10174</v>
       </c>
       <c r="O172" t="n">
-        <v>162784</v>
+        <v>122088</v>
       </c>
       <c r="P172" t="n">
         <v>16900</v>
       </c>
       <c r="Q172" t="n">
-        <v>270400</v>
+        <v>202800</v>
       </c>
     </row>
     <row r="173">
@@ -8299,10 +8299,10 @@
         <v>11</v>
       </c>
       <c r="N180" t="n">
-        <v>23521.62453125</v>
+        <v>23521.624354839</v>
       </c>
       <c r="O180" t="n">
-        <v>258737.86984375</v>
+        <v>258737.867903229</v>
       </c>
       <c r="P180" t="n">
         <v>39000</v>
@@ -8391,10 +8391,10 @@
         <v>680</v>
       </c>
       <c r="N182" t="n">
-        <v>1778.4725740823</v>
+        <v>1778.4725809313</v>
       </c>
       <c r="O182" t="n">
-        <v>1209361.350375964</v>
+        <v>1209361.355033284</v>
       </c>
       <c r="P182" t="n">
         <v>4900</v>
@@ -9958,10 +9958,10 @@
         <v>280</v>
       </c>
       <c r="N216" t="n">
-        <v>3903.7362017804</v>
+        <v>3903.736812933</v>
       </c>
       <c r="O216" t="n">
-        <v>1093046.136498512</v>
+        <v>1093046.30762124</v>
       </c>
       <c r="P216" t="n">
         <v>7500</v>
@@ -10316,10 +10316,10 @@
         <v>144</v>
       </c>
       <c r="N224" t="n">
-        <v>5869.1727464789</v>
+        <v>5869.1727391742</v>
       </c>
       <c r="O224" t="n">
-        <v>845160.8754929616</v>
+        <v>845160.8744410848</v>
       </c>
       <c r="P224" t="n">
         <v>9500</v>
@@ -13491,10 +13491,10 @@
         <v>1440</v>
       </c>
       <c r="N293" t="n">
-        <v>1690.8700089847</v>
+        <v>1690.870009009</v>
       </c>
       <c r="O293" t="n">
-        <v>2434852.812937968</v>
+        <v>2434852.81297296</v>
       </c>
       <c r="P293" t="n">
         <v>3000</v>
@@ -14045,10 +14045,10 @@
         <v>16596</v>
       </c>
       <c r="N305" t="n">
-        <v>703.79529676406</v>
+        <v>703.79526826968</v>
       </c>
       <c r="O305" t="n">
-        <v>11680186.74509634</v>
+        <v>11680186.27220361</v>
       </c>
       <c r="P305" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-19</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -7919,13 +7919,13 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
         <v>12</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -603,10 +603,10 @@
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>66707.977837838</v>
+        <v>66707.978055556</v>
       </c>
       <c r="O5" t="n">
-        <v>333539.88918919</v>
+        <v>333539.89027778</v>
       </c>
       <c r="P5" t="n">
         <v>125900</v>
@@ -800,22 +800,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>6338</v>
       </c>
       <c r="O10" t="n">
-        <v>152112</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>10900</v>
       </c>
       <c r="Q10" t="n">
-        <v>261600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1988,10 +1988,10 @@
         <v>40</v>
       </c>
       <c r="N39" t="n">
-        <v>200072.20015748</v>
+        <v>200072.20040323</v>
       </c>
       <c r="O39" t="n">
-        <v>8002888.0062992</v>
+        <v>8002888.0161292</v>
       </c>
       <c r="P39" t="n">
         <v>312000</v>
@@ -3407,22 +3407,22 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M72" t="n">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.255965161</v>
+        <v>2582.2559238797</v>
       </c>
       <c r="O72" t="n">
-        <v>1859224.29491592</v>
+        <v>1846312.985573985</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
       </c>
       <c r="Q72" t="n">
-        <v>3240000</v>
+        <v>3217500</v>
       </c>
     </row>
     <row r="73">
@@ -3453,22 +3453,22 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M73" t="n">
-        <v>1440</v>
+        <v>1400</v>
       </c>
       <c r="N73" t="n">
-        <v>5216.8962134973</v>
+        <v>5216.8961954233</v>
       </c>
       <c r="O73" t="n">
-        <v>7512330.547436112</v>
+        <v>7303654.67359262</v>
       </c>
       <c r="P73" t="n">
         <v>8500</v>
       </c>
       <c r="Q73" t="n">
-        <v>12240000</v>
+        <v>11900000</v>
       </c>
     </row>
     <row r="74">
@@ -3505,10 +3505,10 @@
         <v>2592</v>
       </c>
       <c r="N74" t="n">
-        <v>3158.86082365</v>
+        <v>3158.860824576</v>
       </c>
       <c r="O74" t="n">
-        <v>8187767.2549008</v>
+        <v>8187767.257300992</v>
       </c>
       <c r="P74" t="n">
         <v>5600</v>
@@ -3551,10 +3551,10 @@
         <v>77</v>
       </c>
       <c r="N75" t="n">
-        <v>3841.6247693817</v>
+        <v>3841.6247787611</v>
       </c>
       <c r="O75" t="n">
-        <v>295805.1072423909</v>
+        <v>295805.1079646047</v>
       </c>
       <c r="P75" t="n">
         <v>6900</v>
@@ -3689,10 +3689,10 @@
         <v>648</v>
       </c>
       <c r="N78" t="n">
-        <v>3795.7100070872</v>
+        <v>3795.7100071023</v>
       </c>
       <c r="O78" t="n">
-        <v>2459620.084592506</v>
+        <v>2459620.08460229</v>
       </c>
       <c r="P78" t="n">
         <v>6200</v>
@@ -3868,10 +3868,10 @@
         <v>396</v>
       </c>
       <c r="N82" t="n">
-        <v>4890.9300468384</v>
+        <v>4890.9300473934</v>
       </c>
       <c r="O82" t="n">
-        <v>1936808.298548006</v>
+        <v>1936808.298767786</v>
       </c>
       <c r="P82" t="n">
         <v>8200</v>
@@ -4096,10 +4096,10 @@
         <v>288</v>
       </c>
       <c r="N87" t="n">
-        <v>3594.2541140405</v>
+        <v>3594.2540923077</v>
       </c>
       <c r="O87" t="n">
-        <v>1035145.184843664</v>
+        <v>1035145.178584618</v>
       </c>
       <c r="P87" t="n">
         <v>6500</v>
@@ -4234,10 +4234,10 @@
         <v>336</v>
       </c>
       <c r="N90" t="n">
-        <v>14822.378858502</v>
+        <v>14822.378857823</v>
       </c>
       <c r="O90" t="n">
-        <v>4980319.296456671</v>
+        <v>4980319.296228528</v>
       </c>
       <c r="P90" t="n">
         <v>24900</v>
@@ -4509,10 +4509,10 @@
         <v>5516</v>
       </c>
       <c r="N96" t="n">
-        <v>19098.75000466</v>
+        <v>19098.750004662</v>
       </c>
       <c r="O96" t="n">
-        <v>105348705.0257046</v>
+        <v>105348705.0257156</v>
       </c>
       <c r="P96" t="n">
         <v>15000</v>
@@ -4645,10 +4645,10 @@
         <v>1406</v>
       </c>
       <c r="N99" t="n">
-        <v>4372.2107879391</v>
+        <v>4372.210788556</v>
       </c>
       <c r="O99" t="n">
-        <v>6147328.367842374</v>
+        <v>6147328.368709736</v>
       </c>
       <c r="P99" t="n">
         <v>7500</v>
@@ -6055,10 +6055,10 @@
         <v>352</v>
       </c>
       <c r="N130" t="n">
-        <v>8794.48</v>
+        <v>8799.395863611</v>
       </c>
       <c r="O130" t="n">
-        <v>3095656.96</v>
+        <v>3097387.343991072</v>
       </c>
       <c r="P130" t="n">
         <v>14500</v>
@@ -6142,10 +6142,10 @@
         <v>432</v>
       </c>
       <c r="N132" t="n">
-        <v>2029.8737110341</v>
+        <v>2029.8737332006</v>
       </c>
       <c r="O132" t="n">
-        <v>876905.4431667313</v>
+        <v>876905.4527426593</v>
       </c>
       <c r="P132" t="n">
         <v>3600</v>
@@ -6634,10 +6634,10 @@
         <v>36</v>
       </c>
       <c r="N143" t="n">
-        <v>4285.1953699789</v>
+        <v>4285.1953813559</v>
       </c>
       <c r="O143" t="n">
-        <v>154267.0333192404</v>
+        <v>154267.0337288124</v>
       </c>
       <c r="P143" t="n">
         <v>6900</v>
@@ -7350,10 +7350,10 @@
         <v>221</v>
       </c>
       <c r="N159" t="n">
-        <v>8332.7796240601</v>
+        <v>8332.779624999999</v>
       </c>
       <c r="O159" t="n">
-        <v>1841544.296917282</v>
+        <v>1841544.297125</v>
       </c>
       <c r="P159" t="n">
         <v>14900</v>
@@ -7442,10 +7442,10 @@
         <v>714</v>
       </c>
       <c r="N161" t="n">
-        <v>1560.9996939288</v>
+        <v>1560.9997428139</v>
       </c>
       <c r="O161" t="n">
-        <v>1114553.781465163</v>
+        <v>1114553.816369124</v>
       </c>
       <c r="P161" t="n">
         <v>2900</v>
@@ -8299,10 +8299,10 @@
         <v>11</v>
       </c>
       <c r="N180" t="n">
-        <v>23521.624354839</v>
+        <v>23521.624262295</v>
       </c>
       <c r="O180" t="n">
-        <v>258737.867903229</v>
+        <v>258737.866885245</v>
       </c>
       <c r="P180" t="n">
         <v>39000</v>
@@ -8391,10 +8391,10 @@
         <v>680</v>
       </c>
       <c r="N182" t="n">
-        <v>1778.4725809313</v>
+        <v>1778.4725908889</v>
       </c>
       <c r="O182" t="n">
-        <v>1209361.355033284</v>
+        <v>1209361.361804452</v>
       </c>
       <c r="P182" t="n">
         <v>4900</v>
@@ -9728,10 +9728,10 @@
         <v>162</v>
       </c>
       <c r="N211" t="n">
-        <v>4907.8219812793</v>
+        <v>4907.8220190779</v>
       </c>
       <c r="O211" t="n">
-        <v>795067.1609672466</v>
+        <v>795067.1670906198</v>
       </c>
       <c r="P211" t="n">
         <v>8200</v>
@@ -9958,10 +9958,10 @@
         <v>280</v>
       </c>
       <c r="N216" t="n">
-        <v>3903.736812933</v>
+        <v>3903.7361538462</v>
       </c>
       <c r="O216" t="n">
-        <v>1093046.30762124</v>
+        <v>1093046.123076936</v>
       </c>
       <c r="P216" t="n">
         <v>7500</v>
@@ -10316,10 +10316,10 @@
         <v>144</v>
       </c>
       <c r="N224" t="n">
-        <v>5869.1727391742</v>
+        <v>5869.1727171717</v>
       </c>
       <c r="O224" t="n">
-        <v>845160.8744410848</v>
+        <v>845160.8712727248</v>
       </c>
       <c r="P224" t="n">
         <v>9500</v>
@@ -10408,10 +10408,10 @@
         <v>792</v>
       </c>
       <c r="N226" t="n">
-        <v>5772</v>
+        <v>5775.9026369168</v>
       </c>
       <c r="O226" t="n">
-        <v>4571424</v>
+        <v>4574514.888438106</v>
       </c>
       <c r="P226" t="n">
         <v>9900</v>
@@ -10684,10 +10684,10 @@
         <v>144</v>
       </c>
       <c r="N232" t="n">
-        <v>3898</v>
+        <v>3904.1097178683</v>
       </c>
       <c r="O232" t="n">
-        <v>561312</v>
+        <v>562191.7993730352</v>
       </c>
       <c r="P232" t="n">
         <v>6900</v>
@@ -12849,10 +12849,10 @@
         <v>1152</v>
       </c>
       <c r="N279" t="n">
-        <v>1516.0388052024</v>
+        <v>1516.0388047383</v>
       </c>
       <c r="O279" t="n">
-        <v>1746476.703593165</v>
+        <v>1746476.703058522</v>
       </c>
       <c r="P279" t="n">
         <v>2300</v>
@@ -13491,10 +13491,10 @@
         <v>1440</v>
       </c>
       <c r="N293" t="n">
-        <v>1690.870009009</v>
+        <v>1690.8700090131</v>
       </c>
       <c r="O293" t="n">
-        <v>2434852.81297296</v>
+        <v>2434852.812978864</v>
       </c>
       <c r="P293" t="n">
         <v>3000</v>
@@ -14045,10 +14045,10 @@
         <v>16596</v>
       </c>
       <c r="N305" t="n">
-        <v>703.79526826968</v>
+        <v>703.7952483310401</v>
       </c>
       <c r="O305" t="n">
-        <v>11680186.27220361</v>
+        <v>11680185.94130194</v>
       </c>
       <c r="P305" t="n">
         <v>900</v>
@@ -14850,10 +14850,10 @@
         <v>48</v>
       </c>
       <c r="N322" t="n">
-        <v>9746.880188679201</v>
+        <v>9746.8801904762</v>
       </c>
       <c r="O322" t="n">
-        <v>467850.2490566017</v>
+        <v>467850.2491428576</v>
       </c>
       <c r="P322" t="n">
         <v>18500</v>
@@ -15046,10 +15046,10 @@
         <v>21</v>
       </c>
       <c r="N326" t="n">
-        <v>2992.5688235294</v>
+        <v>2992.5689285714</v>
       </c>
       <c r="O326" t="n">
-        <v>62843.9452941174</v>
+        <v>62843.94749999941</v>
       </c>
       <c r="P326" t="n">
         <v>6000</v>
@@ -15144,10 +15144,10 @@
         <v>45</v>
       </c>
       <c r="N328" t="n">
-        <v>3067.0905454545</v>
+        <v>3067.0905844156</v>
       </c>
       <c r="O328" t="n">
-        <v>138019.0745454525</v>
+        <v>138019.076298702</v>
       </c>
       <c r="P328" t="n">
         <v>7200</v>
@@ -15955,10 +15955,10 @@
         <v>699</v>
       </c>
       <c r="N345" t="n">
-        <v>7046.9398286204</v>
+        <v>7046.9398281418</v>
       </c>
       <c r="O345" t="n">
-        <v>4925810.94020566</v>
+        <v>4925810.939871118</v>
       </c>
       <c r="P345" t="n">
         <v>9900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-21</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -603,10 +603,10 @@
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>66707.978055556</v>
+        <v>66707.990714286</v>
       </c>
       <c r="O5" t="n">
-        <v>333539.89027778</v>
+        <v>333539.95357143</v>
       </c>
       <c r="P5" t="n">
         <v>125900</v>
@@ -650,10 +650,10 @@
         <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>74676.651794872</v>
+        <v>74676.651315789</v>
       </c>
       <c r="O6" t="n">
-        <v>1493533.03589744</v>
+        <v>1493533.02631578</v>
       </c>
       <c r="P6" t="n">
         <v>144900</v>
@@ -1566,10 +1566,10 @@
         <v>20</v>
       </c>
       <c r="N29" t="n">
-        <v>9392.0746575342</v>
+        <v>9392.0747222222</v>
       </c>
       <c r="O29" t="n">
-        <v>187841.493150684</v>
+        <v>187841.494444444</v>
       </c>
       <c r="P29" t="n">
         <v>18500</v>
@@ -1813,10 +1813,10 @@
         <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>62349.659444444</v>
+        <v>62349.658857143</v>
       </c>
       <c r="O35" t="n">
-        <v>249398.637777776</v>
+        <v>249398.635428572</v>
       </c>
       <c r="P35" t="n">
         <v>109900</v>
@@ -1949,10 +1949,10 @@
         <v>40</v>
       </c>
       <c r="N38" t="n">
-        <v>200072.20040323</v>
+        <v>200072.2004878</v>
       </c>
       <c r="O38" t="n">
-        <v>8002888.0161292</v>
+        <v>8002888.019512</v>
       </c>
       <c r="P38" t="n">
         <v>312000</v>
@@ -2246,10 +2246,10 @@
         <v>77</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.874015957</v>
+        <v>61666.874026667</v>
       </c>
       <c r="O45" t="n">
-        <v>4748349.299228689</v>
+        <v>4748349.300053359</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>715</v>
+        <v>672</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3371,19 +3371,19 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>715</v>
+        <v>672</v>
       </c>
       <c r="N71" t="n">
-        <v>2582.2559238797</v>
+        <v>2582.2558919365</v>
       </c>
       <c r="O71" t="n">
-        <v>1846312.985573985</v>
+        <v>1735275.959381328</v>
       </c>
       <c r="P71" t="n">
         <v>4500</v>
       </c>
       <c r="Q71" t="n">
-        <v>3217500</v>
+        <v>3024000</v>
       </c>
     </row>
     <row r="72">
@@ -3420,10 +3420,10 @@
         <v>1400</v>
       </c>
       <c r="N72" t="n">
-        <v>5216.8961954233</v>
+        <v>5216.8961798703</v>
       </c>
       <c r="O72" t="n">
-        <v>7303654.67359262</v>
+        <v>7303654.651818421</v>
       </c>
       <c r="P72" t="n">
         <v>8500</v>
@@ -3466,10 +3466,10 @@
         <v>2592</v>
       </c>
       <c r="N73" t="n">
-        <v>3158.860824576</v>
+        <v>3158.8608246566</v>
       </c>
       <c r="O73" t="n">
-        <v>8187767.257300992</v>
+        <v>8187767.257509908</v>
       </c>
       <c r="P73" t="n">
         <v>5600</v>
@@ -3650,10 +3650,10 @@
         <v>648</v>
       </c>
       <c r="N77" t="n">
-        <v>3795.7100071023</v>
+        <v>3795.7100071073</v>
       </c>
       <c r="O77" t="n">
-        <v>2459620.08460229</v>
+        <v>2459620.08460553</v>
       </c>
       <c r="P77" t="n">
         <v>6200</v>
@@ -3829,10 +3829,10 @@
         <v>396</v>
       </c>
       <c r="N81" t="n">
-        <v>4890.9300473934</v>
+        <v>4890.9300476474</v>
       </c>
       <c r="O81" t="n">
-        <v>1936808.298767786</v>
+        <v>1936808.29886837</v>
       </c>
       <c r="P81" t="n">
         <v>8200</v>
@@ -4057,10 +4057,10 @@
         <v>288</v>
       </c>
       <c r="N86" t="n">
-        <v>3594.2540923077</v>
+        <v>3594.25408867</v>
       </c>
       <c r="O86" t="n">
-        <v>1035145.178584618</v>
+        <v>1035145.17753696</v>
       </c>
       <c r="P86" t="n">
         <v>6500</v>
@@ -4195,10 +4195,10 @@
         <v>336</v>
       </c>
       <c r="N89" t="n">
-        <v>14822.378857823</v>
+        <v>14822.378855098</v>
       </c>
       <c r="O89" t="n">
-        <v>4980319.296228528</v>
+        <v>4980319.295312928</v>
       </c>
       <c r="P89" t="n">
         <v>24900</v>
@@ -4470,10 +4470,10 @@
         <v>5516</v>
       </c>
       <c r="N95" t="n">
-        <v>19098.750004662</v>
+        <v>19098.750004663</v>
       </c>
       <c r="O95" t="n">
-        <v>105348705.0257156</v>
+        <v>105348705.0257211</v>
       </c>
       <c r="P95" t="n">
         <v>15000</v>
@@ -5929,10 +5929,10 @@
         <v>480</v>
       </c>
       <c r="N127" t="n">
-        <v>4196.8725263158</v>
+        <v>4196.872528417</v>
       </c>
       <c r="O127" t="n">
-        <v>2014498.812631584</v>
+        <v>2014498.81364016</v>
       </c>
       <c r="P127" t="n">
         <v>5900</v>
@@ -6144,10 +6144,10 @@
         <v>528</v>
       </c>
       <c r="N132" t="n">
-        <v>22485.695899772</v>
+        <v>22485.695890411</v>
       </c>
       <c r="O132" t="n">
-        <v>11872447.43507962</v>
+        <v>11872447.43013701</v>
       </c>
       <c r="P132" t="n">
         <v>36500</v>
@@ -6595,10 +6595,10 @@
         <v>36</v>
       </c>
       <c r="N142" t="n">
-        <v>4285.1953813559</v>
+        <v>4285.1953927813</v>
       </c>
       <c r="O142" t="n">
-        <v>154267.0337288124</v>
+        <v>154267.0341401268</v>
       </c>
       <c r="P142" t="n">
         <v>6900</v>
@@ -6769,10 +6769,10 @@
         <v>228</v>
       </c>
       <c r="N146" t="n">
-        <v>4605.2146574074</v>
+        <v>4605.2146617238</v>
       </c>
       <c r="O146" t="n">
-        <v>1049988.941888887</v>
+        <v>1049988.942873026</v>
       </c>
       <c r="P146" t="n">
         <v>7600</v>
@@ -7311,10 +7311,10 @@
         <v>221</v>
       </c>
       <c r="N158" t="n">
-        <v>8332.779624999999</v>
+        <v>8332.7796240601</v>
       </c>
       <c r="O158" t="n">
-        <v>1841544.297125</v>
+        <v>1841544.296917282</v>
       </c>
       <c r="P158" t="n">
         <v>14900</v>
@@ -7403,10 +7403,10 @@
         <v>714</v>
       </c>
       <c r="N160" t="n">
-        <v>1560.9997428139</v>
+        <v>1561</v>
       </c>
       <c r="O160" t="n">
-        <v>1114553.816369124</v>
+        <v>1114554</v>
       </c>
       <c r="P160" t="n">
         <v>2900</v>
@@ -8352,10 +8352,10 @@
         <v>680</v>
       </c>
       <c r="N181" t="n">
-        <v>1778.4725908889</v>
+        <v>1778.4725974412</v>
       </c>
       <c r="O181" t="n">
-        <v>1209361.361804452</v>
+        <v>1209361.366260016</v>
       </c>
       <c r="P181" t="n">
         <v>4900</v>
@@ -9689,10 +9689,10 @@
         <v>162</v>
       </c>
       <c r="N210" t="n">
-        <v>4907.8220190779</v>
+        <v>4907.8220483871</v>
       </c>
       <c r="O210" t="n">
-        <v>795067.1670906198</v>
+        <v>795067.1718387102</v>
       </c>
       <c r="P210" t="n">
         <v>8200</v>
@@ -9919,10 +9919,10 @@
         <v>280</v>
       </c>
       <c r="N215" t="n">
-        <v>3903.7361538462</v>
+        <v>3903.7363106796</v>
       </c>
       <c r="O215" t="n">
-        <v>1093046.123076936</v>
+        <v>1093046.166990288</v>
       </c>
       <c r="P215" t="n">
         <v>7500</v>
@@ -10277,10 +10277,10 @@
         <v>144</v>
       </c>
       <c r="N223" t="n">
-        <v>5869.1727171717</v>
+        <v>5869.1726950355</v>
       </c>
       <c r="O223" t="n">
-        <v>845160.8712727248</v>
+        <v>845160.868085112</v>
       </c>
       <c r="P223" t="n">
         <v>9500</v>
@@ -12810,10 +12810,10 @@
         <v>1152</v>
       </c>
       <c r="N278" t="n">
-        <v>1516.0388047383</v>
+        <v>1516.0388031113</v>
       </c>
       <c r="O278" t="n">
-        <v>1746476.703058522</v>
+        <v>1746476.701184218</v>
       </c>
       <c r="P278" t="n">
         <v>2300</v>
@@ -13452,10 +13452,10 @@
         <v>1440</v>
       </c>
       <c r="N292" t="n">
-        <v>1690.8700090131</v>
+        <v>1690.870009058</v>
       </c>
       <c r="O292" t="n">
-        <v>2434852.812978864</v>
+        <v>2434852.81304352</v>
       </c>
       <c r="P292" t="n">
         <v>3000</v>
@@ -13994,7 +13994,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>16596</v>
+        <v>15732</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14003,19 +14003,19 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>16596</v>
+        <v>15732</v>
       </c>
       <c r="N304" t="n">
-        <v>703.7952483310401</v>
+        <v>703.79522697548</v>
       </c>
       <c r="O304" t="n">
-        <v>11680185.94130194</v>
+        <v>11072106.51077825</v>
       </c>
       <c r="P304" t="n">
         <v>900</v>
       </c>
       <c r="Q304" t="n">
-        <v>14936400</v>
+        <v>14158800</v>
       </c>
     </row>
     <row r="305">
@@ -15442,10 +15442,10 @@
         <v>120</v>
       </c>
       <c r="N334" t="n">
-        <v>4159.0002919708</v>
+        <v>4159.0002941176</v>
       </c>
       <c r="O334" t="n">
-        <v>499080.0350364961</v>
+        <v>499080.035294112</v>
       </c>
       <c r="P334" t="n">
         <v>8900</v>
@@ -16054,10 +16054,10 @@
         <v>10</v>
       </c>
       <c r="N347" t="n">
-        <v>44113.603675676</v>
+        <v>44113.603820225</v>
       </c>
       <c r="O347" t="n">
-        <v>441136.03675676</v>
+        <v>441136.03820225</v>
       </c>
       <c r="P347" t="n">
         <v>71900</v>
@@ -16423,10 +16423,10 @@
         <v>282</v>
       </c>
       <c r="N355" t="n">
-        <v>1008.817540395</v>
+        <v>1008.817266055</v>
       </c>
       <c r="O355" t="n">
-        <v>284486.54639139</v>
+        <v>284486.46902751</v>
       </c>
       <c r="P355" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -767,10 +767,10 @@
         <v>476</v>
       </c>
       <c r="N9" t="n">
-        <v>3376.7464891304</v>
+        <v>3376.7464843537</v>
       </c>
       <c r="O9" t="n">
-        <v>1607331.32882607</v>
+        <v>1607331.326552361</v>
       </c>
       <c r="P9" t="n">
         <v>4500</v>
@@ -806,10 +806,10 @@
         <v>96</v>
       </c>
       <c r="N10" t="n">
-        <v>5758.9597787611</v>
+        <v>5758.9597782705</v>
       </c>
       <c r="O10" t="n">
-        <v>552860.1387610657</v>
+        <v>552860.138713968</v>
       </c>
       <c r="P10" t="n">
         <v>16900</v>
@@ -1519,10 +1519,10 @@
         <v>120</v>
       </c>
       <c r="N28" t="n">
-        <v>3910.6281818182</v>
+        <v>3910.6281707317</v>
       </c>
       <c r="O28" t="n">
-        <v>469275.381818184</v>
+        <v>469275.380487804</v>
       </c>
       <c r="P28" t="n">
         <v>9100</v>
@@ -1813,10 +1813,10 @@
         <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>62349.658857143</v>
+        <v>62349.657575758</v>
       </c>
       <c r="O35" t="n">
-        <v>249398.635428572</v>
+        <v>249398.630303032</v>
       </c>
       <c r="P35" t="n">
         <v>109900</v>
@@ -1949,10 +1949,10 @@
         <v>40</v>
       </c>
       <c r="N38" t="n">
-        <v>200072.2004878</v>
+        <v>200072.20057377</v>
       </c>
       <c r="O38" t="n">
-        <v>8002888.019512</v>
+        <v>8002888.0229508</v>
       </c>
       <c r="P38" t="n">
         <v>312000</v>
@@ -3374,10 +3374,10 @@
         <v>672</v>
       </c>
       <c r="N71" t="n">
-        <v>2582.2558919365</v>
+        <v>2582.2558569052</v>
       </c>
       <c r="O71" t="n">
-        <v>1735275.959381328</v>
+        <v>1735275.935840294</v>
       </c>
       <c r="P71" t="n">
         <v>4500</v>
@@ -3420,10 +3420,10 @@
         <v>1400</v>
       </c>
       <c r="N72" t="n">
-        <v>5216.8961798703</v>
+        <v>5216.8961652752</v>
       </c>
       <c r="O72" t="n">
-        <v>7303654.651818421</v>
+        <v>7303654.63138528</v>
       </c>
       <c r="P72" t="n">
         <v>8500</v>
@@ -3466,10 +3466,10 @@
         <v>2592</v>
       </c>
       <c r="N73" t="n">
-        <v>3158.8608246566</v>
+        <v>3158.8608249792</v>
       </c>
       <c r="O73" t="n">
-        <v>8187767.257509908</v>
+        <v>8187767.258346086</v>
       </c>
       <c r="P73" t="n">
         <v>5600</v>
@@ -3829,10 +3829,10 @@
         <v>396</v>
       </c>
       <c r="N81" t="n">
-        <v>4890.9300476474</v>
+        <v>4890.9300481348</v>
       </c>
       <c r="O81" t="n">
-        <v>1936808.29886837</v>
+        <v>1936808.299061381</v>
       </c>
       <c r="P81" t="n">
         <v>8200</v>
@@ -4057,10 +4057,10 @@
         <v>288</v>
       </c>
       <c r="N86" t="n">
-        <v>3594.25408867</v>
+        <v>3594.2540740741</v>
       </c>
       <c r="O86" t="n">
-        <v>1035145.17753696</v>
+        <v>1035145.173333341</v>
       </c>
       <c r="P86" t="n">
         <v>6500</v>
@@ -4195,10 +4195,10 @@
         <v>336</v>
       </c>
       <c r="N89" t="n">
-        <v>14822.378855098</v>
+        <v>14822.378854415</v>
       </c>
       <c r="O89" t="n">
-        <v>4980319.295312928</v>
+        <v>4980319.29508344</v>
       </c>
       <c r="P89" t="n">
         <v>24900</v>
@@ -4606,10 +4606,10 @@
         <v>1406</v>
       </c>
       <c r="N98" t="n">
-        <v>4372.210788556</v>
+        <v>4372.2107886682</v>
       </c>
       <c r="O98" t="n">
-        <v>6147328.368709736</v>
+        <v>6147328.368867489</v>
       </c>
       <c r="P98" t="n">
         <v>7500</v>
@@ -6103,10 +6103,10 @@
         <v>432</v>
       </c>
       <c r="N131" t="n">
-        <v>2029.8737332006</v>
+        <v>2029.8737350598</v>
       </c>
       <c r="O131" t="n">
-        <v>876905.4527426593</v>
+        <v>876905.4535458336</v>
       </c>
       <c r="P131" t="n">
         <v>3600</v>
@@ -6144,10 +6144,10 @@
         <v>528</v>
       </c>
       <c r="N132" t="n">
-        <v>22485.695890411</v>
+        <v>22485.695885714</v>
       </c>
       <c r="O132" t="n">
-        <v>11872447.43013701</v>
+        <v>11872447.42765699</v>
       </c>
       <c r="P132" t="n">
         <v>36500</v>
@@ -6316,10 +6316,10 @@
         <v>310</v>
       </c>
       <c r="N136" t="n">
-        <v>2680.7396999388</v>
+        <v>2680.7396995708</v>
       </c>
       <c r="O136" t="n">
-        <v>831029.3069810281</v>
+        <v>831029.306866948</v>
       </c>
       <c r="P136" t="n">
         <v>4900</v>
@@ -6595,10 +6595,10 @@
         <v>36</v>
       </c>
       <c r="N142" t="n">
-        <v>4285.1953927813</v>
+        <v>4285.1954215582</v>
       </c>
       <c r="O142" t="n">
-        <v>154267.0341401268</v>
+        <v>154267.0351760952</v>
       </c>
       <c r="P142" t="n">
         <v>6900</v>
@@ -6769,10 +6769,10 @@
         <v>228</v>
       </c>
       <c r="N146" t="n">
-        <v>4605.2146617238</v>
+        <v>4605.2146660482</v>
       </c>
       <c r="O146" t="n">
-        <v>1049988.942873026</v>
+        <v>1049988.94385899</v>
       </c>
       <c r="P146" t="n">
         <v>7600</v>
@@ -7403,10 +7403,10 @@
         <v>714</v>
       </c>
       <c r="N160" t="n">
-        <v>1561</v>
+        <v>1561.0000887728</v>
       </c>
       <c r="O160" t="n">
-        <v>1114554</v>
+        <v>1114554.063383779</v>
       </c>
       <c r="P160" t="n">
         <v>2900</v>
@@ -8352,10 +8352,10 @@
         <v>680</v>
       </c>
       <c r="N181" t="n">
-        <v>1778.4725974412</v>
+        <v>1778.4725978277</v>
       </c>
       <c r="O181" t="n">
-        <v>1209361.366260016</v>
+        <v>1209361.366522836</v>
       </c>
       <c r="P181" t="n">
         <v>4900</v>
@@ -9689,10 +9689,10 @@
         <v>162</v>
       </c>
       <c r="N210" t="n">
-        <v>4907.8220483871</v>
+        <v>4907.8220583468</v>
       </c>
       <c r="O210" t="n">
-        <v>795067.1718387102</v>
+        <v>795067.1734521816</v>
       </c>
       <c r="P210" t="n">
         <v>8200</v>
@@ -9919,10 +9919,10 @@
         <v>280</v>
       </c>
       <c r="N215" t="n">
-        <v>3903.7363106796</v>
+        <v>3903.7364457831</v>
       </c>
       <c r="O215" t="n">
-        <v>1093046.166990288</v>
+        <v>1093046.204819268</v>
       </c>
       <c r="P215" t="n">
         <v>7500</v>
@@ -11289,10 +11289,10 @@
         <v>192</v>
       </c>
       <c r="N245" t="n">
-        <v>17075.98952381</v>
+        <v>17075.989523481</v>
       </c>
       <c r="O245" t="n">
-        <v>3278589.98857152</v>
+        <v>3278589.988508352</v>
       </c>
       <c r="P245" t="n">
         <v>27500</v>
@@ -12810,10 +12810,10 @@
         <v>1152</v>
       </c>
       <c r="N278" t="n">
-        <v>1516.0388031113</v>
+        <v>1516.0388018299</v>
       </c>
       <c r="O278" t="n">
-        <v>1746476.701184218</v>
+        <v>1746476.699708045</v>
       </c>
       <c r="P278" t="n">
         <v>2300</v>
@@ -13452,10 +13452,10 @@
         <v>1440</v>
       </c>
       <c r="N292" t="n">
-        <v>1690.870009058</v>
+        <v>1690.8700090909</v>
       </c>
       <c r="O292" t="n">
-        <v>2434852.81304352</v>
+        <v>2434852.813090896</v>
       </c>
       <c r="P292" t="n">
         <v>3000</v>
@@ -14006,10 +14006,10 @@
         <v>15732</v>
       </c>
       <c r="N304" t="n">
-        <v>703.79522697548</v>
+        <v>703.79521051815</v>
       </c>
       <c r="O304" t="n">
-        <v>11072106.51077825</v>
+        <v>11072106.25187154</v>
       </c>
       <c r="P304" t="n">
         <v>900</v>
@@ -15442,10 +15442,10 @@
         <v>120</v>
       </c>
       <c r="N334" t="n">
-        <v>4159.0002941176</v>
+        <v>4159.000295203</v>
       </c>
       <c r="O334" t="n">
-        <v>499080.035294112</v>
+        <v>499080.03542436</v>
       </c>
       <c r="P334" t="n">
         <v>8900</v>
@@ -16417,22 +16417,22 @@
         <v>0</v>
       </c>
       <c r="L355" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M355" t="n">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="N355" t="n">
-        <v>1008.817266055</v>
+        <v>1008.8171243043</v>
       </c>
       <c r="O355" t="n">
-        <v>284486.46902751</v>
+        <v>278433.5263079868</v>
       </c>
       <c r="P355" t="n">
         <v>1500</v>
       </c>
       <c r="Q355" t="n">
-        <v>423000</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="356">

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-22</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -16411,13 +16411,13 @@
         </is>
       </c>
       <c r="J355" t="n">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="K355" t="n">
         <v>0</v>
       </c>
       <c r="L355" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M355" t="n">
         <v>276</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -767,10 +767,10 @@
         <v>476</v>
       </c>
       <c r="N9" t="n">
-        <v>3376.7464843537</v>
+        <v>3376.7464728365</v>
       </c>
       <c r="O9" t="n">
-        <v>1607331.326552361</v>
+        <v>1607331.321070174</v>
       </c>
       <c r="P9" t="n">
         <v>4500</v>
@@ -806,10 +806,10 @@
         <v>96</v>
       </c>
       <c r="N10" t="n">
-        <v>5758.9597782705</v>
+        <v>5758.9597777778</v>
       </c>
       <c r="O10" t="n">
-        <v>552860.138713968</v>
+        <v>552860.1386666688</v>
       </c>
       <c r="P10" t="n">
         <v>16900</v>
@@ -1168,10 +1168,10 @@
         <v>36</v>
       </c>
       <c r="N19" t="n">
-        <v>12357.960416667</v>
+        <v>12357.96041958</v>
       </c>
       <c r="O19" t="n">
-        <v>444886.575000012</v>
+        <v>444886.57510488</v>
       </c>
       <c r="P19" t="n">
         <v>15900</v>
@@ -1566,10 +1566,10 @@
         <v>20</v>
       </c>
       <c r="N29" t="n">
-        <v>9392.0747222222</v>
+        <v>9392.075000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>187841.494444444</v>
+        <v>187841.5</v>
       </c>
       <c r="P29" t="n">
         <v>18500</v>
@@ -2037,22 +2037,22 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>263530.17666667</v>
+        <v>263530.17529412</v>
       </c>
       <c r="O40" t="n">
-        <v>263530.17666667</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>402900</v>
       </c>
       <c r="Q40" t="n">
-        <v>402900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2407,10 +2407,10 @@
         <v>76</v>
       </c>
       <c r="N49" t="n">
-        <v>16010.3</v>
+        <v>16128.022794118</v>
       </c>
       <c r="O49" t="n">
-        <v>1216782.8</v>
+        <v>1225729.732352968</v>
       </c>
       <c r="P49" t="n">
         <v>30500</v>
@@ -2446,10 +2446,10 @@
         <v>208</v>
       </c>
       <c r="N50" t="n">
-        <v>8046.39</v>
+        <v>8106.4376865672</v>
       </c>
       <c r="O50" t="n">
-        <v>1673649.12</v>
+        <v>1686139.038805978</v>
       </c>
       <c r="P50" t="n">
         <v>20900</v>
@@ -3151,10 +3151,10 @@
         <v>60</v>
       </c>
       <c r="N66" t="n">
-        <v>7569</v>
+        <v>7769.0616740088</v>
       </c>
       <c r="O66" t="n">
-        <v>454140</v>
+        <v>466143.700440528</v>
       </c>
       <c r="P66" t="n">
         <v>12900</v>
@@ -3374,10 +3374,10 @@
         <v>672</v>
       </c>
       <c r="N71" t="n">
-        <v>2582.2558569052</v>
+        <v>2582.2558256496</v>
       </c>
       <c r="O71" t="n">
-        <v>1735275.935840294</v>
+        <v>1735275.914836531</v>
       </c>
       <c r="P71" t="n">
         <v>4500</v>
@@ -3420,10 +3420,10 @@
         <v>1400</v>
       </c>
       <c r="N72" t="n">
-        <v>5216.8961652752</v>
+        <v>5216.8961603854</v>
       </c>
       <c r="O72" t="n">
-        <v>7303654.63138528</v>
+        <v>7303654.624539561</v>
       </c>
       <c r="P72" t="n">
         <v>8500</v>
@@ -3466,10 +3466,10 @@
         <v>2592</v>
       </c>
       <c r="N73" t="n">
-        <v>3158.8608249792</v>
+        <v>3158.860825504</v>
       </c>
       <c r="O73" t="n">
-        <v>8187767.258346086</v>
+        <v>8187767.259706368</v>
       </c>
       <c r="P73" t="n">
         <v>5600</v>
@@ -3512,10 +3512,10 @@
         <v>77</v>
       </c>
       <c r="N74" t="n">
-        <v>3841.6247787611</v>
+        <v>3841.6247928994</v>
       </c>
       <c r="O74" t="n">
-        <v>295805.1079646047</v>
+        <v>295805.1090532538</v>
       </c>
       <c r="P74" t="n">
         <v>6900</v>
@@ -3650,10 +3650,10 @@
         <v>648</v>
       </c>
       <c r="N77" t="n">
-        <v>3795.7100071073</v>
+        <v>3795.7100075415</v>
       </c>
       <c r="O77" t="n">
-        <v>2459620.08460553</v>
+        <v>2459620.084886892</v>
       </c>
       <c r="P77" t="n">
         <v>6200</v>
@@ -3829,10 +3829,10 @@
         <v>396</v>
       </c>
       <c r="N81" t="n">
-        <v>4890.9300481348</v>
+        <v>4914.5862998791</v>
       </c>
       <c r="O81" t="n">
-        <v>1936808.299061381</v>
+        <v>1946176.174752124</v>
       </c>
       <c r="P81" t="n">
         <v>8200</v>
@@ -3962,10 +3962,10 @@
         <v>296</v>
       </c>
       <c r="N84" t="n">
-        <v>7041</v>
+        <v>7095.9541463415</v>
       </c>
       <c r="O84" t="n">
-        <v>2084136</v>
+        <v>2100402.427317084</v>
       </c>
       <c r="P84" t="n">
         <v>11500</v>
@@ -4057,10 +4057,10 @@
         <v>288</v>
       </c>
       <c r="N86" t="n">
-        <v>3594.2540740741</v>
+        <v>3594.2540520446</v>
       </c>
       <c r="O86" t="n">
-        <v>1035145.173333341</v>
+        <v>1035145.166988845</v>
       </c>
       <c r="P86" t="n">
         <v>6500</v>
@@ -4103,10 +4103,10 @@
         <v>424</v>
       </c>
       <c r="N87" t="n">
-        <v>4891</v>
+        <v>4913.5912240185</v>
       </c>
       <c r="O87" t="n">
-        <v>2073784</v>
+        <v>2083362.678983844</v>
       </c>
       <c r="P87" t="n">
         <v>8200</v>
@@ -4470,10 +4470,10 @@
         <v>5516</v>
       </c>
       <c r="N95" t="n">
-        <v>19098.750004663</v>
+        <v>19098.750004664</v>
       </c>
       <c r="O95" t="n">
-        <v>105348705.0257211</v>
+        <v>105348705.0257266</v>
       </c>
       <c r="P95" t="n">
         <v>15000</v>
@@ -4606,10 +4606,10 @@
         <v>1406</v>
       </c>
       <c r="N98" t="n">
-        <v>4372.2107886682</v>
+        <v>4374.7024319704</v>
       </c>
       <c r="O98" t="n">
-        <v>6147328.368867489</v>
+        <v>6150831.619350382</v>
       </c>
       <c r="P98" t="n">
         <v>7500</v>
@@ -6103,10 +6103,10 @@
         <v>432</v>
       </c>
       <c r="N131" t="n">
-        <v>2029.8737350598</v>
+        <v>2029.8737443834</v>
       </c>
       <c r="O131" t="n">
-        <v>876905.4535458336</v>
+        <v>876905.4575736288</v>
       </c>
       <c r="P131" t="n">
         <v>3600</v>
@@ -6144,10 +6144,10 @@
         <v>528</v>
       </c>
       <c r="N132" t="n">
-        <v>22485.695885714</v>
+        <v>22485.695881007</v>
       </c>
       <c r="O132" t="n">
-        <v>11872447.42765699</v>
+        <v>11872447.4251717</v>
       </c>
       <c r="P132" t="n">
         <v>36500</v>
@@ -6595,10 +6595,10 @@
         <v>36</v>
       </c>
       <c r="N142" t="n">
-        <v>4285.1954215582</v>
+        <v>4285.1954682454</v>
       </c>
       <c r="O142" t="n">
-        <v>154267.0351760952</v>
+        <v>154267.0368568344</v>
       </c>
       <c r="P142" t="n">
         <v>6900</v>
@@ -6769,10 +6769,10 @@
         <v>228</v>
       </c>
       <c r="N146" t="n">
-        <v>4605.2146660482</v>
+        <v>4657.0557317073</v>
       </c>
       <c r="O146" t="n">
-        <v>1049988.94385899</v>
+        <v>1061808.706829264</v>
       </c>
       <c r="P146" t="n">
         <v>7600</v>
@@ -6810,10 +6810,10 @@
         <v>1278</v>
       </c>
       <c r="N147" t="n">
-        <v>3591.13</v>
+        <v>3598.612819934</v>
       </c>
       <c r="O147" t="n">
-        <v>4589464.140000001</v>
+        <v>4599027.183875652</v>
       </c>
       <c r="P147" t="n">
         <v>6300</v>
@@ -7034,22 +7034,22 @@
         <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M152" t="n">
-        <v>1090</v>
+        <v>970</v>
       </c>
       <c r="N152" t="n">
         <v>4793.53</v>
       </c>
       <c r="O152" t="n">
-        <v>5224947.7</v>
+        <v>4649724.1</v>
       </c>
       <c r="P152" t="n">
         <v>7900</v>
       </c>
       <c r="Q152" t="n">
-        <v>8611000</v>
+        <v>7663000</v>
       </c>
     </row>
     <row r="153">
@@ -7403,10 +7403,10 @@
         <v>714</v>
       </c>
       <c r="N160" t="n">
-        <v>1561.0000887728</v>
+        <v>1561.000152391</v>
       </c>
       <c r="O160" t="n">
-        <v>1114554.063383779</v>
+        <v>1114554.108807174</v>
       </c>
       <c r="P160" t="n">
         <v>2900</v>
@@ -8352,10 +8352,10 @@
         <v>680</v>
       </c>
       <c r="N181" t="n">
-        <v>1778.4725978277</v>
+        <v>1778.4726172988</v>
       </c>
       <c r="O181" t="n">
-        <v>1209361.366522836</v>
+        <v>1209361.379763184</v>
       </c>
       <c r="P181" t="n">
         <v>4900</v>
@@ -9919,10 +9919,10 @@
         <v>280</v>
       </c>
       <c r="N215" t="n">
-        <v>3903.7364457831</v>
+        <v>3903.7364581763</v>
       </c>
       <c r="O215" t="n">
-        <v>1093046.204819268</v>
+        <v>1093046.208289364</v>
       </c>
       <c r="P215" t="n">
         <v>7500</v>
@@ -10277,10 +10277,10 @@
         <v>144</v>
       </c>
       <c r="N223" t="n">
-        <v>5869.1726950355</v>
+        <v>5869.172680203</v>
       </c>
       <c r="O223" t="n">
-        <v>845160.868085112</v>
+        <v>845160.865949232</v>
       </c>
       <c r="P223" t="n">
         <v>9500</v>
@@ -10415,10 +10415,10 @@
         <v>552</v>
       </c>
       <c r="N226" t="n">
-        <v>6645</v>
+        <v>6666.7987971569</v>
       </c>
       <c r="O226" t="n">
-        <v>3668040</v>
+        <v>3680072.936030609</v>
       </c>
       <c r="P226" t="n">
         <v>10900</v>
@@ -10599,10 +10599,10 @@
         <v>153</v>
       </c>
       <c r="N230" t="n">
-        <v>7562</v>
+        <v>7693.5130434783</v>
       </c>
       <c r="O230" t="n">
-        <v>1156986</v>
+        <v>1177107.49565218</v>
       </c>
       <c r="P230" t="n">
         <v>12900</v>
@@ -13452,10 +13452,10 @@
         <v>1440</v>
       </c>
       <c r="N292" t="n">
-        <v>1690.8700090909</v>
+        <v>1690.870009095</v>
       </c>
       <c r="O292" t="n">
-        <v>2434852.813090896</v>
+        <v>2434852.8130968</v>
       </c>
       <c r="P292" t="n">
         <v>3000</v>
@@ -14006,10 +14006,10 @@
         <v>15732</v>
       </c>
       <c r="N304" t="n">
-        <v>703.79521051815</v>
+        <v>703.79520622865</v>
       </c>
       <c r="O304" t="n">
-        <v>11072106.25187154</v>
+        <v>11072106.18438912</v>
       </c>
       <c r="P304" t="n">
         <v>900</v>
@@ -16054,10 +16054,10 @@
         <v>10</v>
       </c>
       <c r="N347" t="n">
-        <v>44113.603820225</v>
+        <v>44113.603841808</v>
       </c>
       <c r="O347" t="n">
-        <v>441136.03820225</v>
+        <v>441136.03841808</v>
       </c>
       <c r="P347" t="n">
         <v>71900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -1324,10 +1324,10 @@
         <v>40</v>
       </c>
       <c r="N23" t="n">
-        <v>3716.3301935484</v>
+        <v>3716.3301938611</v>
       </c>
       <c r="O23" t="n">
-        <v>148653.207741936</v>
+        <v>148653.207754444</v>
       </c>
       <c r="P23" t="n">
         <v>9500</v>
@@ -1519,10 +1519,10 @@
         <v>120</v>
       </c>
       <c r="N28" t="n">
-        <v>3910.6281707317</v>
+        <v>3910.6281632653</v>
       </c>
       <c r="O28" t="n">
-        <v>469275.380487804</v>
+        <v>469275.379591836</v>
       </c>
       <c r="P28" t="n">
         <v>9100</v>
@@ -2199,10 +2199,10 @@
         <v>77</v>
       </c>
       <c r="N44" t="n">
-        <v>61666.874026667</v>
+        <v>61666.874048257</v>
       </c>
       <c r="O44" t="n">
-        <v>4748349.300053359</v>
+        <v>4748349.301715789</v>
       </c>
       <c r="P44" t="n">
         <v>98900</v>
@@ -3327,10 +3327,10 @@
         <v>672</v>
       </c>
       <c r="N70" t="n">
-        <v>2582.2558256496</v>
+        <v>2582.2557662062</v>
       </c>
       <c r="O70" t="n">
-        <v>1735275.914836531</v>
+        <v>1735275.874890566</v>
       </c>
       <c r="P70" t="n">
         <v>4500</v>
@@ -3373,10 +3373,10 @@
         <v>1400</v>
       </c>
       <c r="N71" t="n">
-        <v>5216.8961603854</v>
+        <v>5216.8961467368</v>
       </c>
       <c r="O71" t="n">
-        <v>7303654.624539561</v>
+        <v>7303654.605431519</v>
       </c>
       <c r="P71" t="n">
         <v>8500</v>
@@ -3782,10 +3782,10 @@
         <v>396</v>
       </c>
       <c r="N80" t="n">
-        <v>4890.9300483676</v>
+        <v>4890.9300485437</v>
       </c>
       <c r="O80" t="n">
-        <v>1936808.299153569</v>
+        <v>1936808.299223305</v>
       </c>
       <c r="P80" t="n">
         <v>8200</v>
@@ -4010,10 +4010,10 @@
         <v>288</v>
       </c>
       <c r="N85" t="n">
-        <v>3594.2540520446</v>
+        <v>3594.2540372671</v>
       </c>
       <c r="O85" t="n">
-        <v>1035145.166988845</v>
+        <v>1035145.162732925</v>
       </c>
       <c r="P85" t="n">
         <v>6500</v>
@@ -4148,10 +4148,10 @@
         <v>336</v>
       </c>
       <c r="N88" t="n">
-        <v>14822.378854415</v>
+        <v>14822.378852361</v>
       </c>
       <c r="O88" t="n">
-        <v>4980319.29508344</v>
+        <v>4980319.294393296</v>
       </c>
       <c r="P88" t="n">
         <v>24900</v>
@@ -4559,10 +4559,10 @@
         <v>1406</v>
       </c>
       <c r="N97" t="n">
-        <v>4372.2107892862</v>
+        <v>4372.2107896237</v>
       </c>
       <c r="O97" t="n">
-        <v>6147328.369736398</v>
+        <v>6147328.370210922</v>
       </c>
       <c r="P97" t="n">
         <v>7500</v>
@@ -6097,10 +6097,10 @@
         <v>528</v>
       </c>
       <c r="N131" t="n">
-        <v>22485.695881007</v>
+        <v>22485.695577396</v>
       </c>
       <c r="O131" t="n">
-        <v>11872447.4251717</v>
+        <v>11872447.26486509</v>
       </c>
       <c r="P131" t="n">
         <v>36500</v>
@@ -6548,10 +6548,10 @@
         <v>36</v>
       </c>
       <c r="N141" t="n">
-        <v>4285.1954682454</v>
+        <v>4285.1954741379</v>
       </c>
       <c r="O141" t="n">
-        <v>154267.0368568344</v>
+        <v>154267.0370689644</v>
       </c>
       <c r="P141" t="n">
         <v>6900</v>
@@ -6676,10 +6676,10 @@
         <v>55</v>
       </c>
       <c r="N144" t="n">
-        <v>30244.600034702</v>
+        <v>30244.600034722</v>
       </c>
       <c r="O144" t="n">
-        <v>1663453.00190861</v>
+        <v>1663453.00190971</v>
       </c>
       <c r="P144" t="n">
         <v>48900</v>
@@ -6722,10 +6722,10 @@
         <v>228</v>
       </c>
       <c r="N145" t="n">
-        <v>4605.2147185741</v>
+        <v>4605.2147274436</v>
       </c>
       <c r="O145" t="n">
-        <v>1049988.955834895</v>
+        <v>1049988.957857141</v>
       </c>
       <c r="P145" t="n">
         <v>7600</v>
@@ -7264,10 +7264,10 @@
         <v>221</v>
       </c>
       <c r="N157" t="n">
-        <v>8332.7796240601</v>
+        <v>8332.779622166199</v>
       </c>
       <c r="O157" t="n">
-        <v>1841544.296917282</v>
+        <v>1841544.29649873</v>
       </c>
       <c r="P157" t="n">
         <v>14900</v>
@@ -7356,10 +7356,10 @@
         <v>714</v>
       </c>
       <c r="N159" t="n">
-        <v>1561.000152391</v>
+        <v>1561.0001684211</v>
       </c>
       <c r="O159" t="n">
-        <v>1114554.108807174</v>
+        <v>1114554.120252665</v>
       </c>
       <c r="P159" t="n">
         <v>2900</v>
@@ -9642,10 +9642,10 @@
         <v>162</v>
       </c>
       <c r="N209" t="n">
-        <v>4907.8220583468</v>
+        <v>4907.8220751634</v>
       </c>
       <c r="O209" t="n">
-        <v>795067.1734521816</v>
+        <v>795067.1761764708</v>
       </c>
       <c r="P209" t="n">
         <v>8200</v>
@@ -10230,10 +10230,10 @@
         <v>144</v>
       </c>
       <c r="N222" t="n">
-        <v>5869.172680203</v>
+        <v>5869.1726653103</v>
       </c>
       <c r="O222" t="n">
-        <v>845160.865949232</v>
+        <v>845160.8638046831</v>
       </c>
       <c r="P222" t="n">
         <v>9500</v>
@@ -12067,22 +12067,22 @@
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M262" t="n">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="N262" t="n">
         <v>3639.35</v>
       </c>
       <c r="O262" t="n">
-        <v>1626789.45</v>
+        <v>1583117.25</v>
       </c>
       <c r="P262" t="n">
         <v>7500</v>
       </c>
       <c r="Q262" t="n">
-        <v>3352500</v>
+        <v>3262500</v>
       </c>
     </row>
     <row r="263">
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>2081</v>
+        <v>2069</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -12116,19 +12116,19 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>2081</v>
+        <v>2069</v>
       </c>
       <c r="N263" t="n">
         <v>1326</v>
       </c>
       <c r="O263" t="n">
-        <v>2759406</v>
+        <v>2743494</v>
       </c>
       <c r="P263" t="n">
         <v>2500</v>
       </c>
       <c r="Q263" t="n">
-        <v>5202500</v>
+        <v>5172500</v>
       </c>
     </row>
     <row r="264">
@@ -12763,10 +12763,10 @@
         <v>1152</v>
       </c>
       <c r="N277" t="n">
-        <v>1516.0388018299</v>
+        <v>1516.038799961</v>
       </c>
       <c r="O277" t="n">
-        <v>1746476.699708045</v>
+        <v>1746476.697555072</v>
       </c>
       <c r="P277" t="n">
         <v>2300</v>
@@ -13630,10 +13630,10 @@
         <v>11416</v>
       </c>
       <c r="N296" t="n">
-        <v>711.3366499515799</v>
+        <v>711.33664971986</v>
       </c>
       <c r="O296" t="n">
-        <v>8120619.195847237</v>
+        <v>8120619.193201922</v>
       </c>
       <c r="P296" t="n">
         <v>900</v>
@@ -13959,10 +13959,10 @@
         <v>15732</v>
       </c>
       <c r="N303" t="n">
-        <v>703.79520622865</v>
+        <v>703.79518726322</v>
       </c>
       <c r="O303" t="n">
-        <v>11072106.18438912</v>
+        <v>11072105.88602498</v>
       </c>
       <c r="P303" t="n">
         <v>900</v>
@@ -16376,10 +16376,10 @@
         <v>276</v>
       </c>
       <c r="N354" t="n">
-        <v>1008.8171243043</v>
+        <v>1008.8169793621</v>
       </c>
       <c r="O354" t="n">
-        <v>278433.5263079868</v>
+        <v>278433.4863039396</v>
       </c>
       <c r="P354" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-25</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -12061,13 +12061,13 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
         <v>435</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -603,10 +603,10 @@
         <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>87122.75208333301</v>
+        <v>74676.64464285701</v>
       </c>
       <c r="O5" t="n">
-        <v>871227.52083333</v>
+        <v>746766.4464285701</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -1199,10 +1199,10 @@
         <v>180</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8371059432</v>
+        <v>3926.8370969414</v>
       </c>
       <c r="O20" t="n">
-        <v>706830.6790697761</v>
+        <v>706830.677449452</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1433,10 +1433,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>15403.520914286</v>
+        <v>15403.520977011</v>
       </c>
       <c r="O26" t="n">
-        <v>261859.855542862</v>
+        <v>261859.856609187</v>
       </c>
       <c r="P26" t="n">
         <v>33500</v>
@@ -1472,10 +1472,10 @@
         <v>120</v>
       </c>
       <c r="N27" t="n">
-        <v>3910.6281481481</v>
+        <v>3910.6281404959</v>
       </c>
       <c r="O27" t="n">
-        <v>469275.377777772</v>
+        <v>469275.376859508</v>
       </c>
       <c r="P27" t="n">
         <v>9100</v>
@@ -2113,10 +2113,10 @@
         <v>77</v>
       </c>
       <c r="N42" t="n">
-        <v>61666.874081081</v>
+        <v>61666.874092141</v>
       </c>
       <c r="O42" t="n">
-        <v>4748349.304243237</v>
+        <v>4748349.305094857</v>
       </c>
       <c r="P42" t="n">
         <v>98900</v>
@@ -3241,10 +3241,10 @@
         <v>1320</v>
       </c>
       <c r="N68" t="n">
-        <v>5216.8961258041</v>
+        <v>5216.8961202577</v>
       </c>
       <c r="O68" t="n">
-        <v>6886302.886061412</v>
+        <v>6886302.878740164</v>
       </c>
       <c r="P68" t="n">
         <v>8500</v>
@@ -3878,10 +3878,10 @@
         <v>288</v>
       </c>
       <c r="N82" t="n">
-        <v>3594.2540224159</v>
+        <v>3594.2540186916</v>
       </c>
       <c r="O82" t="n">
-        <v>1035145.158455779</v>
+        <v>1035145.157383181</v>
       </c>
       <c r="P82" t="n">
         <v>6500</v>
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107901305</v>
+        <v>4372.2107902432</v>
       </c>
       <c r="O94" t="n">
-        <v>5928717.831416958</v>
+        <v>5928717.831569779</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4741,19 +4741,19 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="N101" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O101" t="n">
-        <v>4057567.61</v>
+        <v>3775138.31</v>
       </c>
       <c r="P101" t="n">
         <v>16900</v>
       </c>
       <c r="Q101" t="n">
-        <v>7283900</v>
+        <v>6776900</v>
       </c>
     </row>
     <row r="102">
@@ -5924,10 +5924,10 @@
         <v>432</v>
       </c>
       <c r="N127" t="n">
-        <v>2029.8738600103</v>
+        <v>2029.8738129131</v>
       </c>
       <c r="O127" t="n">
-        <v>876905.5075244496</v>
+        <v>876905.4871784592</v>
       </c>
       <c r="P127" t="n">
         <v>3600</v>
@@ -6137,10 +6137,10 @@
         <v>310</v>
       </c>
       <c r="N132" t="n">
-        <v>2680.739699202</v>
+        <v>2680.7396988322</v>
       </c>
       <c r="O132" t="n">
-        <v>831029.3067526199</v>
+        <v>831029.3066379819</v>
       </c>
       <c r="P132" t="n">
         <v>4900</v>
@@ -6416,10 +6416,10 @@
         <v>36</v>
       </c>
       <c r="N138" t="n">
-        <v>4285.1954978355</v>
+        <v>4285.1955097614</v>
       </c>
       <c r="O138" t="n">
-        <v>154267.037922078</v>
+        <v>154267.0383514104</v>
       </c>
       <c r="P138" t="n">
         <v>6900</v>
@@ -7224,10 +7224,10 @@
         <v>714</v>
       </c>
       <c r="N156" t="n">
-        <v>1561.0003094984</v>
+        <v>1561.0003205128</v>
       </c>
       <c r="O156" t="n">
-        <v>1114554.220981858</v>
+        <v>1114554.228846139</v>
       </c>
       <c r="P156" t="n">
         <v>2900</v>
@@ -7701,13 +7701,13 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>8</v>
@@ -8173,10 +8173,10 @@
         <v>680</v>
       </c>
       <c r="N177" t="n">
-        <v>1778.4726394558</v>
+        <v>1778.4726299141</v>
       </c>
       <c r="O177" t="n">
-        <v>1209361.394829944</v>
+        <v>1209361.388341588</v>
       </c>
       <c r="P177" t="n">
         <v>4900</v>
@@ -9740,10 +9740,10 @@
         <v>280</v>
       </c>
       <c r="N211" t="n">
-        <v>3903.736684492</v>
+        <v>3903.7366972477</v>
       </c>
       <c r="O211" t="n">
-        <v>1093046.27165776</v>
+        <v>1093046.275229356</v>
       </c>
       <c r="P211" t="n">
         <v>7500</v>
@@ -10224,7 +10224,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>552</v>
+        <v>456</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -10233,19 +10233,19 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>552</v>
+        <v>456</v>
       </c>
       <c r="N222" t="n">
         <v>6645</v>
       </c>
       <c r="O222" t="n">
-        <v>3668040</v>
+        <v>3030120</v>
       </c>
       <c r="P222" t="n">
         <v>10900</v>
       </c>
       <c r="Q222" t="n">
-        <v>6016800</v>
+        <v>4970400</v>
       </c>
     </row>
     <row r="223">
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11938,19 +11938,19 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="N259" t="n">
         <v>3639.35</v>
       </c>
       <c r="O259" t="n">
-        <v>1583117.25</v>
+        <v>1401149.75</v>
       </c>
       <c r="P259" t="n">
         <v>7500</v>
       </c>
       <c r="Q259" t="n">
-        <v>3262500</v>
+        <v>2887500</v>
       </c>
     </row>
     <row r="260">
@@ -12631,10 +12631,10 @@
         <v>1152</v>
       </c>
       <c r="N274" t="n">
-        <v>1516.0387953812</v>
+        <v>1516.0387982037</v>
       </c>
       <c r="O274" t="n">
-        <v>1746476.692279143</v>
+        <v>1746476.695530662</v>
       </c>
       <c r="P274" t="n">
         <v>2300</v>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -12764,19 +12764,19 @@
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="N277" t="n">
         <v>5347.73</v>
       </c>
       <c r="O277" t="n">
-        <v>422470.67</v>
+        <v>288777.42</v>
       </c>
       <c r="P277" t="n">
         <v>9500</v>
       </c>
       <c r="Q277" t="n">
-        <v>750500</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="278">
@@ -13827,10 +13827,10 @@
         <v>15732</v>
       </c>
       <c r="N300" t="n">
-        <v>703.79517569581</v>
+        <v>703.795175</v>
       </c>
       <c r="O300" t="n">
-        <v>11072105.70404648</v>
+        <v>11072105.6931</v>
       </c>
       <c r="P300" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q359"/>
+  <dimension ref="A1:Q358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N27" t="n">
-        <v>3910.6281404959</v>
+        <v>3910.628136646</v>
       </c>
       <c r="O27" t="n">
-        <v>469275.376859508</v>
+        <v>465364.748260874</v>
       </c>
       <c r="P27" t="n">
         <v>9100</v>
       </c>
       <c r="Q27" t="n">
-        <v>1092000</v>
+        <v>1082900</v>
       </c>
     </row>
     <row r="28">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>672</v>
+        <v>624</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3192,19 +3192,19 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>672</v>
+        <v>624</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2557142857</v>
+        <v>2582.2556563454</v>
       </c>
       <c r="O67" t="n">
-        <v>1735275.83999999</v>
+        <v>1611327.52955953</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
       </c>
       <c r="Q67" t="n">
-        <v>3024000</v>
+        <v>2808000</v>
       </c>
     </row>
     <row r="68">
@@ -3229,22 +3229,22 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
         <v>1312</v>
       </c>
       <c r="N68" t="n">
-        <v>5216.8961124659</v>
+        <v>5216.8961063218</v>
       </c>
       <c r="O68" t="n">
-        <v>6844567.699555261</v>
+        <v>6844567.691494202</v>
       </c>
       <c r="P68" t="n">
         <v>8500</v>
@@ -3650,10 +3650,10 @@
         <v>346</v>
       </c>
       <c r="N77" t="n">
-        <v>4890.93004884</v>
+        <v>4890.9300488998</v>
       </c>
       <c r="O77" t="n">
-        <v>1692261.79689864</v>
+        <v>1692261.796919331</v>
       </c>
       <c r="P77" t="n">
         <v>8200</v>
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107902432</v>
+        <v>4372.2107903559</v>
       </c>
       <c r="O94" t="n">
-        <v>5928717.831569779</v>
+        <v>5928717.8317226</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -6137,10 +6137,10 @@
         <v>310</v>
       </c>
       <c r="N132" t="n">
-        <v>2680.7396988322</v>
+        <v>2680.739695084</v>
       </c>
       <c r="O132" t="n">
-        <v>831029.3066379819</v>
+        <v>831029.3054760399</v>
       </c>
       <c r="P132" t="n">
         <v>4900</v>
@@ -7178,10 +7178,10 @@
         <v>714</v>
       </c>
       <c r="N155" t="n">
-        <v>1561.0009152542</v>
+        <v>1561.0009337861</v>
       </c>
       <c r="O155" t="n">
-        <v>1114554.653491499</v>
+        <v>1114554.666723275</v>
       </c>
       <c r="P155" t="n">
         <v>2900</v>
@@ -13060,17 +13060,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>C5075</t>
+          <t>C510-IO</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>CUBO DIDACTICO C5075</t>
+          <t>GLOBO BURBUJA METALIZADO</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -13079,7 +13079,7 @@
         </is>
       </c>
       <c r="J284" t="n">
-        <v>88</v>
+        <v>3896</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -13088,44 +13088,42 @@
         <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>88</v>
+        <v>3896</v>
       </c>
       <c r="N284" t="n">
-        <v>1245.62</v>
+        <v>960</v>
       </c>
       <c r="O284" t="n">
-        <v>109614.56</v>
+        <v>3740160</v>
       </c>
       <c r="P284" t="n">
-        <v>4000</v>
+        <v>1200</v>
       </c>
       <c r="Q284" t="n">
-        <v>352000</v>
+        <v>4675200</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>C510-IO</t>
-        </is>
+          <t>C515</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>6953626330010</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA METALIZADO</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>GLOBO FIGURAS BURBUJA</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J285" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -13134,42 +13132,44 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="N285" t="n">
-        <v>960</v>
+        <v>583.7204926325001</v>
       </c>
       <c r="O285" t="n">
-        <v>3740160</v>
+        <v>2218137.8720035</v>
       </c>
       <c r="P285" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="Q285" t="n">
-        <v>4675200</v>
+        <v>2280000</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>C515</t>
-        </is>
-      </c>
-      <c r="B286" t="n">
-        <v>6953626330010</v>
+          <t>C5214</t>
+        </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS BURBUJA</t>
+          <t>CUBO C5214</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J286" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -13178,44 +13178,42 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="N286" t="n">
-        <v>583.7204926325001</v>
+        <v>1690.870009095</v>
       </c>
       <c r="O286" t="n">
-        <v>2218137.8720035</v>
+        <v>2434852.8130968</v>
       </c>
       <c r="P286" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="Q286" t="n">
-        <v>2280000</v>
+        <v>4320000</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>C5214</t>
-        </is>
+          <t>C523</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>6957430180212</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>CUBO C5214</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -13224,33 +13222,33 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="N287" t="n">
-        <v>1690.870009095</v>
+        <v>481.48791273054</v>
       </c>
       <c r="O287" t="n">
-        <v>2434852.8130968</v>
+        <v>1230683.10493926</v>
       </c>
       <c r="P287" t="n">
-        <v>3000</v>
+        <v>650</v>
       </c>
       <c r="Q287" t="n">
-        <v>4320000</v>
+        <v>1661400</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>C523</t>
+          <t>C524</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>6957430180212</v>
+        <v>6957430180229</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
+          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -13259,7 +13257,7 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -13268,42 +13266,47 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="N288" t="n">
-        <v>481.48791273054</v>
+        <v>872.15418687873</v>
       </c>
       <c r="O288" t="n">
-        <v>1230683.10493926</v>
+        <v>535502.6707435403</v>
       </c>
       <c r="P288" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="Q288" t="n">
-        <v>1661400</v>
+        <v>736800</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>C524</t>
+          <t>C5246/C5247</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>6957430180229</v>
+        <v>6900077483239</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
+          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J289" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13312,47 +13315,42 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="N289" t="n">
-        <v>872.15418687873</v>
+        <v>8702.219999999999</v>
       </c>
       <c r="O289" t="n">
-        <v>535502.6707435403</v>
+        <v>1131288.6</v>
       </c>
       <c r="P289" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="Q289" t="n">
-        <v>736800</v>
+        <v>1157000</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>C5246/C5247</t>
+          <t>C525</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>6900077483239</v>
+        <v>6957430180236</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J290" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13361,33 +13359,33 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="N290" t="n">
-        <v>8702.219999999999</v>
+        <v>345.55838633169</v>
       </c>
       <c r="O290" t="n">
-        <v>1131288.6</v>
+        <v>496221.8427723068</v>
       </c>
       <c r="P290" t="n">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="Q290" t="n">
-        <v>1157000</v>
+        <v>861600</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>C525</t>
+          <t>C526</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>6957430180236</v>
+        <v>6957430180243</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
+          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -13396,7 +13394,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13405,42 +13403,47 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="N291" t="n">
-        <v>345.55838633169</v>
+        <v>711.33664971986</v>
       </c>
       <c r="O291" t="n">
-        <v>496221.8427723068</v>
+        <v>8120619.193201922</v>
       </c>
       <c r="P291" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="Q291" t="n">
-        <v>861600</v>
+        <v>10274400</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>C526</t>
+          <t>C527-IO</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>6957430180243</v>
+        <v>6957430180526</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J292" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13449,38 +13452,35 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="N292" t="n">
-        <v>711.33664971986</v>
+        <v>815.0599999999999</v>
       </c>
       <c r="O292" t="n">
-        <v>8120619.193201922</v>
+        <v>1012304.52</v>
       </c>
       <c r="P292" t="n">
         <v>900</v>
       </c>
       <c r="Q292" t="n">
-        <v>10274400</v>
+        <v>1117800</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>C527-IO</t>
-        </is>
-      </c>
-      <c r="B293" t="n">
-        <v>6957430180526</v>
+          <t>C541</t>
+        </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+          <t>GLOBO LLAMA PQÑO</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -13489,7 +13489,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13498,30 +13498,30 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="N293" t="n">
-        <v>815.0599999999999</v>
+        <v>800</v>
       </c>
       <c r="O293" t="n">
-        <v>1012304.52</v>
+        <v>1720000</v>
       </c>
       <c r="P293" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Q293" t="n">
-        <v>1117800</v>
+        <v>2150000</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>C541</t>
+          <t>C575-IO</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>GLOBO LLAMA PQÑO</t>
+          <t>GLOBO UNICORNIO PQÑO</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -13535,7 +13535,7 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13544,35 +13544,38 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="N294" t="n">
-        <v>800</v>
+        <v>320</v>
       </c>
       <c r="O294" t="n">
-        <v>1720000</v>
+        <v>320320</v>
       </c>
       <c r="P294" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="Q294" t="n">
-        <v>2150000</v>
+        <v>400400</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>C575-IO</t>
-        </is>
+          <t>C596-IO</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>8596162180268</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO PQÑO</t>
+          <t>GLOBO TE AMO</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -13581,7 +13584,7 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13590,33 +13593,33 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="N295" t="n">
-        <v>320</v>
+        <v>1044.54</v>
       </c>
       <c r="O295" t="n">
-        <v>320320</v>
+        <v>1519805.7</v>
       </c>
       <c r="P295" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="Q295" t="n">
-        <v>400400</v>
+        <v>1746000</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C596-IO</t>
+          <t>C60-IO</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>8596162180268</v>
+        <v>6524521011245</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>GLOBO TE AMO</t>
+          <t>GLOBO TIKTOK BOUQUET</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -13630,7 +13633,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13639,38 +13642,35 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="N296" t="n">
-        <v>1044.54</v>
+        <v>1989.05</v>
       </c>
       <c r="O296" t="n">
-        <v>1519805.7</v>
+        <v>1471897</v>
       </c>
       <c r="P296" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="Q296" t="n">
-        <v>1746000</v>
+        <v>2220000</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C60-IO</t>
-        </is>
-      </c>
-      <c r="B297" t="n">
-        <v>6524521011245</v>
+          <t>C6074</t>
+        </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>GLOBO TIKTOK BOUQUET</t>
+          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -13679,7 +13679,7 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13688,44 +13688,42 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="N297" t="n">
-        <v>1989.05</v>
+        <v>9447.25</v>
       </c>
       <c r="O297" t="n">
-        <v>1471897</v>
+        <v>236181.25</v>
       </c>
       <c r="P297" t="n">
-        <v>3000</v>
+        <v>9900</v>
       </c>
       <c r="Q297" t="n">
-        <v>2220000</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C6074</t>
-        </is>
+          <t>C629</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>7791638082188</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>BURBUJERO PITO STD</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J298" t="n">
-        <v>25</v>
+        <v>15732</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13734,42 +13732,47 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>25</v>
+        <v>15732</v>
       </c>
       <c r="N298" t="n">
-        <v>9447.25</v>
+        <v>703.79516599434</v>
       </c>
       <c r="O298" t="n">
-        <v>236181.25</v>
+        <v>11072105.55142296</v>
       </c>
       <c r="P298" t="n">
-        <v>9900</v>
+        <v>900</v>
       </c>
       <c r="Q298" t="n">
-        <v>247500</v>
+        <v>14158800</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C629</t>
+          <t>C6406</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>7791638082188</v>
+        <v>6820212541115</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>BURBUJERO PITO STD</t>
+          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J299" t="n">
-        <v>15732</v>
+        <v>52</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13778,47 +13781,39 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>15732</v>
+        <v>52</v>
       </c>
       <c r="N299" t="n">
-        <v>703.79516919374</v>
+        <v>14260.14</v>
       </c>
       <c r="O299" t="n">
-        <v>11072105.60175592</v>
+        <v>741527.28</v>
       </c>
       <c r="P299" t="n">
-        <v>900</v>
+        <v>15900</v>
       </c>
       <c r="Q299" t="n">
-        <v>14158800</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C6406</t>
-        </is>
-      </c>
-      <c r="B300" t="n">
-        <v>6820212541115</v>
+          <t>C642</t>
+        </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>LANZADOR AGUA</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J300" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13827,39 +13822,44 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="N300" t="n">
-        <v>14260.14</v>
+        <v>2529.19</v>
       </c>
       <c r="O300" t="n">
-        <v>741527.28</v>
+        <v>1514984.81</v>
       </c>
       <c r="P300" t="n">
-        <v>15900</v>
+        <v>5100</v>
       </c>
       <c r="Q300" t="n">
-        <v>826800</v>
+        <v>3054900</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C642</t>
+          <t>C671-LJ</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA</t>
+          <t>GLOBO UNICORNIO MEDIANO</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J301" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13868,35 +13868,38 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="N301" t="n">
-        <v>2529.19</v>
+        <v>400</v>
       </c>
       <c r="O301" t="n">
-        <v>1514984.81</v>
+        <v>558800</v>
       </c>
       <c r="P301" t="n">
-        <v>5100</v>
+        <v>500</v>
       </c>
       <c r="Q301" t="n">
-        <v>3054900</v>
+        <v>698500</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C671-LJ</t>
-        </is>
+          <t>C7005</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>6874123039124</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MEDIANO</t>
+          <t>MAQUINA DE COSER C7005</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -13905,7 +13908,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13914,38 +13917,38 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="N302" t="n">
-        <v>400</v>
+        <v>6078.9925934066</v>
       </c>
       <c r="O302" t="n">
-        <v>558800</v>
+        <v>1264430.459428573</v>
       </c>
       <c r="P302" t="n">
-        <v>500</v>
+        <v>18500</v>
       </c>
       <c r="Q302" t="n">
-        <v>698500</v>
+        <v>3848000</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C7005</t>
+          <t>C7009</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>6874123039124</v>
+        <v>2024250256831</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER C7005</t>
+          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -13954,7 +13957,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -13963,33 +13966,33 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="N303" t="n">
-        <v>6078.9925934066</v>
+        <v>5899.18</v>
       </c>
       <c r="O303" t="n">
-        <v>1264430.459428573</v>
+        <v>70790.16</v>
       </c>
       <c r="P303" t="n">
-        <v>18500</v>
+        <v>12500</v>
       </c>
       <c r="Q303" t="n">
-        <v>3848000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C7009</t>
+          <t>C7038</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>2024250256831</v>
+        <v>5132595141631</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
+          <t>LANZADORA DE AGUA GLOBO C7038</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -14003,7 +14006,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14012,38 +14015,38 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N304" t="n">
-        <v>5899.18</v>
+        <v>18423.71</v>
       </c>
       <c r="O304" t="n">
-        <v>70790.16</v>
+        <v>423745.33</v>
       </c>
       <c r="P304" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="Q304" t="n">
-        <v>150000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C7038</t>
+          <t>C7039</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>5132595141631</v>
+        <v>5132594521182</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA GLOBO C7038</t>
+          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -14052,7 +14055,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -14061,38 +14064,38 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N305" t="n">
-        <v>18423.71</v>
+        <v>10985.78</v>
       </c>
       <c r="O305" t="n">
-        <v>423745.33</v>
+        <v>219715.6</v>
       </c>
       <c r="P305" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q305" t="n">
-        <v>230000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C7039</t>
+          <t>C7040</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>5132594521182</v>
+        <v>6920373004365</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
+          <t>GARAJE EXIBICION CON LUZ C7040</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -14101,7 +14104,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14110,38 +14113,38 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="N306" t="n">
-        <v>10985.78</v>
+        <v>23452.77</v>
       </c>
       <c r="O306" t="n">
-        <v>219715.6</v>
+        <v>1102280.19</v>
       </c>
       <c r="P306" t="n">
-        <v>15000</v>
+        <v>39900</v>
       </c>
       <c r="Q306" t="n">
-        <v>300000</v>
+        <v>1875300</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C7040</t>
+          <t>C7042</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>6920373004365</v>
+        <v>2024081616255</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>GARAJE EXIBICION CON LUZ C7040</t>
+          <t>CANCHA BASKETBALL WIN24 C7042</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -14150,7 +14153,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -14159,38 +14162,35 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="N307" t="n">
-        <v>23452.77</v>
+        <v>9694.41</v>
       </c>
       <c r="O307" t="n">
-        <v>1102280.19</v>
+        <v>96944.10000000001</v>
       </c>
       <c r="P307" t="n">
-        <v>39900</v>
+        <v>32500</v>
       </c>
       <c r="Q307" t="n">
-        <v>1875300</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C7042</t>
-        </is>
-      </c>
-      <c r="B308" t="n">
-        <v>2024081616255</v>
+          <t>C7080-BC</t>
+        </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>CANCHA BASKETBALL WIN24 C7042</t>
+          <t>ROBOT TRANSFORME STD C7080-BC</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -14208,35 +14208,38 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="N308" t="n">
-        <v>9694.41</v>
+        <v>10556.12</v>
       </c>
       <c r="O308" t="n">
-        <v>96944.10000000001</v>
+        <v>411688.6800000001</v>
       </c>
       <c r="P308" t="n">
-        <v>32500</v>
+        <v>32900</v>
       </c>
       <c r="Q308" t="n">
-        <v>325000</v>
+        <v>1283100</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C7080-BC</t>
-        </is>
+          <t>C7081</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>6301582313156</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>ROBOT TRANSFORME STD C7080-BC</t>
+          <t>LANZADORA DARDOS DE PILA C7081</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>MUÑECOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -14245,7 +14248,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -14254,47 +14257,42 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="N309" t="n">
-        <v>10556.12</v>
+        <v>22470.62</v>
       </c>
       <c r="O309" t="n">
-        <v>411688.6800000001</v>
+        <v>471883.02</v>
       </c>
       <c r="P309" t="n">
-        <v>32900</v>
+        <v>41900</v>
       </c>
       <c r="Q309" t="n">
-        <v>1283100</v>
+        <v>879900</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C7081</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>6301582313156</v>
+        <v>5899989622205</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS DE PILA C7081</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>LANZADORES</t>
+          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J310" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -14303,42 +14301,44 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="N310" t="n">
-        <v>22470.62</v>
+        <v>1669.6</v>
       </c>
       <c r="O310" t="n">
-        <v>471883.02</v>
+        <v>654483.2</v>
       </c>
       <c r="P310" t="n">
-        <v>41900</v>
+        <v>2900</v>
       </c>
       <c r="Q310" t="n">
-        <v>879900</v>
+        <v>1136800</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C71</t>
-        </is>
-      </c>
-      <c r="B311" t="n">
-        <v>5899989622205</v>
+          <t>C7117</t>
+        </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
+          <t>BINGO LOTTO C7117</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>JUEGOS DE MESA</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J311" t="n">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14347,35 +14347,35 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="N311" t="n">
-        <v>1669.6</v>
+        <v>5798.41</v>
       </c>
       <c r="O311" t="n">
-        <v>654483.2</v>
+        <v>115968.2</v>
       </c>
       <c r="P311" t="n">
-        <v>2900</v>
+        <v>14900</v>
       </c>
       <c r="Q311" t="n">
-        <v>1136800</v>
+        <v>298000</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C7117</t>
+          <t>C7124</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>BINGO LOTTO C7117</t>
+          <t>TRAILER TRANFORME XQ05 C7124</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>JUEGOS DE MESA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -14384,7 +14384,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -14393,35 +14393,35 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N312" t="n">
-        <v>5798.41</v>
+        <v>19587.53</v>
       </c>
       <c r="O312" t="n">
-        <v>115968.2</v>
+        <v>783501.2</v>
       </c>
       <c r="P312" t="n">
-        <v>14900</v>
+        <v>65000</v>
       </c>
       <c r="Q312" t="n">
-        <v>298000</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C7124</t>
+          <t>C7132</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>TRAILER TRANFORME XQ05 C7124</t>
+          <t>SET PULSERAS Y CAUCHOS C7132</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -14430,7 +14430,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -14439,30 +14439,33 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="N313" t="n">
-        <v>19587.53</v>
+        <v>3100.87</v>
       </c>
       <c r="O313" t="n">
-        <v>783501.2</v>
+        <v>669787.9199999999</v>
       </c>
       <c r="P313" t="n">
-        <v>65000</v>
+        <v>9900</v>
       </c>
       <c r="Q313" t="n">
-        <v>2600000</v>
+        <v>2138400</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C7132</t>
-        </is>
+          <t>C7147-A</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>6912209205022</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>SET PULSERAS Y CAUCHOS C7132</t>
+          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -14476,7 +14479,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>216</v>
+        <v>57</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -14485,33 +14488,33 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>216</v>
+        <v>57</v>
       </c>
       <c r="N314" t="n">
-        <v>3100.87</v>
+        <v>10348.08</v>
       </c>
       <c r="O314" t="n">
-        <v>669787.9199999999</v>
+        <v>589840.5599999999</v>
       </c>
       <c r="P314" t="n">
-        <v>9900</v>
+        <v>16900</v>
       </c>
       <c r="Q314" t="n">
-        <v>2138400</v>
+        <v>963300</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C7147-A</t>
+          <t>C7213</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>6912209205022</v>
+        <v>6987540143012</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
+          <t>PESCADO CON LUZ Y SONIDO C7213</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -14525,7 +14528,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14534,33 +14537,33 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="N315" t="n">
-        <v>10348.08</v>
+        <v>9746.880194174801</v>
       </c>
       <c r="O315" t="n">
-        <v>589840.5599999999</v>
+        <v>467850.2493203904</v>
       </c>
       <c r="P315" t="n">
-        <v>16900</v>
+        <v>18500</v>
       </c>
       <c r="Q315" t="n">
-        <v>963300</v>
+        <v>888000</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C7213</t>
+          <t>C7218</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>6987540143012</v>
+        <v>6920240872189</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>PESCADO CON LUZ Y SONIDO C7213</t>
+          <t>CAJA REGISTRADORA SHOPPING C7218</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -14574,7 +14577,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14583,33 +14586,33 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="N316" t="n">
-        <v>9746.8801904762</v>
+        <v>13623.91</v>
       </c>
       <c r="O316" t="n">
-        <v>467850.2491428576</v>
+        <v>204358.65</v>
       </c>
       <c r="P316" t="n">
-        <v>18500</v>
+        <v>26900</v>
       </c>
       <c r="Q316" t="n">
-        <v>888000</v>
+        <v>403500</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C7218</t>
+          <t>C7221</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>6920240872189</v>
+        <v>7453100037446</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>CAJA REGISTRADORA SHOPPING C7218</t>
+          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -14623,7 +14626,7 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>15</v>
+        <v>347</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -14632,33 +14635,33 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>15</v>
+        <v>347</v>
       </c>
       <c r="N317" t="n">
-        <v>13623.91</v>
+        <v>2672.89</v>
       </c>
       <c r="O317" t="n">
-        <v>204358.65</v>
+        <v>927492.83</v>
       </c>
       <c r="P317" t="n">
-        <v>26900</v>
+        <v>10200</v>
       </c>
       <c r="Q317" t="n">
-        <v>403500</v>
+        <v>3539400</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C7221</t>
+          <t>C7222</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>7453100037446</v>
+        <v>7453100037453</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
+          <t>RELOJ DIDACTICO CARACOL C7222</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -14672,7 +14675,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -14681,33 +14684,33 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="N318" t="n">
-        <v>2672.89</v>
+        <v>4795.69</v>
       </c>
       <c r="O318" t="n">
-        <v>927492.83</v>
+        <v>1103008.7</v>
       </c>
       <c r="P318" t="n">
         <v>10200</v>
       </c>
       <c r="Q318" t="n">
-        <v>3539400</v>
+        <v>2346000</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C7222</t>
+          <t>C7246</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>7453100037453</v>
+        <v>6902024622111</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>RELOJ DIDACTICO CARACOL C7222</t>
+          <t>BLÍSTER SKATE X4 C7246</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -14721,7 +14724,7 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14730,38 +14733,38 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="N319" t="n">
-        <v>4795.69</v>
+        <v>2992.5689285714</v>
       </c>
       <c r="O319" t="n">
-        <v>1103008.7</v>
+        <v>62843.94749999941</v>
       </c>
       <c r="P319" t="n">
-        <v>10200</v>
+        <v>6000</v>
       </c>
       <c r="Q319" t="n">
-        <v>2346000</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C7246</t>
+          <t>C7294</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>6902024622111</v>
+        <v>6895675680022</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>BLÍSTER SKATE X4 C7246</t>
+          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -14770,7 +14773,7 @@
         </is>
       </c>
       <c r="J320" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14779,38 +14782,38 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="N320" t="n">
-        <v>2992.5689285714</v>
+        <v>4337.31</v>
       </c>
       <c r="O320" t="n">
-        <v>62843.94749999941</v>
+        <v>260238.6</v>
       </c>
       <c r="P320" t="n">
-        <v>6000</v>
+        <v>12900</v>
       </c>
       <c r="Q320" t="n">
-        <v>126000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C7294</t>
+          <t>C7325</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>6895675680022</v>
+        <v>6974555555022</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>PISTA EN BLISTER C7325</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -14819,7 +14822,7 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14828,38 +14831,35 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N321" t="n">
-        <v>4337.31</v>
+        <v>3067.0905844156</v>
       </c>
       <c r="O321" t="n">
-        <v>260238.6</v>
+        <v>138019.076298702</v>
       </c>
       <c r="P321" t="n">
-        <v>12900</v>
+        <v>7200</v>
       </c>
       <c r="Q321" t="n">
-        <v>774000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>C7325</t>
-        </is>
-      </c>
-      <c r="B322" t="n">
-        <v>6974555555022</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -14868,7 +14868,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14877,35 +14877,38 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="N322" t="n">
-        <v>3067.0905844156</v>
+        <v>640</v>
       </c>
       <c r="O322" t="n">
-        <v>138019.076298702</v>
+        <v>1728000</v>
       </c>
       <c r="P322" t="n">
-        <v>7200</v>
+        <v>800</v>
       </c>
       <c r="Q322" t="n">
-        <v>324000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7365</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>6920240750050</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -14914,7 +14917,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14923,33 +14926,33 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="N323" t="n">
-        <v>640</v>
+        <v>4190.77</v>
       </c>
       <c r="O323" t="n">
-        <v>1728000</v>
+        <v>79624.63</v>
       </c>
       <c r="P323" t="n">
-        <v>800</v>
+        <v>5900</v>
       </c>
       <c r="Q323" t="n">
-        <v>2160000</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7366</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>6920240750050</v>
+        <v>6920240750098</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -14963,7 +14966,7 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -14972,33 +14975,33 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="N324" t="n">
-        <v>4190.77</v>
+        <v>3499.72</v>
       </c>
       <c r="O324" t="n">
-        <v>79624.63</v>
+        <v>363970.88</v>
       </c>
       <c r="P324" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q324" t="n">
-        <v>112100</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>C7366</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>6920240750098</v>
+        <v>6920240750159</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -15012,7 +15015,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -15021,38 +15024,35 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="N325" t="n">
-        <v>3499.72</v>
+        <v>4578.04</v>
       </c>
       <c r="O325" t="n">
-        <v>363970.88</v>
+        <v>723330.3199999999</v>
       </c>
       <c r="P325" t="n">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="Q325" t="n">
-        <v>717600</v>
+        <v>1185000</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>C7368</t>
-        </is>
-      </c>
-      <c r="B326" t="n">
-        <v>6920240750159</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -15070,35 +15070,38 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="N326" t="n">
-        <v>4578.04</v>
+        <v>480</v>
       </c>
       <c r="O326" t="n">
-        <v>723330.3199999999</v>
+        <v>900480</v>
       </c>
       <c r="P326" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q326" t="n">
-        <v>1185000</v>
+        <v>1125600</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7402</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>6920601877891</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>PANDERETA X 3 C7402</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -15107,7 +15110,7 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>1876</v>
+        <v>60</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15116,38 +15119,38 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>1876</v>
+        <v>60</v>
       </c>
       <c r="N327" t="n">
-        <v>480</v>
+        <v>2356.29</v>
       </c>
       <c r="O327" t="n">
-        <v>900480</v>
+        <v>141377.4</v>
       </c>
       <c r="P327" t="n">
-        <v>600</v>
+        <v>6500</v>
       </c>
       <c r="Q327" t="n">
-        <v>1125600</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>C7402</t>
+          <t>C7413</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>6920601877891</v>
+        <v>6921202412870</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>PANDERETA X 3 C7402</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -15156,7 +15159,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15165,38 +15168,35 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="N328" t="n">
-        <v>2356.29</v>
+        <v>4159.000295203</v>
       </c>
       <c r="O328" t="n">
-        <v>141377.4</v>
+        <v>499080.03542436</v>
       </c>
       <c r="P328" t="n">
-        <v>6500</v>
+        <v>8900</v>
       </c>
       <c r="Q328" t="n">
-        <v>390000</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>C7413</t>
-        </is>
-      </c>
-      <c r="B329" t="n">
-        <v>6921202412870</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -15205,7 +15205,7 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -15214,35 +15214,38 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>120</v>
+        <v>478</v>
       </c>
       <c r="N329" t="n">
-        <v>4159.000295203</v>
+        <v>1554.12</v>
       </c>
       <c r="O329" t="n">
-        <v>499080.03542436</v>
+        <v>742869.36</v>
       </c>
       <c r="P329" t="n">
-        <v>8900</v>
+        <v>1900</v>
       </c>
       <c r="Q329" t="n">
-        <v>1068000</v>
+        <v>908200</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>C744-IO</t>
-        </is>
+          <t>C7453</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>6920247274535</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>JUEGO DE MESA BALONCESTO C7453</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -15251,7 +15254,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>478</v>
+        <v>8</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -15260,33 +15263,30 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>478</v>
+        <v>8</v>
       </c>
       <c r="N330" t="n">
-        <v>1554.12</v>
+        <v>27938.1</v>
       </c>
       <c r="O330" t="n">
-        <v>742869.36</v>
+        <v>223504.8</v>
       </c>
       <c r="P330" t="n">
-        <v>1900</v>
+        <v>18000</v>
       </c>
       <c r="Q330" t="n">
-        <v>908200</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>C7453</t>
-        </is>
-      </c>
-      <c r="B331" t="n">
-        <v>6920247274535</v>
+          <t>C7462</t>
+        </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>JUEGO DE MESA BALONCESTO C7453</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -15300,7 +15300,7 @@
         </is>
       </c>
       <c r="J331" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
@@ -15309,30 +15309,33 @@
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N331" t="n">
-        <v>27938.1</v>
+        <v>14751.820322581</v>
       </c>
       <c r="O331" t="n">
-        <v>223504.8</v>
+        <v>162270.023548391</v>
       </c>
       <c r="P331" t="n">
-        <v>18000</v>
+        <v>37100</v>
       </c>
       <c r="Q331" t="n">
-        <v>144000</v>
+        <v>408100</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>C7462</t>
-        </is>
+          <t>C7467</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>6920241023009</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -15346,7 +15349,7 @@
         </is>
       </c>
       <c r="J332" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -15355,38 +15358,38 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N332" t="n">
-        <v>14751.820322581</v>
+        <v>15347.45</v>
       </c>
       <c r="O332" t="n">
-        <v>162270.023548391</v>
+        <v>230211.75</v>
       </c>
       <c r="P332" t="n">
-        <v>37100</v>
+        <v>23900</v>
       </c>
       <c r="Q332" t="n">
-        <v>408100</v>
+        <v>358500</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>C7467</t>
+          <t>C7488</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>6920241023009</v>
+        <v>6945158254520</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -15395,7 +15398,7 @@
         </is>
       </c>
       <c r="J333" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
@@ -15404,38 +15407,38 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="N333" t="n">
-        <v>15347.45</v>
+        <v>8919.16</v>
       </c>
       <c r="O333" t="n">
-        <v>230211.75</v>
+        <v>258655.64</v>
       </c>
       <c r="P333" t="n">
-        <v>23900</v>
+        <v>10000</v>
       </c>
       <c r="Q333" t="n">
-        <v>358500</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>6945158254520</v>
+        <v>6905698382824</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -15444,7 +15447,7 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
@@ -15453,47 +15456,42 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="N334" t="n">
-        <v>8919.16</v>
+        <v>1024.29</v>
       </c>
       <c r="O334" t="n">
-        <v>258655.64</v>
+        <v>1024.29</v>
       </c>
       <c r="P334" t="n">
-        <v>10000</v>
+        <v>2900</v>
       </c>
       <c r="Q334" t="n">
-        <v>290000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>6905698382824</v>
+        <v>8596162180497</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J335" t="n">
-        <v>1</v>
+        <v>1398</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -15502,33 +15500,33 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>1</v>
+        <v>1398</v>
       </c>
       <c r="N335" t="n">
-        <v>1024.29</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O335" t="n">
-        <v>1024.29</v>
+        <v>1626915.200678939</v>
       </c>
       <c r="P335" t="n">
-        <v>2900</v>
+        <v>1500</v>
       </c>
       <c r="Q335" t="n">
-        <v>2900</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C753</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>8596162180497</v>
+        <v>8596162180503</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -15537,7 +15535,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>1398</v>
+        <v>277</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -15546,42 +15544,47 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>1398</v>
+        <v>277</v>
       </c>
       <c r="N336" t="n">
-        <v>1163.7447787403</v>
+        <v>5113.4625508318</v>
       </c>
       <c r="O336" t="n">
-        <v>1626915.200678939</v>
+        <v>1416429.126580409</v>
       </c>
       <c r="P336" t="n">
-        <v>1500</v>
+        <v>7000</v>
       </c>
       <c r="Q336" t="n">
-        <v>2097000</v>
+        <v>1939000</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>C753</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>8596162180503</v>
+        <v>6923669699979</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J337" t="n">
-        <v>277</v>
+        <v>12023</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -15590,33 +15593,33 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>277</v>
+        <v>12023</v>
       </c>
       <c r="N337" t="n">
-        <v>5113.4625508318</v>
+        <v>509.69</v>
       </c>
       <c r="O337" t="n">
-        <v>1416429.126580409</v>
+        <v>6128002.87</v>
       </c>
       <c r="P337" t="n">
-        <v>7000</v>
+        <v>750</v>
       </c>
       <c r="Q337" t="n">
-        <v>1939000</v>
+        <v>9017250</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>C7533</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>6923669699979</v>
+        <v>6951241752002</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -15630,7 +15633,7 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>12023</v>
+        <v>499</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -15639,38 +15642,35 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>12023</v>
+        <v>499</v>
       </c>
       <c r="N338" t="n">
-        <v>509.69</v>
+        <v>7046.93982792</v>
       </c>
       <c r="O338" t="n">
-        <v>6128002.87</v>
+        <v>3516422.97413208</v>
       </c>
       <c r="P338" t="n">
-        <v>750</v>
+        <v>9900</v>
       </c>
       <c r="Q338" t="n">
-        <v>9017250</v>
+        <v>4940100</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B339" t="n">
-        <v>6951241752002</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -15679,7 +15679,7 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
@@ -15688,35 +15688,35 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="N339" t="n">
-        <v>7046.93982792</v>
+        <v>24338.47</v>
       </c>
       <c r="O339" t="n">
-        <v>3516422.97413208</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P339" t="n">
-        <v>9900</v>
+        <v>27900</v>
       </c>
       <c r="Q339" t="n">
-        <v>4940100</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>C7535</t>
+          <t>C7560</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
@@ -15734,35 +15734,35 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="N340" t="n">
-        <v>24338.47</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O340" t="n">
-        <v>730154.1000000001</v>
+        <v>149706.28</v>
       </c>
       <c r="P340" t="n">
-        <v>27900</v>
+        <v>2500</v>
       </c>
       <c r="Q340" t="n">
-        <v>837000</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>C7560</t>
+          <t>C7560AC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>TRICICLO INFANTIL OSITO C756AC</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="K341" t="n">
         <v>0</v>
@@ -15780,35 +15780,38 @@
         <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="N341" t="n">
-        <v>796.3099999999999</v>
+        <v>44113.603841808</v>
       </c>
       <c r="O341" t="n">
-        <v>149706.28</v>
+        <v>441136.03841808</v>
       </c>
       <c r="P341" t="n">
-        <v>2500</v>
+        <v>71900</v>
       </c>
       <c r="Q341" t="n">
-        <v>470000</v>
+        <v>719000</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>C7560AC</t>
-        </is>
+          <t>C7588</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>7588228020244</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>TRICICLO INFANTIL OSITO C756AC</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -15817,7 +15820,7 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>10</v>
+        <v>1432</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
@@ -15826,38 +15829,38 @@
         <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>10</v>
+        <v>1432</v>
       </c>
       <c r="N342" t="n">
-        <v>44113.603841808</v>
+        <v>641.78</v>
       </c>
       <c r="O342" t="n">
-        <v>441136.03841808</v>
+        <v>919028.96</v>
       </c>
       <c r="P342" t="n">
-        <v>71900</v>
+        <v>2500</v>
       </c>
       <c r="Q342" t="n">
-        <v>719000</v>
+        <v>3580000</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>7588228020244</v>
+        <v>6999899236093</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -15866,7 +15869,7 @@
         </is>
       </c>
       <c r="J343" t="n">
-        <v>1432</v>
+        <v>276</v>
       </c>
       <c r="K343" t="n">
         <v>0</v>
@@ -15875,38 +15878,38 @@
         <v>0</v>
       </c>
       <c r="M343" t="n">
-        <v>1432</v>
+        <v>276</v>
       </c>
       <c r="N343" t="n">
-        <v>641.78</v>
+        <v>7811.9</v>
       </c>
       <c r="O343" t="n">
-        <v>919028.96</v>
+        <v>2156084.4</v>
       </c>
       <c r="P343" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q343" t="n">
-        <v>3580000</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>6999899236093</v>
+        <v>6999899236130</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -15915,7 +15918,7 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>276</v>
+        <v>460</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
@@ -15924,47 +15927,42 @@
         <v>0</v>
       </c>
       <c r="M344" t="n">
-        <v>276</v>
+        <v>460</v>
       </c>
       <c r="N344" t="n">
-        <v>7811.9</v>
+        <v>3155</v>
       </c>
       <c r="O344" t="n">
-        <v>2156084.4</v>
+        <v>1451300</v>
       </c>
       <c r="P344" t="n">
-        <v>13900</v>
+        <v>5900</v>
       </c>
       <c r="Q344" t="n">
-        <v>3836400</v>
+        <v>2714000</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>C7614-F</t>
+          <t>C784</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>6999899236130</v>
+        <v>8913992935507</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J345" t="n">
-        <v>460</v>
+        <v>1450</v>
       </c>
       <c r="K345" t="n">
         <v>0</v>
@@ -15973,33 +15971,30 @@
         <v>0</v>
       </c>
       <c r="M345" t="n">
-        <v>460</v>
+        <v>1450</v>
       </c>
       <c r="N345" t="n">
-        <v>3155</v>
+        <v>704.8968946963899</v>
       </c>
       <c r="O345" t="n">
-        <v>1451300</v>
+        <v>1022100.497309765</v>
       </c>
       <c r="P345" t="n">
-        <v>5900</v>
+        <v>900</v>
       </c>
       <c r="Q345" t="n">
-        <v>2714000</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>C784</t>
-        </is>
-      </c>
-      <c r="B346" t="n">
-        <v>8913992935507</v>
+          <t>C815</t>
+        </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>SCOOTER HUMO</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -16008,7 +16003,7 @@
         </is>
       </c>
       <c r="J346" t="n">
-        <v>1450</v>
+        <v>6</v>
       </c>
       <c r="K346" t="n">
         <v>0</v>
@@ -16017,30 +16012,33 @@
         <v>0</v>
       </c>
       <c r="M346" t="n">
-        <v>1450</v>
+        <v>6</v>
       </c>
       <c r="N346" t="n">
-        <v>704.8968946963899</v>
+        <v>110520.77</v>
       </c>
       <c r="O346" t="n">
-        <v>1022100.497309765</v>
+        <v>663124.62</v>
       </c>
       <c r="P346" t="n">
-        <v>900</v>
+        <v>176900</v>
       </c>
       <c r="Q346" t="n">
-        <v>1305000</v>
+        <v>1061400</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>C815</t>
-        </is>
+          <t>C819</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>2087202108190</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>SCOOTER HUMO</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -16049,7 +16047,7 @@
         </is>
       </c>
       <c r="J347" t="n">
-        <v>6</v>
+        <v>468</v>
       </c>
       <c r="K347" t="n">
         <v>0</v>
@@ -16058,33 +16056,33 @@
         <v>0</v>
       </c>
       <c r="M347" t="n">
-        <v>6</v>
+        <v>468</v>
       </c>
       <c r="N347" t="n">
-        <v>110520.77</v>
+        <v>6761.25</v>
       </c>
       <c r="O347" t="n">
-        <v>663124.62</v>
+        <v>3164265</v>
       </c>
       <c r="P347" t="n">
-        <v>176900</v>
+        <v>5200</v>
       </c>
       <c r="Q347" t="n">
-        <v>1061400</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>C819</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>2087202108190</v>
+        <v>2021010563031</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -16093,7 +16091,7 @@
         </is>
       </c>
       <c r="J348" t="n">
-        <v>468</v>
+        <v>270</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
@@ -16102,33 +16100,35 @@
         <v>0</v>
       </c>
       <c r="M348" t="n">
-        <v>468</v>
+        <v>270</v>
       </c>
       <c r="N348" t="n">
-        <v>6761.25</v>
+        <v>1008.8168311195</v>
       </c>
       <c r="O348" t="n">
-        <v>3164265</v>
+        <v>272380.544402265</v>
       </c>
       <c r="P348" t="n">
-        <v>5200</v>
+        <v>1500</v>
       </c>
       <c r="Q348" t="n">
-        <v>2433600</v>
+        <v>405000</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B349" t="n">
-        <v>2021010563031</v>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
+        </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -16137,7 +16137,7 @@
         </is>
       </c>
       <c r="J349" t="n">
-        <v>270</v>
+        <v>121</v>
       </c>
       <c r="K349" t="n">
         <v>0</v>
@@ -16146,44 +16146,49 @@
         <v>0</v>
       </c>
       <c r="M349" t="n">
-        <v>270</v>
+        <v>121</v>
       </c>
       <c r="N349" t="n">
-        <v>1008.8168311195</v>
+        <v>1520</v>
       </c>
       <c r="O349" t="n">
-        <v>272380.544402265</v>
+        <v>183920</v>
       </c>
       <c r="P349" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q349" t="n">
-        <v>405000</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>C879</t>
+          <t>C880</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>CG-2016-212</t>
+          <t>cg2016213</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J350" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="K350" t="n">
         <v>0</v>
@@ -16192,49 +16197,39 @@
         <v>0</v>
       </c>
       <c r="M350" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="N350" t="n">
         <v>1520</v>
       </c>
       <c r="O350" t="n">
-        <v>183920</v>
+        <v>304000</v>
       </c>
       <c r="P350" t="n">
         <v>1900</v>
       </c>
       <c r="Q350" t="n">
-        <v>229900</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>C880</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>cg2016213</t>
+          <t>C888</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>VELA</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J351" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="K351" t="n">
         <v>0</v>
@@ -16243,39 +16238,44 @@
         <v>0</v>
       </c>
       <c r="M351" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="N351" t="n">
-        <v>1520</v>
+        <v>1213.6821359223</v>
       </c>
       <c r="O351" t="n">
-        <v>304000</v>
+        <v>205112.2809708687</v>
       </c>
       <c r="P351" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q351" t="n">
-        <v>380000</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>SNORKEL 66046A</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J352" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
@@ -16284,30 +16284,30 @@
         <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="N352" t="n">
-        <v>1213.6821359223</v>
+        <v>13493.858308157</v>
       </c>
       <c r="O352" t="n">
-        <v>205112.2809708687</v>
+        <v>2415400.637160103</v>
       </c>
       <c r="P352" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="Q352" t="n">
-        <v>253500</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -16321,7 +16321,7 @@
         </is>
       </c>
       <c r="J353" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="K353" t="n">
         <v>0</v>
@@ -16330,35 +16330,40 @@
         <v>0</v>
       </c>
       <c r="M353" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="N353" t="n">
-        <v>13493.858308157</v>
+        <v>2644.9</v>
       </c>
       <c r="O353" t="n">
-        <v>2415400.637160103</v>
+        <v>917780.3</v>
       </c>
       <c r="P353" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q353" t="n">
-        <v>3025100</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -16367,7 +16372,7 @@
         </is>
       </c>
       <c r="J354" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
@@ -16376,35 +16381,30 @@
         <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="N354" t="n">
-        <v>2644.9</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O354" t="n">
-        <v>917780.3</v>
+        <v>33759.88</v>
       </c>
       <c r="P354" t="n">
-        <v>3900</v>
+        <v>29500</v>
       </c>
       <c r="Q354" t="n">
-        <v>1353300</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -16418,7 +16418,7 @@
         </is>
       </c>
       <c r="J355" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K355" t="n">
         <v>0</v>
@@ -16427,35 +16427,40 @@
         <v>0</v>
       </c>
       <c r="M355" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N355" t="n">
-        <v>8439.969999999999</v>
+        <v>12189.832</v>
       </c>
       <c r="O355" t="n">
-        <v>33759.88</v>
+        <v>219416.976</v>
       </c>
       <c r="P355" t="n">
-        <v>29500</v>
+        <v>30900</v>
       </c>
       <c r="Q355" t="n">
-        <v>118000</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -16464,7 +16469,7 @@
         </is>
       </c>
       <c r="J356" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K356" t="n">
         <v>0</v>
@@ -16473,35 +16478,30 @@
         <v>0</v>
       </c>
       <c r="M356" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="N356" t="n">
-        <v>12189.832</v>
+        <v>15452.21</v>
       </c>
       <c r="O356" t="n">
-        <v>219416.976</v>
+        <v>741706.08</v>
       </c>
       <c r="P356" t="n">
-        <v>30900</v>
+        <v>36500</v>
       </c>
       <c r="Q356" t="n">
-        <v>556200</v>
+        <v>1752000</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>MG30151</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -16515,7 +16515,7 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>48</v>
+        <v>363</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -16524,35 +16524,40 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>48</v>
+        <v>363</v>
       </c>
       <c r="N357" t="n">
-        <v>15452.21</v>
+        <v>571.87</v>
       </c>
       <c r="O357" t="n">
-        <v>741706.08</v>
+        <v>207588.81</v>
       </c>
       <c r="P357" t="n">
-        <v>36500</v>
+        <v>2500</v>
       </c>
       <c r="Q357" t="n">
-        <v>1752000</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -16561,7 +16566,7 @@
         </is>
       </c>
       <c r="J358" t="n">
-        <v>363</v>
+        <v>64</v>
       </c>
       <c r="K358" t="n">
         <v>0</v>
@@ -16570,69 +16575,18 @@
         <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>363</v>
+        <v>64</v>
       </c>
       <c r="N358" t="n">
-        <v>571.87</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O358" t="n">
-        <v>207588.81</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P358" t="n">
-        <v>2500</v>
+        <v>15900</v>
       </c>
       <c r="Q358" t="n">
-        <v>907500</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J359" t="n">
-        <v>64</v>
-      </c>
-      <c r="K359" t="n">
-        <v>0</v>
-      </c>
-      <c r="L359" t="n">
-        <v>0</v>
-      </c>
-      <c r="M359" t="n">
-        <v>64</v>
-      </c>
-      <c r="N359" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O359" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P359" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q359" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -1199,10 +1199,10 @@
         <v>180</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O20" t="n">
-        <v>706830.677449452</v>
+        <v>706830.6771784261</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -3287,10 +3287,10 @@
         <v>2592</v>
       </c>
       <c r="N69" t="n">
-        <v>3158.8608262318</v>
+        <v>3160.2538267431</v>
       </c>
       <c r="O69" t="n">
-        <v>8187767.261592825</v>
+        <v>8191377.918918115</v>
       </c>
       <c r="P69" t="n">
         <v>5600</v>
@@ -3333,10 +3333,10 @@
         <v>77</v>
       </c>
       <c r="N70" t="n">
-        <v>3841.6248214286</v>
+        <v>3856.9300996016</v>
       </c>
       <c r="O70" t="n">
-        <v>295805.1112500022</v>
+        <v>296983.6176693232</v>
       </c>
       <c r="P70" t="n">
         <v>6900</v>
@@ -3878,10 +3878,10 @@
         <v>288</v>
       </c>
       <c r="N82" t="n">
-        <v>3594.254</v>
+        <v>3594.2539962477</v>
       </c>
       <c r="O82" t="n">
-        <v>1035145.152</v>
+        <v>1035145.150919338</v>
       </c>
       <c r="P82" t="n">
         <v>6500</v>
@@ -4104,10 +4104,10 @@
         <v>2346</v>
       </c>
       <c r="N87" t="n">
-        <v>2090.85</v>
+        <v>2091.1308394896</v>
       </c>
       <c r="O87" t="n">
-        <v>4905134.1</v>
+        <v>4905792.949442602</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107903559</v>
+        <v>4372.2107904123</v>
       </c>
       <c r="O94" t="n">
-        <v>5928717.8317226</v>
+        <v>5928717.83179908</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -6137,10 +6137,10 @@
         <v>310</v>
       </c>
       <c r="N132" t="n">
-        <v>2680.739695084</v>
+        <v>2680.7396948941</v>
       </c>
       <c r="O132" t="n">
-        <v>831029.3054760399</v>
+        <v>831029.305417171</v>
       </c>
       <c r="P132" t="n">
         <v>4900</v>
@@ -7178,10 +7178,10 @@
         <v>714</v>
       </c>
       <c r="N155" t="n">
-        <v>1561.0009337861</v>
+        <v>1561.000952381</v>
       </c>
       <c r="O155" t="n">
-        <v>1114554.666723275</v>
+        <v>1114554.680000034</v>
       </c>
       <c r="P155" t="n">
         <v>2900</v>
@@ -9464,10 +9464,10 @@
         <v>162</v>
       </c>
       <c r="N205" t="n">
-        <v>4907.822092257</v>
+        <v>4956.8186522463</v>
       </c>
       <c r="O205" t="n">
-        <v>795067.1789456339</v>
+        <v>803004.6216639007</v>
       </c>
       <c r="P205" t="n">
         <v>8200</v>
@@ -13735,10 +13735,10 @@
         <v>15732</v>
       </c>
       <c r="N298" t="n">
-        <v>703.79516599434</v>
+        <v>703.79516401441</v>
       </c>
       <c r="O298" t="n">
-        <v>11072105.55142296</v>
+        <v>11072105.5202747</v>
       </c>
       <c r="P298" t="n">
         <v>900</v>
@@ -14736,10 +14736,10 @@
         <v>21</v>
       </c>
       <c r="N319" t="n">
-        <v>2992.5689285714</v>
+        <v>3065.5584146341</v>
       </c>
       <c r="O319" t="n">
-        <v>62843.94749999941</v>
+        <v>64376.7267073161</v>
       </c>
       <c r="P319" t="n">
         <v>6000</v>
@@ -16097,22 +16097,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M348" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="N348" t="n">
-        <v>1008.8168311195</v>
+        <v>1008.8166794626</v>
       </c>
       <c r="O348" t="n">
-        <v>272380.544402265</v>
+        <v>266327.6033781264</v>
       </c>
       <c r="P348" t="n">
         <v>1500</v>
       </c>
       <c r="Q348" t="n">
-        <v>405000</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="349">

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>376</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464651163</v>
+        <v>3376.7464631809</v>
       </c>
       <c r="O8" t="n">
-        <v>1269656.670883729</v>
+        <v>1269656.670156018</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -921,10 +921,10 @@
         <v>6</v>
       </c>
       <c r="N13" t="n">
-        <v>31658.725454545</v>
+        <v>31658.725660377</v>
       </c>
       <c r="O13" t="n">
-        <v>189952.35272727</v>
+        <v>189952.353962262</v>
       </c>
       <c r="P13" t="n">
         <v>62900</v>
@@ -1277,10 +1277,10 @@
         <v>40</v>
       </c>
       <c r="N22" t="n">
-        <v>3716.3301938611</v>
+        <v>3716.3301954397</v>
       </c>
       <c r="O22" t="n">
-        <v>148653.207754444</v>
+        <v>148653.207817588</v>
       </c>
       <c r="P22" t="n">
         <v>9500</v>
@@ -1472,10 +1472,10 @@
         <v>119</v>
       </c>
       <c r="N27" t="n">
-        <v>3910.628136646</v>
+        <v>3910.628089172</v>
       </c>
       <c r="O27" t="n">
-        <v>465364.748260874</v>
+        <v>465364.742611468</v>
       </c>
       <c r="P27" t="n">
         <v>9100</v>
@@ -1727,10 +1727,10 @@
         <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>62349.657575758</v>
+        <v>62349.656875</v>
       </c>
       <c r="O33" t="n">
-        <v>249398.630303032</v>
+        <v>249398.6275</v>
       </c>
       <c r="P33" t="n">
         <v>109900</v>
@@ -1910,10 +1910,10 @@
         <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>344599.17862745</v>
+        <v>344599.1786</v>
       </c>
       <c r="O37" t="n">
-        <v>2067595.0717647</v>
+        <v>2067595.0716</v>
       </c>
       <c r="P37" t="n">
         <v>532900</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>624</v>
+        <v>542</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3192,19 +3192,19 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>624</v>
+        <v>542</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2556563454</v>
+        <v>2582.2556363636</v>
       </c>
       <c r="O67" t="n">
-        <v>1611327.52955953</v>
+        <v>1399582.554909071</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
       </c>
       <c r="Q67" t="n">
-        <v>2808000</v>
+        <v>2439000</v>
       </c>
     </row>
     <row r="68">
@@ -3241,10 +3241,10 @@
         <v>1312</v>
       </c>
       <c r="N68" t="n">
-        <v>5216.8961063218</v>
+        <v>5216.8960979122</v>
       </c>
       <c r="O68" t="n">
-        <v>6844567.691494202</v>
+        <v>6844567.680460807</v>
       </c>
       <c r="P68" t="n">
         <v>8500</v>
@@ -3287,10 +3287,10 @@
         <v>2592</v>
       </c>
       <c r="N69" t="n">
-        <v>3160.2538267431</v>
+        <v>3158.8608271635</v>
       </c>
       <c r="O69" t="n">
-        <v>8191377.918918115</v>
+        <v>8187767.264007792</v>
       </c>
       <c r="P69" t="n">
         <v>5600</v>
@@ -3333,10 +3333,10 @@
         <v>77</v>
       </c>
       <c r="N70" t="n">
-        <v>3856.9300996016</v>
+        <v>3841.6248454636</v>
       </c>
       <c r="O70" t="n">
-        <v>296983.6176693232</v>
+        <v>295805.1131006972</v>
       </c>
       <c r="P70" t="n">
         <v>6900</v>
@@ -3471,10 +3471,10 @@
         <v>648</v>
       </c>
       <c r="N73" t="n">
-        <v>3795.7100075529</v>
+        <v>3795.7100075657</v>
       </c>
       <c r="O73" t="n">
-        <v>2459620.084894279</v>
+        <v>2459620.084902573</v>
       </c>
       <c r="P73" t="n">
         <v>6200</v>
@@ -3650,10 +3650,10 @@
         <v>346</v>
       </c>
       <c r="N77" t="n">
-        <v>4890.9300488998</v>
+        <v>4890.9300489297</v>
       </c>
       <c r="O77" t="n">
-        <v>1692261.796919331</v>
+        <v>1692261.796929676</v>
       </c>
       <c r="P77" t="n">
         <v>8200</v>
@@ -3878,10 +3878,10 @@
         <v>288</v>
       </c>
       <c r="N82" t="n">
-        <v>3594.2539962477</v>
+        <v>3594.2539736347</v>
       </c>
       <c r="O82" t="n">
-        <v>1035145.150919338</v>
+        <v>1035145.144406794</v>
       </c>
       <c r="P82" t="n">
         <v>6500</v>
@@ -4016,10 +4016,10 @@
         <v>336</v>
       </c>
       <c r="N85" t="n">
-        <v>14822.378849611</v>
+        <v>14822.37884823</v>
       </c>
       <c r="O85" t="n">
-        <v>4980319.293469296</v>
+        <v>4980319.29300528</v>
       </c>
       <c r="P85" t="n">
         <v>24900</v>
@@ -4104,10 +4104,10 @@
         <v>2346</v>
       </c>
       <c r="N87" t="n">
-        <v>2091.1308394896</v>
+        <v>2090.85</v>
       </c>
       <c r="O87" t="n">
-        <v>4905792.949442602</v>
+        <v>4905134.1</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107904123</v>
+        <v>4372.2107907508</v>
       </c>
       <c r="O94" t="n">
-        <v>5928717.83179908</v>
+        <v>5928717.832258085</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -5924,10 +5924,10 @@
         <v>432</v>
       </c>
       <c r="N127" t="n">
-        <v>2029.8738600103</v>
+        <v>2029.8738739669</v>
       </c>
       <c r="O127" t="n">
-        <v>876905.5075244496</v>
+        <v>876905.5135537008</v>
       </c>
       <c r="P127" t="n">
         <v>3600</v>
@@ -6370,10 +6370,10 @@
         <v>36</v>
       </c>
       <c r="N137" t="n">
-        <v>4285.1955337691</v>
+        <v>4285.1956570156</v>
       </c>
       <c r="O137" t="n">
-        <v>154267.0392156876</v>
+        <v>154267.0436525616</v>
       </c>
       <c r="P137" t="n">
         <v>6900</v>
@@ -6544,10 +6544,10 @@
         <v>228</v>
       </c>
       <c r="N141" t="n">
-        <v>4605.2147408106</v>
+        <v>4605.2147497639</v>
       </c>
       <c r="O141" t="n">
-        <v>1049988.960904817</v>
+        <v>1049988.962946169</v>
       </c>
       <c r="P141" t="n">
         <v>7600</v>
@@ -6994,10 +6994,10 @@
         <v>144</v>
       </c>
       <c r="N151" t="n">
-        <v>27123.765205993</v>
+        <v>27123.765196998</v>
       </c>
       <c r="O151" t="n">
-        <v>3905822.189662992</v>
+        <v>3905822.188367712</v>
       </c>
       <c r="P151" t="n">
         <v>44500</v>
@@ -7086,10 +7086,10 @@
         <v>221</v>
       </c>
       <c r="N153" t="n">
-        <v>8332.779622166199</v>
+        <v>8332.779621212099</v>
       </c>
       <c r="O153" t="n">
-        <v>1841544.29649873</v>
+        <v>1841544.296287874</v>
       </c>
       <c r="P153" t="n">
         <v>14900</v>
@@ -7178,10 +7178,10 @@
         <v>714</v>
       </c>
       <c r="N155" t="n">
-        <v>1561.000952381</v>
+        <v>1561.0010652921</v>
       </c>
       <c r="O155" t="n">
-        <v>1114554.680000034</v>
+        <v>1114554.76061856</v>
       </c>
       <c r="P155" t="n">
         <v>2900</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -7664,19 +7664,19 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N166" t="n">
         <v>10174</v>
       </c>
       <c r="O166" t="n">
-        <v>81392</v>
+        <v>40696</v>
       </c>
       <c r="P166" t="n">
         <v>16900</v>
       </c>
       <c r="Q166" t="n">
-        <v>135200</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="167">
@@ -8035,10 +8035,10 @@
         <v>11</v>
       </c>
       <c r="N174" t="n">
-        <v>23521.624262295</v>
+        <v>23521.624067797</v>
       </c>
       <c r="O174" t="n">
-        <v>258737.866885245</v>
+        <v>258737.864745767</v>
       </c>
       <c r="P174" t="n">
         <v>39000</v>
@@ -8127,10 +8127,10 @@
         <v>680</v>
       </c>
       <c r="N176" t="n">
-        <v>1778.4726458554</v>
+        <v>1778.4726494689</v>
       </c>
       <c r="O176" t="n">
-        <v>1209361.399181672</v>
+        <v>1209361.401638852</v>
       </c>
       <c r="P176" t="n">
         <v>4900</v>
@@ -9694,10 +9694,10 @@
         <v>280</v>
       </c>
       <c r="N210" t="n">
-        <v>3903.7366972477</v>
+        <v>3903.736710023</v>
       </c>
       <c r="O210" t="n">
-        <v>1093046.275229356</v>
+        <v>1093046.27880644</v>
       </c>
       <c r="P210" t="n">
         <v>7500</v>
@@ -10052,10 +10052,10 @@
         <v>144</v>
       </c>
       <c r="N218" t="n">
-        <v>5869.1726202661</v>
+        <v>5869.1726127049</v>
       </c>
       <c r="O218" t="n">
-        <v>845160.8573183184</v>
+        <v>845160.8562295055</v>
       </c>
       <c r="P218" t="n">
         <v>9500</v>
@@ -11064,10 +11064,10 @@
         <v>192</v>
       </c>
       <c r="N240" t="n">
-        <v>17075.989522822</v>
+        <v>17075.989522491</v>
       </c>
       <c r="O240" t="n">
-        <v>3278589.988381824</v>
+        <v>3278589.988318272</v>
       </c>
       <c r="P240" t="n">
         <v>27500</v>
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -11984,19 +11984,19 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="N260" t="n">
         <v>5640</v>
       </c>
       <c r="O260" t="n">
-        <v>1105440</v>
+        <v>992640</v>
       </c>
       <c r="P260" t="n">
         <v>9900</v>
       </c>
       <c r="Q260" t="n">
-        <v>1940400</v>
+        <v>1742400</v>
       </c>
     </row>
     <row r="261">
@@ -12585,10 +12585,10 @@
         <v>1152</v>
       </c>
       <c r="N273" t="n">
-        <v>1516.0387951453</v>
+        <v>1516.0387934921</v>
       </c>
       <c r="O273" t="n">
-        <v>1746476.692007385</v>
+        <v>1746476.690102899</v>
       </c>
       <c r="P273" t="n">
         <v>2300</v>
@@ -13181,10 +13181,10 @@
         <v>1440</v>
       </c>
       <c r="N286" t="n">
-        <v>1690.870009095</v>
+        <v>1690.8700091449</v>
       </c>
       <c r="O286" t="n">
-        <v>2434852.8130968</v>
+        <v>2434852.813168656</v>
       </c>
       <c r="P286" t="n">
         <v>3000</v>
@@ -13406,10 +13406,10 @@
         <v>11416</v>
       </c>
       <c r="N291" t="n">
-        <v>711.33664971986</v>
+        <v>711.3366494881</v>
       </c>
       <c r="O291" t="n">
-        <v>8120619.193201922</v>
+        <v>8120619.190556149</v>
       </c>
       <c r="P291" t="n">
         <v>900</v>
@@ -13735,10 +13735,10 @@
         <v>15732</v>
       </c>
       <c r="N298" t="n">
-        <v>703.79516401441</v>
+        <v>703.79514130448</v>
       </c>
       <c r="O298" t="n">
-        <v>11072105.5202747</v>
+        <v>11072105.16300208</v>
       </c>
       <c r="P298" t="n">
         <v>900</v>
@@ -14736,10 +14736,10 @@
         <v>21</v>
       </c>
       <c r="N319" t="n">
-        <v>3065.5584146341</v>
+        <v>2992.569375</v>
       </c>
       <c r="O319" t="n">
-        <v>64376.7267073161</v>
+        <v>62843.956875</v>
       </c>
       <c r="P319" t="n">
         <v>6000</v>
@@ -15645,10 +15645,10 @@
         <v>499</v>
       </c>
       <c r="N338" t="n">
-        <v>7046.93982792</v>
+        <v>7046.939827883</v>
       </c>
       <c r="O338" t="n">
-        <v>3516422.97413208</v>
+        <v>3516422.974113617</v>
       </c>
       <c r="P338" t="n">
         <v>9900</v>
@@ -16091,13 +16091,13 @@
         </is>
       </c>
       <c r="J348" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M348" t="n">
         <v>264</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -9464,10 +9464,10 @@
         <v>162</v>
       </c>
       <c r="N205" t="n">
-        <v>4956.8186522463</v>
+        <v>4907.8221131448</v>
       </c>
       <c r="O205" t="n">
-        <v>803004.6216639007</v>
+        <v>795067.1823294576</v>
       </c>
       <c r="P205" t="n">
         <v>8200</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -3195,10 +3195,10 @@
         <v>542</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2556363636</v>
+        <v>2582.2556074972</v>
       </c>
       <c r="O67" t="n">
-        <v>1399582.554909071</v>
+        <v>1399582.539263482</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
@@ -3241,10 +3241,10 @@
         <v>1312</v>
       </c>
       <c r="N68" t="n">
-        <v>5216.8960979122</v>
+        <v>5216.8960939752</v>
       </c>
       <c r="O68" t="n">
-        <v>6844567.680460807</v>
+        <v>6844567.675295462</v>
       </c>
       <c r="P68" t="n">
         <v>8500</v>
@@ -3650,10 +3650,10 @@
         <v>346</v>
       </c>
       <c r="N77" t="n">
-        <v>4890.9300489297</v>
+        <v>4890.9300489596</v>
       </c>
       <c r="O77" t="n">
-        <v>1692261.796929676</v>
+        <v>1692261.796940021</v>
       </c>
       <c r="P77" t="n">
         <v>8200</v>
@@ -3878,10 +3878,10 @@
         <v>288</v>
       </c>
       <c r="N82" t="n">
-        <v>3594.2539736347</v>
+        <v>3594.2539698492</v>
       </c>
       <c r="O82" t="n">
-        <v>1035145.144406794</v>
+        <v>1035145.14331657</v>
       </c>
       <c r="P82" t="n">
         <v>6500</v>
@@ -4060,10 +4060,10 @@
         <v>3200</v>
       </c>
       <c r="N86" t="n">
-        <v>616.01871898278</v>
+        <v>616.01871837471</v>
       </c>
       <c r="O86" t="n">
-        <v>1971259.900744896</v>
+        <v>1971259.898799072</v>
       </c>
       <c r="P86" t="n">
         <v>800</v>
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107907508</v>
+        <v>4372.2107910895</v>
       </c>
       <c r="O94" t="n">
-        <v>5928717.832258085</v>
+        <v>5928717.832717362</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -5924,10 +5924,10 @@
         <v>432</v>
       </c>
       <c r="N127" t="n">
-        <v>2029.8738739669</v>
+        <v>2029.8739473684</v>
       </c>
       <c r="O127" t="n">
-        <v>876905.5135537008</v>
+        <v>876905.5452631488</v>
       </c>
       <c r="P127" t="n">
         <v>3600</v>
@@ -6370,10 +6370,10 @@
         <v>36</v>
       </c>
       <c r="N137" t="n">
-        <v>4285.1956570156</v>
+        <v>4285.195701459</v>
       </c>
       <c r="O137" t="n">
-        <v>154267.0436525616</v>
+        <v>154267.045252524</v>
       </c>
       <c r="P137" t="n">
         <v>6900</v>
@@ -7172,22 +7172,22 @@
         <v>0</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>714</v>
       </c>
       <c r="M155" t="n">
-        <v>714</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>1561.0010652921</v>
+        <v>1561.0013915094</v>
       </c>
       <c r="O155" t="n">
-        <v>1114554.76061856</v>
+        <v>0</v>
       </c>
       <c r="P155" t="n">
         <v>2900</v>
       </c>
       <c r="Q155" t="n">
-        <v>2070600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -9464,10 +9464,10 @@
         <v>162</v>
       </c>
       <c r="N205" t="n">
-        <v>4907.8221131448</v>
+        <v>4907.8221561969</v>
       </c>
       <c r="O205" t="n">
-        <v>795067.1823294576</v>
+        <v>795067.1893038979</v>
       </c>
       <c r="P205" t="n">
         <v>8200</v>
@@ -10414,22 +10414,22 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M226" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
         <v>3898</v>
       </c>
       <c r="O226" t="n">
-        <v>561312</v>
+        <v>0</v>
       </c>
       <c r="P226" t="n">
         <v>6900</v>
       </c>
       <c r="Q226" t="n">
-        <v>993600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -12395,22 +12395,22 @@
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M269" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="N269" t="n">
         <v>7253</v>
       </c>
       <c r="O269" t="n">
-        <v>696288</v>
+        <v>0</v>
       </c>
       <c r="P269" t="n">
         <v>11900</v>
       </c>
       <c r="Q269" t="n">
-        <v>1142400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -13181,10 +13181,10 @@
         <v>1440</v>
       </c>
       <c r="N286" t="n">
-        <v>1690.8700091449</v>
+        <v>1690.8700091701</v>
       </c>
       <c r="O286" t="n">
-        <v>2434852.813168656</v>
+        <v>2434852.813204944</v>
       </c>
       <c r="P286" t="n">
         <v>3000</v>
@@ -13735,10 +13735,10 @@
         <v>15732</v>
       </c>
       <c r="N298" t="n">
-        <v>703.79514130448</v>
+        <v>703.79512253205</v>
       </c>
       <c r="O298" t="n">
-        <v>11072105.16300208</v>
+        <v>11072104.86767421</v>
       </c>
       <c r="P298" t="n">
         <v>900</v>
@@ -16241,10 +16241,10 @@
         <v>169</v>
       </c>
       <c r="N351" t="n">
-        <v>1213.6821359223</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O351" t="n">
-        <v>205112.2809708687</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P351" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -3287,10 +3287,10 @@
         <v>2592</v>
       </c>
       <c r="N69" t="n">
-        <v>3158.8608271635</v>
+        <v>3158.8608272041</v>
       </c>
       <c r="O69" t="n">
-        <v>8187767.264007792</v>
+        <v>8187767.264113028</v>
       </c>
       <c r="P69" t="n">
         <v>5600</v>
@@ -3878,10 +3878,10 @@
         <v>288</v>
       </c>
       <c r="N82" t="n">
-        <v>3594.2539622642</v>
+        <v>3594.2539546599</v>
       </c>
       <c r="O82" t="n">
-        <v>1035145.14113209</v>
+        <v>1035145.138942051</v>
       </c>
       <c r="P82" t="n">
         <v>6500</v>
@@ -6498,10 +6498,10 @@
         <v>55</v>
       </c>
       <c r="N140" t="n">
-        <v>30244.600034762</v>
+        <v>30244.600034742</v>
       </c>
       <c r="O140" t="n">
-        <v>1663453.00191191</v>
+        <v>1663453.00191081</v>
       </c>
       <c r="P140" t="n">
         <v>48900</v>
@@ -13597,10 +13597,10 @@
         <v>15732</v>
       </c>
       <c r="N295" t="n">
-        <v>703.79511760843</v>
+        <v>703.79511689575</v>
       </c>
       <c r="O295" t="n">
-        <v>11072104.79021582</v>
+        <v>11072104.77900394</v>
       </c>
       <c r="P295" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q355"/>
+  <dimension ref="A1:Q353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-01</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>376</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.746460274</v>
+        <v>3376.7464583333</v>
       </c>
       <c r="O8" t="n">
-        <v>1269656.669063024</v>
+        <v>1269656.668333321</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1121,10 +1121,10 @@
         <v>36</v>
       </c>
       <c r="N18" t="n">
-        <v>12357.96041958</v>
+        <v>12357.960422535</v>
       </c>
       <c r="O18" t="n">
-        <v>444886.57510488</v>
+        <v>444886.57521126</v>
       </c>
       <c r="P18" t="n">
         <v>15900</v>
@@ -1277,10 +1277,10 @@
         <v>40</v>
       </c>
       <c r="N22" t="n">
-        <v>3716.3301957586</v>
+        <v>3716.3301963993</v>
       </c>
       <c r="O22" t="n">
-        <v>148653.207830344</v>
+        <v>148653.207855972</v>
       </c>
       <c r="P22" t="n">
         <v>9500</v>
@@ -1472,10 +1472,10 @@
         <v>119</v>
       </c>
       <c r="N27" t="n">
-        <v>3910.628089172</v>
+        <v>3910.6280686695</v>
       </c>
       <c r="O27" t="n">
-        <v>465364.742611468</v>
+        <v>465364.7401716705</v>
       </c>
       <c r="P27" t="n">
         <v>9100</v>
@@ -1863,10 +1863,10 @@
         <v>36</v>
       </c>
       <c r="N36" t="n">
-        <v>200072.20066116</v>
+        <v>200072.20075</v>
       </c>
       <c r="O36" t="n">
-        <v>7202599.22380176</v>
+        <v>7202599.227</v>
       </c>
       <c r="P36" t="n">
         <v>312000</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>2156</v>
+        <v>1806</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2843,19 +2843,19 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2156</v>
+        <v>1806</v>
       </c>
       <c r="N59" t="n">
         <v>1726.32</v>
       </c>
       <c r="O59" t="n">
-        <v>3721945.92</v>
+        <v>3117733.92</v>
       </c>
       <c r="P59" t="n">
         <v>1500</v>
       </c>
       <c r="Q59" t="n">
-        <v>3234000</v>
+        <v>2709000</v>
       </c>
     </row>
     <row r="60">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>542</v>
+        <v>350</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3192,19 +3192,19 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>542</v>
+        <v>350</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2555674232</v>
+        <v>2582.2555555556</v>
       </c>
       <c r="O67" t="n">
-        <v>1399582.517543374</v>
+        <v>903789.44444446</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
       </c>
       <c r="Q67" t="n">
-        <v>2439000</v>
+        <v>1575000</v>
       </c>
     </row>
     <row r="68">
@@ -3241,10 +3241,10 @@
         <v>1312</v>
       </c>
       <c r="N68" t="n">
-        <v>5216.8960872076</v>
+        <v>5216.89608155</v>
       </c>
       <c r="O68" t="n">
-        <v>6844567.666416372</v>
+        <v>6844567.658993601</v>
       </c>
       <c r="P68" t="n">
         <v>8500</v>
@@ -3287,10 +3287,10 @@
         <v>2592</v>
       </c>
       <c r="N69" t="n">
-        <v>3158.8608272041</v>
+        <v>3158.8608285041</v>
       </c>
       <c r="O69" t="n">
-        <v>8187767.264113028</v>
+        <v>8187767.267482627</v>
       </c>
       <c r="P69" t="n">
         <v>5600</v>
@@ -3471,10 +3471,10 @@
         <v>648</v>
       </c>
       <c r="N73" t="n">
-        <v>3795.7100075657</v>
+        <v>3795.7100075672</v>
       </c>
       <c r="O73" t="n">
-        <v>2459620.084902573</v>
+        <v>2459620.084903546</v>
       </c>
       <c r="P73" t="n">
         <v>6200</v>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3875,19 +3875,19 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="N82" t="n">
-        <v>3594.2539546599</v>
+        <v>3594.2538892425</v>
       </c>
       <c r="O82" t="n">
-        <v>1035145.138942051</v>
+        <v>862620.9334182</v>
       </c>
       <c r="P82" t="n">
         <v>6500</v>
       </c>
       <c r="Q82" t="n">
-        <v>1872000</v>
+        <v>1560000</v>
       </c>
     </row>
     <row r="83">
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107910895</v>
+        <v>4372.2107914851</v>
       </c>
       <c r="O94" t="n">
-        <v>5928717.832717362</v>
+        <v>5928717.833253796</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -5750,10 +5750,10 @@
         <v>480</v>
       </c>
       <c r="N123" t="n">
-        <v>4196.8725298197</v>
+        <v>4196.8725305216</v>
       </c>
       <c r="O123" t="n">
-        <v>2014498.814313456</v>
+        <v>2014498.814650368</v>
       </c>
       <c r="P123" t="n">
         <v>5900</v>
@@ -5924,10 +5924,10 @@
         <v>432</v>
       </c>
       <c r="N127" t="n">
-        <v>2029.8739473684</v>
+        <v>2029.8739515279</v>
       </c>
       <c r="O127" t="n">
-        <v>876905.5452631488</v>
+        <v>876905.5470600529</v>
       </c>
       <c r="P127" t="n">
         <v>3600</v>
@@ -5965,10 +5965,10 @@
         <v>528</v>
       </c>
       <c r="N128" t="n">
-        <v>22485.695571956</v>
+        <v>22485.695561036</v>
       </c>
       <c r="O128" t="n">
-        <v>11872447.26199277</v>
+        <v>11872447.25622701</v>
       </c>
       <c r="P128" t="n">
         <v>36500</v>
@@ -6370,10 +6370,10 @@
         <v>36</v>
       </c>
       <c r="N137" t="n">
-        <v>4285.1957207207</v>
+        <v>4285.195740113</v>
       </c>
       <c r="O137" t="n">
-        <v>154267.0459459452</v>
+        <v>154267.046644068</v>
       </c>
       <c r="P137" t="n">
         <v>6900</v>
@@ -9387,12 +9387,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>C4498</t>
+          <t>C4499</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>RELOJ PROYECTOR STD C4498</t>
+          <t>PIANO ELEFANTE PQÑ C4499</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>162</v>
+        <v>252</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -9415,30 +9415,30 @@
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>162</v>
+        <v>252</v>
       </c>
       <c r="N204" t="n">
-        <v>4907.8221561969</v>
+        <v>6414</v>
       </c>
       <c r="O204" t="n">
-        <v>795067.1893038979</v>
+        <v>1616328</v>
       </c>
       <c r="P204" t="n">
-        <v>8200</v>
+        <v>10900</v>
       </c>
       <c r="Q204" t="n">
-        <v>1328400</v>
+        <v>2746800</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>C4499</t>
+          <t>C4504</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PIANO ELEFANTE PQÑ C4499</t>
+          <t>CASTILLO ACCESORIOS STD C4504</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>252</v>
+        <v>12</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -9461,30 +9461,30 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>252</v>
+        <v>12</v>
       </c>
       <c r="N205" t="n">
-        <v>6414</v>
+        <v>23376.36</v>
       </c>
       <c r="O205" t="n">
-        <v>1616328</v>
+        <v>280516.32</v>
       </c>
       <c r="P205" t="n">
-        <v>10900</v>
+        <v>40900</v>
       </c>
       <c r="Q205" t="n">
-        <v>2746800</v>
+        <v>490800</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>C4504</t>
+          <t>C4505</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>CASTILLO ACCESORIOS STD C4504</t>
+          <t>PESCADITO Y TIBURON  LUZ Y SONIDO C4505</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>12</v>
+        <v>502</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -9507,30 +9507,30 @@
         <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>12</v>
+        <v>502</v>
       </c>
       <c r="N206" t="n">
-        <v>23376.36</v>
+        <v>13210</v>
       </c>
       <c r="O206" t="n">
-        <v>280516.32</v>
+        <v>6631420</v>
       </c>
       <c r="P206" t="n">
-        <v>40900</v>
+        <v>23900</v>
       </c>
       <c r="Q206" t="n">
-        <v>490800</v>
+        <v>11997800</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>C4505</t>
+          <t>C4510</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PESCADITO Y TIBURON  LUZ Y SONIDO C4505</t>
+          <t>TOCADOR CASTILLO MUSICA Y LUZ C4510</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>502</v>
+        <v>144</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -9553,30 +9553,30 @@
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>502</v>
+        <v>144</v>
       </c>
       <c r="N207" t="n">
-        <v>13210</v>
+        <v>52443</v>
       </c>
       <c r="O207" t="n">
-        <v>6631420</v>
+        <v>7551792</v>
       </c>
       <c r="P207" t="n">
-        <v>23900</v>
+        <v>83900</v>
       </c>
       <c r="Q207" t="n">
-        <v>11997800</v>
+        <v>12081600</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>C4510</t>
+          <t>C4511</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>TOCADOR CASTILLO MUSICA Y LUZ C4510</t>
+          <t>BURBUJERO MODELOS STDS C4511</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>144</v>
+        <v>280</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -9599,35 +9599,30 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>144</v>
+        <v>280</v>
       </c>
       <c r="N208" t="n">
-        <v>52443</v>
+        <v>3903.736877898</v>
       </c>
       <c r="O208" t="n">
-        <v>7551792</v>
+        <v>1093046.32581144</v>
       </c>
       <c r="P208" t="n">
-        <v>83900</v>
+        <v>7500</v>
       </c>
       <c r="Q208" t="n">
-        <v>12081600</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>C4511</t>
+          <t>C4512</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BURBUJERO MODELOS STDS C4511</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MAQUILLAJE ESTUCHE UNICORNIO C4512</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -9636,7 +9631,7 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -9645,30 +9640,30 @@
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="N209" t="n">
-        <v>3903.7367356322</v>
+        <v>20726</v>
       </c>
       <c r="O209" t="n">
-        <v>1093046.285977016</v>
+        <v>829040</v>
       </c>
       <c r="P209" t="n">
-        <v>7500</v>
+        <v>33900</v>
       </c>
       <c r="Q209" t="n">
-        <v>2100000</v>
+        <v>1356000</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>C4512</t>
+          <t>C4513</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>MAQUILLAJE ESTUCHE UNICORNIO C4512</t>
+          <t>ESTUCHE MAQUILLAJE UNICORNIO CON BALACA C4513</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -9677,7 +9672,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -9686,30 +9681,35 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="N210" t="n">
-        <v>20726</v>
+        <v>35864.602142857</v>
       </c>
       <c r="O210" t="n">
-        <v>829040</v>
+        <v>1829094.709285707</v>
       </c>
       <c r="P210" t="n">
-        <v>33900</v>
+        <v>62900</v>
       </c>
       <c r="Q210" t="n">
-        <v>1356000</v>
+        <v>3207900</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>C4513</t>
+          <t>C4514</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ESTUCHE MAQUILLAJE UNICORNIO CON BALACA C4513</t>
+          <t>ESTUCHE MAQUILLAJE PARA UÑAS C4514</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -9718,7 +9718,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9727,30 +9727,30 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N211" t="n">
-        <v>35864.602142857</v>
+        <v>20731</v>
       </c>
       <c r="O211" t="n">
-        <v>1829094.709285707</v>
+        <v>953626</v>
       </c>
       <c r="P211" t="n">
-        <v>62900</v>
+        <v>33900</v>
       </c>
       <c r="Q211" t="n">
-        <v>3207900</v>
+        <v>1559400</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>C4514</t>
+          <t>C4521</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ESTUCHE MAQUILLAJE PARA UÑAS C4514</t>
+          <t>JUEGO DE AJEDREZ 3EN1</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -9773,30 +9773,30 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="N212" t="n">
-        <v>20731</v>
+        <v>4202</v>
       </c>
       <c r="O212" t="n">
-        <v>953626</v>
+        <v>495836</v>
       </c>
       <c r="P212" t="n">
-        <v>33900</v>
+        <v>7900</v>
       </c>
       <c r="Q212" t="n">
-        <v>1559400</v>
+        <v>932200</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>C4521</t>
+          <t>C4523</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>JUEGO DE AJEDREZ 3EN1</t>
+          <t>PIANO TAPETE MUSICAL C4523</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -9819,30 +9819,30 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="N213" t="n">
-        <v>4202</v>
+        <v>16469</v>
       </c>
       <c r="O213" t="n">
-        <v>495836</v>
+        <v>2371536</v>
       </c>
       <c r="P213" t="n">
-        <v>7900</v>
+        <v>26900</v>
       </c>
       <c r="Q213" t="n">
-        <v>932200</v>
+        <v>3873600</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>C4523</t>
+          <t>C4525</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>PIANO TAPETE MUSICAL C4523</t>
+          <t>LANZADORA CATAPULTA C4525</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -9865,30 +9865,30 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="N214" t="n">
-        <v>16469</v>
+        <v>11922</v>
       </c>
       <c r="O214" t="n">
-        <v>2371536</v>
+        <v>214596</v>
       </c>
       <c r="P214" t="n">
-        <v>26900</v>
+        <v>19900</v>
       </c>
       <c r="Q214" t="n">
-        <v>3873600</v>
+        <v>358200</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>C4525</t>
+          <t>C4527</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>LANZADORA CATAPULTA C4525</t>
+          <t>MINI PIANO C4527</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -9911,30 +9911,30 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="N215" t="n">
-        <v>11922</v>
+        <v>12556</v>
       </c>
       <c r="O215" t="n">
-        <v>214596</v>
+        <v>1356048</v>
       </c>
       <c r="P215" t="n">
-        <v>19900</v>
+        <v>21900</v>
       </c>
       <c r="Q215" t="n">
-        <v>358200</v>
+        <v>2365200</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>C4527</t>
+          <t>C4530</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>MINI PIANO C4527</t>
+          <t>CARRO FORMULAY DINO BURBUJERA C4530</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -9948,7 +9948,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9957,30 +9957,30 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="N216" t="n">
-        <v>12556</v>
+        <v>5869.1726051282</v>
       </c>
       <c r="O216" t="n">
-        <v>1356048</v>
+        <v>845160.8551384609</v>
       </c>
       <c r="P216" t="n">
-        <v>21900</v>
+        <v>9500</v>
       </c>
       <c r="Q216" t="n">
-        <v>2365200</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>C4530</t>
+          <t>C4531</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>CARRO FORMULAY DINO BURBUJERA C4530</t>
+          <t>CARROS RETRO/GRUA STD BOLSA PVC C4531</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -9994,7 +9994,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>144</v>
+        <v>443</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -10003,30 +10003,30 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>144</v>
+        <v>443</v>
       </c>
       <c r="N217" t="n">
-        <v>5869.1726127049</v>
+        <v>6849.2</v>
       </c>
       <c r="O217" t="n">
-        <v>845160.8562295055</v>
+        <v>3034195.6</v>
       </c>
       <c r="P217" t="n">
-        <v>9500</v>
+        <v>11500</v>
       </c>
       <c r="Q217" t="n">
-        <v>1368000</v>
+        <v>5094500</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>C4531</t>
+          <t>C4534</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>CARROS RETRO/GRUA STD BOLSA PVC C4531</t>
+          <t>CARROS RETROS STD CAJA X 12 C4534</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10040,7 +10040,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>443</v>
+        <v>792</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -10049,30 +10049,30 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>443</v>
+        <v>792</v>
       </c>
       <c r="N218" t="n">
-        <v>6849.2</v>
+        <v>5772</v>
       </c>
       <c r="O218" t="n">
-        <v>3034195.6</v>
+        <v>4571424</v>
       </c>
       <c r="P218" t="n">
-        <v>11500</v>
+        <v>9900</v>
       </c>
       <c r="Q218" t="n">
-        <v>5094500</v>
+        <v>7840800</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>C4534</t>
+          <t>C4541</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CARROS RETROS STD CAJA X 12 C4534</t>
+          <t>LANZADORADARDOS MED C4541</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>792</v>
+        <v>456</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -10095,30 +10095,30 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>792</v>
+        <v>456</v>
       </c>
       <c r="N219" t="n">
-        <v>5772</v>
+        <v>6645</v>
       </c>
       <c r="O219" t="n">
-        <v>4571424</v>
+        <v>3030120</v>
       </c>
       <c r="P219" t="n">
-        <v>9900</v>
+        <v>10900</v>
       </c>
       <c r="Q219" t="n">
-        <v>7840800</v>
+        <v>4970400</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>C4541</t>
+          <t>C4542</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>LANZADORADARDOS MED C4541</t>
+          <t>LANZDORA DE DARDOS Y BIOGEL C4542</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>456</v>
+        <v>256</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -10141,30 +10141,30 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>456</v>
+        <v>256</v>
       </c>
       <c r="N220" t="n">
-        <v>6645</v>
+        <v>13098</v>
       </c>
       <c r="O220" t="n">
-        <v>3030120</v>
+        <v>3353088</v>
       </c>
       <c r="P220" t="n">
-        <v>10900</v>
+        <v>21200</v>
       </c>
       <c r="Q220" t="n">
-        <v>4970400</v>
+        <v>5427200</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>C4542</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>LANZDORA DE DARDOS Y BIOGEL C4542</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -10187,30 +10187,30 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="N221" t="n">
-        <v>13098</v>
+        <v>27186</v>
       </c>
       <c r="O221" t="n">
-        <v>3353088</v>
+        <v>3588552</v>
       </c>
       <c r="P221" t="n">
-        <v>21200</v>
+        <v>43900</v>
       </c>
       <c r="Q221" t="n">
-        <v>5427200</v>
+        <v>5794800</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4547</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>CASA VILLA ACCESORIOS C4547</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -10224,7 +10224,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -10233,30 +10233,30 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="N222" t="n">
-        <v>27186</v>
+        <v>72535</v>
       </c>
       <c r="O222" t="n">
-        <v>3588552</v>
+        <v>6092940</v>
       </c>
       <c r="P222" t="n">
-        <v>43900</v>
+        <v>116900</v>
       </c>
       <c r="Q222" t="n">
-        <v>5794800</v>
+        <v>9819600</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>C4547</t>
+          <t>C4548</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>CASA VILLA ACCESORIOS C4547</t>
+          <t>CARRO DIDACTICO X4 BEBE</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -10279,30 +10279,30 @@
         <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="N223" t="n">
-        <v>72535</v>
+        <v>7562</v>
       </c>
       <c r="O223" t="n">
-        <v>6092940</v>
+        <v>1156986</v>
       </c>
       <c r="P223" t="n">
-        <v>116900</v>
+        <v>12900</v>
       </c>
       <c r="Q223" t="n">
-        <v>9819600</v>
+        <v>1973700</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>C4548</t>
+          <t>C4550</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>CARRO DIDACTICO X4 BEBE</t>
+          <t>HELICOPTERO  FASHION C4550</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -10316,7 +10316,7 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -10325,30 +10325,30 @@
         <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="N224" t="n">
-        <v>7562</v>
+        <v>13565</v>
       </c>
       <c r="O224" t="n">
-        <v>1156986</v>
+        <v>3323425</v>
       </c>
       <c r="P224" t="n">
-        <v>12900</v>
+        <v>22500</v>
       </c>
       <c r="Q224" t="n">
-        <v>1973700</v>
+        <v>5512500</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>C4550</t>
+          <t>C4551</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>HELICOPTERO  FASHION C4550</t>
+          <t>PRINCESS EN CASTILLO Y CARRUAJE C4551</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -10362,7 +10362,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>245</v>
+        <v>1162</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -10371,30 +10371,30 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>245</v>
+        <v>1162</v>
       </c>
       <c r="N225" t="n">
-        <v>13565</v>
+        <v>7635</v>
       </c>
       <c r="O225" t="n">
-        <v>3323425</v>
+        <v>8871870</v>
       </c>
       <c r="P225" t="n">
-        <v>22500</v>
+        <v>13900</v>
       </c>
       <c r="Q225" t="n">
-        <v>5512500</v>
+        <v>16151800</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>C4551</t>
+          <t>C4552</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>PRINCESS EN CASTILLO Y CARRUAJE C4551</t>
+          <t>CARRO LAMBO RECARGABLE C4552</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>1162</v>
+        <v>55</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -10417,30 +10417,30 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>1162</v>
+        <v>55</v>
       </c>
       <c r="N226" t="n">
-        <v>7635</v>
+        <v>24480</v>
       </c>
       <c r="O226" t="n">
-        <v>8871870</v>
+        <v>1346400</v>
       </c>
       <c r="P226" t="n">
-        <v>13900</v>
+        <v>39900</v>
       </c>
       <c r="Q226" t="n">
-        <v>16151800</v>
+        <v>2194500</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>C4552</t>
+          <t>C4555</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CARRO LAMBO RECARGABLE C4552</t>
+          <t>SONAJERO EN BOLSA 5 PCS C4555</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -10454,7 +10454,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>55</v>
+        <v>336</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -10463,30 +10463,30 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>55</v>
+        <v>336</v>
       </c>
       <c r="N227" t="n">
-        <v>24480</v>
+        <v>5438</v>
       </c>
       <c r="O227" t="n">
-        <v>1346400</v>
+        <v>1827168</v>
       </c>
       <c r="P227" t="n">
-        <v>39900</v>
+        <v>8900</v>
       </c>
       <c r="Q227" t="n">
-        <v>2194500</v>
+        <v>2990400</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>C4553</t>
+          <t>C4556</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>BOLSA CHILLONES X 12 PCS</t>
+          <t>SONAJERO EN CAJA 8PCS C4556</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -10509,30 +10509,30 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="N228" t="n">
-        <v>5682</v>
+        <v>16086</v>
       </c>
       <c r="O228" t="n">
-        <v>750024</v>
+        <v>772128</v>
       </c>
       <c r="P228" t="n">
-        <v>9900</v>
+        <v>25900</v>
       </c>
       <c r="Q228" t="n">
-        <v>1306800</v>
+        <v>1243200</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>C4555</t>
+          <t>C4557</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>SONAJERO EN BOLSA 5 PCS C4555</t>
+          <t>JUEGO DE UÑAS Y MAQUILLAJE C4557</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -10546,7 +10546,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>336</v>
+        <v>560</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10555,30 +10555,30 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>336</v>
+        <v>560</v>
       </c>
       <c r="N229" t="n">
-        <v>5438</v>
+        <v>8806</v>
       </c>
       <c r="O229" t="n">
-        <v>1827168</v>
+        <v>4931360</v>
       </c>
       <c r="P229" t="n">
-        <v>8900</v>
+        <v>14900</v>
       </c>
       <c r="Q229" t="n">
-        <v>2990400</v>
+        <v>8344000</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>C4556</t>
+          <t>C4559</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 8PCS C4556</t>
+          <t>PIANO DIDACTICO 3en1 C4559</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -10601,30 +10601,30 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="N230" t="n">
-        <v>16086</v>
+        <v>19008</v>
       </c>
       <c r="O230" t="n">
-        <v>772128</v>
+        <v>3421440</v>
       </c>
       <c r="P230" t="n">
-        <v>25900</v>
+        <v>30900</v>
       </c>
       <c r="Q230" t="n">
-        <v>1243200</v>
+        <v>5562000</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C4557</t>
+          <t>C4560</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>JUEGO DE UÑAS Y MAQUILLAJE C4557</t>
+          <t>PIANO TAPETE C4560</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10647,30 +10647,30 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="N231" t="n">
-        <v>8806</v>
+        <v>11302</v>
       </c>
       <c r="O231" t="n">
-        <v>4931360</v>
+        <v>5198920</v>
       </c>
       <c r="P231" t="n">
-        <v>14900</v>
+        <v>18900</v>
       </c>
       <c r="Q231" t="n">
-        <v>8344000</v>
+        <v>8694000</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>C4559</t>
+          <t>C4561</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>PIANO DIDACTICO 3en1 C4559</t>
+          <t>ABECEDARIO INGLES MUSICAL C4561</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -10696,27 +10696,27 @@
         <v>180</v>
       </c>
       <c r="N232" t="n">
-        <v>19008</v>
+        <v>17992</v>
       </c>
       <c r="O232" t="n">
-        <v>3421440</v>
+        <v>3238560</v>
       </c>
       <c r="P232" t="n">
-        <v>30900</v>
+        <v>28900</v>
       </c>
       <c r="Q232" t="n">
-        <v>5562000</v>
+        <v>5202000</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>C4560</t>
+          <t>C4562</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>PIANO TAPETE C4560</t>
+          <t>LIBRO INGLES Y ESPAÑOL C4562</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>460</v>
+        <v>32</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -10739,30 +10739,30 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>460</v>
+        <v>32</v>
       </c>
       <c r="N233" t="n">
-        <v>11302</v>
+        <v>12211</v>
       </c>
       <c r="O233" t="n">
-        <v>5198920</v>
+        <v>390752</v>
       </c>
       <c r="P233" t="n">
-        <v>18900</v>
+        <v>19900</v>
       </c>
       <c r="Q233" t="n">
-        <v>8694000</v>
+        <v>636800</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>C4561</t>
+          <t>C4563</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ABECEDARIO INGLES MUSICAL C4561</t>
+          <t>LIBRO MUSICAL ESPAÑOL 4563</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -10776,7 +10776,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -10785,30 +10785,30 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="N234" t="n">
-        <v>17992</v>
+        <v>15461</v>
       </c>
       <c r="O234" t="n">
-        <v>3238560</v>
+        <v>927660</v>
       </c>
       <c r="P234" t="n">
-        <v>28900</v>
+        <v>24900</v>
       </c>
       <c r="Q234" t="n">
-        <v>5202000</v>
+        <v>1494000</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>C4562</t>
+          <t>C4566</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>LIBRO INGLES Y ESPAÑOL C4562</t>
+          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>32</v>
+        <v>290</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -10831,30 +10831,30 @@
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>32</v>
+        <v>290</v>
       </c>
       <c r="N235" t="n">
-        <v>12211</v>
+        <v>11348</v>
       </c>
       <c r="O235" t="n">
-        <v>390752</v>
+        <v>3290920</v>
       </c>
       <c r="P235" t="n">
         <v>19900</v>
       </c>
       <c r="Q235" t="n">
-        <v>636800</v>
+        <v>5771000</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>C4563</t>
+          <t>C4567</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>LIBRO MUSICAL ESPAÑOL 4563</t>
+          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -10877,30 +10877,30 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="N236" t="n">
-        <v>15461</v>
+        <v>17075.989522491</v>
       </c>
       <c r="O236" t="n">
-        <v>927660</v>
+        <v>3278589.988318272</v>
       </c>
       <c r="P236" t="n">
-        <v>24900</v>
+        <v>27500</v>
       </c>
       <c r="Q236" t="n">
-        <v>1494000</v>
+        <v>5280000</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>C4566</t>
+          <t>C4570</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
+          <t>CUBO MAGICO C4570 EQY766</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -10914,7 +10914,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -10923,30 +10923,30 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="N237" t="n">
-        <v>11348</v>
+        <v>10398</v>
       </c>
       <c r="O237" t="n">
-        <v>3290920</v>
+        <v>623880</v>
       </c>
       <c r="P237" t="n">
-        <v>19900</v>
+        <v>16900</v>
       </c>
       <c r="Q237" t="n">
-        <v>5771000</v>
+        <v>1014000</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C4567</t>
+          <t>C4572</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
+          <t>CUBO MAGICO C4572 EQY10130</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -10969,30 +10969,30 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="N238" t="n">
-        <v>17075.989522491</v>
+        <v>4518</v>
       </c>
       <c r="O238" t="n">
-        <v>3278589.988318272</v>
+        <v>487944</v>
       </c>
       <c r="P238" t="n">
-        <v>27500</v>
+        <v>7900</v>
       </c>
       <c r="Q238" t="n">
-        <v>5280000</v>
+        <v>853200</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C4570</t>
+          <t>C4577</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4570 EQY766</t>
+          <t>PISTA DINOSAURIO C4577</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -11006,7 +11006,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -11015,30 +11015,30 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="N239" t="n">
-        <v>10398</v>
+        <v>21346</v>
       </c>
       <c r="O239" t="n">
-        <v>623880</v>
+        <v>1430182</v>
       </c>
       <c r="P239" t="n">
-        <v>16900</v>
+        <v>34900</v>
       </c>
       <c r="Q239" t="n">
-        <v>1014000</v>
+        <v>2338300</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C4572</t>
+          <t>C4578</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4572 EQY10130</t>
+          <t>LANZADORA DE AGUA BOLSA PVC C4578</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -11061,30 +11061,30 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="N240" t="n">
-        <v>4518</v>
+        <v>18001</v>
       </c>
       <c r="O240" t="n">
-        <v>487944</v>
+        <v>1512084</v>
       </c>
       <c r="P240" t="n">
-        <v>7900</v>
+        <v>28900</v>
       </c>
       <c r="Q240" t="n">
-        <v>853200</v>
+        <v>2427600</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C4577</t>
+          <t>C4579</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>PISTA DINOSAURIO C4577</t>
+          <t>LANZADORA DE AGUA C4579</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -11098,7 +11098,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -11107,30 +11107,33 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N241" t="n">
-        <v>21346</v>
+        <v>10219</v>
       </c>
       <c r="O241" t="n">
-        <v>1430182</v>
+        <v>694892</v>
       </c>
       <c r="P241" t="n">
-        <v>34900</v>
+        <v>16900</v>
       </c>
       <c r="Q241" t="n">
-        <v>2338300</v>
+        <v>1149200</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C4578</t>
-        </is>
+          <t>C458</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>6920190230459</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA BOLSA PVC C4578</t>
+          <t>BURRO SENCILLO SONIDO</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -11140,11 +11143,11 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J242" t="n">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -11153,30 +11156,30 @@
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="N242" t="n">
-        <v>18001</v>
+        <v>10755</v>
       </c>
       <c r="O242" t="n">
-        <v>1512084</v>
+        <v>4517100</v>
       </c>
       <c r="P242" t="n">
-        <v>28900</v>
+        <v>17900</v>
       </c>
       <c r="Q242" t="n">
-        <v>2427600</v>
+        <v>7518000</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C4579</t>
+          <t>C4581</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA C4579</t>
+          <t>ESPADA BURBUJERA C4581</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -11190,7 +11193,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -11199,33 +11202,30 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="N243" t="n">
-        <v>10219</v>
+        <v>17168</v>
       </c>
       <c r="O243" t="n">
-        <v>694892</v>
+        <v>1819808</v>
       </c>
       <c r="P243" t="n">
-        <v>16900</v>
+        <v>27900</v>
       </c>
       <c r="Q243" t="n">
-        <v>1149200</v>
+        <v>2957400</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C458</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>6920190230459</v>
+          <t>C4582</t>
+        </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>BURRO SENCILLO SONIDO</t>
+          <t>MUÑECA CHICHI SONIDOS C4582</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -11235,11 +11235,11 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J244" t="n">
-        <v>420</v>
+        <v>32</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -11248,30 +11248,30 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>420</v>
+        <v>32</v>
       </c>
       <c r="N244" t="n">
-        <v>10755</v>
+        <v>20014</v>
       </c>
       <c r="O244" t="n">
-        <v>4517100</v>
+        <v>640448</v>
       </c>
       <c r="P244" t="n">
-        <v>17900</v>
+        <v>33900</v>
       </c>
       <c r="Q244" t="n">
-        <v>7518000</v>
+        <v>1084800</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C4581</t>
+          <t>C4584</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ESPADA BURBUJERA C4581</t>
+          <t>LANZADORA DARDOS C4584</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -11285,7 +11285,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -11294,30 +11294,30 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="N245" t="n">
-        <v>17168</v>
+        <v>27254</v>
       </c>
       <c r="O245" t="n">
-        <v>1819808</v>
+        <v>3597528</v>
       </c>
       <c r="P245" t="n">
-        <v>27900</v>
+        <v>43900</v>
       </c>
       <c r="Q245" t="n">
-        <v>2957400</v>
+        <v>5794800</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>C4582</t>
+          <t>C4586</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>MUÑECA CHICHI SONIDOS C4582</t>
+          <t>DINOSAURIO CONTROL REMOTO HUMO C4586</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -11331,7 +11331,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -11340,30 +11340,30 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="N246" t="n">
-        <v>20014</v>
+        <v>52755</v>
       </c>
       <c r="O246" t="n">
-        <v>640448</v>
+        <v>158265</v>
       </c>
       <c r="P246" t="n">
-        <v>33900</v>
+        <v>85900</v>
       </c>
       <c r="Q246" t="n">
-        <v>1084800</v>
+        <v>257700</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C4584</t>
+          <t>C4593</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS C4584</t>
+          <t>MOTO RECARGABLE C4593</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -11386,30 +11386,30 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="N247" t="n">
-        <v>27254</v>
+        <v>35909</v>
       </c>
       <c r="O247" t="n">
-        <v>3597528</v>
+        <v>502726</v>
       </c>
       <c r="P247" t="n">
-        <v>43900</v>
+        <v>57900</v>
       </c>
       <c r="Q247" t="n">
-        <v>5794800</v>
+        <v>810600</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C4586</t>
+          <t>C4595</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DINOSAURIO CONTROL REMOTO HUMO C4586</t>
+          <t>telefono con camara 2,4 c4595</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -11423,7 +11423,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -11432,30 +11432,30 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="N248" t="n">
-        <v>52755</v>
+        <v>40073</v>
       </c>
       <c r="O248" t="n">
-        <v>158265</v>
+        <v>2404380</v>
       </c>
       <c r="P248" t="n">
-        <v>85900</v>
+        <v>64900</v>
       </c>
       <c r="Q248" t="n">
-        <v>257700</v>
+        <v>3894000</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C4593</t>
+          <t>C4596</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>MOTO RECARGABLE C4593</t>
+          <t>JUEGO ANTIESTRES C4596</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -11469,7 +11469,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -11478,30 +11478,30 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="N249" t="n">
-        <v>35909</v>
+        <v>4303</v>
       </c>
       <c r="O249" t="n">
-        <v>502726</v>
+        <v>464724</v>
       </c>
       <c r="P249" t="n">
-        <v>57900</v>
+        <v>7900</v>
       </c>
       <c r="Q249" t="n">
-        <v>810600</v>
+        <v>853200</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C4595</t>
+          <t>C4599</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>telefono con camara 2,4 c4595</t>
+          <t>VARA HELICE DINOSAURIO C4599</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>60</v>
+        <v>720</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -11524,30 +11524,30 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>60</v>
+        <v>720</v>
       </c>
       <c r="N250" t="n">
-        <v>40073</v>
+        <v>5588</v>
       </c>
       <c r="O250" t="n">
-        <v>2404380</v>
+        <v>4023360</v>
       </c>
       <c r="P250" t="n">
-        <v>64900</v>
+        <v>9500</v>
       </c>
       <c r="Q250" t="n">
-        <v>3894000</v>
+        <v>6840000</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>C4596</t>
+          <t>C4600</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>JUEGO ANTIESTRES C4596</t>
+          <t>SET PERRITO PATROL BUS C4600</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -11570,30 +11570,30 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="N251" t="n">
-        <v>4303</v>
+        <v>16282</v>
       </c>
       <c r="O251" t="n">
-        <v>464724</v>
+        <v>732690</v>
       </c>
       <c r="P251" t="n">
-        <v>7900</v>
+        <v>27900</v>
       </c>
       <c r="Q251" t="n">
-        <v>853200</v>
+        <v>1255500</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C4599</t>
+          <t>C4601</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>VARA HELICE DINOSAURIO C4599</t>
+          <t>SET PERRO PATROL C4601</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>720</v>
+        <v>78</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11616,30 +11616,30 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>720</v>
+        <v>78</v>
       </c>
       <c r="N252" t="n">
-        <v>5588</v>
+        <v>14050</v>
       </c>
       <c r="O252" t="n">
-        <v>4023360</v>
+        <v>1095900</v>
       </c>
       <c r="P252" t="n">
-        <v>9500</v>
+        <v>23900</v>
       </c>
       <c r="Q252" t="n">
-        <v>6840000</v>
+        <v>1864200</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C4600</t>
+          <t>C4602</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>SET PERRITO PATROL BUS C4600</t>
+          <t>AVION CON PISTA MODELOS STD C4602</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>45</v>
+        <v>285</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11662,30 +11662,30 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>45</v>
+        <v>285</v>
       </c>
       <c r="N253" t="n">
-        <v>16282</v>
+        <v>8700</v>
       </c>
       <c r="O253" t="n">
-        <v>732690</v>
+        <v>2479500</v>
       </c>
       <c r="P253" t="n">
-        <v>27900</v>
+        <v>14900</v>
       </c>
       <c r="Q253" t="n">
-        <v>1255500</v>
+        <v>4246500</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C4601</t>
+          <t>C4603</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>SET PERRO PATROL C4601</t>
+          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>78</v>
+        <v>385</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -11708,30 +11708,30 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>78</v>
+        <v>385</v>
       </c>
       <c r="N254" t="n">
-        <v>14050</v>
+        <v>3639.35</v>
       </c>
       <c r="O254" t="n">
-        <v>1095900</v>
+        <v>1401149.75</v>
       </c>
       <c r="P254" t="n">
-        <v>23900</v>
+        <v>7500</v>
       </c>
       <c r="Q254" t="n">
-        <v>1864200</v>
+        <v>2887500</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C4602</t>
+          <t>C4604</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>AVION CON PISTA MODELOS STD C4602</t>
+          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>285</v>
+        <v>1709</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11754,30 +11754,30 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>285</v>
+        <v>1709</v>
       </c>
       <c r="N255" t="n">
-        <v>8700</v>
+        <v>1326</v>
       </c>
       <c r="O255" t="n">
-        <v>2479500</v>
+        <v>2266134</v>
       </c>
       <c r="P255" t="n">
-        <v>14900</v>
+        <v>2500</v>
       </c>
       <c r="Q255" t="n">
-        <v>4246500</v>
+        <v>4272500</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C4603</t>
+          <t>C4605</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
+          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11791,7 +11791,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>385</v>
+        <v>176</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11800,30 +11800,30 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>385</v>
+        <v>176</v>
       </c>
       <c r="N256" t="n">
-        <v>3639.35</v>
+        <v>5640</v>
       </c>
       <c r="O256" t="n">
-        <v>1401149.75</v>
+        <v>992640</v>
       </c>
       <c r="P256" t="n">
-        <v>7500</v>
+        <v>9900</v>
       </c>
       <c r="Q256" t="n">
-        <v>2887500</v>
+        <v>1742400</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C4604</t>
+          <t>C4606</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
+          <t>SONAJERO EN CAJA 6PCS C4606</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>1709</v>
+        <v>279</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -11846,30 +11846,30 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>1709</v>
+        <v>279</v>
       </c>
       <c r="N257" t="n">
-        <v>1326</v>
+        <v>10713.21</v>
       </c>
       <c r="O257" t="n">
-        <v>2266134</v>
+        <v>2988985.59</v>
       </c>
       <c r="P257" t="n">
-        <v>2500</v>
+        <v>20900</v>
       </c>
       <c r="Q257" t="n">
-        <v>4272500</v>
+        <v>5831100</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C4605</t>
+          <t>C4607</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
+          <t>MAQUILLAJE SIRENA C4607</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -11883,7 +11883,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -11892,30 +11892,30 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="N258" t="n">
-        <v>5640</v>
+        <v>10817</v>
       </c>
       <c r="O258" t="n">
-        <v>992640</v>
+        <v>2260753</v>
       </c>
       <c r="P258" t="n">
-        <v>9900</v>
+        <v>17900</v>
       </c>
       <c r="Q258" t="n">
-        <v>1742400</v>
+        <v>3741100</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C4606</t>
+          <t>C4609</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 6PCS C4606</t>
+          <t>MAQUILLAJE UNICORNIO C4609</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>279</v>
+        <v>117</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11938,30 +11938,30 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>279</v>
+        <v>117</v>
       </c>
       <c r="N259" t="n">
-        <v>10713.21</v>
+        <v>12489</v>
       </c>
       <c r="O259" t="n">
-        <v>2988985.59</v>
+        <v>1461213</v>
       </c>
       <c r="P259" t="n">
         <v>20900</v>
       </c>
       <c r="Q259" t="n">
-        <v>5831100</v>
+        <v>2445300</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C4607</t>
+          <t>C4612</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>MAQUILLAJE SIRENA C4607</t>
+          <t>CARRUAJE MUÑECA C4612</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -11984,30 +11984,30 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="N260" t="n">
-        <v>10817</v>
+        <v>21762</v>
       </c>
       <c r="O260" t="n">
-        <v>2260753</v>
+        <v>3938922</v>
       </c>
       <c r="P260" t="n">
-        <v>17900</v>
+        <v>35900</v>
       </c>
       <c r="Q260" t="n">
-        <v>3741100</v>
+        <v>6497900</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>C4609</t>
+          <t>C4613</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>MAQUILLAJE UNICORNIO C4609</t>
+          <t>DIDACTICOS ARMABLES STD C4613</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -12021,7 +12021,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>117</v>
+        <v>934</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -12030,30 +12030,30 @@
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>117</v>
+        <v>934</v>
       </c>
       <c r="N261" t="n">
-        <v>12489</v>
+        <v>3821</v>
       </c>
       <c r="O261" t="n">
-        <v>1461213</v>
+        <v>3568814</v>
       </c>
       <c r="P261" t="n">
-        <v>20900</v>
+        <v>5900</v>
       </c>
       <c r="Q261" t="n">
-        <v>2445300</v>
+        <v>5510600</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>C4612</t>
+          <t>C4614</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CARRUAJE MUÑECA C4612</t>
+          <t>CASTILLO NIÑA C4614</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -12076,30 +12076,30 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="N262" t="n">
-        <v>21762</v>
+        <v>15472</v>
       </c>
       <c r="O262" t="n">
-        <v>3938922</v>
+        <v>2227968</v>
       </c>
       <c r="P262" t="n">
-        <v>35900</v>
+        <v>25900</v>
       </c>
       <c r="Q262" t="n">
-        <v>6497900</v>
+        <v>3729600</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>C4613</t>
+          <t>C4616</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>DIDACTICOS ARMABLES STD C4613</t>
+          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -12113,7 +12113,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>934</v>
+        <v>40</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -12122,30 +12122,30 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>934</v>
+        <v>40</v>
       </c>
       <c r="N263" t="n">
-        <v>3821</v>
+        <v>48522</v>
       </c>
       <c r="O263" t="n">
-        <v>3568814</v>
+        <v>1940880</v>
       </c>
       <c r="P263" t="n">
-        <v>5900</v>
+        <v>77900</v>
       </c>
       <c r="Q263" t="n">
-        <v>5510600</v>
+        <v>3116000</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>C4614</t>
+          <t>C4617</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>CASTILLO NIÑA C4614</t>
+          <t>CARRO TRANSFORME AZUL RECARGABLE C4617</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="J264" t="n">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -12168,30 +12168,30 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="N264" t="n">
-        <v>15472</v>
+        <v>53814.84</v>
       </c>
       <c r="O264" t="n">
-        <v>2227968</v>
+        <v>538148.3999999999</v>
       </c>
       <c r="P264" t="n">
-        <v>25900</v>
+        <v>88900</v>
       </c>
       <c r="Q264" t="n">
-        <v>3729600</v>
+        <v>889000</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>C4616</t>
+          <t>C4622</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
+          <t>CARRO COLECCION X8 C4622</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="J265" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -12214,30 +12214,30 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="N265" t="n">
-        <v>48522</v>
+        <v>5476</v>
       </c>
       <c r="O265" t="n">
-        <v>1940880</v>
+        <v>1314240</v>
       </c>
       <c r="P265" t="n">
-        <v>77900</v>
+        <v>8900</v>
       </c>
       <c r="Q265" t="n">
-        <v>3116000</v>
+        <v>2136000</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>C4617</t>
+          <t>C4629</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CARRO TRANSFORME AZUL RECARGABLE C4617</t>
+          <t>COMPUTADOR USB CABLE C4629</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -12251,7 +12251,7 @@
         </is>
       </c>
       <c r="J266" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -12260,30 +12260,30 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="N266" t="n">
-        <v>53814.84</v>
+        <v>64612</v>
       </c>
       <c r="O266" t="n">
-        <v>538148.3999999999</v>
+        <v>2326032</v>
       </c>
       <c r="P266" t="n">
-        <v>88900</v>
+        <v>103900</v>
       </c>
       <c r="Q266" t="n">
-        <v>889000</v>
+        <v>3740400</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>C4622</t>
+          <t>C4630</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>CARRO COLECCION X8 C4622</t>
+          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -12297,7 +12297,7 @@
         </is>
       </c>
       <c r="J267" t="n">
-        <v>240</v>
+        <v>56</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -12306,30 +12306,30 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>240</v>
+        <v>56</v>
       </c>
       <c r="N267" t="n">
-        <v>5476</v>
+        <v>38252</v>
       </c>
       <c r="O267" t="n">
-        <v>1314240</v>
+        <v>2142112</v>
       </c>
       <c r="P267" t="n">
-        <v>8900</v>
+        <v>61900</v>
       </c>
       <c r="Q267" t="n">
-        <v>2136000</v>
+        <v>3466400</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>C4629</t>
+          <t>C4631</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB CABLE C4629</t>
+          <t>SQUISHY MOSTRICO STD C4631</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>36</v>
+        <v>1152</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -12352,30 +12352,30 @@
         <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>36</v>
+        <v>1152</v>
       </c>
       <c r="N268" t="n">
-        <v>64612</v>
+        <v>1516.0387919529</v>
       </c>
       <c r="O268" t="n">
-        <v>2326032</v>
+        <v>1746476.688329741</v>
       </c>
       <c r="P268" t="n">
-        <v>103900</v>
+        <v>2300</v>
       </c>
       <c r="Q268" t="n">
-        <v>3740400</v>
+        <v>2649600</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>C4630</t>
+          <t>C466-IO</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
+          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -12389,7 +12389,7 @@
         </is>
       </c>
       <c r="J269" t="n">
-        <v>56</v>
+        <v>1050</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -12398,30 +12398,30 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>56</v>
+        <v>1050</v>
       </c>
       <c r="N269" t="n">
-        <v>38252</v>
+        <v>356.78</v>
       </c>
       <c r="O269" t="n">
-        <v>2142112</v>
+        <v>374619</v>
       </c>
       <c r="P269" t="n">
-        <v>61900</v>
+        <v>300</v>
       </c>
       <c r="Q269" t="n">
-        <v>3466400</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>C4631</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SQUISHY MOSTRICO STD C4631</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -12435,7 +12435,7 @@
         </is>
       </c>
       <c r="J270" t="n">
-        <v>1152</v>
+        <v>550</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -12444,44 +12444,42 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>1152</v>
+        <v>550</v>
       </c>
       <c r="N270" t="n">
-        <v>1516.0387920714</v>
+        <v>2454</v>
       </c>
       <c r="O270" t="n">
-        <v>1746476.688466253</v>
+        <v>1349700</v>
       </c>
       <c r="P270" t="n">
-        <v>2300</v>
+        <v>4200</v>
       </c>
       <c r="Q270" t="n">
-        <v>2649600</v>
+        <v>2310000</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>C466-IO</t>
-        </is>
+          <t>C476</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>6932001041468</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>YENGA MADERA GRABDE</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J271" t="n">
-        <v>1050</v>
+        <v>54</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -12490,30 +12488,30 @@
         <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>1050</v>
+        <v>54</v>
       </c>
       <c r="N271" t="n">
-        <v>356.78</v>
+        <v>5347.73</v>
       </c>
       <c r="O271" t="n">
-        <v>374619</v>
+        <v>288777.42</v>
       </c>
       <c r="P271" t="n">
-        <v>300</v>
+        <v>9500</v>
       </c>
       <c r="Q271" t="n">
-        <v>315000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>C4728</t>
+          <t>C4810</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>JUEGO DE AJEDREZ 13 EN 1 C4810</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -12527,7 +12525,7 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>550</v>
+        <v>22</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -12536,42 +12534,44 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>550</v>
+        <v>22</v>
       </c>
       <c r="N272" t="n">
-        <v>2454</v>
+        <v>14003</v>
       </c>
       <c r="O272" t="n">
-        <v>1349700</v>
+        <v>308066</v>
       </c>
       <c r="P272" t="n">
-        <v>4200</v>
+        <v>22500</v>
       </c>
       <c r="Q272" t="n">
-        <v>2310000</v>
+        <v>495000</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>C476</t>
-        </is>
-      </c>
-      <c r="B273" t="n">
-        <v>6932001041468</v>
+          <t>C4812</t>
+        </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>YENGA MADERA GRABDE</t>
+          <t>BURBUJERO DE ESPADA 44cm</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J273" t="n">
-        <v>54</v>
+        <v>4896</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -12580,30 +12580,30 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>54</v>
+        <v>4896</v>
       </c>
       <c r="N273" t="n">
-        <v>5347.73</v>
+        <v>1801</v>
       </c>
       <c r="O273" t="n">
-        <v>288777.42</v>
+        <v>8817696</v>
       </c>
       <c r="P273" t="n">
-        <v>9500</v>
+        <v>2900</v>
       </c>
       <c r="Q273" t="n">
-        <v>513000</v>
+        <v>14198400</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>C4810</t>
+          <t>C494-IO</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>JUEGO DE AJEDREZ 13 EN 1 C4810</t>
+          <t>GLOBO METALIZADO DULCES</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -12617,7 +12617,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>22</v>
+        <v>1352</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12626,44 +12626,42 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>22</v>
+        <v>1352</v>
       </c>
       <c r="N274" t="n">
-        <v>14003</v>
+        <v>1200</v>
       </c>
       <c r="O274" t="n">
-        <v>308066</v>
+        <v>1622400</v>
       </c>
       <c r="P274" t="n">
-        <v>22500</v>
+        <v>1500</v>
       </c>
       <c r="Q274" t="n">
-        <v>495000</v>
+        <v>2028000</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>C4812</t>
-        </is>
+          <t>C502</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>6952216485215</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>BURBUJERO DE ESPADA 44cm</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>C502 MUNECA NANCY GRANDE</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J275" t="n">
-        <v>4896</v>
+        <v>100</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12672,35 +12670,38 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>4896</v>
+        <v>100</v>
       </c>
       <c r="N275" t="n">
-        <v>1801</v>
+        <v>15423.36</v>
       </c>
       <c r="O275" t="n">
-        <v>8817696</v>
+        <v>1542336</v>
       </c>
       <c r="P275" t="n">
-        <v>2900</v>
+        <v>24900</v>
       </c>
       <c r="Q275" t="n">
-        <v>14198400</v>
+        <v>2490000</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>C494-IO</t>
-        </is>
+          <t>C5030</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>6999899236062</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>GLOBO METALIZADO DULCES</t>
+          <t>INFLABLE DONA LLANTA C5030</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -12709,7 +12710,7 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>1352</v>
+        <v>121</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -12718,42 +12719,47 @@
         <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>1352</v>
+        <v>121</v>
       </c>
       <c r="N276" t="n">
-        <v>1200</v>
+        <v>2857.22</v>
       </c>
       <c r="O276" t="n">
-        <v>1622400</v>
+        <v>345723.62</v>
       </c>
       <c r="P276" t="n">
-        <v>1500</v>
+        <v>4900</v>
       </c>
       <c r="Q276" t="n">
-        <v>2028000</v>
+        <v>592900</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>C502</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>6952216485215</v>
+        <v>6999899236154</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>C502 MUNECA NANCY GRANDE</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J277" t="n">
-        <v>100</v>
+        <v>534</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -12762,47 +12768,42 @@
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>100</v>
+        <v>534</v>
       </c>
       <c r="N277" t="n">
-        <v>15423.36</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O277" t="n">
-        <v>1542336</v>
+        <v>4776832.92</v>
       </c>
       <c r="P277" t="n">
-        <v>24900</v>
+        <v>14900</v>
       </c>
       <c r="Q277" t="n">
-        <v>2490000</v>
+        <v>7956600</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>C5030</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>6999899236062</v>
+        <v>6952365180054</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>INFLABLE DONA LLANTA C5030</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO BURBUJA 30</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J278" t="n">
-        <v>121</v>
+        <v>3650</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12811,38 +12812,35 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>121</v>
+        <v>3650</v>
       </c>
       <c r="N278" t="n">
-        <v>2857.22</v>
+        <v>675.2255375485</v>
       </c>
       <c r="O278" t="n">
-        <v>345723.62</v>
+        <v>2464573.212052025</v>
       </c>
       <c r="P278" t="n">
-        <v>4900</v>
+        <v>1300</v>
       </c>
       <c r="Q278" t="n">
-        <v>592900</v>
+        <v>4745000</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>C5032</t>
-        </is>
-      </c>
-      <c r="B279" t="n">
-        <v>6999899236154</v>
+          <t>C510-IO</t>
+        </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>GLOBO BURBUJA METALIZADO</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -12851,7 +12849,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>534</v>
+        <v>3896</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12860,33 +12858,33 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>534</v>
+        <v>3896</v>
       </c>
       <c r="N279" t="n">
-        <v>8945.379999999999</v>
+        <v>960</v>
       </c>
       <c r="O279" t="n">
-        <v>4776832.92</v>
+        <v>3740160</v>
       </c>
       <c r="P279" t="n">
-        <v>14900</v>
+        <v>1200</v>
       </c>
       <c r="Q279" t="n">
-        <v>7956600</v>
+        <v>4675200</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>C515</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>6952365180054</v>
+        <v>6953626330010</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA 30</t>
+          <t>GLOBO FIGURAS BURBUJA</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -12895,7 +12893,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>3650</v>
+        <v>3800</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12904,35 +12902,35 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>3650</v>
+        <v>3800</v>
       </c>
       <c r="N280" t="n">
-        <v>675.2255375485</v>
+        <v>583.7204926325001</v>
       </c>
       <c r="O280" t="n">
-        <v>2464573.212052025</v>
+        <v>2218137.8720035</v>
       </c>
       <c r="P280" t="n">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="Q280" t="n">
-        <v>4745000</v>
+        <v>2280000</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>C510-IO</t>
+          <t>C5214</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA METALIZADO</t>
+          <t>CUBO C5214</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -12941,7 +12939,7 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>3896</v>
+        <v>1440</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -12950,33 +12948,33 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>3896</v>
+        <v>1440</v>
       </c>
       <c r="N281" t="n">
-        <v>960</v>
+        <v>1690.8700091743</v>
       </c>
       <c r="O281" t="n">
-        <v>3740160</v>
+        <v>2434852.813210992</v>
       </c>
       <c r="P281" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="Q281" t="n">
-        <v>4675200</v>
+        <v>4320000</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>C515</t>
+          <t>C523</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>6953626330010</v>
+        <v>6957430180212</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS BURBUJA</t>
+          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -12985,7 +12983,7 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>3800</v>
+        <v>2556</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -12994,44 +12992,42 @@
         <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>3800</v>
+        <v>2556</v>
       </c>
       <c r="N282" t="n">
-        <v>583.7204926325001</v>
+        <v>481.48791273054</v>
       </c>
       <c r="O282" t="n">
-        <v>2218137.8720035</v>
+        <v>1230683.10493926</v>
       </c>
       <c r="P282" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="Q282" t="n">
-        <v>2280000</v>
+        <v>1661400</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>C5214</t>
-        </is>
+          <t>C524</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>6957430180229</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>CUBO C5214</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J283" t="n">
-        <v>1440</v>
+        <v>614</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -13040,42 +13036,47 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>1440</v>
+        <v>614</v>
       </c>
       <c r="N283" t="n">
-        <v>1690.8700091701</v>
+        <v>872.15418687873</v>
       </c>
       <c r="O283" t="n">
-        <v>2434852.813204944</v>
+        <v>535502.6707435403</v>
       </c>
       <c r="P283" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="Q283" t="n">
-        <v>4320000</v>
+        <v>736800</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>C523</t>
+          <t>C5246/C5247</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>6957430180212</v>
+        <v>6900077483239</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
+          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J284" t="n">
-        <v>2556</v>
+        <v>130</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -13084,33 +13085,33 @@
         <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>2556</v>
+        <v>130</v>
       </c>
       <c r="N284" t="n">
-        <v>481.48791273054</v>
+        <v>8702.219999999999</v>
       </c>
       <c r="O284" t="n">
-        <v>1230683.10493926</v>
+        <v>1131288.6</v>
       </c>
       <c r="P284" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="Q284" t="n">
-        <v>1661400</v>
+        <v>1157000</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>C524</t>
+          <t>C525</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>6957430180229</v>
+        <v>6957430180236</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
+          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -13119,7 +13120,7 @@
         </is>
       </c>
       <c r="J285" t="n">
-        <v>614</v>
+        <v>1436</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -13128,47 +13129,42 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>614</v>
+        <v>1436</v>
       </c>
       <c r="N285" t="n">
-        <v>872.15418687873</v>
+        <v>345.55838633169</v>
       </c>
       <c r="O285" t="n">
-        <v>535502.6707435403</v>
+        <v>496221.8427723068</v>
       </c>
       <c r="P285" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="Q285" t="n">
-        <v>736800</v>
+        <v>861600</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>C5246/C5247</t>
+          <t>C526</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>6900077483239</v>
+        <v>6957430180243</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J286" t="n">
-        <v>130</v>
+        <v>11416</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -13177,42 +13173,47 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>130</v>
+        <v>11416</v>
       </c>
       <c r="N286" t="n">
-        <v>8702.219999999999</v>
+        <v>711.33664937221</v>
       </c>
       <c r="O286" t="n">
-        <v>1131288.6</v>
+        <v>8120619.189233149</v>
       </c>
       <c r="P286" t="n">
-        <v>8900</v>
+        <v>900</v>
       </c>
       <c r="Q286" t="n">
-        <v>1157000</v>
+        <v>10274400</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>C525</t>
+          <t>C527-IO</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>6957430180236</v>
+        <v>6957430180526</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>1436</v>
+        <v>1242</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -13221,42 +13222,44 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>1436</v>
+        <v>1242</v>
       </c>
       <c r="N287" t="n">
-        <v>345.55838633169</v>
+        <v>815.0599999999999</v>
       </c>
       <c r="O287" t="n">
-        <v>496221.8427723068</v>
+        <v>1012304.52</v>
       </c>
       <c r="P287" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="Q287" t="n">
-        <v>861600</v>
+        <v>1117800</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>C526</t>
-        </is>
-      </c>
-      <c r="B288" t="n">
-        <v>6957430180243</v>
+          <t>C541</t>
+        </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
+          <t>GLOBO LLAMA PQÑO</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J288" t="n">
-        <v>11416</v>
+        <v>2150</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -13265,38 +13268,35 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>11416</v>
+        <v>2150</v>
       </c>
       <c r="N288" t="n">
-        <v>711.33664937221</v>
+        <v>800</v>
       </c>
       <c r="O288" t="n">
-        <v>8120619.189233149</v>
+        <v>1720000</v>
       </c>
       <c r="P288" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Q288" t="n">
-        <v>10274400</v>
+        <v>2150000</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>C527-IO</t>
-        </is>
-      </c>
-      <c r="B289" t="n">
-        <v>6957430180526</v>
+          <t>C575-IO</t>
+        </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+          <t>GLOBO UNICORNIO PQÑO</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -13305,7 +13305,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>1242</v>
+        <v>1001</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13314,35 +13314,38 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>1242</v>
+        <v>1001</v>
       </c>
       <c r="N289" t="n">
-        <v>815.0599999999999</v>
+        <v>320</v>
       </c>
       <c r="O289" t="n">
-        <v>1012304.52</v>
+        <v>320320</v>
       </c>
       <c r="P289" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="Q289" t="n">
-        <v>1117800</v>
+        <v>400400</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>C541</t>
-        </is>
+          <t>C596-IO</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>8596162180268</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>GLOBO LLAMA PQÑO</t>
+          <t>GLOBO TE AMO</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -13351,7 +13354,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>2150</v>
+        <v>1455</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13360,35 +13363,38 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>2150</v>
+        <v>1455</v>
       </c>
       <c r="N290" t="n">
-        <v>800</v>
+        <v>1044.54</v>
       </c>
       <c r="O290" t="n">
-        <v>1720000</v>
+        <v>1519805.7</v>
       </c>
       <c r="P290" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="Q290" t="n">
-        <v>2150000</v>
+        <v>1746000</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>C575-IO</t>
-        </is>
+          <t>C60-IO</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>6524521011245</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO PQÑO</t>
+          <t>GLOBO TIKTOK BOUQUET</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -13397,7 +13403,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>1001</v>
+        <v>740</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13406,38 +13412,35 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>1001</v>
+        <v>740</v>
       </c>
       <c r="N291" t="n">
-        <v>320</v>
+        <v>1989.05</v>
       </c>
       <c r="O291" t="n">
-        <v>320320</v>
+        <v>1471897</v>
       </c>
       <c r="P291" t="n">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="Q291" t="n">
-        <v>400400</v>
+        <v>2220000</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>C596-IO</t>
-        </is>
-      </c>
-      <c r="B292" t="n">
-        <v>8596162180268</v>
+          <t>C6074</t>
+        </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>GLOBO TE AMO</t>
+          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -13446,7 +13449,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>1455</v>
+        <v>25</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13455,47 +13458,42 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>1455</v>
+        <v>25</v>
       </c>
       <c r="N292" t="n">
-        <v>1044.54</v>
+        <v>9447.25</v>
       </c>
       <c r="O292" t="n">
-        <v>1519805.7</v>
+        <v>236181.25</v>
       </c>
       <c r="P292" t="n">
-        <v>1200</v>
+        <v>9900</v>
       </c>
       <c r="Q292" t="n">
-        <v>1746000</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>C60-IO</t>
+          <t>C629</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>6524521011245</v>
+        <v>7791638082188</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>GLOBO TIKTOK BOUQUET</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>BURBUJERO PITO STD</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J293" t="n">
-        <v>740</v>
+        <v>15732</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13504,35 +13502,38 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>740</v>
+        <v>15732</v>
       </c>
       <c r="N293" t="n">
-        <v>1989.05</v>
+        <v>703.79510612101</v>
       </c>
       <c r="O293" t="n">
-        <v>1471897</v>
+        <v>11072104.60949573</v>
       </c>
       <c r="P293" t="n">
-        <v>3000</v>
+        <v>900</v>
       </c>
       <c r="Q293" t="n">
-        <v>2220000</v>
+        <v>14158800</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>C6074</t>
-        </is>
+          <t>C6406</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>6820212541115</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
+          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -13541,7 +13542,7 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13550,33 +13551,30 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="N294" t="n">
-        <v>9447.25</v>
+        <v>14260.14</v>
       </c>
       <c r="O294" t="n">
-        <v>236181.25</v>
+        <v>741527.28</v>
       </c>
       <c r="P294" t="n">
-        <v>9900</v>
+        <v>15900</v>
       </c>
       <c r="Q294" t="n">
-        <v>247500</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>C629</t>
-        </is>
-      </c>
-      <c r="B295" t="n">
-        <v>7791638082188</v>
+          <t>C642</t>
+        </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>BURBUJERO PITO STD</t>
+          <t>LANZADOR AGUA</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -13585,7 +13583,7 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>15732</v>
+        <v>599</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13594,38 +13592,35 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>15732</v>
+        <v>599</v>
       </c>
       <c r="N295" t="n">
-        <v>703.79511689575</v>
+        <v>2529.19</v>
       </c>
       <c r="O295" t="n">
-        <v>11072104.77900394</v>
+        <v>1514984.81</v>
       </c>
       <c r="P295" t="n">
-        <v>900</v>
+        <v>5100</v>
       </c>
       <c r="Q295" t="n">
-        <v>14158800</v>
+        <v>3054900</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C6406</t>
-        </is>
-      </c>
-      <c r="B296" t="n">
-        <v>6820212541115</v>
+          <t>C671-LJ</t>
+        </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
+          <t>GLOBO UNICORNIO MEDIANO</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -13634,7 +13629,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>52</v>
+        <v>1397</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13643,39 +13638,47 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>52</v>
+        <v>1397</v>
       </c>
       <c r="N296" t="n">
-        <v>14260.14</v>
+        <v>400</v>
       </c>
       <c r="O296" t="n">
-        <v>741527.28</v>
+        <v>558800</v>
       </c>
       <c r="P296" t="n">
-        <v>15900</v>
+        <v>500</v>
       </c>
       <c r="Q296" t="n">
-        <v>826800</v>
+        <v>698500</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C642</t>
-        </is>
+          <t>C7005</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>6874123039124</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA</t>
+          <t>MAQUINA DE COSER C7005</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J297" t="n">
-        <v>599</v>
+        <v>208</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13684,35 +13687,38 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>599</v>
+        <v>208</v>
       </c>
       <c r="N297" t="n">
-        <v>2529.19</v>
+        <v>6078.9925934066</v>
       </c>
       <c r="O297" t="n">
-        <v>1514984.81</v>
+        <v>1264430.459428573</v>
       </c>
       <c r="P297" t="n">
-        <v>5100</v>
+        <v>18500</v>
       </c>
       <c r="Q297" t="n">
-        <v>3054900</v>
+        <v>3848000</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C671-LJ</t>
-        </is>
+          <t>C7009</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>2024250256831</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MEDIANO</t>
+          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -13721,7 +13727,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>1397</v>
+        <v>12</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13730,38 +13736,38 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>1397</v>
+        <v>12</v>
       </c>
       <c r="N298" t="n">
-        <v>400</v>
+        <v>5899.18</v>
       </c>
       <c r="O298" t="n">
-        <v>558800</v>
+        <v>70790.16</v>
       </c>
       <c r="P298" t="n">
-        <v>500</v>
+        <v>12500</v>
       </c>
       <c r="Q298" t="n">
-        <v>698500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C7005</t>
+          <t>C7038</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>6874123039124</v>
+        <v>5132595141631</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER C7005</t>
+          <t>LANZADORA DE AGUA GLOBO C7038</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -13770,7 +13776,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>208</v>
+        <v>23</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13779,38 +13785,38 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>208</v>
+        <v>23</v>
       </c>
       <c r="N299" t="n">
-        <v>6078.9925934066</v>
+        <v>18423.71</v>
       </c>
       <c r="O299" t="n">
-        <v>1264430.459428573</v>
+        <v>423745.33</v>
       </c>
       <c r="P299" t="n">
-        <v>18500</v>
+        <v>10000</v>
       </c>
       <c r="Q299" t="n">
-        <v>3848000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C7009</t>
+          <t>C7039</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>2024250256831</v>
+        <v>5132594521182</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
+          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -13819,7 +13825,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13828,38 +13834,38 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N300" t="n">
-        <v>5899.18</v>
+        <v>10985.78</v>
       </c>
       <c r="O300" t="n">
-        <v>70790.16</v>
+        <v>219715.6</v>
       </c>
       <c r="P300" t="n">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="Q300" t="n">
-        <v>150000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C7038</t>
+          <t>C7040</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>5132595141631</v>
+        <v>6920373004365</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA GLOBO C7038</t>
+          <t>GARAJE EXIBICION CON LUZ C7040</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -13868,7 +13874,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13877,33 +13883,33 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="N301" t="n">
-        <v>18423.71</v>
+        <v>23452.77</v>
       </c>
       <c r="O301" t="n">
-        <v>423745.33</v>
+        <v>1102280.19</v>
       </c>
       <c r="P301" t="n">
-        <v>10000</v>
+        <v>39900</v>
       </c>
       <c r="Q301" t="n">
-        <v>230000</v>
+        <v>1875300</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C7039</t>
+          <t>C7042</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>5132594521182</v>
+        <v>2024081616255</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
+          <t>CANCHA BASKETBALL WIN24 C7042</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -13917,7 +13923,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13926,38 +13932,35 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N302" t="n">
-        <v>10985.78</v>
+        <v>9694.41</v>
       </c>
       <c r="O302" t="n">
-        <v>219715.6</v>
+        <v>96944.10000000001</v>
       </c>
       <c r="P302" t="n">
-        <v>15000</v>
+        <v>32500</v>
       </c>
       <c r="Q302" t="n">
-        <v>300000</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C7040</t>
-        </is>
-      </c>
-      <c r="B303" t="n">
-        <v>6920373004365</v>
+          <t>C7080-BC</t>
+        </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>GARAJE EXIBICION CON LUZ C7040</t>
+          <t>ROBOT TRANSFORME STD C7080-BC</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -13966,7 +13969,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -13975,38 +13978,38 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N303" t="n">
-        <v>23452.77</v>
+        <v>10556.12</v>
       </c>
       <c r="O303" t="n">
-        <v>1102280.19</v>
+        <v>411688.6800000001</v>
       </c>
       <c r="P303" t="n">
-        <v>39900</v>
+        <v>32900</v>
       </c>
       <c r="Q303" t="n">
-        <v>1875300</v>
+        <v>1283100</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C7042</t>
+          <t>C7081</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>2024081616255</v>
+        <v>6301582313156</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>CANCHA BASKETBALL WIN24 C7042</t>
+          <t>LANZADORA DARDOS DE PILA C7081</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -14015,7 +14018,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14024,44 +14027,42 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="N304" t="n">
-        <v>9694.41</v>
+        <v>22470.62</v>
       </c>
       <c r="O304" t="n">
-        <v>96944.10000000001</v>
+        <v>471883.02</v>
       </c>
       <c r="P304" t="n">
-        <v>32500</v>
+        <v>41900</v>
       </c>
       <c r="Q304" t="n">
-        <v>325000</v>
+        <v>879900</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C7080-BC</t>
-        </is>
+          <t>C71</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>5899989622205</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>ROBOT TRANSFORME STD C7080-BC</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>MUÑECOS</t>
+          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J305" t="n">
-        <v>39</v>
+        <v>392</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -14070,38 +14071,35 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>39</v>
+        <v>392</v>
       </c>
       <c r="N305" t="n">
-        <v>10556.12</v>
+        <v>1669.6</v>
       </c>
       <c r="O305" t="n">
-        <v>411688.6800000001</v>
+        <v>654483.2</v>
       </c>
       <c r="P305" t="n">
-        <v>32900</v>
+        <v>2900</v>
       </c>
       <c r="Q305" t="n">
-        <v>1283100</v>
+        <v>1136800</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C7081</t>
-        </is>
-      </c>
-      <c r="B306" t="n">
-        <v>6301582313156</v>
+          <t>C7117</t>
+        </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS DE PILA C7081</t>
+          <t>BINGO LOTTO C7117</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>JUEGOS DE MESA</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -14110,7 +14108,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14119,42 +14117,44 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N306" t="n">
-        <v>22470.62</v>
+        <v>5798.41</v>
       </c>
       <c r="O306" t="n">
-        <v>471883.02</v>
+        <v>115968.2</v>
       </c>
       <c r="P306" t="n">
-        <v>41900</v>
+        <v>14900</v>
       </c>
       <c r="Q306" t="n">
-        <v>879900</v>
+        <v>298000</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C71</t>
-        </is>
-      </c>
-      <c r="B307" t="n">
-        <v>5899989622205</v>
+          <t>C7124</t>
+        </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
+          <t>TRAILER TRANFORME XQ05 C7124</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J307" t="n">
-        <v>392</v>
+        <v>40</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -14163,35 +14163,35 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>392</v>
+        <v>40</v>
       </c>
       <c r="N307" t="n">
-        <v>1669.6</v>
+        <v>19587.53</v>
       </c>
       <c r="O307" t="n">
-        <v>654483.2</v>
+        <v>783501.2</v>
       </c>
       <c r="P307" t="n">
-        <v>2900</v>
+        <v>65000</v>
       </c>
       <c r="Q307" t="n">
-        <v>1136800</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C7117</t>
+          <t>C7132</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>BINGO LOTTO C7117</t>
+          <t>SET PULSERAS Y CAUCHOS C7132</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>JUEGOS DE MESA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -14200,7 +14200,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -14209,35 +14209,38 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="N308" t="n">
-        <v>5798.41</v>
+        <v>3100.87</v>
       </c>
       <c r="O308" t="n">
-        <v>115968.2</v>
+        <v>669787.9199999999</v>
       </c>
       <c r="P308" t="n">
-        <v>14900</v>
+        <v>9900</v>
       </c>
       <c r="Q308" t="n">
-        <v>298000</v>
+        <v>2138400</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C7124</t>
-        </is>
+          <t>C7147-A</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>6912209205022</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>TRAILER TRANFORME XQ05 C7124</t>
+          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -14246,7 +14249,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -14255,30 +14258,33 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="N309" t="n">
-        <v>19587.53</v>
+        <v>10348.08</v>
       </c>
       <c r="O309" t="n">
-        <v>783501.2</v>
+        <v>589840.5599999999</v>
       </c>
       <c r="P309" t="n">
-        <v>65000</v>
+        <v>16900</v>
       </c>
       <c r="Q309" t="n">
-        <v>2600000</v>
+        <v>963300</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C7132</t>
-        </is>
+          <t>C7213</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>6987540143012</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>SET PULSERAS Y CAUCHOS C7132</t>
+          <t>PESCADO CON LUZ Y SONIDO C7213</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -14292,7 +14298,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>216</v>
+        <v>48</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -14301,33 +14307,33 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>216</v>
+        <v>48</v>
       </c>
       <c r="N310" t="n">
-        <v>3100.87</v>
+        <v>9746.880194174801</v>
       </c>
       <c r="O310" t="n">
-        <v>669787.9199999999</v>
+        <v>467850.2493203904</v>
       </c>
       <c r="P310" t="n">
-        <v>9900</v>
+        <v>18500</v>
       </c>
       <c r="Q310" t="n">
-        <v>2138400</v>
+        <v>888000</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C7147-A</t>
+          <t>C7218</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>6912209205022</v>
+        <v>6920240872189</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
+          <t>CAJA REGISTRADORA SHOPPING C7218</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -14341,7 +14347,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14350,33 +14356,33 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="N311" t="n">
-        <v>10348.08</v>
+        <v>13623.91</v>
       </c>
       <c r="O311" t="n">
-        <v>589840.5599999999</v>
+        <v>204358.65</v>
       </c>
       <c r="P311" t="n">
-        <v>16900</v>
+        <v>26900</v>
       </c>
       <c r="Q311" t="n">
-        <v>963300</v>
+        <v>403500</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C7213</t>
+          <t>C7221</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>6987540143012</v>
+        <v>7453100037446</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>PESCADO CON LUZ Y SONIDO C7213</t>
+          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -14390,7 +14396,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -14399,33 +14405,33 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="N312" t="n">
-        <v>9746.880194174801</v>
+        <v>2672.89</v>
       </c>
       <c r="O312" t="n">
-        <v>467850.2493203904</v>
+        <v>927492.83</v>
       </c>
       <c r="P312" t="n">
-        <v>18500</v>
+        <v>10200</v>
       </c>
       <c r="Q312" t="n">
-        <v>888000</v>
+        <v>3539400</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C7218</t>
+          <t>C7222</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>6920240872189</v>
+        <v>7453100037453</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>CAJA REGISTRADORA SHOPPING C7218</t>
+          <t>RELOJ DIDACTICO CARACOL C7222</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -14439,7 +14445,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>15</v>
+        <v>230</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -14448,33 +14454,33 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>15</v>
+        <v>230</v>
       </c>
       <c r="N313" t="n">
-        <v>13623.91</v>
+        <v>4795.69</v>
       </c>
       <c r="O313" t="n">
-        <v>204358.65</v>
+        <v>1103008.7</v>
       </c>
       <c r="P313" t="n">
-        <v>26900</v>
+        <v>10200</v>
       </c>
       <c r="Q313" t="n">
-        <v>403500</v>
+        <v>2346000</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C7221</t>
+          <t>C7246</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>7453100037446</v>
+        <v>6902024622111</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
+          <t>BLÍSTER SKATE X4 C7246</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -14488,7 +14494,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -14497,38 +14503,38 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="N314" t="n">
-        <v>2672.89</v>
+        <v>2992.5698684211</v>
       </c>
       <c r="O314" t="n">
-        <v>927492.83</v>
+        <v>62843.96723684311</v>
       </c>
       <c r="P314" t="n">
-        <v>10200</v>
+        <v>6000</v>
       </c>
       <c r="Q314" t="n">
-        <v>3539400</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C7222</t>
+          <t>C7294</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>7453100037453</v>
+        <v>6895675680022</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>RELOJ DIDACTICO CARACOL C7222</t>
+          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -14537,7 +14543,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14546,38 +14552,38 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="N315" t="n">
-        <v>4795.69</v>
+        <v>4337.31</v>
       </c>
       <c r="O315" t="n">
-        <v>1103008.7</v>
+        <v>260238.6</v>
       </c>
       <c r="P315" t="n">
-        <v>10200</v>
+        <v>12900</v>
       </c>
       <c r="Q315" t="n">
-        <v>2346000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C7246</t>
+          <t>C7325</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>6902024622111</v>
+        <v>6974555555022</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>BLÍSTER SKATE X4 C7246</t>
+          <t>PISTA EN BLISTER C7325</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -14586,7 +14592,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14595,38 +14601,35 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N316" t="n">
-        <v>2992.569375</v>
+        <v>3067.0905844156</v>
       </c>
       <c r="O316" t="n">
-        <v>62843.956875</v>
+        <v>138019.076298702</v>
       </c>
       <c r="P316" t="n">
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="Q316" t="n">
-        <v>126000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C7294</t>
-        </is>
-      </c>
-      <c r="B317" t="n">
-        <v>6895675680022</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -14635,7 +14638,7 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>60</v>
+        <v>2700</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -14644,38 +14647,38 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>60</v>
+        <v>2700</v>
       </c>
       <c r="N317" t="n">
-        <v>4337.31</v>
+        <v>640</v>
       </c>
       <c r="O317" t="n">
-        <v>260238.6</v>
+        <v>1728000</v>
       </c>
       <c r="P317" t="n">
-        <v>12900</v>
+        <v>800</v>
       </c>
       <c r="Q317" t="n">
-        <v>774000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C7325</t>
+          <t>C7365</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>6974555555022</v>
+        <v>6920240750050</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -14684,7 +14687,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -14693,35 +14696,38 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="N318" t="n">
-        <v>3067.0905844156</v>
+        <v>4190.77</v>
       </c>
       <c r="O318" t="n">
-        <v>138019.076298702</v>
+        <v>79624.63</v>
       </c>
       <c r="P318" t="n">
-        <v>7200</v>
+        <v>5900</v>
       </c>
       <c r="Q318" t="n">
-        <v>324000</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7366</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>6920240750098</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -14730,7 +14736,7 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>2700</v>
+        <v>104</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14739,33 +14745,33 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>2700</v>
+        <v>104</v>
       </c>
       <c r="N319" t="n">
-        <v>640</v>
+        <v>3499.72</v>
       </c>
       <c r="O319" t="n">
-        <v>1728000</v>
+        <v>363970.88</v>
       </c>
       <c r="P319" t="n">
-        <v>800</v>
+        <v>6900</v>
       </c>
       <c r="Q319" t="n">
-        <v>2160000</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>6920240750050</v>
+        <v>6920240750159</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -14779,7 +14785,7 @@
         </is>
       </c>
       <c r="J320" t="n">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14788,38 +14794,35 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="N320" t="n">
-        <v>4190.77</v>
+        <v>4578.04</v>
       </c>
       <c r="O320" t="n">
-        <v>79624.63</v>
+        <v>723330.3199999999</v>
       </c>
       <c r="P320" t="n">
-        <v>5900</v>
+        <v>7500</v>
       </c>
       <c r="Q320" t="n">
-        <v>112100</v>
+        <v>1185000</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C7366</t>
-        </is>
-      </c>
-      <c r="B321" t="n">
-        <v>6920240750098</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -14828,7 +14831,7 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>104</v>
+        <v>1876</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14837,38 +14840,38 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>104</v>
+        <v>1876</v>
       </c>
       <c r="N321" t="n">
-        <v>3499.72</v>
+        <v>480</v>
       </c>
       <c r="O321" t="n">
-        <v>363970.88</v>
+        <v>900480</v>
       </c>
       <c r="P321" t="n">
-        <v>6900</v>
+        <v>600</v>
       </c>
       <c r="Q321" t="n">
-        <v>717600</v>
+        <v>1125600</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>C7368</t>
+          <t>C7402</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>6920240750159</v>
+        <v>6920601877891</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>PANDERETA X 3 C7402</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -14877,7 +14880,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14886,35 +14889,38 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="N322" t="n">
-        <v>4578.04</v>
+        <v>2356.29</v>
       </c>
       <c r="O322" t="n">
-        <v>723330.3199999999</v>
+        <v>141377.4</v>
       </c>
       <c r="P322" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="Q322" t="n">
-        <v>1185000</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7413</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>6921202412870</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -14923,7 +14929,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14932,38 +14938,35 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="N323" t="n">
-        <v>480</v>
+        <v>4159.000295203</v>
       </c>
       <c r="O323" t="n">
-        <v>900480</v>
+        <v>499080.03542436</v>
       </c>
       <c r="P323" t="n">
-        <v>600</v>
+        <v>8900</v>
       </c>
       <c r="Q323" t="n">
-        <v>1125600</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>C7402</t>
-        </is>
-      </c>
-      <c r="B324" t="n">
-        <v>6920601877891</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>PANDERETA X 3 C7402</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -14972,7 +14975,7 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>60</v>
+        <v>478</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -14981,38 +14984,38 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>60</v>
+        <v>478</v>
       </c>
       <c r="N324" t="n">
-        <v>2356.29</v>
+        <v>1554.12</v>
       </c>
       <c r="O324" t="n">
-        <v>141377.4</v>
+        <v>742869.36</v>
       </c>
       <c r="P324" t="n">
-        <v>6500</v>
+        <v>1900</v>
       </c>
       <c r="Q324" t="n">
-        <v>390000</v>
+        <v>908200</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>C7413</t>
+          <t>C7453</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>6921202412870</v>
+        <v>6920247274535</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
+          <t>JUEGO DE MESA BALONCESTO C7453</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -15021,7 +15024,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -15030,35 +15033,35 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="N325" t="n">
-        <v>4159.000295203</v>
+        <v>27938.1</v>
       </c>
       <c r="O325" t="n">
-        <v>499080.03542436</v>
+        <v>223504.8</v>
       </c>
       <c r="P325" t="n">
-        <v>8900</v>
+        <v>18000</v>
       </c>
       <c r="Q325" t="n">
-        <v>1068000</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>C744-IO</t>
+          <t>C7462</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -15067,7 +15070,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -15076,33 +15079,33 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="N326" t="n">
-        <v>1554.12</v>
+        <v>14751.820322581</v>
       </c>
       <c r="O326" t="n">
-        <v>742869.36</v>
+        <v>162270.023548391</v>
       </c>
       <c r="P326" t="n">
-        <v>1900</v>
+        <v>37100</v>
       </c>
       <c r="Q326" t="n">
-        <v>908200</v>
+        <v>408100</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>C7453</t>
+          <t>C7467</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>6920247274535</v>
+        <v>6920241023009</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>JUEGO DE MESA BALONCESTO C7453</t>
+          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -15116,7 +15119,7 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15125,35 +15128,38 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N327" t="n">
-        <v>27938.1</v>
+        <v>15347.45</v>
       </c>
       <c r="O327" t="n">
-        <v>223504.8</v>
+        <v>230211.75</v>
       </c>
       <c r="P327" t="n">
-        <v>18000</v>
+        <v>23900</v>
       </c>
       <c r="Q327" t="n">
-        <v>144000</v>
+        <v>358500</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>C7462</t>
-        </is>
+          <t>C7488</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>6945158254520</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -15162,7 +15168,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15171,33 +15177,33 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="N328" t="n">
-        <v>14751.820322581</v>
+        <v>8919.16</v>
       </c>
       <c r="O328" t="n">
-        <v>162270.023548391</v>
+        <v>258655.64</v>
       </c>
       <c r="P328" t="n">
-        <v>37100</v>
+        <v>10000</v>
       </c>
       <c r="Q328" t="n">
-        <v>408100</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>C7467</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>6920241023009</v>
+        <v>6905698382824</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -15211,7 +15217,7 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -15220,47 +15226,42 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N329" t="n">
-        <v>15347.45</v>
+        <v>1024.29</v>
       </c>
       <c r="O329" t="n">
-        <v>230211.75</v>
+        <v>1024.29</v>
       </c>
       <c r="P329" t="n">
-        <v>23900</v>
+        <v>2900</v>
       </c>
       <c r="Q329" t="n">
-        <v>358500</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>6945158254520</v>
+        <v>8596162180497</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J330" t="n">
-        <v>29</v>
+        <v>1398</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -15269,47 +15270,42 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>29</v>
+        <v>1398</v>
       </c>
       <c r="N330" t="n">
-        <v>8919.16</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O330" t="n">
-        <v>258655.64</v>
+        <v>1626915.200678939</v>
       </c>
       <c r="P330" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="Q330" t="n">
-        <v>290000</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C753</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>6905698382824</v>
+        <v>8596162180503</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J331" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
@@ -15318,42 +15314,47 @@
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="N331" t="n">
-        <v>1024.29</v>
+        <v>5113.4625508318</v>
       </c>
       <c r="O331" t="n">
-        <v>1024.29</v>
+        <v>1416429.126580409</v>
       </c>
       <c r="P331" t="n">
-        <v>2900</v>
+        <v>7000</v>
       </c>
       <c r="Q331" t="n">
-        <v>2900</v>
+        <v>1939000</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>8596162180497</v>
+        <v>6923669699979</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J332" t="n">
-        <v>1398</v>
+        <v>12023</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -15362,42 +15363,47 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>1398</v>
+        <v>12023</v>
       </c>
       <c r="N332" t="n">
-        <v>1163.7447787403</v>
+        <v>509.69</v>
       </c>
       <c r="O332" t="n">
-        <v>1626915.200678939</v>
+        <v>6128002.87</v>
       </c>
       <c r="P332" t="n">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="Q332" t="n">
-        <v>2097000</v>
+        <v>9017250</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>C753</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>8596162180503</v>
+        <v>6951241752002</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J333" t="n">
-        <v>277</v>
+        <v>499</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
@@ -15406,38 +15412,35 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>277</v>
+        <v>499</v>
       </c>
       <c r="N333" t="n">
-        <v>5113.4625508318</v>
+        <v>7046.9398275862</v>
       </c>
       <c r="O333" t="n">
-        <v>1416429.126580409</v>
+        <v>3516422.973965514</v>
       </c>
       <c r="P333" t="n">
-        <v>7000</v>
+        <v>9900</v>
       </c>
       <c r="Q333" t="n">
-        <v>1939000</v>
+        <v>4940100</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>C7533</t>
-        </is>
-      </c>
-      <c r="B334" t="n">
-        <v>6923669699979</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -15446,7 +15449,7 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>12023</v>
+        <v>30</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
@@ -15455,33 +15458,30 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>12023</v>
+        <v>30</v>
       </c>
       <c r="N334" t="n">
-        <v>509.69</v>
+        <v>24338.47</v>
       </c>
       <c r="O334" t="n">
-        <v>6128002.87</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P334" t="n">
-        <v>750</v>
+        <v>27900</v>
       </c>
       <c r="Q334" t="n">
-        <v>9017250</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B335" t="n">
-        <v>6951241752002</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -15495,7 +15495,7 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>499</v>
+        <v>188</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -15504,35 +15504,35 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>499</v>
+        <v>188</v>
       </c>
       <c r="N335" t="n">
-        <v>7046.939827883</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O335" t="n">
-        <v>3516422.974113617</v>
+        <v>149706.28</v>
       </c>
       <c r="P335" t="n">
-        <v>9900</v>
+        <v>2500</v>
       </c>
       <c r="Q335" t="n">
-        <v>4940100</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>C7535</t>
+          <t>C7560AC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>TRICICLO INFANTIL OSITO C756AC</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -15541,7 +15541,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -15550,30 +15550,33 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N336" t="n">
-        <v>24338.47</v>
+        <v>44113.603841808</v>
       </c>
       <c r="O336" t="n">
-        <v>730154.1000000001</v>
+        <v>441136.03841808</v>
       </c>
       <c r="P336" t="n">
-        <v>27900</v>
+        <v>71900</v>
       </c>
       <c r="Q336" t="n">
-        <v>837000</v>
+        <v>719000</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7588</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>7588228020244</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -15587,7 +15590,7 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>188</v>
+        <v>1432</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -15596,35 +15599,38 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>188</v>
+        <v>1432</v>
       </c>
       <c r="N337" t="n">
-        <v>796.3099999999999</v>
+        <v>641.78</v>
       </c>
       <c r="O337" t="n">
-        <v>149706.28</v>
+        <v>919028.96</v>
       </c>
       <c r="P337" t="n">
         <v>2500</v>
       </c>
       <c r="Q337" t="n">
-        <v>470000</v>
+        <v>3580000</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>C7560AC</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>TRICICLO INFANTIL OSITO C756AC</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -15633,7 +15639,7 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>10</v>
+        <v>276</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -15642,38 +15648,38 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>10</v>
+        <v>276</v>
       </c>
       <c r="N338" t="n">
-        <v>44113.603841808</v>
+        <v>7811.9</v>
       </c>
       <c r="O338" t="n">
-        <v>441136.03841808</v>
+        <v>2156084.4</v>
       </c>
       <c r="P338" t="n">
-        <v>71900</v>
+        <v>13900</v>
       </c>
       <c r="Q338" t="n">
-        <v>719000</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>7588228020244</v>
+        <v>6999899236130</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -15682,7 +15688,7 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>1432</v>
+        <v>460</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
@@ -15691,47 +15697,42 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>1432</v>
+        <v>460</v>
       </c>
       <c r="N339" t="n">
-        <v>641.78</v>
+        <v>3155</v>
       </c>
       <c r="O339" t="n">
-        <v>919028.96</v>
+        <v>1451300</v>
       </c>
       <c r="P339" t="n">
-        <v>2500</v>
+        <v>5900</v>
       </c>
       <c r="Q339" t="n">
-        <v>3580000</v>
+        <v>2714000</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C784</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>6999899236093</v>
+        <v>8913992935507</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J340" t="n">
-        <v>276</v>
+        <v>1450</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
@@ -15740,47 +15741,39 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>276</v>
+        <v>1450</v>
       </c>
       <c r="N340" t="n">
-        <v>7811.9</v>
+        <v>704.8968946963899</v>
       </c>
       <c r="O340" t="n">
-        <v>2156084.4</v>
+        <v>1022100.497309765</v>
       </c>
       <c r="P340" t="n">
-        <v>13900</v>
+        <v>900</v>
       </c>
       <c r="Q340" t="n">
-        <v>3836400</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>C7614-F</t>
-        </is>
-      </c>
-      <c r="B341" t="n">
-        <v>6999899236130</v>
+          <t>C815</t>
+        </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>SCOOTER HUMO</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J341" t="n">
-        <v>460</v>
+        <v>6</v>
       </c>
       <c r="K341" t="n">
         <v>0</v>
@@ -15789,33 +15782,33 @@
         <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>460</v>
+        <v>6</v>
       </c>
       <c r="N341" t="n">
-        <v>3155</v>
+        <v>110520.77</v>
       </c>
       <c r="O341" t="n">
-        <v>1451300</v>
+        <v>663124.62</v>
       </c>
       <c r="P341" t="n">
-        <v>5900</v>
+        <v>176900</v>
       </c>
       <c r="Q341" t="n">
-        <v>2714000</v>
+        <v>1061400</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>C784</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>8913992935507</v>
+        <v>2087202108190</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -15824,7 +15817,7 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>1450</v>
+        <v>468</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
@@ -15833,30 +15826,33 @@
         <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>1450</v>
+        <v>468</v>
       </c>
       <c r="N342" t="n">
-        <v>704.8968946963899</v>
+        <v>6761.25</v>
       </c>
       <c r="O342" t="n">
-        <v>1022100.497309765</v>
+        <v>3164265</v>
       </c>
       <c r="P342" t="n">
-        <v>900</v>
+        <v>5200</v>
       </c>
       <c r="Q342" t="n">
-        <v>1305000</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>C815</t>
-        </is>
+          <t>C84</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>2021010563031</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>SCOOTER HUMO</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -15865,7 +15861,7 @@
         </is>
       </c>
       <c r="J343" t="n">
-        <v>6</v>
+        <v>264</v>
       </c>
       <c r="K343" t="n">
         <v>0</v>
@@ -15874,33 +15870,35 @@
         <v>0</v>
       </c>
       <c r="M343" t="n">
-        <v>6</v>
+        <v>264</v>
       </c>
       <c r="N343" t="n">
-        <v>110520.77</v>
+        <v>1008.8165242718</v>
       </c>
       <c r="O343" t="n">
-        <v>663124.62</v>
+        <v>266327.5624077552</v>
       </c>
       <c r="P343" t="n">
-        <v>176900</v>
+        <v>1500</v>
       </c>
       <c r="Q343" t="n">
-        <v>1061400</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>C819</t>
-        </is>
-      </c>
-      <c r="B344" t="n">
-        <v>2087202108190</v>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
+        </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -15909,7 +15907,7 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>468</v>
+        <v>121</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
@@ -15918,42 +15916,49 @@
         <v>0</v>
       </c>
       <c r="M344" t="n">
-        <v>468</v>
+        <v>121</v>
       </c>
       <c r="N344" t="n">
-        <v>6761.25</v>
+        <v>1520</v>
       </c>
       <c r="O344" t="n">
-        <v>3164265</v>
+        <v>183920</v>
       </c>
       <c r="P344" t="n">
-        <v>5200</v>
+        <v>1900</v>
       </c>
       <c r="Q344" t="n">
-        <v>2433600</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B345" t="n">
-        <v>2021010563031</v>
+          <t>C880</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>cg2016213</t>
+        </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J345" t="n">
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="K345" t="n">
         <v>0</v>
@@ -15962,35 +15967,30 @@
         <v>0</v>
       </c>
       <c r="M345" t="n">
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="N345" t="n">
-        <v>1008.8166794626</v>
+        <v>1520</v>
       </c>
       <c r="O345" t="n">
-        <v>266327.6033781264</v>
+        <v>304000</v>
       </c>
       <c r="P345" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q345" t="n">
-        <v>396000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>C879</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>CG-2016-212</t>
+          <t>C888</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -15999,7 +15999,7 @@
         </is>
       </c>
       <c r="J346" t="n">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="K346" t="n">
         <v>0</v>
@@ -16008,40 +16008,35 @@
         <v>0</v>
       </c>
       <c r="M346" t="n">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="N346" t="n">
-        <v>1520</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O346" t="n">
-        <v>183920</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P346" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q346" t="n">
-        <v>229900</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>C880</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>cg2016213</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
+          <t>SNORKEL 66046A</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -16050,7 +16045,7 @@
         </is>
       </c>
       <c r="J347" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="K347" t="n">
         <v>0</v>
@@ -16059,39 +16054,44 @@
         <v>0</v>
       </c>
       <c r="M347" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="N347" t="n">
-        <v>1520</v>
+        <v>13493.858308157</v>
       </c>
       <c r="O347" t="n">
-        <v>304000</v>
+        <v>2415400.637160103</v>
       </c>
       <c r="P347" t="n">
-        <v>1900</v>
+        <v>16900</v>
       </c>
       <c r="Q347" t="n">
-        <v>380000</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J348" t="n">
-        <v>169</v>
+        <v>347</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
@@ -16100,35 +16100,40 @@
         <v>0</v>
       </c>
       <c r="M348" t="n">
-        <v>169</v>
+        <v>347</v>
       </c>
       <c r="N348" t="n">
-        <v>1213.6821400778</v>
+        <v>2644.9</v>
       </c>
       <c r="O348" t="n">
-        <v>205112.2816731482</v>
+        <v>917780.3</v>
       </c>
       <c r="P348" t="n">
-        <v>1500</v>
+        <v>3900</v>
       </c>
       <c r="Q348" t="n">
-        <v>253500</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -16137,7 +16142,7 @@
         </is>
       </c>
       <c r="J349" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="K349" t="n">
         <v>0</v>
@@ -16146,35 +16151,35 @@
         <v>0</v>
       </c>
       <c r="M349" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="N349" t="n">
-        <v>13493.858308157</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O349" t="n">
-        <v>2415400.637160103</v>
+        <v>33759.88</v>
       </c>
       <c r="P349" t="n">
-        <v>16900</v>
+        <v>29500</v>
       </c>
       <c r="Q349" t="n">
-        <v>3025100</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -16183,7 +16188,7 @@
         </is>
       </c>
       <c r="J350" t="n">
-        <v>347</v>
+        <v>18</v>
       </c>
       <c r="K350" t="n">
         <v>0</v>
@@ -16192,40 +16197,40 @@
         <v>0</v>
       </c>
       <c r="M350" t="n">
-        <v>347</v>
+        <v>18</v>
       </c>
       <c r="N350" t="n">
-        <v>2644.9</v>
+        <v>12189.832</v>
       </c>
       <c r="O350" t="n">
-        <v>917780.3</v>
+        <v>219416.976</v>
       </c>
       <c r="P350" t="n">
-        <v>3900</v>
+        <v>30900</v>
       </c>
       <c r="Q350" t="n">
-        <v>1353300</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>MG16332</t>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>MG16332</t>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -16234,7 +16239,7 @@
         </is>
       </c>
       <c r="J351" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="K351" t="n">
         <v>0</v>
@@ -16243,35 +16248,35 @@
         <v>0</v>
       </c>
       <c r="M351" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="N351" t="n">
-        <v>8439.969999999999</v>
+        <v>15452.21</v>
       </c>
       <c r="O351" t="n">
-        <v>33759.88</v>
+        <v>741706.08</v>
       </c>
       <c r="P351" t="n">
-        <v>29500</v>
+        <v>36500</v>
       </c>
       <c r="Q351" t="n">
-        <v>118000</v>
+        <v>1752000</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -16280,7 +16285,7 @@
         </is>
       </c>
       <c r="J352" t="n">
-        <v>18</v>
+        <v>363</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
@@ -16289,40 +16294,40 @@
         <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>18</v>
+        <v>363</v>
       </c>
       <c r="N352" t="n">
-        <v>12189.832</v>
+        <v>571.87</v>
       </c>
       <c r="O352" t="n">
-        <v>219416.976</v>
+        <v>207588.81</v>
       </c>
       <c r="P352" t="n">
-        <v>30900</v>
+        <v>2500</v>
       </c>
       <c r="Q352" t="n">
-        <v>556200</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>MG30151</t>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>MG30151</t>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -16331,7 +16336,7 @@
         </is>
       </c>
       <c r="J353" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="K353" t="n">
         <v>0</v>
@@ -16340,115 +16345,18 @@
         <v>0</v>
       </c>
       <c r="M353" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="N353" t="n">
-        <v>15452.21</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O353" t="n">
-        <v>741706.08</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P353" t="n">
-        <v>36500</v>
+        <v>15900</v>
       </c>
       <c r="Q353" t="n">
-        <v>1752000</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>MG40210</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>SONAJERO OSO MG40210</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J354" t="n">
-        <v>363</v>
-      </c>
-      <c r="K354" t="n">
-        <v>0</v>
-      </c>
-      <c r="L354" t="n">
-        <v>0</v>
-      </c>
-      <c r="M354" t="n">
-        <v>363</v>
-      </c>
-      <c r="N354" t="n">
-        <v>571.87</v>
-      </c>
-      <c r="O354" t="n">
-        <v>207588.81</v>
-      </c>
-      <c r="P354" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q354" t="n">
-        <v>907500</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J355" t="n">
-        <v>64</v>
-      </c>
-      <c r="K355" t="n">
-        <v>0</v>
-      </c>
-      <c r="L355" t="n">
-        <v>0</v>
-      </c>
-      <c r="M355" t="n">
-        <v>64</v>
-      </c>
-      <c r="N355" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O355" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P355" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q355" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -1519,10 +1519,10 @@
         <v>20</v>
       </c>
       <c r="N28" t="n">
-        <v>9392.075000000001</v>
+        <v>9392.0750746269</v>
       </c>
       <c r="O28" t="n">
-        <v>187841.5</v>
+        <v>187841.501492538</v>
       </c>
       <c r="P28" t="n">
         <v>18500</v>
@@ -3195,10 +3195,10 @@
         <v>350</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2555555556</v>
+        <v>2582.2555535714</v>
       </c>
       <c r="O67" t="n">
-        <v>903789.44444446</v>
+        <v>903789.44374999</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-02</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>376</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464583333</v>
+        <v>3376.7464524986</v>
       </c>
       <c r="O8" t="n">
-        <v>1269656.668333321</v>
+        <v>1269656.666139473</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1472,10 +1472,10 @@
         <v>119</v>
       </c>
       <c r="N27" t="n">
-        <v>3910.6280686695</v>
+        <v>3910.6280519481</v>
       </c>
       <c r="O27" t="n">
-        <v>465364.7401716705</v>
+        <v>465364.7381818239</v>
       </c>
       <c r="P27" t="n">
         <v>9100</v>
@@ -3195,10 +3195,10 @@
         <v>350</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2555535714</v>
+        <v>2582.255546613</v>
       </c>
       <c r="O67" t="n">
-        <v>903789.44374999</v>
+        <v>903789.4413145501</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
@@ -3241,10 +3241,10 @@
         <v>1312</v>
       </c>
       <c r="N68" t="n">
-        <v>5216.89608155</v>
+        <v>5216.8960627633</v>
       </c>
       <c r="O68" t="n">
-        <v>6844567.658993601</v>
+        <v>6844567.63434545</v>
       </c>
       <c r="P68" t="n">
         <v>8500</v>
@@ -3287,10 +3287,10 @@
         <v>2592</v>
       </c>
       <c r="N69" t="n">
-        <v>3158.8608285041</v>
+        <v>3158.8608303391</v>
       </c>
       <c r="O69" t="n">
-        <v>8187767.267482627</v>
+        <v>8187767.272238947</v>
       </c>
       <c r="P69" t="n">
         <v>5600</v>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3330,19 +3330,19 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N70" t="n">
-        <v>3841.6248454636</v>
+        <v>3841.62486</v>
       </c>
       <c r="O70" t="n">
-        <v>295805.1131006972</v>
+        <v>284280.23964</v>
       </c>
       <c r="P70" t="n">
         <v>6900</v>
       </c>
       <c r="Q70" t="n">
-        <v>531300</v>
+        <v>510600</v>
       </c>
     </row>
     <row r="71">
@@ -3471,10 +3471,10 @@
         <v>648</v>
       </c>
       <c r="N73" t="n">
-        <v>3795.7100075672</v>
+        <v>3795.7100075815</v>
       </c>
       <c r="O73" t="n">
-        <v>2459620.084903546</v>
+        <v>2459620.084912812</v>
       </c>
       <c r="P73" t="n">
         <v>6200</v>
@@ -3878,10 +3878,10 @@
         <v>240</v>
       </c>
       <c r="N82" t="n">
-        <v>3594.2538892425</v>
+        <v>3594.2538618926</v>
       </c>
       <c r="O82" t="n">
-        <v>862620.9334182</v>
+        <v>862620.9268542241</v>
       </c>
       <c r="P82" t="n">
         <v>6500</v>
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107914851</v>
+        <v>4372.2107916548</v>
       </c>
       <c r="O94" t="n">
-        <v>5928717.833253796</v>
+        <v>5928717.833483909</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -5205,19 +5205,19 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="N111" t="n">
         <v>11921.4</v>
       </c>
       <c r="O111" t="n">
-        <v>5865328.8</v>
+        <v>5150044.8</v>
       </c>
       <c r="P111" t="n">
         <v>19900</v>
       </c>
       <c r="Q111" t="n">
-        <v>9790800</v>
+        <v>8596800</v>
       </c>
     </row>
     <row r="112">
@@ -5750,10 +5750,10 @@
         <v>480</v>
       </c>
       <c r="N123" t="n">
-        <v>4196.8725305216</v>
+        <v>4196.872531224</v>
       </c>
       <c r="O123" t="n">
-        <v>2014498.814650368</v>
+        <v>2014498.81498752</v>
       </c>
       <c r="P123" t="n">
         <v>5900</v>
@@ -6370,10 +6370,10 @@
         <v>36</v>
       </c>
       <c r="N137" t="n">
-        <v>4285.195740113</v>
+        <v>4285.1957531144</v>
       </c>
       <c r="O137" t="n">
-        <v>154267.046644068</v>
+        <v>154267.0471121184</v>
       </c>
       <c r="P137" t="n">
         <v>6900</v>
@@ -6544,10 +6544,10 @@
         <v>228</v>
       </c>
       <c r="N141" t="n">
-        <v>4605.2147497639</v>
+        <v>4605.2147542533</v>
       </c>
       <c r="O141" t="n">
-        <v>1049988.962946169</v>
+        <v>1049988.963969752</v>
       </c>
       <c r="P141" t="n">
         <v>7600</v>
@@ -6994,10 +6994,10 @@
         <v>144</v>
       </c>
       <c r="N151" t="n">
-        <v>27123.765196998</v>
+        <v>27123.76518797</v>
       </c>
       <c r="O151" t="n">
-        <v>3905822.188367712</v>
+        <v>3905822.18706768</v>
       </c>
       <c r="P151" t="n">
         <v>44500</v>
@@ -7989,10 +7989,10 @@
         <v>11</v>
       </c>
       <c r="N173" t="n">
-        <v>23521.624067797</v>
+        <v>23521.623965517</v>
       </c>
       <c r="O173" t="n">
-        <v>258737.864745767</v>
+        <v>258737.863620687</v>
       </c>
       <c r="P173" t="n">
         <v>39000</v>
@@ -8081,10 +8081,10 @@
         <v>680</v>
       </c>
       <c r="N175" t="n">
-        <v>1778.4726494689</v>
+        <v>1778.4726526892</v>
       </c>
       <c r="O175" t="n">
-        <v>1209361.401638852</v>
+        <v>1209361.403828656</v>
       </c>
       <c r="P175" t="n">
         <v>4900</v>
@@ -9602,10 +9602,10 @@
         <v>280</v>
       </c>
       <c r="N208" t="n">
-        <v>3903.736877898</v>
+        <v>3903.7369302326</v>
       </c>
       <c r="O208" t="n">
-        <v>1093046.32581144</v>
+        <v>1093046.340465128</v>
       </c>
       <c r="P208" t="n">
         <v>7500</v>
@@ -12355,10 +12355,10 @@
         <v>1152</v>
       </c>
       <c r="N268" t="n">
-        <v>1516.0387919529</v>
+        <v>1516.0387905286</v>
       </c>
       <c r="O268" t="n">
-        <v>1746476.688329741</v>
+        <v>1746476.686688947</v>
       </c>
       <c r="P268" t="n">
         <v>2300</v>
@@ -12951,10 +12951,10 @@
         <v>1440</v>
       </c>
       <c r="N281" t="n">
-        <v>1690.8700091743</v>
+        <v>1690.8700092251</v>
       </c>
       <c r="O281" t="n">
-        <v>2434852.813210992</v>
+        <v>2434852.813284144</v>
       </c>
       <c r="P281" t="n">
         <v>3000</v>
@@ -13505,10 +13505,10 @@
         <v>15732</v>
       </c>
       <c r="N293" t="n">
-        <v>703.79510612101</v>
+        <v>703.79509062003</v>
       </c>
       <c r="O293" t="n">
-        <v>11072104.60949573</v>
+        <v>11072104.36563431</v>
       </c>
       <c r="P293" t="n">
         <v>900</v>
@@ -14506,10 +14506,10 @@
         <v>21</v>
       </c>
       <c r="N314" t="n">
-        <v>2992.5698684211</v>
+        <v>2992.57</v>
       </c>
       <c r="O314" t="n">
-        <v>62843.96723684311</v>
+        <v>62843.97</v>
       </c>
       <c r="P314" t="n">
         <v>6000</v>
@@ -15873,10 +15873,10 @@
         <v>264</v>
       </c>
       <c r="N343" t="n">
-        <v>1008.8165242718</v>
+        <v>1008.8156907216</v>
       </c>
       <c r="O343" t="n">
-        <v>266327.5624077552</v>
+        <v>266327.3423505024</v>
       </c>
       <c r="P343" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -3195,10 +3195,10 @@
         <v>350</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.255546613</v>
+        <v>2582.2555436242</v>
       </c>
       <c r="O67" t="n">
-        <v>903789.4413145501</v>
+        <v>903789.44026847</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
@@ -7086,10 +7086,10 @@
         <v>221</v>
       </c>
       <c r="N153" t="n">
-        <v>8332.779621212099</v>
+        <v>8332.779620253201</v>
       </c>
       <c r="O153" t="n">
-        <v>1841544.296287874</v>
+        <v>1841544.296075957</v>
       </c>
       <c r="P153" t="n">
         <v>14900</v>
@@ -10880,10 +10880,10 @@
         <v>192</v>
       </c>
       <c r="N236" t="n">
-        <v>17075.989522491</v>
+        <v>17075.989522161</v>
       </c>
       <c r="O236" t="n">
-        <v>3278589.988318272</v>
+        <v>3278589.988254912</v>
       </c>
       <c r="P236" t="n">
         <v>27500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>376</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464524986</v>
+        <v>3376.7464515243</v>
       </c>
       <c r="O8" t="n">
-        <v>1269656.666139473</v>
+        <v>1269656.665773137</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1199,10 +1199,10 @@
         <v>180</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8370954357</v>
+        <v>3926.8370909091</v>
       </c>
       <c r="O20" t="n">
-        <v>706830.6771784261</v>
+        <v>706830.676363638</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1433,10 +1433,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>15403.520977011</v>
+        <v>15403.521040462</v>
       </c>
       <c r="O26" t="n">
-        <v>261859.856609187</v>
+        <v>261859.857687854</v>
       </c>
       <c r="P26" t="n">
         <v>33500</v>
@@ -1472,10 +1472,10 @@
         <v>119</v>
       </c>
       <c r="N27" t="n">
-        <v>3910.6280519481</v>
+        <v>3910.6280349345</v>
       </c>
       <c r="O27" t="n">
-        <v>465364.7381818239</v>
+        <v>465364.7361572055</v>
       </c>
       <c r="P27" t="n">
         <v>9100</v>
@@ -1863,10 +1863,10 @@
         <v>36</v>
       </c>
       <c r="N36" t="n">
-        <v>200072.20075</v>
+        <v>200072.20121739</v>
       </c>
       <c r="O36" t="n">
-        <v>7202599.227</v>
+        <v>7202599.243826039</v>
       </c>
       <c r="P36" t="n">
         <v>312000</v>
@@ -3195,10 +3195,10 @@
         <v>350</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2555436242</v>
+        <v>2582.2555195682</v>
       </c>
       <c r="O67" t="n">
-        <v>903789.44026847</v>
+        <v>903789.4318488699</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
@@ -3241,10 +3241,10 @@
         <v>1312</v>
       </c>
       <c r="N68" t="n">
-        <v>5216.8960627633</v>
+        <v>5216.8960541642</v>
       </c>
       <c r="O68" t="n">
-        <v>6844567.63434545</v>
+        <v>6844567.62306343</v>
       </c>
       <c r="P68" t="n">
         <v>8500</v>
@@ -3471,10 +3471,10 @@
         <v>648</v>
       </c>
       <c r="N73" t="n">
-        <v>3795.7100075815</v>
+        <v>3795.7100075887</v>
       </c>
       <c r="O73" t="n">
-        <v>2459620.084912812</v>
+        <v>2459620.084917478</v>
       </c>
       <c r="P73" t="n">
         <v>6200</v>
@@ -3650,10 +3650,10 @@
         <v>346</v>
       </c>
       <c r="N77" t="n">
-        <v>4890.9300489596</v>
+        <v>4890.9300493218</v>
       </c>
       <c r="O77" t="n">
-        <v>1692261.796940021</v>
+        <v>1692261.797065343</v>
       </c>
       <c r="P77" t="n">
         <v>8200</v>
@@ -3878,10 +3878,10 @@
         <v>240</v>
       </c>
       <c r="N82" t="n">
-        <v>3594.2538618926</v>
+        <v>3594.2537131631</v>
       </c>
       <c r="O82" t="n">
-        <v>862620.9268542241</v>
+        <v>862620.891159144</v>
       </c>
       <c r="P82" t="n">
         <v>6500</v>
@@ -4060,10 +4060,10 @@
         <v>3200</v>
       </c>
       <c r="N86" t="n">
-        <v>616.01871837471</v>
+        <v>616.01871807046</v>
       </c>
       <c r="O86" t="n">
-        <v>1971259.898799072</v>
+        <v>1971259.897825472</v>
       </c>
       <c r="P86" t="n">
         <v>800</v>
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107916548</v>
+        <v>4372.2107917679</v>
       </c>
       <c r="O94" t="n">
-        <v>5928717.833483909</v>
+        <v>5928717.833637273</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -5750,10 +5750,10 @@
         <v>480</v>
       </c>
       <c r="N123" t="n">
-        <v>4196.872531224</v>
+        <v>4196.8725319267</v>
       </c>
       <c r="O123" t="n">
-        <v>2014498.81498752</v>
+        <v>2014498.815324816</v>
       </c>
       <c r="P123" t="n">
         <v>5900</v>
@@ -5965,10 +5965,10 @@
         <v>528</v>
       </c>
       <c r="N128" t="n">
-        <v>22485.695561036</v>
+        <v>22485.695555556</v>
       </c>
       <c r="O128" t="n">
-        <v>11872447.25622701</v>
+        <v>11872447.25333357</v>
       </c>
       <c r="P128" t="n">
         <v>36500</v>
@@ -6137,10 +6137,10 @@
         <v>310</v>
       </c>
       <c r="N132" t="n">
-        <v>2680.7396948941</v>
+        <v>2680.739694704</v>
       </c>
       <c r="O132" t="n">
-        <v>831029.305417171</v>
+        <v>831029.30535824</v>
       </c>
       <c r="P132" t="n">
         <v>4900</v>
@@ -6994,10 +6994,10 @@
         <v>144</v>
       </c>
       <c r="N151" t="n">
-        <v>27123.76518797</v>
+        <v>27123.765160681</v>
       </c>
       <c r="O151" t="n">
-        <v>3905822.18706768</v>
+        <v>3905822.183138064</v>
       </c>
       <c r="P151" t="n">
         <v>44500</v>
@@ -8081,10 +8081,10 @@
         <v>680</v>
       </c>
       <c r="N175" t="n">
-        <v>1778.4726526892</v>
+        <v>1778.4726559172</v>
       </c>
       <c r="O175" t="n">
-        <v>1209361.403828656</v>
+        <v>1209361.406023696</v>
       </c>
       <c r="P175" t="n">
         <v>4900</v>
@@ -9602,10 +9602,10 @@
         <v>280</v>
       </c>
       <c r="N208" t="n">
-        <v>3903.7369302326</v>
+        <v>3903.736969697</v>
       </c>
       <c r="O208" t="n">
-        <v>1093046.340465128</v>
+        <v>1093046.35151516</v>
       </c>
       <c r="P208" t="n">
         <v>7500</v>
@@ -9960,10 +9960,10 @@
         <v>144</v>
       </c>
       <c r="N216" t="n">
-        <v>5869.1726051282</v>
+        <v>5869.1725975359</v>
       </c>
       <c r="O216" t="n">
-        <v>845160.8551384609</v>
+        <v>845160.8540451697</v>
       </c>
       <c r="P216" t="n">
         <v>9500</v>
@@ -10040,7 +10040,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>792</v>
+        <v>702</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -10049,19 +10049,19 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>792</v>
+        <v>702</v>
       </c>
       <c r="N218" t="n">
         <v>5772</v>
       </c>
       <c r="O218" t="n">
-        <v>4571424</v>
+        <v>4051944</v>
       </c>
       <c r="P218" t="n">
         <v>9900</v>
       </c>
       <c r="Q218" t="n">
-        <v>7840800</v>
+        <v>6949800</v>
       </c>
     </row>
     <row r="219">
@@ -12355,10 +12355,10 @@
         <v>1152</v>
       </c>
       <c r="N268" t="n">
-        <v>1516.0387905286</v>
+        <v>1516.0387891009</v>
       </c>
       <c r="O268" t="n">
-        <v>1746476.686688947</v>
+        <v>1746476.685044237</v>
       </c>
       <c r="P268" t="n">
         <v>2300</v>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>4896</v>
+        <v>4464</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -12580,19 +12580,19 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>4896</v>
+        <v>4464</v>
       </c>
       <c r="N273" t="n">
         <v>1801</v>
       </c>
       <c r="O273" t="n">
-        <v>8817696</v>
+        <v>8039664</v>
       </c>
       <c r="P273" t="n">
         <v>2900</v>
       </c>
       <c r="Q273" t="n">
-        <v>14198400</v>
+        <v>12945600</v>
       </c>
     </row>
     <row r="274">
@@ -12951,10 +12951,10 @@
         <v>1440</v>
       </c>
       <c r="N281" t="n">
-        <v>1690.8700092251</v>
+        <v>1690.8700092336</v>
       </c>
       <c r="O281" t="n">
-        <v>2434852.813284144</v>
+        <v>2434852.813296384</v>
       </c>
       <c r="P281" t="n">
         <v>3000</v>
@@ -13505,10 +13505,10 @@
         <v>15732</v>
       </c>
       <c r="N293" t="n">
-        <v>703.79509062003</v>
+        <v>703.79502188713</v>
       </c>
       <c r="O293" t="n">
-        <v>11072104.36563431</v>
+        <v>11072103.28432833</v>
       </c>
       <c r="P293" t="n">
         <v>900</v>
@@ -14506,10 +14506,10 @@
         <v>21</v>
       </c>
       <c r="N314" t="n">
-        <v>2992.57</v>
+        <v>2992.5702739726</v>
       </c>
       <c r="O314" t="n">
-        <v>62843.97</v>
+        <v>62843.97575342459</v>
       </c>
       <c r="P314" t="n">
         <v>6000</v>
@@ -15553,10 +15553,10 @@
         <v>10</v>
       </c>
       <c r="N336" t="n">
-        <v>44113.603841808</v>
+        <v>44113.603953488</v>
       </c>
       <c r="O336" t="n">
-        <v>441136.03841808</v>
+        <v>441136.03953488</v>
       </c>
       <c r="P336" t="n">
         <v>71900</v>
@@ -15688,7 +15688,7 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>460</v>
+        <v>382</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
@@ -15697,19 +15697,19 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>460</v>
+        <v>382</v>
       </c>
       <c r="N339" t="n">
         <v>3155</v>
       </c>
       <c r="O339" t="n">
-        <v>1451300</v>
+        <v>1205210</v>
       </c>
       <c r="P339" t="n">
         <v>5900</v>
       </c>
       <c r="Q339" t="n">
-        <v>2714000</v>
+        <v>2253800</v>
       </c>
     </row>
     <row r="340">
@@ -15873,10 +15873,10 @@
         <v>264</v>
       </c>
       <c r="N343" t="n">
-        <v>1008.8156907216</v>
+        <v>1008.8155114823</v>
       </c>
       <c r="O343" t="n">
-        <v>266327.3423505024</v>
+        <v>266327.2950313272</v>
       </c>
       <c r="P343" t="n">
         <v>1500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -3425,10 +3425,10 @@
         <v>576</v>
       </c>
       <c r="N72" t="n">
-        <v>5002</v>
+        <v>5013.3940774487</v>
       </c>
       <c r="O72" t="n">
-        <v>2881152</v>
+        <v>2887714.988610451</v>
       </c>
       <c r="P72" t="n">
         <v>8400</v>
@@ -3650,10 +3650,10 @@
         <v>346</v>
       </c>
       <c r="N77" t="n">
-        <v>4890.9300493218</v>
+        <v>4890.9300493827</v>
       </c>
       <c r="O77" t="n">
-        <v>1692261.797065343</v>
+        <v>1692261.797086414</v>
       </c>
       <c r="P77" t="n">
         <v>8200</v>
@@ -4104,10 +4104,10 @@
         <v>2346</v>
       </c>
       <c r="N87" t="n">
-        <v>2090.85</v>
+        <v>2092.643951094</v>
       </c>
       <c r="O87" t="n">
-        <v>4905134.1</v>
+        <v>4909342.709266524</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107917679</v>
+        <v>4372.2107918811</v>
       </c>
       <c r="O94" t="n">
-        <v>5928717.833637273</v>
+        <v>5928717.833790772</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -12355,10 +12355,10 @@
         <v>1152</v>
       </c>
       <c r="N268" t="n">
-        <v>1516.0387891009</v>
+        <v>1517.8304441599</v>
       </c>
       <c r="O268" t="n">
-        <v>1746476.685044237</v>
+        <v>1748540.671672205</v>
       </c>
       <c r="P268" t="n">
         <v>2300</v>
@@ -13505,10 +13505,10 @@
         <v>15732</v>
       </c>
       <c r="N293" t="n">
-        <v>703.79502188713</v>
+        <v>703.79501848956</v>
       </c>
       <c r="O293" t="n">
-        <v>11072103.28432833</v>
+        <v>11072103.23087776</v>
       </c>
       <c r="P293" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-04</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -1472,10 +1472,10 @@
         <v>119</v>
       </c>
       <c r="N27" t="n">
-        <v>3910.6280349345</v>
+        <v>3910.6280306346</v>
       </c>
       <c r="O27" t="n">
-        <v>465364.7361572055</v>
+        <v>465364.7356455174</v>
       </c>
       <c r="P27" t="n">
         <v>9100</v>
@@ -1863,10 +1863,10 @@
         <v>36</v>
       </c>
       <c r="N36" t="n">
-        <v>200072.20121739</v>
+        <v>200072.20172727</v>
       </c>
       <c r="O36" t="n">
-        <v>7202599.243826039</v>
+        <v>7202599.26218172</v>
       </c>
       <c r="P36" t="n">
         <v>312000</v>
@@ -1910,10 +1910,10 @@
         <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>344599.1786</v>
+        <v>344599.17851064</v>
       </c>
       <c r="O37" t="n">
-        <v>2067595.0716</v>
+        <v>2067595.07106384</v>
       </c>
       <c r="P37" t="n">
         <v>532900</v>
@@ -3195,10 +3195,10 @@
         <v>350</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2555195682</v>
+        <v>2582.2555145238</v>
       </c>
       <c r="O67" t="n">
-        <v>903789.4318488699</v>
+        <v>903789.4300833299</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>1312</v>
+        <v>1232</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3238,19 +3238,19 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1312</v>
+        <v>1232</v>
       </c>
       <c r="N68" t="n">
-        <v>5216.8960541642</v>
+        <v>5216.8960524399</v>
       </c>
       <c r="O68" t="n">
-        <v>6844567.62306343</v>
+        <v>6427215.936605956</v>
       </c>
       <c r="P68" t="n">
         <v>8500</v>
       </c>
       <c r="Q68" t="n">
-        <v>11152000</v>
+        <v>10472000</v>
       </c>
     </row>
     <row r="69">
@@ -3287,10 +3287,10 @@
         <v>2592</v>
       </c>
       <c r="N69" t="n">
-        <v>3158.8608303391</v>
+        <v>3158.8608305026</v>
       </c>
       <c r="O69" t="n">
-        <v>8187767.272238947</v>
+        <v>8187767.272662739</v>
       </c>
       <c r="P69" t="n">
         <v>5600</v>
@@ -3425,10 +3425,10 @@
         <v>576</v>
       </c>
       <c r="N72" t="n">
-        <v>5013.3940774487</v>
+        <v>5002</v>
       </c>
       <c r="O72" t="n">
-        <v>2887714.988610451</v>
+        <v>2881152</v>
       </c>
       <c r="P72" t="n">
         <v>8400</v>
@@ -3878,10 +3878,10 @@
         <v>240</v>
       </c>
       <c r="N82" t="n">
-        <v>3594.2537131631</v>
+        <v>3594.2536883629</v>
       </c>
       <c r="O82" t="n">
-        <v>862620.891159144</v>
+        <v>862620.885207096</v>
       </c>
       <c r="P82" t="n">
         <v>6500</v>
@@ -4104,10 +4104,10 @@
         <v>2346</v>
       </c>
       <c r="N87" t="n">
-        <v>2092.643951094</v>
+        <v>2090.85</v>
       </c>
       <c r="O87" t="n">
-        <v>4909342.709266524</v>
+        <v>4905134.1</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.2107918811</v>
+        <v>4372.2107921642</v>
       </c>
       <c r="O94" t="n">
-        <v>5928717.833790772</v>
+        <v>5928717.834174655</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -5750,10 +5750,10 @@
         <v>480</v>
       </c>
       <c r="N123" t="n">
-        <v>4196.8725319267</v>
+        <v>4196.8725326298</v>
       </c>
       <c r="O123" t="n">
-        <v>2014498.815324816</v>
+        <v>2014498.815662304</v>
       </c>
       <c r="P123" t="n">
         <v>5900</v>
@@ -5924,10 +5924,10 @@
         <v>432</v>
       </c>
       <c r="N127" t="n">
-        <v>2029.8739515279</v>
+        <v>2029.873953611</v>
       </c>
       <c r="O127" t="n">
-        <v>876905.5470600529</v>
+        <v>876905.5479599519</v>
       </c>
       <c r="P127" t="n">
         <v>3600</v>
@@ -6370,10 +6370,10 @@
         <v>36</v>
       </c>
       <c r="N137" t="n">
-        <v>4285.1957531144</v>
+        <v>4285.1957990868</v>
       </c>
       <c r="O137" t="n">
-        <v>154267.0471121184</v>
+        <v>154267.0487671248</v>
       </c>
       <c r="P137" t="n">
         <v>6900</v>
@@ -6544,10 +6544,10 @@
         <v>228</v>
       </c>
       <c r="N141" t="n">
-        <v>4605.2147542533</v>
+        <v>4605.2147677725</v>
       </c>
       <c r="O141" t="n">
-        <v>1049988.963969752</v>
+        <v>1049988.96705213</v>
       </c>
       <c r="P141" t="n">
         <v>7600</v>
@@ -6994,10 +6994,10 @@
         <v>144</v>
       </c>
       <c r="N151" t="n">
-        <v>27123.765160681</v>
+        <v>27123.765142315</v>
       </c>
       <c r="O151" t="n">
-        <v>3905822.183138064</v>
+        <v>3905822.18049336</v>
       </c>
       <c r="P151" t="n">
         <v>44500</v>
@@ -7086,10 +7086,10 @@
         <v>221</v>
       </c>
       <c r="N153" t="n">
-        <v>8332.779620253201</v>
+        <v>8332.7796143959</v>
       </c>
       <c r="O153" t="n">
-        <v>1841544.296075957</v>
+        <v>1841544.294781494</v>
       </c>
       <c r="P153" t="n">
         <v>14900</v>
@@ -8081,10 +8081,10 @@
         <v>680</v>
       </c>
       <c r="N175" t="n">
-        <v>1778.4726559172</v>
+        <v>1778.4726787358</v>
       </c>
       <c r="O175" t="n">
-        <v>1209361.406023696</v>
+        <v>1209361.421540344</v>
       </c>
       <c r="P175" t="n">
         <v>4900</v>
@@ -9602,10 +9602,10 @@
         <v>280</v>
       </c>
       <c r="N208" t="n">
-        <v>3903.736969697</v>
+        <v>3903.7370093458</v>
       </c>
       <c r="O208" t="n">
-        <v>1093046.35151516</v>
+        <v>1093046.362616824</v>
       </c>
       <c r="P208" t="n">
         <v>7500</v>
@@ -9960,10 +9960,10 @@
         <v>144</v>
       </c>
       <c r="N216" t="n">
-        <v>5869.1725975359</v>
+        <v>5869.1725823045</v>
       </c>
       <c r="O216" t="n">
-        <v>845160.8540451697</v>
+        <v>845160.851851848</v>
       </c>
       <c r="P216" t="n">
         <v>9500</v>
@@ -12355,10 +12355,10 @@
         <v>1152</v>
       </c>
       <c r="N268" t="n">
-        <v>1517.8304441599</v>
+        <v>1516.0387847976</v>
       </c>
       <c r="O268" t="n">
-        <v>1748540.671672205</v>
+        <v>1746476.680086835</v>
       </c>
       <c r="P268" t="n">
         <v>2300</v>
@@ -12951,10 +12951,10 @@
         <v>1440</v>
       </c>
       <c r="N281" t="n">
-        <v>1690.8700092336</v>
+        <v>1690.8700092421</v>
       </c>
       <c r="O281" t="n">
-        <v>2434852.813296384</v>
+        <v>2434852.813308624</v>
       </c>
       <c r="P281" t="n">
         <v>3000</v>
@@ -13505,10 +13505,10 @@
         <v>15732</v>
       </c>
       <c r="N293" t="n">
-        <v>703.79501848956</v>
+        <v>703.79500857932</v>
       </c>
       <c r="O293" t="n">
-        <v>11072103.23087776</v>
+        <v>11072103.07496986</v>
       </c>
       <c r="P293" t="n">
         <v>900</v>
@@ -15415,10 +15415,10 @@
         <v>499</v>
       </c>
       <c r="N333" t="n">
-        <v>7046.9398275862</v>
+        <v>7046.9398275119</v>
       </c>
       <c r="O333" t="n">
-        <v>3516422.973965514</v>
+        <v>3516422.973928438</v>
       </c>
       <c r="P333" t="n">
         <v>9900</v>
@@ -15861,7 +15861,7 @@
         </is>
       </c>
       <c r="J343" t="n">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="K343" t="n">
         <v>0</v>
@@ -15870,19 +15870,19 @@
         <v>0</v>
       </c>
       <c r="M343" t="n">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="N343" t="n">
-        <v>1008.8155114823</v>
+        <v>1008.8149457701</v>
       </c>
       <c r="O343" t="n">
-        <v>266327.2950313272</v>
+        <v>248168.4766594446</v>
       </c>
       <c r="P343" t="n">
         <v>1500</v>
       </c>
       <c r="Q343" t="n">
-        <v>396000</v>
+        <v>369000</v>
       </c>
     </row>
     <row r="344">

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -3195,10 +3195,10 @@
         <v>350</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2555145238</v>
+        <v>2582.2555084555</v>
       </c>
       <c r="O67" t="n">
-        <v>903789.4300833299</v>
+        <v>903789.427959425</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
@@ -3333,10 +3333,10 @@
         <v>74</v>
       </c>
       <c r="N70" t="n">
-        <v>3841.62486</v>
+        <v>3841.6248746239</v>
       </c>
       <c r="O70" t="n">
-        <v>284280.23964</v>
+        <v>284280.2407221686</v>
       </c>
       <c r="P70" t="n">
         <v>6900</v>
@@ -13505,10 +13505,10 @@
         <v>15732</v>
       </c>
       <c r="N293" t="n">
-        <v>703.79500857932</v>
+        <v>703.79500789654</v>
       </c>
       <c r="O293" t="n">
-        <v>11072103.07496986</v>
+        <v>11072103.06422837</v>
       </c>
       <c r="P293" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -642,10 +642,10 @@
         <v>275</v>
       </c>
       <c r="N6" t="n">
-        <v>27035.809018568</v>
+        <v>27000</v>
       </c>
       <c r="O6" t="n">
-        <v>7434847.4801062</v>
+        <v>7425000</v>
       </c>
       <c r="P6" t="n">
         <v>20000</v>
@@ -4427,10 +4427,10 @@
         <v>1356</v>
       </c>
       <c r="N94" t="n">
-        <v>4372.5234503719</v>
+        <v>4372.2107923341</v>
       </c>
       <c r="O94" t="n">
-        <v>5929141.798704296</v>
+        <v>5928717.834405039</v>
       </c>
       <c r="P94" t="n">
         <v>7500</v>
@@ -4612,10 +4612,10 @@
         <v>4733</v>
       </c>
       <c r="N98" t="n">
-        <v>17473.953844316</v>
+        <v>17472.91</v>
       </c>
       <c r="O98" t="n">
-        <v>82704223.54514764</v>
+        <v>82699283.03</v>
       </c>
       <c r="P98" t="n">
         <v>2900</v>
@@ -4700,10 +4700,10 @@
         <v>4735</v>
       </c>
       <c r="N100" t="n">
-        <v>1530.7162764218</v>
+        <v>1530.63</v>
       </c>
       <c r="O100" t="n">
-        <v>7247941.568857224</v>
+        <v>7247533.050000001</v>
       </c>
       <c r="P100" t="n">
         <v>2900</v>
@@ -5883,10 +5883,10 @@
         <v>576</v>
       </c>
       <c r="N126" t="n">
-        <v>2569.7269830028</v>
+        <v>2567</v>
       </c>
       <c r="O126" t="n">
-        <v>1480162.742209613</v>
+        <v>1478592</v>
       </c>
       <c r="P126" t="n">
         <v>4500</v>
@@ -11069,10 +11069,10 @@
         <v>68</v>
       </c>
       <c r="N240" t="n">
-        <v>10270.481108312</v>
+        <v>10219</v>
       </c>
       <c r="O240" t="n">
-        <v>698392.715365216</v>
+        <v>694892</v>
       </c>
       <c r="P240" t="n">
         <v>16900</v>
@@ -11992,10 +11992,10 @@
         <v>934</v>
       </c>
       <c r="N260" t="n">
-        <v>3821.6520477816</v>
+        <v>3821</v>
       </c>
       <c r="O260" t="n">
-        <v>3569423.012628014</v>
+        <v>3568814</v>
       </c>
       <c r="P260" t="n">
         <v>5900</v>
@@ -12038,10 +12038,10 @@
         <v>144</v>
       </c>
       <c r="N261" t="n">
-        <v>15512.291666667</v>
+        <v>15472</v>
       </c>
       <c r="O261" t="n">
-        <v>2233770.000000048</v>
+        <v>2227968</v>
       </c>
       <c r="P261" t="n">
         <v>25900</v>
@@ -12176,10 +12176,10 @@
         <v>240</v>
       </c>
       <c r="N264" t="n">
-        <v>5486.9301397206</v>
+        <v>5476</v>
       </c>
       <c r="O264" t="n">
-        <v>1316863.233532944</v>
+        <v>1314240</v>
       </c>
       <c r="P264" t="n">
         <v>8900</v>
@@ -12450,10 +12450,10 @@
         <v>54</v>
       </c>
       <c r="N270" t="n">
-        <v>5372.836713615</v>
+        <v>5347.73</v>
       </c>
       <c r="O270" t="n">
-        <v>290133.18253521</v>
+        <v>288777.42</v>
       </c>
       <c r="P270" t="n">
         <v>9500</v>
@@ -15374,10 +15374,10 @@
         <v>499</v>
       </c>
       <c r="N332" t="n">
-        <v>7049.9805782093</v>
+        <v>7046.9398274002</v>
       </c>
       <c r="O332" t="n">
-        <v>3517940.308526441</v>
+        <v>3516422.9738727</v>
       </c>
       <c r="P332" t="n">
         <v>9900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -1121,10 +1121,10 @@
         <v>36</v>
       </c>
       <c r="N18" t="n">
-        <v>12357.960422535</v>
+        <v>12357.960425532</v>
       </c>
       <c r="O18" t="n">
-        <v>444886.57521126</v>
+        <v>444886.575319152</v>
       </c>
       <c r="P18" t="n">
         <v>15900</v>
@@ -1519,10 +1519,10 @@
         <v>20</v>
       </c>
       <c r="N28" t="n">
-        <v>9392.0750746269</v>
+        <v>9392.075312499999</v>
       </c>
       <c r="O28" t="n">
-        <v>187841.501492538</v>
+        <v>187841.50625</v>
       </c>
       <c r="P28" t="n">
         <v>18500</v>
@@ -1727,10 +1727,10 @@
         <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>62349.656875</v>
+        <v>62349.656129032</v>
       </c>
       <c r="O33" t="n">
-        <v>249398.6275</v>
+        <v>249398.624516128</v>
       </c>
       <c r="P33" t="n">
         <v>109900</v>
@@ -1821,10 +1821,10 @@
         <v>65</v>
       </c>
       <c r="N35" t="n">
-        <v>141416.88459016</v>
+        <v>141416.88460526</v>
       </c>
       <c r="O35" t="n">
-        <v>9192097.498360401</v>
+        <v>9192097.499341901</v>
       </c>
       <c r="P35" t="n">
         <v>251900</v>
@@ -1863,10 +1863,10 @@
         <v>36</v>
       </c>
       <c r="N36" t="n">
-        <v>200072.20183486</v>
+        <v>200072.20194444</v>
       </c>
       <c r="O36" t="n">
-        <v>7202599.26605496</v>
+        <v>7202599.269999839</v>
       </c>
       <c r="P36" t="n">
         <v>312000</v>
@@ -1910,10 +1910,10 @@
         <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>344599.17851064</v>
+        <v>344599.17844444</v>
       </c>
       <c r="O37" t="n">
-        <v>2067595.07106384</v>
+        <v>2067595.07066664</v>
       </c>
       <c r="P37" t="n">
         <v>532900</v>
@@ -2113,10 +2113,10 @@
         <v>77</v>
       </c>
       <c r="N42" t="n">
-        <v>61666.874148352</v>
+        <v>61666.87415978</v>
       </c>
       <c r="O42" t="n">
-        <v>4748349.309423104</v>
+        <v>4748349.31030306</v>
       </c>
       <c r="P42" t="n">
         <v>98900</v>
@@ -3195,10 +3195,10 @@
         <v>350</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2554768392</v>
+        <v>2582.2554727273</v>
       </c>
       <c r="O67" t="n">
-        <v>903789.41689372</v>
+        <v>903789.415454555</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
@@ -3878,10 +3878,10 @@
         <v>240</v>
       </c>
       <c r="N82" t="n">
-        <v>3594.253608522</v>
+        <v>3594.2536</v>
       </c>
       <c r="O82" t="n">
-        <v>862620.86604528</v>
+        <v>862620.8640000001</v>
       </c>
       <c r="P82" t="n">
         <v>6500</v>
@@ -4016,10 +4016,10 @@
         <v>336</v>
       </c>
       <c r="N85" t="n">
-        <v>14822.378837068</v>
+        <v>14822.378836364</v>
       </c>
       <c r="O85" t="n">
-        <v>4980319.289254848</v>
+        <v>4980319.289018304</v>
       </c>
       <c r="P85" t="n">
         <v>24900</v>
@@ -5924,10 +5924,10 @@
         <v>432</v>
       </c>
       <c r="N127" t="n">
-        <v>2029.8739872408</v>
+        <v>2029.8739957379</v>
       </c>
       <c r="O127" t="n">
-        <v>876905.5624880256</v>
+        <v>876905.5661587728</v>
       </c>
       <c r="P127" t="n">
         <v>3600</v>
@@ -6370,10 +6370,10 @@
         <v>36</v>
       </c>
       <c r="N137" t="n">
-        <v>4285.1958525346</v>
+        <v>4285.1958592849</v>
       </c>
       <c r="O137" t="n">
-        <v>154267.0506912456</v>
+        <v>154267.0509342564</v>
       </c>
       <c r="P137" t="n">
         <v>6900</v>
@@ -7034,22 +7034,22 @@
         <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M152" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="N152" t="n">
         <v>16974.69</v>
       </c>
       <c r="O152" t="n">
-        <v>1731418.38</v>
+        <v>1052430.78</v>
       </c>
       <c r="P152" t="n">
         <v>26900</v>
       </c>
       <c r="Q152" t="n">
-        <v>2743800</v>
+        <v>1667800</v>
       </c>
     </row>
     <row r="153">
@@ -7620,22 +7620,22 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M165" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N165" t="n">
         <v>38449</v>
       </c>
       <c r="O165" t="n">
-        <v>1153470</v>
+        <v>576735</v>
       </c>
       <c r="P165" t="n">
         <v>62900</v>
       </c>
       <c r="Q165" t="n">
-        <v>1887000</v>
+        <v>943500</v>
       </c>
     </row>
     <row r="166">
@@ -8040,10 +8040,10 @@
         <v>680</v>
       </c>
       <c r="N174" t="n">
-        <v>1778.4726973583</v>
+        <v>1778.472697775</v>
       </c>
       <c r="O174" t="n">
-        <v>1209361.434203644</v>
+        <v>1209361.434487</v>
       </c>
       <c r="P174" t="n">
         <v>4900</v>
@@ -8264,22 +8264,22 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M179" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="N179" t="n">
         <v>72889</v>
       </c>
       <c r="O179" t="n">
-        <v>8455124</v>
+        <v>7288900</v>
       </c>
       <c r="P179" t="n">
         <v>117500</v>
       </c>
       <c r="Q179" t="n">
-        <v>13630000</v>
+        <v>11750000</v>
       </c>
     </row>
     <row r="180">
@@ -10839,10 +10839,10 @@
         <v>192</v>
       </c>
       <c r="N235" t="n">
-        <v>17075.98952183</v>
+        <v>17075.989521166</v>
       </c>
       <c r="O235" t="n">
-        <v>3278589.98819136</v>
+        <v>3278589.988063872</v>
       </c>
       <c r="P235" t="n">
         <v>27500</v>
@@ -12078,22 +12078,22 @@
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M262" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="N262" t="n">
         <v>48522</v>
       </c>
       <c r="O262" t="n">
-        <v>1358616</v>
+        <v>388176</v>
       </c>
       <c r="P262" t="n">
         <v>77900</v>
       </c>
       <c r="Q262" t="n">
-        <v>2181200</v>
+        <v>623200</v>
       </c>
     </row>
     <row r="263">

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -3195,10 +3195,10 @@
         <v>350</v>
       </c>
       <c r="N67" t="n">
-        <v>2582.2554675768</v>
+        <v>2582.2554613807</v>
       </c>
       <c r="O67" t="n">
-        <v>903789.41365188</v>
+        <v>903789.4114832451</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
@@ -7948,10 +7948,10 @@
         <v>680</v>
       </c>
       <c r="N172" t="n">
-        <v>1778.4727006961</v>
+        <v>1778.4727011139</v>
       </c>
       <c r="O172" t="n">
-        <v>1209361.436473348</v>
+        <v>1209361.436757452</v>
       </c>
       <c r="P172" t="n">
         <v>4900</v>
@@ -8549,10 +8549,10 @@
         <v>12</v>
       </c>
       <c r="N185" t="n">
-        <v>28116</v>
+        <v>28613.628318584</v>
       </c>
       <c r="O185" t="n">
-        <v>337392</v>
+        <v>343363.539823008</v>
       </c>
       <c r="P185" t="n">
         <v>45900</v>
@@ -10057,10 +10057,10 @@
         <v>132</v>
       </c>
       <c r="N218" t="n">
-        <v>27186</v>
+        <v>27309.572727273</v>
       </c>
       <c r="O218" t="n">
-        <v>3588552</v>
+        <v>3604863.600000036</v>
       </c>
       <c r="P218" t="n">
         <v>43900</v>
@@ -10980,10 +10980,10 @@
         <v>420</v>
       </c>
       <c r="N238" t="n">
-        <v>10755</v>
+        <v>10792.803163445</v>
       </c>
       <c r="O238" t="n">
-        <v>4517100</v>
+        <v>4532977.3286469</v>
       </c>
       <c r="P238" t="n">
         <v>17900</v>
@@ -11670,10 +11670,10 @@
         <v>279</v>
       </c>
       <c r="N253" t="n">
-        <v>10713.21</v>
+        <v>10792.371650246</v>
       </c>
       <c r="O253" t="n">
-        <v>2988985.59</v>
+        <v>3011071.690418634</v>
       </c>
       <c r="P253" t="n">
         <v>20900</v>
@@ -13326,10 +13326,10 @@
         <v>15732</v>
       </c>
       <c r="N289" t="n">
-        <v>703.79497049501</v>
+        <v>703.79496992783</v>
       </c>
       <c r="O289" t="n">
-        <v>11072102.4758275</v>
+        <v>11072102.46690462</v>
       </c>
       <c r="P289" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -2971,10 +2971,10 @@
         <v>248</v>
       </c>
       <c r="N62" t="n">
-        <v>13642.54185766</v>
+        <v>13593.35</v>
       </c>
       <c r="O62" t="n">
-        <v>3383350.38069968</v>
+        <v>3371150.8</v>
       </c>
       <c r="P62" t="n">
         <v>25500</v>
@@ -3148,10 +3148,10 @@
         <v>350</v>
       </c>
       <c r="N66" t="n">
-        <v>2584.0407928094</v>
+        <v>2582.2554090804</v>
       </c>
       <c r="O66" t="n">
-        <v>904414.2774832901</v>
+        <v>903789.39317814</v>
       </c>
       <c r="P66" t="n">
         <v>4500</v>
@@ -3194,10 +3194,10 @@
         <v>1232</v>
       </c>
       <c r="N67" t="n">
-        <v>5216.8960111863</v>
+        <v>5216.8960094242</v>
       </c>
       <c r="O67" t="n">
-        <v>6427215.885781521</v>
+        <v>6427215.883610615</v>
       </c>
       <c r="P67" t="n">
         <v>8500</v>
@@ -3240,10 +3240,10 @@
         <v>2592</v>
       </c>
       <c r="N68" t="n">
-        <v>3161.3542590035</v>
+        <v>3158.8608322644</v>
       </c>
       <c r="O68" t="n">
-        <v>8194230.239337072</v>
+        <v>8187767.277229325</v>
       </c>
       <c r="P68" t="n">
         <v>5600</v>
@@ -3511,10 +3511,10 @@
         <v>100</v>
       </c>
       <c r="N74" t="n">
-        <v>2619.5155335628</v>
+        <v>2612.77</v>
       </c>
       <c r="O74" t="n">
-        <v>261951.55335628</v>
+        <v>261277</v>
       </c>
       <c r="P74" t="n">
         <v>4900</v>
@@ -3557,10 +3557,10 @@
         <v>1964</v>
       </c>
       <c r="N75" t="n">
-        <v>4362.7231895528</v>
+        <v>4357.55</v>
       </c>
       <c r="O75" t="n">
-        <v>8568388.3442817</v>
+        <v>8558228.200000001</v>
       </c>
       <c r="P75" t="n">
         <v>7500</v>
@@ -3603,10 +3603,10 @@
         <v>346</v>
       </c>
       <c r="N76" t="n">
-        <v>4890.9300496586</v>
+        <v>4890.9300497203</v>
       </c>
       <c r="O76" t="n">
-        <v>1692261.797181876</v>
+        <v>1692261.797203224</v>
       </c>
       <c r="P76" t="n">
         <v>8200</v>
@@ -3831,10 +3831,10 @@
         <v>240</v>
       </c>
       <c r="N81" t="n">
-        <v>3594.2535785953</v>
+        <v>3594.2535742972</v>
       </c>
       <c r="O81" t="n">
-        <v>862620.858862872</v>
+        <v>862620.8578313279</v>
       </c>
       <c r="P81" t="n">
         <v>6500</v>
@@ -3969,10 +3969,10 @@
         <v>316</v>
       </c>
       <c r="N84" t="n">
-        <v>14849.377704918</v>
+        <v>14822.378834244</v>
       </c>
       <c r="O84" t="n">
-        <v>4692403.354754088</v>
+        <v>4683871.711621104</v>
       </c>
       <c r="P84" t="n">
         <v>24900</v>
@@ -4380,10 +4380,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4372.2107926742</v>
+        <v>4374.7145640659</v>
       </c>
       <c r="O93" t="n">
-        <v>5928717.834866215</v>
+        <v>5932112.948873361</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -4697,10 +4697,10 @@
         <v>401</v>
       </c>
       <c r="N100" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O100" t="n">
-        <v>3778470.294386597</v>
+        <v>3775138.31</v>
       </c>
       <c r="P100" t="n">
         <v>16900</v>
@@ -4932,10 +4932,10 @@
         <v>23</v>
       </c>
       <c r="N105" t="n">
-        <v>16960.16635514</v>
+        <v>16897</v>
       </c>
       <c r="O105" t="n">
-        <v>390083.82616822</v>
+        <v>388631</v>
       </c>
       <c r="P105" t="n">
         <v>27900</v>
@@ -5161,10 +5161,10 @@
         <v>432</v>
       </c>
       <c r="N110" t="n">
-        <v>11939.712442396</v>
+        <v>11921.4</v>
       </c>
       <c r="O110" t="n">
-        <v>5157955.775115072</v>
+        <v>5150044.8</v>
       </c>
       <c r="P110" t="n">
         <v>19900</v>
@@ -5295,10 +5295,10 @@
         <v>525</v>
       </c>
       <c r="N113" t="n">
-        <v>9926.065993788799</v>
+        <v>9903</v>
       </c>
       <c r="O113" t="n">
-        <v>5211184.64673912</v>
+        <v>5199075</v>
       </c>
       <c r="P113" t="n">
         <v>15900</v>
@@ -5341,10 +5341,10 @@
         <v>2</v>
       </c>
       <c r="N114" t="n">
-        <v>16994.7</v>
+        <v>14778</v>
       </c>
       <c r="O114" t="n">
-        <v>33989.4</v>
+        <v>29556</v>
       </c>
       <c r="P114" t="n">
         <v>24900</v>
@@ -5790,10 +5790,10 @@
         <v>352</v>
       </c>
       <c r="N124" t="n">
-        <v>8799.4430248307</v>
+        <v>8794.48</v>
       </c>
       <c r="O124" t="n">
-        <v>3097403.944740406</v>
+        <v>3095656.96</v>
       </c>
       <c r="P124" t="n">
         <v>14500</v>
@@ -6136,10 +6136,10 @@
         <v>48</v>
       </c>
       <c r="N132" t="n">
-        <v>14161.073142857</v>
+        <v>14060.64</v>
       </c>
       <c r="O132" t="n">
-        <v>679731.510857136</v>
+        <v>674910.72</v>
       </c>
       <c r="P132" t="n">
         <v>22900</v>
@@ -6323,10 +6323,10 @@
         <v>36</v>
       </c>
       <c r="N136" t="n">
-        <v>4285.1958660508</v>
+        <v>4285.1959694477</v>
       </c>
       <c r="O136" t="n">
-        <v>154267.0511778288</v>
+        <v>154267.0549001172</v>
       </c>
       <c r="P136" t="n">
         <v>6900</v>
@@ -6901,10 +6901,10 @@
         <v>144</v>
       </c>
       <c r="N149" t="n">
-        <v>27871.270433071</v>
+        <v>27123.76496063</v>
       </c>
       <c r="O149" t="n">
-        <v>4013462.942362224</v>
+        <v>3905822.15433072</v>
       </c>
       <c r="P149" t="n">
         <v>44500</v>
@@ -6947,10 +6947,10 @@
         <v>72</v>
       </c>
       <c r="N150" t="n">
-        <v>17070.322056338</v>
+        <v>16974.69</v>
       </c>
       <c r="O150" t="n">
-        <v>1229063.188056336</v>
+        <v>1222177.68</v>
       </c>
       <c r="P150" t="n">
         <v>26900</v>
@@ -7625,10 +7625,10 @@
         <v>96</v>
       </c>
       <c r="N165" t="n">
-        <v>15867.472527473</v>
+        <v>15824</v>
       </c>
       <c r="O165" t="n">
-        <v>1523277.362637408</v>
+        <v>1519104</v>
       </c>
       <c r="P165" t="n">
         <v>26900</v>
@@ -7855,10 +7855,10 @@
         <v>128</v>
       </c>
       <c r="N170" t="n">
-        <v>3494.4765957447</v>
+        <v>3486</v>
       </c>
       <c r="O170" t="n">
-        <v>447293.0042553216</v>
+        <v>446208</v>
       </c>
       <c r="P170" t="n">
         <v>6900</v>
@@ -7901,10 +7901,10 @@
         <v>680</v>
       </c>
       <c r="N171" t="n">
-        <v>1778.4727221703</v>
+        <v>1778.4727234441</v>
       </c>
       <c r="O171" t="n">
-        <v>1209361.451075804</v>
+        <v>1209361.451941988</v>
       </c>
       <c r="P171" t="n">
         <v>4900</v>
@@ -8318,10 +8318,10 @@
         <v>84</v>
       </c>
       <c r="N180" t="n">
-        <v>32376.967005076</v>
+        <v>32295</v>
       </c>
       <c r="O180" t="n">
-        <v>2719665.228426384</v>
+        <v>2712780</v>
       </c>
       <c r="P180" t="n">
         <v>51900</v>
@@ -8824,10 +8824,10 @@
         <v>103</v>
       </c>
       <c r="N191" t="n">
-        <v>9384</v>
+        <v>9686.7096774194</v>
       </c>
       <c r="O191" t="n">
-        <v>966552</v>
+        <v>997731.0967741981</v>
       </c>
       <c r="P191" t="n">
         <v>15900</v>
@@ -8916,10 +8916,10 @@
         <v>20</v>
       </c>
       <c r="N193" t="n">
-        <v>35287.397849462</v>
+        <v>34912</v>
       </c>
       <c r="O193" t="n">
-        <v>705747.95698924</v>
+        <v>698240</v>
       </c>
       <c r="P193" t="n">
         <v>56900</v>
@@ -9422,10 +9422,10 @@
         <v>280</v>
       </c>
       <c r="N204" t="n">
-        <v>3922.9680788177</v>
+        <v>3903.7379310345</v>
       </c>
       <c r="O204" t="n">
-        <v>1098431.062068956</v>
+        <v>1093046.62068966</v>
       </c>
       <c r="P204" t="n">
         <v>7500</v>
@@ -9688,10 +9688,10 @@
         <v>18</v>
       </c>
       <c r="N210" t="n">
-        <v>12463.909090909</v>
+        <v>11922</v>
       </c>
       <c r="O210" t="n">
-        <v>224350.363636362</v>
+        <v>214596</v>
       </c>
       <c r="P210" t="n">
         <v>19900</v>
@@ -10102,10 +10102,10 @@
         <v>153</v>
       </c>
       <c r="N219" t="n">
-        <v>7668.5070422535</v>
+        <v>7562</v>
       </c>
       <c r="O219" t="n">
-        <v>1173281.577464785</v>
+        <v>1156986</v>
       </c>
       <c r="P219" t="n">
         <v>12900</v>
@@ -10148,10 +10148,10 @@
         <v>245</v>
       </c>
       <c r="N220" t="n">
-        <v>13606.546707504</v>
+        <v>13565</v>
       </c>
       <c r="O220" t="n">
-        <v>3333603.94333848</v>
+        <v>3323425</v>
       </c>
       <c r="P220" t="n">
         <v>22500</v>
@@ -10194,10 +10194,10 @@
         <v>1162</v>
       </c>
       <c r="N221" t="n">
-        <v>7647.7960893855</v>
+        <v>7635</v>
       </c>
       <c r="O221" t="n">
-        <v>8886739.055865951</v>
+        <v>8871870</v>
       </c>
       <c r="P221" t="n">
         <v>13900</v>
@@ -10240,10 +10240,10 @@
         <v>336</v>
       </c>
       <c r="N222" t="n">
-        <v>5465.19</v>
+        <v>5438</v>
       </c>
       <c r="O222" t="n">
-        <v>1836303.84</v>
+        <v>1827168</v>
       </c>
       <c r="P222" t="n">
         <v>8900</v>
@@ -11301,10 +11301,10 @@
         <v>78</v>
       </c>
       <c r="N245" t="n">
-        <v>14348.936170213</v>
+        <v>14050</v>
       </c>
       <c r="O245" t="n">
-        <v>1119217.021276614</v>
+        <v>1095900</v>
       </c>
       <c r="P245" t="n">
         <v>23900</v>
@@ -11347,10 +11347,10 @@
         <v>285</v>
       </c>
       <c r="N246" t="n">
-        <v>8721.0653753027</v>
+        <v>8700</v>
       </c>
       <c r="O246" t="n">
-        <v>2485503.631961269</v>
+        <v>2479500</v>
       </c>
       <c r="P246" t="n">
         <v>14900</v>
@@ -11669,10 +11669,10 @@
         <v>181</v>
       </c>
       <c r="N253" t="n">
-        <v>21822.282548476</v>
+        <v>21762</v>
       </c>
       <c r="O253" t="n">
-        <v>3949833.141274156</v>
+        <v>3938922</v>
       </c>
       <c r="P253" t="n">
         <v>35900</v>
@@ -11761,10 +11761,10 @@
         <v>144</v>
       </c>
       <c r="N255" t="n">
-        <v>15512.396866841</v>
+        <v>15472</v>
       </c>
       <c r="O255" t="n">
-        <v>2233785.148825104</v>
+        <v>2227968</v>
       </c>
       <c r="P255" t="n">
         <v>25900</v>
@@ -11899,10 +11899,10 @@
         <v>240</v>
       </c>
       <c r="N258" t="n">
-        <v>5483.2964690207</v>
+        <v>5476</v>
       </c>
       <c r="O258" t="n">
-        <v>1315991.152564968</v>
+        <v>1314240</v>
       </c>
       <c r="P258" t="n">
         <v>8900</v>
@@ -11991,10 +11991,10 @@
         <v>56</v>
       </c>
       <c r="N260" t="n">
-        <v>38558.016</v>
+        <v>38252</v>
       </c>
       <c r="O260" t="n">
-        <v>2159248.896</v>
+        <v>2142112</v>
       </c>
       <c r="P260" t="n">
         <v>61900</v>
@@ -12355,10 +12355,10 @@
         <v>55</v>
       </c>
       <c r="N268" t="n">
-        <v>15733.897449664</v>
+        <v>15423.36</v>
       </c>
       <c r="O268" t="n">
-        <v>865364.3597315201</v>
+        <v>848284.8</v>
       </c>
       <c r="P268" t="n">
         <v>24900</v>
@@ -13470,10 +13470,10 @@
         <v>23</v>
       </c>
       <c r="N292" t="n">
-        <v>18621.814408602</v>
+        <v>18423.71</v>
       </c>
       <c r="O292" t="n">
-        <v>428301.731397846</v>
+        <v>423745.33</v>
       </c>
       <c r="P292" t="n">
         <v>10000</v>
@@ -14237,10 +14237,10 @@
         <v>45</v>
       </c>
       <c r="N308" t="n">
-        <v>3098.3874489796</v>
+        <v>3067.0906122449</v>
       </c>
       <c r="O308" t="n">
-        <v>139427.435204082</v>
+        <v>138019.0775510205</v>
       </c>
       <c r="P308" t="n">
         <v>7200</v>
@@ -15094,10 +15094,10 @@
         <v>30</v>
       </c>
       <c r="N326" t="n">
-        <v>24490.111557632</v>
+        <v>24338.47</v>
       </c>
       <c r="O326" t="n">
-        <v>734703.3467289601</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P326" t="n">
         <v>27900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -1519,10 +1519,10 @@
         <v>20</v>
       </c>
       <c r="N28" t="n">
-        <v>9392.0755737705</v>
+        <v>9392.0756666667</v>
       </c>
       <c r="O28" t="n">
-        <v>187841.51147541</v>
+        <v>187841.513333334</v>
       </c>
       <c r="P28" t="n">
         <v>18500</v>
@@ -1774,10 +1774,10 @@
         <v>65</v>
       </c>
       <c r="N34" t="n">
-        <v>141416.88460526</v>
+        <v>141416.88462046</v>
       </c>
       <c r="O34" t="n">
-        <v>9192097.499341901</v>
+        <v>9192097.500329901</v>
       </c>
       <c r="P34" t="n">
         <v>251900</v>
@@ -1816,10 +1816,10 @@
         <v>36</v>
       </c>
       <c r="N35" t="n">
-        <v>200072.20205607</v>
+        <v>200072.20216981</v>
       </c>
       <c r="O35" t="n">
-        <v>7202599.27401852</v>
+        <v>7202599.27811316</v>
       </c>
       <c r="P35" t="n">
         <v>312000</v>
@@ -3148,10 +3148,10 @@
         <v>350</v>
       </c>
       <c r="N66" t="n">
-        <v>2582.2554090804</v>
+        <v>2582.2554027233</v>
       </c>
       <c r="O66" t="n">
-        <v>903789.39317814</v>
+        <v>903789.390953155</v>
       </c>
       <c r="P66" t="n">
         <v>4500</v>
@@ -3194,10 +3194,10 @@
         <v>1232</v>
       </c>
       <c r="N67" t="n">
-        <v>5216.8960094242</v>
+        <v>5216.8960047177</v>
       </c>
       <c r="O67" t="n">
-        <v>6427215.883610615</v>
+        <v>6427215.877812206</v>
       </c>
       <c r="P67" t="n">
         <v>8500</v>
@@ -3240,10 +3240,10 @@
         <v>2592</v>
       </c>
       <c r="N68" t="n">
-        <v>3158.8608322644</v>
+        <v>3158.8608345701</v>
       </c>
       <c r="O68" t="n">
-        <v>8187767.277229325</v>
+        <v>8187767.283205699</v>
       </c>
       <c r="P68" t="n">
         <v>5600</v>
@@ -3286,10 +3286,10 @@
         <v>74</v>
       </c>
       <c r="N69" t="n">
-        <v>3841.6249390244</v>
+        <v>3841.6250103093</v>
       </c>
       <c r="O69" t="n">
-        <v>284280.2454878056</v>
+        <v>284280.2507628882</v>
       </c>
       <c r="P69" t="n">
         <v>6900</v>
@@ -3603,10 +3603,10 @@
         <v>346</v>
       </c>
       <c r="N76" t="n">
-        <v>4890.9300497203</v>
+        <v>4890.9300498132</v>
       </c>
       <c r="O76" t="n">
-        <v>1692261.797203224</v>
+        <v>1692261.797235367</v>
       </c>
       <c r="P76" t="n">
         <v>8200</v>
@@ -3831,10 +3831,10 @@
         <v>240</v>
       </c>
       <c r="N81" t="n">
-        <v>3594.2535742972</v>
+        <v>3594.2535483871</v>
       </c>
       <c r="O81" t="n">
-        <v>862620.8578313279</v>
+        <v>862620.851612904</v>
       </c>
       <c r="P81" t="n">
         <v>6500</v>
@@ -3969,10 +3969,10 @@
         <v>316</v>
       </c>
       <c r="N84" t="n">
-        <v>14822.378834244</v>
+        <v>14822.378831406</v>
       </c>
       <c r="O84" t="n">
-        <v>4683871.711621104</v>
+        <v>4683871.710724296</v>
       </c>
       <c r="P84" t="n">
         <v>24900</v>
@@ -4380,10 +4380,10 @@
         <v>1356</v>
       </c>
       <c r="N93" t="n">
-        <v>4374.7145640659</v>
+        <v>4372.2107930714</v>
       </c>
       <c r="O93" t="n">
-        <v>5932112.948873361</v>
+        <v>5928717.835404819</v>
       </c>
       <c r="P93" t="n">
         <v>7500</v>
@@ -5703,10 +5703,10 @@
         <v>480</v>
       </c>
       <c r="N122" t="n">
-        <v>4196.8725389755</v>
+        <v>4196.8725410978</v>
       </c>
       <c r="O122" t="n">
-        <v>2014498.81870824</v>
+        <v>2014498.819726944</v>
       </c>
       <c r="P122" t="n">
         <v>5900</v>
@@ -6323,10 +6323,10 @@
         <v>36</v>
       </c>
       <c r="N136" t="n">
-        <v>4285.1959694477</v>
+        <v>4285.1960260973</v>
       </c>
       <c r="O136" t="n">
-        <v>154267.0549001172</v>
+        <v>154267.0569395028</v>
       </c>
       <c r="P136" t="n">
         <v>6900</v>
@@ -6451,10 +6451,10 @@
         <v>55</v>
       </c>
       <c r="N139" t="n">
-        <v>30244.600034762</v>
+        <v>30244.600034924</v>
       </c>
       <c r="O139" t="n">
-        <v>1663453.00191191</v>
+        <v>1663453.00192082</v>
       </c>
       <c r="P139" t="n">
         <v>48900</v>
@@ -7901,10 +7901,10 @@
         <v>680</v>
       </c>
       <c r="N171" t="n">
-        <v>1778.4727234441</v>
+        <v>1778.4727448514</v>
       </c>
       <c r="O171" t="n">
-        <v>1209361.451941988</v>
+        <v>1209361.466498952</v>
       </c>
       <c r="P171" t="n">
         <v>4900</v>
@@ -8824,10 +8824,10 @@
         <v>103</v>
       </c>
       <c r="N191" t="n">
-        <v>9686.7096774194</v>
+        <v>9384</v>
       </c>
       <c r="O191" t="n">
-        <v>997731.0967741981</v>
+        <v>966552</v>
       </c>
       <c r="P191" t="n">
         <v>15900</v>
@@ -9422,10 +9422,10 @@
         <v>280</v>
       </c>
       <c r="N204" t="n">
-        <v>3903.7379310345</v>
+        <v>3903.7383067896</v>
       </c>
       <c r="O204" t="n">
-        <v>1093046.62068966</v>
+        <v>1093046.725901088</v>
       </c>
       <c r="P204" t="n">
         <v>7500</v>
@@ -12037,10 +12037,10 @@
         <v>864</v>
       </c>
       <c r="N261" t="n">
-        <v>1516.0387724372</v>
+        <v>1516.0387635597</v>
       </c>
       <c r="O261" t="n">
-        <v>1309857.499385741</v>
+        <v>1309857.491715581</v>
       </c>
       <c r="P261" t="n">
         <v>2300</v>
@@ -13187,10 +13187,10 @@
         <v>15732</v>
       </c>
       <c r="N286" t="n">
-        <v>703.7949437622</v>
+        <v>703.79492130965</v>
       </c>
       <c r="O286" t="n">
-        <v>11072102.05526693</v>
+        <v>11072101.70204341</v>
       </c>
       <c r="P286" t="n">
         <v>900</v>
@@ -13992,10 +13992,10 @@
         <v>48</v>
       </c>
       <c r="N303" t="n">
-        <v>9746.880194174801</v>
+        <v>9746.8801960784</v>
       </c>
       <c r="O303" t="n">
-        <v>467850.2493203904</v>
+        <v>467850.2494117632</v>
       </c>
       <c r="P303" t="n">
         <v>18500</v>
@@ -14127,7 +14127,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14136,19 +14136,19 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N306" t="n">
-        <v>2992.5705633803</v>
+        <v>2992.5708695652</v>
       </c>
       <c r="O306" t="n">
-        <v>62843.9818309863</v>
+        <v>56858.8465217388</v>
       </c>
       <c r="P306" t="n">
         <v>6000</v>
       </c>
       <c r="Q306" t="n">
-        <v>126000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="307">
@@ -15186,10 +15186,10 @@
         <v>10</v>
       </c>
       <c r="N328" t="n">
-        <v>44113.603953488</v>
+        <v>44113.604096386</v>
       </c>
       <c r="O328" t="n">
-        <v>441136.03953488</v>
+        <v>441136.04096386</v>
       </c>
       <c r="P328" t="n">
         <v>71900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -3148,10 +3148,10 @@
         <v>350</v>
       </c>
       <c r="N66" t="n">
-        <v>2582.2554027233</v>
+        <v>2582.2553995381</v>
       </c>
       <c r="O66" t="n">
-        <v>903789.390953155</v>
+        <v>903789.389838335</v>
       </c>
       <c r="P66" t="n">
         <v>4500</v>
@@ -5161,10 +5161,10 @@
         <v>432</v>
       </c>
       <c r="N110" t="n">
-        <v>11921.4</v>
+        <v>11949.297191888</v>
       </c>
       <c r="O110" t="n">
-        <v>5150044.8</v>
+        <v>5162096.386895616</v>
       </c>
       <c r="P110" t="n">
         <v>19900</v>
@@ -6993,10 +6993,10 @@
         <v>221</v>
       </c>
       <c r="N151" t="n">
-        <v>8332.779613402099</v>
+        <v>8397.710363636401</v>
       </c>
       <c r="O151" t="n">
-        <v>1841544.294561864</v>
+        <v>1855893.990363645</v>
       </c>
       <c r="P151" t="n">
         <v>14900</v>
@@ -9422,10 +9422,10 @@
         <v>280</v>
       </c>
       <c r="N204" t="n">
-        <v>3903.7383067896</v>
+        <v>3903.7383529412</v>
       </c>
       <c r="O204" t="n">
-        <v>1093046.725901088</v>
+        <v>1093046.738823536</v>
       </c>
       <c r="P204" t="n">
         <v>7500</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -13061,10 +13061,10 @@
         <v>15264</v>
       </c>
       <c r="N283" t="n">
-        <v>703.79488487659</v>
+        <v>703.79488357273</v>
       </c>
       <c r="O283" t="n">
-        <v>10742725.12275627</v>
+        <v>10742725.10285415</v>
       </c>
       <c r="P283" t="n">
         <v>900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q342"/>
+  <dimension ref="A1:Q339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-11</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -642,10 +642,10 @@
         <v>275</v>
       </c>
       <c r="N6" t="n">
-        <v>27000</v>
+        <v>27108.144192256</v>
       </c>
       <c r="O6" t="n">
-        <v>7425000</v>
+        <v>7454739.6528704</v>
       </c>
       <c r="P6" t="n">
         <v>20000</v>
@@ -681,10 +681,10 @@
         <v>63</v>
       </c>
       <c r="N7" t="n">
-        <v>27000</v>
+        <v>27117.391304348</v>
       </c>
       <c r="O7" t="n">
-        <v>1701000</v>
+        <v>1708395.652173924</v>
       </c>
       <c r="P7" t="n">
         <v>30000</v>
@@ -720,10 +720,10 @@
         <v>376</v>
       </c>
       <c r="N8" t="n">
-        <v>3376.7464397906</v>
+        <v>3376.7464388093</v>
       </c>
       <c r="O8" t="n">
-        <v>1269656.661361266</v>
+        <v>1269656.660992297</v>
       </c>
       <c r="P8" t="n">
         <v>4500</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>224</v>
+        <v>152</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1040,19 +1040,19 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>224</v>
+        <v>152</v>
       </c>
       <c r="N16" t="n">
         <v>2812</v>
       </c>
       <c r="O16" t="n">
-        <v>629888</v>
+        <v>427424</v>
       </c>
       <c r="P16" t="n">
         <v>5000</v>
       </c>
       <c r="Q16" t="n">
-        <v>1120000</v>
+        <v>760000</v>
       </c>
     </row>
     <row r="17">
@@ -1871,10 +1871,10 @@
         <v>62</v>
       </c>
       <c r="N36" t="n">
-        <v>27000</v>
+        <v>27229.787234043</v>
       </c>
       <c r="O36" t="n">
-        <v>1674000</v>
+        <v>1688246.808510666</v>
       </c>
       <c r="P36" t="n">
         <v>20000</v>
@@ -3109,10 +3109,10 @@
         <v>350</v>
       </c>
       <c r="N65" t="n">
-        <v>2582.2552</v>
+        <v>2582.2551814224</v>
       </c>
       <c r="O65" t="n">
-        <v>903789.3200000001</v>
+        <v>903789.31349784</v>
       </c>
       <c r="P65" t="n">
         <v>4500</v>
@@ -3155,10 +3155,10 @@
         <v>1232</v>
       </c>
       <c r="N66" t="n">
-        <v>5216.8959994095</v>
+        <v>5224.6087374335</v>
       </c>
       <c r="O66" t="n">
-        <v>6427215.871272504</v>
+        <v>6436717.964518072</v>
       </c>
       <c r="P66" t="n">
         <v>8500</v>
@@ -3201,10 +3201,10 @@
         <v>2592</v>
       </c>
       <c r="N67" t="n">
-        <v>3158.8608346114</v>
+        <v>3158.8608347353</v>
       </c>
       <c r="O67" t="n">
-        <v>8187767.283312749</v>
+        <v>8187767.283633898</v>
       </c>
       <c r="P67" t="n">
         <v>5600</v>
@@ -3385,10 +3385,10 @@
         <v>648</v>
       </c>
       <c r="N71" t="n">
-        <v>3795.7100076089</v>
+        <v>3795.7100076132</v>
       </c>
       <c r="O71" t="n">
-        <v>2459620.084930567</v>
+        <v>2459620.084933354</v>
       </c>
       <c r="P71" t="n">
         <v>6200</v>
@@ -3564,10 +3564,10 @@
         <v>346</v>
       </c>
       <c r="N75" t="n">
-        <v>4890.9300498132</v>
+        <v>4903.3514603175</v>
       </c>
       <c r="O75" t="n">
-        <v>1692261.797235367</v>
+        <v>1696559.605269855</v>
       </c>
       <c r="P75" t="n">
         <v>8200</v>
@@ -3792,10 +3792,10 @@
         <v>240</v>
       </c>
       <c r="N80" t="n">
-        <v>3594.2535397039</v>
+        <v>3594.2534111187</v>
       </c>
       <c r="O80" t="n">
-        <v>862620.849528936</v>
+        <v>862620.8186684881</v>
       </c>
       <c r="P80" t="n">
         <v>6500</v>
@@ -3884,10 +3884,10 @@
         <v>192</v>
       </c>
       <c r="N82" t="n">
-        <v>8154</v>
+        <v>8184.2747524752</v>
       </c>
       <c r="O82" t="n">
-        <v>1565568</v>
+        <v>1571380.752475238</v>
       </c>
       <c r="P82" t="n">
         <v>13500</v>
@@ -3930,10 +3930,10 @@
         <v>316</v>
       </c>
       <c r="N83" t="n">
-        <v>14822.378830694</v>
+        <v>14831.411358927</v>
       </c>
       <c r="O83" t="n">
-        <v>4683871.710499304</v>
+        <v>4686725.989420932</v>
       </c>
       <c r="P83" t="n">
         <v>24900</v>
@@ -4341,10 +4341,10 @@
         <v>1356</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1712607216</v>
+        <v>4371.171261065</v>
       </c>
       <c r="O92" t="n">
-        <v>5927308.22953849</v>
+        <v>5927308.23000414</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -5122,10 +5122,10 @@
         <v>432</v>
       </c>
       <c r="N109" t="n">
-        <v>11921.4</v>
+        <v>11959.066350711</v>
       </c>
       <c r="O109" t="n">
-        <v>5150044.8</v>
+        <v>5166316.663507152</v>
       </c>
       <c r="P109" t="n">
         <v>19900</v>
@@ -5838,10 +5838,10 @@
         <v>432</v>
       </c>
       <c r="N125" t="n">
-        <v>2029.8740606389</v>
+        <v>2029.8740628386</v>
       </c>
       <c r="O125" t="n">
-        <v>876905.5941960048</v>
+        <v>876905.5951462751</v>
       </c>
       <c r="P125" t="n">
         <v>3600</v>
@@ -5879,10 +5879,10 @@
         <v>528</v>
       </c>
       <c r="N126" t="n">
-        <v>22485.69552795</v>
+        <v>22541.90975</v>
       </c>
       <c r="O126" t="n">
-        <v>11872447.2387576</v>
+        <v>11902128.348</v>
       </c>
       <c r="P126" t="n">
         <v>36500</v>
@@ -6010,10 +6010,10 @@
         <v>180</v>
       </c>
       <c r="N129" t="n">
-        <v>24538.02</v>
+        <v>24573.894298246</v>
       </c>
       <c r="O129" t="n">
-        <v>4416843.6</v>
+        <v>4423300.97368428</v>
       </c>
       <c r="P129" t="n">
         <v>52900</v>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -6140,19 +6140,19 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="N132" t="n">
         <v>30611</v>
       </c>
       <c r="O132" t="n">
-        <v>7346640</v>
+        <v>5877312</v>
       </c>
       <c r="P132" t="n">
         <v>38900</v>
       </c>
       <c r="Q132" t="n">
-        <v>9336000</v>
+        <v>7468800</v>
       </c>
     </row>
     <row r="133">
@@ -6284,10 +6284,10 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>4285.1960260973</v>
+        <v>4285.1960620525</v>
       </c>
       <c r="O135" t="n">
-        <v>154267.0569395028</v>
+        <v>154267.05823389</v>
       </c>
       <c r="P135" t="n">
         <v>6900</v>
@@ -6458,10 +6458,10 @@
         <v>228</v>
       </c>
       <c r="N139" t="n">
-        <v>4813.4669326076</v>
+        <v>4814.2679276196</v>
       </c>
       <c r="O139" t="n">
-        <v>1097470.460634533</v>
+        <v>1097653.087497269</v>
       </c>
       <c r="P139" t="n">
         <v>9900</v>
@@ -6591,10 +6591,10 @@
         <v>60</v>
       </c>
       <c r="N142" t="n">
-        <v>21418.04</v>
+        <v>22690.398811881</v>
       </c>
       <c r="O142" t="n">
-        <v>1285082.4</v>
+        <v>1361423.92871286</v>
       </c>
       <c r="P142" t="n">
         <v>34900</v>
@@ -6862,10 +6862,10 @@
         <v>144</v>
       </c>
       <c r="N148" t="n">
-        <v>27123.764900398</v>
+        <v>27232.25996</v>
       </c>
       <c r="O148" t="n">
-        <v>3905822.145657312</v>
+        <v>3921445.43424</v>
       </c>
       <c r="P148" t="n">
         <v>44500</v>
@@ -7046,10 +7046,10 @@
         <v>144</v>
       </c>
       <c r="N152" t="n">
-        <v>26854</v>
+        <v>27011.040935673</v>
       </c>
       <c r="O152" t="n">
-        <v>3866976</v>
+        <v>3889589.894736912</v>
       </c>
       <c r="P152" t="n">
         <v>43900</v>
@@ -7133,10 +7133,10 @@
         <v>31</v>
       </c>
       <c r="N154" t="n">
-        <v>12981.59</v>
+        <v>13079.564264151</v>
       </c>
       <c r="O154" t="n">
-        <v>402429.29</v>
+        <v>405466.492188681</v>
       </c>
       <c r="P154" t="n">
         <v>21900</v>
@@ -7179,10 +7179,10 @@
         <v>85</v>
       </c>
       <c r="N155" t="n">
-        <v>13878.97</v>
+        <v>13974.031438356</v>
       </c>
       <c r="O155" t="n">
-        <v>1179712.45</v>
+        <v>1187792.67226026</v>
       </c>
       <c r="P155" t="n">
         <v>21900</v>
@@ -7729,10 +7729,10 @@
         <v>11</v>
       </c>
       <c r="N167" t="n">
-        <v>23521.623137255</v>
+        <v>23521.623</v>
       </c>
       <c r="O167" t="n">
-        <v>258737.854509805</v>
+        <v>258737.853</v>
       </c>
       <c r="P167" t="n">
         <v>39000</v>
@@ -7821,10 +7821,10 @@
         <v>680</v>
       </c>
       <c r="N169" t="n">
-        <v>1778.4727414037</v>
+        <v>1778.4727487406</v>
       </c>
       <c r="O169" t="n">
-        <v>1209361.464154516</v>
+        <v>1209361.469143608</v>
       </c>
       <c r="P169" t="n">
         <v>4900</v>
@@ -9020,10 +9020,10 @@
         <v>216</v>
       </c>
       <c r="N195" t="n">
-        <v>9178</v>
+        <v>9198.3277962348</v>
       </c>
       <c r="O195" t="n">
-        <v>1982448</v>
+        <v>1986838.803986717</v>
       </c>
       <c r="P195" t="n">
         <v>14900</v>
@@ -9066,10 +9066,10 @@
         <v>147</v>
       </c>
       <c r="N196" t="n">
-        <v>13922</v>
+        <v>13948.467680608</v>
       </c>
       <c r="O196" t="n">
-        <v>2046534</v>
+        <v>2050424.749049376</v>
       </c>
       <c r="P196" t="n">
         <v>22900</v>
@@ -9112,10 +9112,10 @@
         <v>24</v>
       </c>
       <c r="N197" t="n">
-        <v>25076</v>
+        <v>25260.382352941</v>
       </c>
       <c r="O197" t="n">
-        <v>601824</v>
+        <v>606249.176470584</v>
       </c>
       <c r="P197" t="n">
         <v>40900</v>
@@ -9342,10 +9342,10 @@
         <v>280</v>
       </c>
       <c r="N202" t="n">
-        <v>3903.7383683768</v>
+        <v>3903.7386507259</v>
       </c>
       <c r="O202" t="n">
-        <v>1093046.743145504</v>
+        <v>1093046.822203252</v>
       </c>
       <c r="P202" t="n">
         <v>7500</v>
@@ -9700,10 +9700,10 @@
         <v>144</v>
       </c>
       <c r="N210" t="n">
-        <v>5869.1725746653</v>
+        <v>5869.1725593395</v>
       </c>
       <c r="O210" t="n">
-        <v>845160.8507518033</v>
+        <v>845160.8485448881</v>
       </c>
       <c r="P210" t="n">
         <v>9500</v>
@@ -9884,10 +9884,10 @@
         <v>256</v>
       </c>
       <c r="N214" t="n">
-        <v>13098</v>
+        <v>13121.945155393</v>
       </c>
       <c r="O214" t="n">
-        <v>3353088</v>
+        <v>3359217.959780608</v>
       </c>
       <c r="P214" t="n">
         <v>21200</v>
@@ -10405,12 +10405,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>C4563</t>
+          <t>C4566</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>LIBRO MUSICAL ESPAÑOL 4563</t>
+          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -10433,30 +10433,30 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="N226" t="n">
-        <v>15461</v>
+        <v>11348</v>
       </c>
       <c r="O226" t="n">
-        <v>927660</v>
+        <v>3290920</v>
       </c>
       <c r="P226" t="n">
-        <v>24900</v>
+        <v>19900</v>
       </c>
       <c r="Q226" t="n">
-        <v>1494000</v>
+        <v>5771000</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>C4566</t>
+          <t>C4567</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
+          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>290</v>
+        <v>192</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -10479,30 +10479,30 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>290</v>
+        <v>192</v>
       </c>
       <c r="N227" t="n">
-        <v>11348</v>
+        <v>17123.621290098</v>
       </c>
       <c r="O227" t="n">
-        <v>3290920</v>
+        <v>3287735.287698816</v>
       </c>
       <c r="P227" t="n">
-        <v>19900</v>
+        <v>27500</v>
       </c>
       <c r="Q227" t="n">
-        <v>5771000</v>
+        <v>5280000</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>C4567</t>
+          <t>C4570</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
+          <t>CUBO MAGICO C4570 EQY766</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -10525,30 +10525,30 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="N228" t="n">
-        <v>17075.989520833</v>
+        <v>10398</v>
       </c>
       <c r="O228" t="n">
-        <v>3278589.987999937</v>
+        <v>623880</v>
       </c>
       <c r="P228" t="n">
-        <v>27500</v>
+        <v>16900</v>
       </c>
       <c r="Q228" t="n">
-        <v>5280000</v>
+        <v>1014000</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>C4570</t>
+          <t>C4572</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4570 EQY766</t>
+          <t>CUBO MAGICO C4572 EQY10130</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -10562,7 +10562,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10571,30 +10571,30 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="N229" t="n">
-        <v>10398</v>
+        <v>4518</v>
       </c>
       <c r="O229" t="n">
-        <v>623880</v>
+        <v>487944</v>
       </c>
       <c r="P229" t="n">
-        <v>16900</v>
+        <v>7900</v>
       </c>
       <c r="Q229" t="n">
-        <v>1014000</v>
+        <v>853200</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>C4572</t>
+          <t>C4577</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4572 EQY10130</t>
+          <t>PISTA DINOSAURIO C4577</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -10608,7 +10608,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -10617,30 +10617,30 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="N230" t="n">
-        <v>4518</v>
+        <v>21666.992481203</v>
       </c>
       <c r="O230" t="n">
-        <v>487944</v>
+        <v>1451688.496240601</v>
       </c>
       <c r="P230" t="n">
-        <v>7900</v>
+        <v>34900</v>
       </c>
       <c r="Q230" t="n">
-        <v>853200</v>
+        <v>2338300</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C4577</t>
+          <t>C4578</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>PISTA DINOSAURIO C4577</t>
+          <t>LANZADORA DE AGUA BOLSA PVC C4578</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10663,30 +10663,30 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N231" t="n">
-        <v>21346</v>
+        <v>18001</v>
       </c>
       <c r="O231" t="n">
-        <v>1430182</v>
+        <v>1512084</v>
       </c>
       <c r="P231" t="n">
-        <v>34900</v>
+        <v>28900</v>
       </c>
       <c r="Q231" t="n">
-        <v>2338300</v>
+        <v>2427600</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>C4578</t>
+          <t>C4579</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA BOLSA PVC C4578</t>
+          <t>LANZADORA DE AGUA C4579</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -10709,30 +10709,33 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="N232" t="n">
-        <v>18001</v>
+        <v>10219</v>
       </c>
       <c r="O232" t="n">
-        <v>1512084</v>
+        <v>694892</v>
       </c>
       <c r="P232" t="n">
-        <v>28900</v>
+        <v>16900</v>
       </c>
       <c r="Q232" t="n">
-        <v>2427600</v>
+        <v>1149200</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>C4579</t>
-        </is>
+          <t>C458</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>6920190230459</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA C4579</t>
+          <t>BURRO SENCILLO SONIDO</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -10742,11 +10745,11 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J233" t="n">
-        <v>68</v>
+        <v>420</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -10755,33 +10758,30 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>68</v>
+        <v>420</v>
       </c>
       <c r="N233" t="n">
-        <v>10219</v>
+        <v>10755</v>
       </c>
       <c r="O233" t="n">
-        <v>694892</v>
+        <v>4517100</v>
       </c>
       <c r="P233" t="n">
-        <v>16900</v>
+        <v>17900</v>
       </c>
       <c r="Q233" t="n">
-        <v>1149200</v>
+        <v>7518000</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>C458</t>
-        </is>
-      </c>
-      <c r="B234" t="n">
-        <v>6920190230459</v>
+          <t>C4581</t>
+        </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>BURRO SENCILLO SONIDO</t>
+          <t>ESPADA BURBUJERA C4581</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -10791,11 +10791,11 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J234" t="n">
-        <v>420</v>
+        <v>106</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -10804,30 +10804,30 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>420</v>
+        <v>106</v>
       </c>
       <c r="N234" t="n">
-        <v>10755</v>
+        <v>17325.987730061</v>
       </c>
       <c r="O234" t="n">
-        <v>4517100</v>
+        <v>1836554.699386466</v>
       </c>
       <c r="P234" t="n">
-        <v>17900</v>
+        <v>27900</v>
       </c>
       <c r="Q234" t="n">
-        <v>7518000</v>
+        <v>2957400</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>C4581</t>
+          <t>C4582</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ESPADA BURBUJERA C4581</t>
+          <t>MUÑECA CHICHI SONIDOS C4582</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -10850,30 +10850,30 @@
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="N235" t="n">
-        <v>17168</v>
+        <v>20944.88372093</v>
       </c>
       <c r="O235" t="n">
-        <v>1819808</v>
+        <v>670236.27906976</v>
       </c>
       <c r="P235" t="n">
-        <v>27900</v>
+        <v>33900</v>
       </c>
       <c r="Q235" t="n">
-        <v>2957400</v>
+        <v>1084800</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>C4582</t>
+          <t>C4584</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>MUÑECA CHICHI SONIDOS C4582</t>
+          <t>LANZADORA DARDOS C4584</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -10896,30 +10896,30 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="N236" t="n">
-        <v>20014</v>
+        <v>27289.075933076</v>
       </c>
       <c r="O236" t="n">
-        <v>640448</v>
+        <v>3602158.023166032</v>
       </c>
       <c r="P236" t="n">
-        <v>33900</v>
+        <v>43900</v>
       </c>
       <c r="Q236" t="n">
-        <v>1084800</v>
+        <v>5794800</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>C4584</t>
+          <t>C4586</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS C4584</t>
+          <t>DINOSAURIO CONTROL REMOTO HUMO C4586</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -10942,30 +10942,30 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="N237" t="n">
-        <v>27254</v>
+        <v>52755</v>
       </c>
       <c r="O237" t="n">
-        <v>3597528</v>
+        <v>158265</v>
       </c>
       <c r="P237" t="n">
-        <v>43900</v>
+        <v>85900</v>
       </c>
       <c r="Q237" t="n">
-        <v>5794800</v>
+        <v>257700</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C4586</t>
+          <t>C4596</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>DINOSAURIO CONTROL REMOTO HUMO C4586</t>
+          <t>JUEGO ANTIESTRES C4596</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -10979,7 +10979,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -10988,30 +10988,30 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="N238" t="n">
-        <v>52755</v>
+        <v>4303</v>
       </c>
       <c r="O238" t="n">
-        <v>158265</v>
+        <v>464724</v>
       </c>
       <c r="P238" t="n">
-        <v>85900</v>
+        <v>7900</v>
       </c>
       <c r="Q238" t="n">
-        <v>257700</v>
+        <v>853200</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C4596</t>
+          <t>C4599</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>JUEGO ANTIESTRES C4596</t>
+          <t>VARA HELICE DINOSAURIO C4599</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>108</v>
+        <v>720</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -11034,30 +11034,30 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>108</v>
+        <v>720</v>
       </c>
       <c r="N239" t="n">
-        <v>4303</v>
+        <v>5588</v>
       </c>
       <c r="O239" t="n">
-        <v>464724</v>
+        <v>4023360</v>
       </c>
       <c r="P239" t="n">
-        <v>7900</v>
+        <v>9500</v>
       </c>
       <c r="Q239" t="n">
-        <v>853200</v>
+        <v>6840000</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C4599</t>
+          <t>C4600</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>VARA HELICE DINOSAURIO C4599</t>
+          <t>SET PERRITO PATROL BUS C4600</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -11071,7 +11071,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>720</v>
+        <v>45</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -11080,30 +11080,30 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>720</v>
+        <v>45</v>
       </c>
       <c r="N240" t="n">
-        <v>5588</v>
+        <v>16282</v>
       </c>
       <c r="O240" t="n">
-        <v>4023360</v>
+        <v>732690</v>
       </c>
       <c r="P240" t="n">
-        <v>9500</v>
+        <v>27900</v>
       </c>
       <c r="Q240" t="n">
-        <v>6840000</v>
+        <v>1255500</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C4600</t>
+          <t>C4601</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SET PERRITO PATROL BUS C4600</t>
+          <t>SET PERRO PATROL C4601</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -11126,30 +11126,30 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="N241" t="n">
-        <v>16282</v>
+        <v>14050</v>
       </c>
       <c r="O241" t="n">
-        <v>732690</v>
+        <v>1095900</v>
       </c>
       <c r="P241" t="n">
-        <v>27900</v>
+        <v>23900</v>
       </c>
       <c r="Q241" t="n">
-        <v>1255500</v>
+        <v>1864200</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C4601</t>
+          <t>C4602</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SET PERRO PATROL C4601</t>
+          <t>AVION CON PISTA MODELOS STD C4602</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -11172,30 +11172,30 @@
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="N242" t="n">
-        <v>14050</v>
+        <v>8721.297429620599</v>
       </c>
       <c r="O242" t="n">
-        <v>1095900</v>
+        <v>2485569.767441871</v>
       </c>
       <c r="P242" t="n">
-        <v>23900</v>
+        <v>14900</v>
       </c>
       <c r="Q242" t="n">
-        <v>1864200</v>
+        <v>4246500</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C4602</t>
+          <t>C4603</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>AVION CON PISTA MODELOS STD C4602</t>
+          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -11218,30 +11218,30 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="N243" t="n">
-        <v>8700</v>
+        <v>3639.35</v>
       </c>
       <c r="O243" t="n">
-        <v>2479500</v>
+        <v>1401149.75</v>
       </c>
       <c r="P243" t="n">
-        <v>14900</v>
+        <v>7500</v>
       </c>
       <c r="Q243" t="n">
-        <v>4246500</v>
+        <v>2887500</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C4603</t>
+          <t>C4604</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER SENCILLO C4603</t>
+          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>385</v>
+        <v>1709</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -11264,30 +11264,30 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>385</v>
+        <v>1709</v>
       </c>
       <c r="N244" t="n">
-        <v>3639.35</v>
+        <v>1326</v>
       </c>
       <c r="O244" t="n">
-        <v>1401149.75</v>
+        <v>2266134</v>
       </c>
       <c r="P244" t="n">
-        <v>7500</v>
+        <v>2500</v>
       </c>
       <c r="Q244" t="n">
-        <v>2887500</v>
+        <v>4272500</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C4604</t>
+          <t>C4605</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>MQUILLAJE BLISTER MODELOS STDS C4604</t>
+          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>1709</v>
+        <v>176</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -11310,30 +11310,30 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>1709</v>
+        <v>176</v>
       </c>
       <c r="N245" t="n">
-        <v>1326</v>
+        <v>5640</v>
       </c>
       <c r="O245" t="n">
-        <v>2266134</v>
+        <v>992640</v>
       </c>
       <c r="P245" t="n">
-        <v>2500</v>
+        <v>9900</v>
       </c>
       <c r="Q245" t="n">
-        <v>4272500</v>
+        <v>1742400</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>C4605</t>
+          <t>C4606</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>MAQUILLAJE BLISTER  CORAZON C4605</t>
+          <t>SONAJERO EN CAJA 6PCS C4606</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -11356,30 +11356,30 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="N246" t="n">
-        <v>5640</v>
+        <v>10713.21</v>
       </c>
       <c r="O246" t="n">
-        <v>992640</v>
+        <v>2988985.59</v>
       </c>
       <c r="P246" t="n">
-        <v>9900</v>
+        <v>20900</v>
       </c>
       <c r="Q246" t="n">
-        <v>1742400</v>
+        <v>5831100</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C4606</t>
+          <t>C4607</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 6PCS C4606</t>
+          <t>MAQUILLAJE SIRENA C4607</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -11402,30 +11402,30 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="N247" t="n">
-        <v>10713.21</v>
+        <v>10817</v>
       </c>
       <c r="O247" t="n">
-        <v>2988985.59</v>
+        <v>1719903</v>
       </c>
       <c r="P247" t="n">
-        <v>20900</v>
+        <v>17900</v>
       </c>
       <c r="Q247" t="n">
-        <v>5831100</v>
+        <v>2846100</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C4607</t>
+          <t>C4609</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>MAQUILLAJE SIRENA C4607</t>
+          <t>MAQUILLAJE UNICORNIO C4609</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -11448,30 +11448,30 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N248" t="n">
-        <v>10817</v>
+        <v>12489</v>
       </c>
       <c r="O248" t="n">
-        <v>1719903</v>
+        <v>1461213</v>
       </c>
       <c r="P248" t="n">
-        <v>17900</v>
+        <v>20900</v>
       </c>
       <c r="Q248" t="n">
-        <v>2846100</v>
+        <v>2445300</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C4609</t>
+          <t>C4612</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>MAQUILLAJE UNICORNIO C4609</t>
+          <t>CARRUAJE MUÑECA C4612</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>117</v>
+        <v>181</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -11494,30 +11494,30 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>117</v>
+        <v>181</v>
       </c>
       <c r="N249" t="n">
-        <v>12489</v>
+        <v>21762</v>
       </c>
       <c r="O249" t="n">
-        <v>1461213</v>
+        <v>3938922</v>
       </c>
       <c r="P249" t="n">
-        <v>20900</v>
+        <v>35900</v>
       </c>
       <c r="Q249" t="n">
-        <v>2445300</v>
+        <v>6497900</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C4612</t>
+          <t>C4613</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CARRUAJE MUÑECA C4612</t>
+          <t>DIDACTICOS ARMABLES STD C4613</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>181</v>
+        <v>934</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -11540,30 +11540,30 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>181</v>
+        <v>934</v>
       </c>
       <c r="N250" t="n">
-        <v>21762</v>
+        <v>3821</v>
       </c>
       <c r="O250" t="n">
-        <v>3938922</v>
+        <v>3568814</v>
       </c>
       <c r="P250" t="n">
-        <v>35900</v>
+        <v>5900</v>
       </c>
       <c r="Q250" t="n">
-        <v>6497900</v>
+        <v>5510600</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>C4613</t>
+          <t>C4614</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>DIDACTICOS ARMABLES STD C4613</t>
+          <t>CASTILLO NIÑA C4614</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>934</v>
+        <v>144</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -11586,30 +11586,30 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>934</v>
+        <v>144</v>
       </c>
       <c r="N251" t="n">
-        <v>3821</v>
+        <v>15472</v>
       </c>
       <c r="O251" t="n">
-        <v>3568814</v>
+        <v>2227968</v>
       </c>
       <c r="P251" t="n">
-        <v>5900</v>
+        <v>25900</v>
       </c>
       <c r="Q251" t="n">
-        <v>5510600</v>
+        <v>3729600</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C4614</t>
+          <t>C4616</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>CASTILLO NIÑA C4614</t>
+          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -11623,7 +11623,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11632,30 +11632,30 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="N252" t="n">
-        <v>15472</v>
+        <v>48522</v>
       </c>
       <c r="O252" t="n">
-        <v>2227968</v>
+        <v>388176</v>
       </c>
       <c r="P252" t="n">
-        <v>25900</v>
+        <v>77900</v>
       </c>
       <c r="Q252" t="n">
-        <v>3729600</v>
+        <v>623200</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C4616</t>
+          <t>C4617</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>CARRO TRANSFORME AMARILLO RECARGABLE C4616</t>
+          <t>CARRO TRANSFORME AZUL RECARGABLE C4617</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -11669,7 +11669,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11678,30 +11678,30 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N253" t="n">
-        <v>48522</v>
+        <v>53814.84</v>
       </c>
       <c r="O253" t="n">
-        <v>388176</v>
+        <v>538148.3999999999</v>
       </c>
       <c r="P253" t="n">
-        <v>77900</v>
+        <v>88900</v>
       </c>
       <c r="Q253" t="n">
-        <v>623200</v>
+        <v>889000</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C4617</t>
+          <t>C4622</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>CARRO TRANSFORME AZUL RECARGABLE C4617</t>
+          <t>CARRO COLECCION X8 C4622</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -11724,30 +11724,30 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="N254" t="n">
-        <v>53814.84</v>
+        <v>5476</v>
       </c>
       <c r="O254" t="n">
-        <v>538148.3999999999</v>
+        <v>1314240</v>
       </c>
       <c r="P254" t="n">
-        <v>88900</v>
+        <v>8900</v>
       </c>
       <c r="Q254" t="n">
-        <v>889000</v>
+        <v>2136000</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C4622</t>
+          <t>C4629</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>CARRO COLECCION X8 C4622</t>
+          <t>COMPUTADOR USB CABLE C4629</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -11761,7 +11761,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11770,30 +11770,30 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="N255" t="n">
-        <v>5476</v>
+        <v>64612</v>
       </c>
       <c r="O255" t="n">
-        <v>1314240</v>
+        <v>2326032</v>
       </c>
       <c r="P255" t="n">
-        <v>8900</v>
+        <v>103900</v>
       </c>
       <c r="Q255" t="n">
-        <v>2136000</v>
+        <v>3740400</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C4629</t>
+          <t>C4630</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB CABLE C4629</t>
+          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11816,30 +11816,30 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N256" t="n">
-        <v>64612</v>
+        <v>38252</v>
       </c>
       <c r="O256" t="n">
-        <v>2326032</v>
+        <v>2142112</v>
       </c>
       <c r="P256" t="n">
-        <v>103900</v>
+        <v>61900</v>
       </c>
       <c r="Q256" t="n">
-        <v>3740400</v>
+        <v>3466400</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C4630</t>
+          <t>C4631</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>COMPUTADOR USB INGLES/ESPAÑOL C4630</t>
+          <t>SQUISHY MOSTRICO STD C4631</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>56</v>
+        <v>864</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -11862,30 +11862,30 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>56</v>
+        <v>864</v>
       </c>
       <c r="N257" t="n">
-        <v>38252</v>
+        <v>1516.0387603223</v>
       </c>
       <c r="O257" t="n">
-        <v>2142112</v>
+        <v>1309857.488918467</v>
       </c>
       <c r="P257" t="n">
-        <v>61900</v>
+        <v>2300</v>
       </c>
       <c r="Q257" t="n">
-        <v>3466400</v>
+        <v>1987200</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C4631</t>
+          <t>C466-IO</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>SQUISHY MOSTRICO STD C4631</t>
+          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -11908,30 +11908,30 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>864</v>
+        <v>1050</v>
       </c>
       <c r="N258" t="n">
-        <v>1516.0387603223</v>
+        <v>356.78</v>
       </c>
       <c r="O258" t="n">
-        <v>1309857.488918467</v>
+        <v>374619</v>
       </c>
       <c r="P258" t="n">
-        <v>2300</v>
+        <v>300</v>
       </c>
       <c r="Q258" t="n">
-        <v>1987200</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C466-IO</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS TORNASOL Y MATE</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11954,44 +11954,42 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="N259" t="n">
-        <v>356.78</v>
+        <v>2454</v>
       </c>
       <c r="O259" t="n">
-        <v>374619</v>
+        <v>1349700</v>
       </c>
       <c r="P259" t="n">
-        <v>300</v>
+        <v>4200</v>
       </c>
       <c r="Q259" t="n">
-        <v>315000</v>
+        <v>2310000</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C476</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>6932001041468</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>YENGA MADERA GRABDE</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J260" t="n">
-        <v>550</v>
+        <v>54</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -12000,42 +11998,44 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>550</v>
+        <v>54</v>
       </c>
       <c r="N260" t="n">
-        <v>2454</v>
+        <v>5347.73</v>
       </c>
       <c r="O260" t="n">
-        <v>1349700</v>
+        <v>288777.42</v>
       </c>
       <c r="P260" t="n">
-        <v>4200</v>
+        <v>9500</v>
       </c>
       <c r="Q260" t="n">
-        <v>2310000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>C476</t>
-        </is>
-      </c>
-      <c r="B261" t="n">
-        <v>6932001041468</v>
+          <t>C4810</t>
+        </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>YENGA MADERA GRABDE</t>
+          <t>JUEGO DE AJEDREZ 13 EN 1 C4810</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J261" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -12044,30 +12044,30 @@
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="N261" t="n">
-        <v>5347.73</v>
+        <v>14003</v>
       </c>
       <c r="O261" t="n">
-        <v>288777.42</v>
+        <v>308066</v>
       </c>
       <c r="P261" t="n">
-        <v>9500</v>
+        <v>22500</v>
       </c>
       <c r="Q261" t="n">
-        <v>513000</v>
+        <v>495000</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>C4810</t>
+          <t>C4812</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>JUEGO DE AJEDREZ 13 EN 1 C4810</t>
+          <t>BURBUJERO DE ESPADA 44cm</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>22</v>
+        <v>4464</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -12090,30 +12090,30 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>22</v>
+        <v>4464</v>
       </c>
       <c r="N262" t="n">
-        <v>14003</v>
+        <v>1801</v>
       </c>
       <c r="O262" t="n">
-        <v>308066</v>
+        <v>8039664</v>
       </c>
       <c r="P262" t="n">
-        <v>22500</v>
+        <v>2900</v>
       </c>
       <c r="Q262" t="n">
-        <v>495000</v>
+        <v>12945600</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>C4812</t>
+          <t>C494-IO</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>BURBUJERO DE ESPADA 44cm</t>
+          <t>GLOBO METALIZADO DULCES</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>4464</v>
+        <v>1352</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -12136,44 +12136,42 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>4464</v>
+        <v>1352</v>
       </c>
       <c r="N263" t="n">
-        <v>1801</v>
+        <v>1200</v>
       </c>
       <c r="O263" t="n">
-        <v>8039664</v>
+        <v>1622400</v>
       </c>
       <c r="P263" t="n">
-        <v>2900</v>
+        <v>1500</v>
       </c>
       <c r="Q263" t="n">
-        <v>12945600</v>
+        <v>2028000</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>C494-IO</t>
-        </is>
+          <t>C502</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>6952216485215</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>GLOBO METALIZADO DULCES</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>C502 MUNECA NANCY GRANDE</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J264" t="n">
-        <v>1352</v>
+        <v>55</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -12182,42 +12180,47 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>1352</v>
+        <v>55</v>
       </c>
       <c r="N264" t="n">
-        <v>1200</v>
+        <v>15423.36</v>
       </c>
       <c r="O264" t="n">
-        <v>1622400</v>
+        <v>848284.8</v>
       </c>
       <c r="P264" t="n">
-        <v>1500</v>
+        <v>24900</v>
       </c>
       <c r="Q264" t="n">
-        <v>2028000</v>
+        <v>1369500</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>C502</t>
+          <t>C5030</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>6952216485215</v>
+        <v>6999899236062</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>C502 MUNECA NANCY GRANDE</t>
+          <t>INFLABLE DONA LLANTA C5030</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J265" t="n">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -12226,33 +12229,33 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="N265" t="n">
-        <v>15423.36</v>
+        <v>2857.22</v>
       </c>
       <c r="O265" t="n">
-        <v>848284.8</v>
+        <v>345723.62</v>
       </c>
       <c r="P265" t="n">
-        <v>24900</v>
+        <v>4900</v>
       </c>
       <c r="Q265" t="n">
-        <v>1369500</v>
+        <v>592900</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>C5030</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>6999899236062</v>
+        <v>6999899236154</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>INFLABLE DONA LLANTA C5030</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -12266,7 +12269,7 @@
         </is>
       </c>
       <c r="J266" t="n">
-        <v>121</v>
+        <v>534</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -12275,47 +12278,42 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>121</v>
+        <v>534</v>
       </c>
       <c r="N266" t="n">
-        <v>2857.22</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O266" t="n">
-        <v>345723.62</v>
+        <v>4776832.92</v>
       </c>
       <c r="P266" t="n">
-        <v>4900</v>
+        <v>14900</v>
       </c>
       <c r="Q266" t="n">
-        <v>592900</v>
+        <v>7956600</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>C5032</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>6999899236154</v>
+        <v>6952365180054</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO BURBUJA 30</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J267" t="n">
-        <v>534</v>
+        <v>3650</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -12324,42 +12322,44 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>534</v>
+        <v>3650</v>
       </c>
       <c r="N267" t="n">
-        <v>8945.379999999999</v>
+        <v>675.2255375485</v>
       </c>
       <c r="O267" t="n">
-        <v>4776832.92</v>
+        <v>2464573.212052025</v>
       </c>
       <c r="P267" t="n">
-        <v>14900</v>
+        <v>1300</v>
       </c>
       <c r="Q267" t="n">
-        <v>7956600</v>
+        <v>4745000</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>C506</t>
-        </is>
-      </c>
-      <c r="B268" t="n">
-        <v>6952365180054</v>
+          <t>C510-IO</t>
+        </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA 30</t>
+          <t>GLOBO BURBUJA METALIZADO</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J268" t="n">
-        <v>3650</v>
+        <v>3896</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -12368,44 +12368,42 @@
         <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>3650</v>
+        <v>3896</v>
       </c>
       <c r="N268" t="n">
-        <v>675.2255375485</v>
+        <v>960</v>
       </c>
       <c r="O268" t="n">
-        <v>2464573.212052025</v>
+        <v>3740160</v>
       </c>
       <c r="P268" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="Q268" t="n">
-        <v>4745000</v>
+        <v>4675200</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>C510-IO</t>
-        </is>
+          <t>C515</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>6953626330010</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA METALIZADO</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>GLOBO FIGURAS BURBUJA</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J269" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -12414,42 +12412,44 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>3896</v>
+        <v>3800</v>
       </c>
       <c r="N269" t="n">
-        <v>960</v>
+        <v>583.7204926325001</v>
       </c>
       <c r="O269" t="n">
-        <v>3740160</v>
+        <v>2218137.8720035</v>
       </c>
       <c r="P269" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="Q269" t="n">
-        <v>4675200</v>
+        <v>2280000</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>C515</t>
-        </is>
-      </c>
-      <c r="B270" t="n">
-        <v>6953626330010</v>
+          <t>C5214</t>
+        </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>GLOBO FIGURAS BURBUJA</t>
+          <t>CUBO C5214</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J270" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -12458,44 +12458,42 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>3800</v>
+        <v>1440</v>
       </c>
       <c r="N270" t="n">
-        <v>583.7204926325001</v>
+        <v>1690.8700092894</v>
       </c>
       <c r="O270" t="n">
-        <v>2218137.8720035</v>
+        <v>2434852.813376736</v>
       </c>
       <c r="P270" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="Q270" t="n">
-        <v>2280000</v>
+        <v>4320000</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>C5214</t>
-        </is>
+          <t>C523</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>6957430180212</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>CUBO C5214</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J271" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -12504,33 +12502,33 @@
         <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>1440</v>
+        <v>2556</v>
       </c>
       <c r="N271" t="n">
-        <v>1690.8700092807</v>
+        <v>481.48791226097</v>
       </c>
       <c r="O271" t="n">
-        <v>2434852.813364208</v>
+        <v>1230683.103739039</v>
       </c>
       <c r="P271" t="n">
-        <v>3000</v>
+        <v>650</v>
       </c>
       <c r="Q271" t="n">
-        <v>4320000</v>
+        <v>1661400</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>C523</t>
+          <t>C524</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>6957430180212</v>
+        <v>6957430180229</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16PLATEADO Y DORADO</t>
+          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -12539,7 +12537,7 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -12548,42 +12546,47 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>2556</v>
+        <v>614</v>
       </c>
       <c r="N272" t="n">
-        <v>481.48791226097</v>
+        <v>872.15418687873</v>
       </c>
       <c r="O272" t="n">
-        <v>1230683.103739039</v>
+        <v>535502.6707435403</v>
       </c>
       <c r="P272" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="Q272" t="n">
-        <v>1661400</v>
+        <v>736800</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>C524</t>
+          <t>C5246/C5247</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>6957430180229</v>
+        <v>6900077483239</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 PLATEADO Y DORADO</t>
+          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J273" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -12592,47 +12595,42 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>614</v>
+        <v>130</v>
       </c>
       <c r="N273" t="n">
-        <v>872.15418687873</v>
+        <v>8702.219999999999</v>
       </c>
       <c r="O273" t="n">
-        <v>535502.6707435403</v>
+        <v>1131288.6</v>
       </c>
       <c r="P273" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="Q273" t="n">
-        <v>736800</v>
+        <v>1157000</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>C5246/C5247</t>
+          <t>C525</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>6900077483239</v>
+        <v>6957430180236</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>MARIONETA DE DEDO ANIMALES STDS C5246/C5247</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J274" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12641,33 +12639,33 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>130</v>
+        <v>1436</v>
       </c>
       <c r="N274" t="n">
-        <v>8702.219999999999</v>
+        <v>345.55838633169</v>
       </c>
       <c r="O274" t="n">
-        <v>1131288.6</v>
+        <v>496221.8427723068</v>
       </c>
       <c r="P274" t="n">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="Q274" t="n">
-        <v>1157000</v>
+        <v>861600</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>C525</t>
+          <t>C526</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>6957430180236</v>
+        <v>6957430180243</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 16 COLORES Y PUNTOS</t>
+          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -12676,7 +12674,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12685,42 +12683,47 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>1436</v>
+        <v>11416</v>
       </c>
       <c r="N275" t="n">
-        <v>345.55838633169</v>
+        <v>711.33664937221</v>
       </c>
       <c r="O275" t="n">
-        <v>496221.8427723068</v>
+        <v>8120619.189233149</v>
       </c>
       <c r="P275" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="Q275" t="n">
-        <v>861600</v>
+        <v>10274400</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>C526</t>
+          <t>C527-IO</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>6957430180243</v>
+        <v>6957430180526</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 30 COLORES Y PUNTOS</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J276" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -12729,38 +12732,35 @@
         <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>11416</v>
+        <v>1242</v>
       </c>
       <c r="N276" t="n">
-        <v>711.33664937221</v>
+        <v>815.0599999999999</v>
       </c>
       <c r="O276" t="n">
-        <v>8120619.189233149</v>
+        <v>1012304.52</v>
       </c>
       <c r="P276" t="n">
         <v>900</v>
       </c>
       <c r="Q276" t="n">
-        <v>10274400</v>
+        <v>1117800</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>C527-IO</t>
-        </is>
-      </c>
-      <c r="B277" t="n">
-        <v>6957430180526</v>
+          <t>C541</t>
+        </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS LISTON</t>
+          <t>GLOBO LLAMA PQÑO</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -12778,30 +12778,30 @@
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>1242</v>
+        <v>2150</v>
       </c>
       <c r="N277" t="n">
-        <v>815.0599999999999</v>
+        <v>800</v>
       </c>
       <c r="O277" t="n">
-        <v>1012304.52</v>
+        <v>1720000</v>
       </c>
       <c r="P277" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Q277" t="n">
-        <v>1117800</v>
+        <v>2150000</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>C541</t>
+          <t>C575-IO</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>GLOBO LLAMA PQÑO</t>
+          <t>GLOBO UNICORNIO PQÑO</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -12815,7 +12815,7 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12824,35 +12824,38 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>2150</v>
+        <v>1001</v>
       </c>
       <c r="N278" t="n">
-        <v>800</v>
+        <v>320</v>
       </c>
       <c r="O278" t="n">
-        <v>1720000</v>
+        <v>320320</v>
       </c>
       <c r="P278" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="Q278" t="n">
-        <v>2150000</v>
+        <v>400400</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>C575-IO</t>
-        </is>
+          <t>C596-IO</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>8596162180268</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO PQÑO</t>
+          <t>GLOBO TE AMO</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -12861,7 +12864,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12870,33 +12873,33 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>1001</v>
+        <v>1455</v>
       </c>
       <c r="N279" t="n">
-        <v>320</v>
+        <v>1044.54</v>
       </c>
       <c r="O279" t="n">
-        <v>320320</v>
+        <v>1519805.7</v>
       </c>
       <c r="P279" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="Q279" t="n">
-        <v>400400</v>
+        <v>1746000</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>C596-IO</t>
+          <t>C60-IO</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>8596162180268</v>
+        <v>6524521011245</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>GLOBO TE AMO</t>
+          <t>GLOBO TIKTOK BOUQUET</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -12910,7 +12913,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12919,38 +12922,35 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>1455</v>
+        <v>740</v>
       </c>
       <c r="N280" t="n">
-        <v>1044.54</v>
+        <v>1989.05</v>
       </c>
       <c r="O280" t="n">
-        <v>1519805.7</v>
+        <v>1471897</v>
       </c>
       <c r="P280" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="Q280" t="n">
-        <v>1746000</v>
+        <v>2220000</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>C60-IO</t>
-        </is>
-      </c>
-      <c r="B281" t="n">
-        <v>6524521011245</v>
+          <t>C6074</t>
+        </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>GLOBO TIKTOK BOUQUET</t>
+          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -12968,44 +12968,42 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>740</v>
+        <v>25</v>
       </c>
       <c r="N281" t="n">
-        <v>1989.05</v>
+        <v>9447.25</v>
       </c>
       <c r="O281" t="n">
-        <v>1471897</v>
+        <v>236181.25</v>
       </c>
       <c r="P281" t="n">
-        <v>3000</v>
+        <v>9900</v>
       </c>
       <c r="Q281" t="n">
-        <v>2220000</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>C6074</t>
-        </is>
+          <t>C629</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>7791638082188</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>FIGURAS ALIMENTOS DECORATIVOS C6074</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>BURBUJERO PITO STD</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J282" t="n">
-        <v>25</v>
+        <v>15264</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -13014,42 +13012,47 @@
         <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>25</v>
+        <v>15264</v>
       </c>
       <c r="N282" t="n">
-        <v>9447.25</v>
+        <v>703.79485280542</v>
       </c>
       <c r="O282" t="n">
-        <v>236181.25</v>
+        <v>10742724.63322193</v>
       </c>
       <c r="P282" t="n">
-        <v>9900</v>
+        <v>900</v>
       </c>
       <c r="Q282" t="n">
-        <v>247500</v>
+        <v>13737600</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>C629</t>
+          <t>C6406</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>7791638082188</v>
+        <v>6820212541115</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>BURBUJERO PITO STD</t>
+          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J283" t="n">
-        <v>15264</v>
+        <v>52</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -13058,47 +13061,39 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>15264</v>
+        <v>52</v>
       </c>
       <c r="N283" t="n">
-        <v>703.79488357273</v>
+        <v>14260.14</v>
       </c>
       <c r="O283" t="n">
-        <v>10742725.10285415</v>
+        <v>741527.28</v>
       </c>
       <c r="P283" t="n">
-        <v>900</v>
+        <v>15900</v>
       </c>
       <c r="Q283" t="n">
-        <v>13737600</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>C6406</t>
-        </is>
-      </c>
-      <c r="B284" t="n">
-        <v>6820212541115</v>
+          <t>C642</t>
+        </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>LANZADOR AGUA</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J284" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -13107,39 +13102,44 @@
         <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>52</v>
+        <v>599</v>
       </c>
       <c r="N284" t="n">
-        <v>14260.14</v>
+        <v>2529.19</v>
       </c>
       <c r="O284" t="n">
-        <v>741527.28</v>
+        <v>1514984.81</v>
       </c>
       <c r="P284" t="n">
-        <v>15900</v>
+        <v>5100</v>
       </c>
       <c r="Q284" t="n">
-        <v>826800</v>
+        <v>3054900</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>C642</t>
+          <t>C671-LJ</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA</t>
+          <t>GLOBO UNICORNIO MEDIANO</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J285" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -13148,35 +13148,38 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>599</v>
+        <v>1397</v>
       </c>
       <c r="N285" t="n">
-        <v>2529.19</v>
+        <v>400</v>
       </c>
       <c r="O285" t="n">
-        <v>1514984.81</v>
+        <v>558800</v>
       </c>
       <c r="P285" t="n">
-        <v>5100</v>
+        <v>500</v>
       </c>
       <c r="Q285" t="n">
-        <v>3054900</v>
+        <v>698500</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>C671-LJ</t>
-        </is>
+          <t>C7005</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>6874123039124</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MEDIANO</t>
+          <t>MAQUINA DE COSER C7005</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -13185,7 +13188,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -13194,38 +13197,38 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>1397</v>
+        <v>208</v>
       </c>
       <c r="N286" t="n">
-        <v>400</v>
+        <v>6078.9925934066</v>
       </c>
       <c r="O286" t="n">
-        <v>558800</v>
+        <v>1264430.459428573</v>
       </c>
       <c r="P286" t="n">
-        <v>500</v>
+        <v>18500</v>
       </c>
       <c r="Q286" t="n">
-        <v>698500</v>
+        <v>3848000</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>C7005</t>
+          <t>C7009</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>6874123039124</v>
+        <v>2024250256831</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER C7005</t>
+          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -13234,7 +13237,7 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -13243,33 +13246,33 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="N287" t="n">
-        <v>6078.9925934066</v>
+        <v>5899.18</v>
       </c>
       <c r="O287" t="n">
-        <v>1264430.459428573</v>
+        <v>70790.16</v>
       </c>
       <c r="P287" t="n">
-        <v>18500</v>
+        <v>12500</v>
       </c>
       <c r="Q287" t="n">
-        <v>3848000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>C7009</t>
+          <t>C7038</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>2024250256831</v>
+        <v>5132595141631</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA  TUBO CON HELICE C7009</t>
+          <t>LANZADORA DE AGUA GLOBO C7038</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -13283,7 +13286,7 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -13292,38 +13295,38 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N288" t="n">
-        <v>5899.18</v>
+        <v>18423.71</v>
       </c>
       <c r="O288" t="n">
-        <v>70790.16</v>
+        <v>423745.33</v>
       </c>
       <c r="P288" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="Q288" t="n">
-        <v>150000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>C7038</t>
+          <t>C7039</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>5132595141631</v>
+        <v>5132594521182</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA GLOBO C7038</t>
+          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -13332,7 +13335,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13341,38 +13344,38 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N289" t="n">
-        <v>18423.71</v>
+        <v>10985.78</v>
       </c>
       <c r="O289" t="n">
-        <v>423745.33</v>
+        <v>219715.6</v>
       </c>
       <c r="P289" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Q289" t="n">
-        <v>230000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>C7039</t>
+          <t>C7040</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>5132594521182</v>
+        <v>6920373004365</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA GLOBO DELFIN C7039/M90-4</t>
+          <t>GARAJE EXIBICION CON LUZ C7040</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -13381,7 +13384,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13390,38 +13393,38 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="N290" t="n">
-        <v>10985.78</v>
+        <v>23452.77</v>
       </c>
       <c r="O290" t="n">
-        <v>219715.6</v>
+        <v>1102280.19</v>
       </c>
       <c r="P290" t="n">
-        <v>15000</v>
+        <v>39900</v>
       </c>
       <c r="Q290" t="n">
-        <v>300000</v>
+        <v>1875300</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>C7040</t>
+          <t>C7042</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>6920373004365</v>
+        <v>2024081616255</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>GARAJE EXIBICION CON LUZ C7040</t>
+          <t>CANCHA BASKETBALL WIN24 C7042</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -13430,7 +13433,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13439,38 +13442,35 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="N291" t="n">
-        <v>23452.77</v>
+        <v>9694.41</v>
       </c>
       <c r="O291" t="n">
-        <v>1102280.19</v>
+        <v>96944.10000000001</v>
       </c>
       <c r="P291" t="n">
-        <v>39900</v>
+        <v>32500</v>
       </c>
       <c r="Q291" t="n">
-        <v>1875300</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>C7042</t>
-        </is>
-      </c>
-      <c r="B292" t="n">
-        <v>2024081616255</v>
+          <t>C7080-BC</t>
+        </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>CANCHA BASKETBALL WIN24 C7042</t>
+          <t>ROBOT TRANSFORME STD C7080-BC</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13488,35 +13488,38 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="N292" t="n">
-        <v>9694.41</v>
+        <v>10556.12</v>
       </c>
       <c r="O292" t="n">
-        <v>96944.10000000001</v>
+        <v>411688.6800000001</v>
       </c>
       <c r="P292" t="n">
-        <v>32500</v>
+        <v>32900</v>
       </c>
       <c r="Q292" t="n">
-        <v>325000</v>
+        <v>1283100</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>C7080-BC</t>
-        </is>
+          <t>C7081</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>6301582313156</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ROBOT TRANSFORME STD C7080-BC</t>
+          <t>LANZADORA DARDOS DE PILA C7081</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>MUÑECOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -13525,7 +13528,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13534,47 +13537,42 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="N293" t="n">
-        <v>10556.12</v>
+        <v>22470.62</v>
       </c>
       <c r="O293" t="n">
-        <v>411688.6800000001</v>
+        <v>471883.02</v>
       </c>
       <c r="P293" t="n">
-        <v>32900</v>
+        <v>41900</v>
       </c>
       <c r="Q293" t="n">
-        <v>1283100</v>
+        <v>879900</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>C7081</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>6301582313156</v>
+        <v>5899989622205</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>LANZADORA DARDOS DE PILA C7081</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>LANZADORES</t>
+          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J294" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13583,42 +13581,44 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="N294" t="n">
-        <v>22470.62</v>
+        <v>1669.6</v>
       </c>
       <c r="O294" t="n">
-        <v>471883.02</v>
+        <v>654483.2</v>
       </c>
       <c r="P294" t="n">
-        <v>41900</v>
+        <v>2900</v>
       </c>
       <c r="Q294" t="n">
-        <v>879900</v>
+        <v>1136800</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>C71</t>
-        </is>
-      </c>
-      <c r="B295" t="n">
-        <v>5899989622205</v>
+          <t>C7117</t>
+        </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
+          <t>BINGO LOTTO C7117</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>JUEGOS DE MESA</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J295" t="n">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13627,35 +13627,35 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="N295" t="n">
-        <v>1669.6</v>
+        <v>5798.41</v>
       </c>
       <c r="O295" t="n">
-        <v>654483.2</v>
+        <v>115968.2</v>
       </c>
       <c r="P295" t="n">
-        <v>2900</v>
+        <v>14900</v>
       </c>
       <c r="Q295" t="n">
-        <v>1136800</v>
+        <v>298000</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>C7117</t>
+          <t>C7124</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>BINGO LOTTO C7117</t>
+          <t>TRAILER TRANFORME XQ05 C7124</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>JUEGOS DE MESA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -13664,7 +13664,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13673,35 +13673,35 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N296" t="n">
-        <v>5798.41</v>
+        <v>19587.53</v>
       </c>
       <c r="O296" t="n">
-        <v>115968.2</v>
+        <v>783501.2</v>
       </c>
       <c r="P296" t="n">
-        <v>14900</v>
+        <v>65000</v>
       </c>
       <c r="Q296" t="n">
-        <v>298000</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>C7124</t>
+          <t>C7132</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>TRAILER TRANFORME XQ05 C7124</t>
+          <t>SET PULSERAS Y CAUCHOS C7132</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13719,30 +13719,33 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="N297" t="n">
-        <v>19587.53</v>
+        <v>3100.87</v>
       </c>
       <c r="O297" t="n">
-        <v>783501.2</v>
+        <v>446525.28</v>
       </c>
       <c r="P297" t="n">
-        <v>65000</v>
+        <v>9900</v>
       </c>
       <c r="Q297" t="n">
-        <v>2600000</v>
+        <v>1425600</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C7132</t>
-        </is>
+          <t>C7147-A</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>6912209205022</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>SET PULSERAS Y CAUCHOS C7132</t>
+          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -13756,7 +13759,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13765,33 +13768,33 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="N298" t="n">
-        <v>3100.87</v>
+        <v>10348.08</v>
       </c>
       <c r="O298" t="n">
-        <v>446525.28</v>
+        <v>589840.5599999999</v>
       </c>
       <c r="P298" t="n">
-        <v>9900</v>
+        <v>16900</v>
       </c>
       <c r="Q298" t="n">
-        <v>1425600</v>
+        <v>963300</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>C7147-A</t>
+          <t>C7213</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>6912209205022</v>
+        <v>6987540143012</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>ANIMAL DINOSAURIO TRICERATOPS CONLUZ C7147-A</t>
+          <t>PESCADO CON LUZ Y SONIDO C7213</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -13805,7 +13808,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13814,33 +13817,33 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="N299" t="n">
-        <v>10348.08</v>
+        <v>9746.8801980198</v>
       </c>
       <c r="O299" t="n">
-        <v>589840.5599999999</v>
+        <v>467850.2495049504</v>
       </c>
       <c r="P299" t="n">
-        <v>16900</v>
+        <v>18500</v>
       </c>
       <c r="Q299" t="n">
-        <v>963300</v>
+        <v>888000</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>C7213</t>
+          <t>C7221</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>6987540143012</v>
+        <v>7453100037446</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>PESCADO CON LUZ Y SONIDO C7213</t>
+          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -13854,7 +13857,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13863,33 +13866,33 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>48</v>
+        <v>347</v>
       </c>
       <c r="N300" t="n">
-        <v>9746.8801980198</v>
+        <v>2672.89</v>
       </c>
       <c r="O300" t="n">
-        <v>467850.2495049504</v>
+        <v>927492.83</v>
       </c>
       <c r="P300" t="n">
-        <v>18500</v>
+        <v>10200</v>
       </c>
       <c r="Q300" t="n">
-        <v>888000</v>
+        <v>3539400</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>C7221</t>
+          <t>C7222</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>7453100037446</v>
+        <v>7453100037453</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>RELOJ CON FICHAS ARMABLES  C7221</t>
+          <t>RELOJ DIDACTICO CARACOL C7222</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -13903,7 +13906,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13912,33 +13915,33 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="N301" t="n">
-        <v>2672.89</v>
+        <v>4795.69</v>
       </c>
       <c r="O301" t="n">
-        <v>927492.83</v>
+        <v>1103008.7</v>
       </c>
       <c r="P301" t="n">
         <v>10200</v>
       </c>
       <c r="Q301" t="n">
-        <v>3539400</v>
+        <v>2346000</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>C7222</t>
+          <t>C7246</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>7453100037453</v>
+        <v>6902024622111</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>RELOJ DIDACTICO CARACOL C7222</t>
+          <t>BLÍSTER SKATE X4 C7246</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -13952,7 +13955,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>230</v>
+        <v>19</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13961,38 +13964,38 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>230</v>
+        <v>19</v>
       </c>
       <c r="N302" t="n">
-        <v>4795.69</v>
+        <v>2992.5708695652</v>
       </c>
       <c r="O302" t="n">
-        <v>1103008.7</v>
+        <v>56858.8465217388</v>
       </c>
       <c r="P302" t="n">
-        <v>10200</v>
+        <v>6000</v>
       </c>
       <c r="Q302" t="n">
-        <v>2346000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>C7246</t>
+          <t>C7294</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>6902024622111</v>
+        <v>6895675680022</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>BLÍSTER SKATE X4 C7246</t>
+          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -14001,7 +14004,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -14010,38 +14013,38 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="N303" t="n">
-        <v>2992.5708695652</v>
+        <v>4337.31</v>
       </c>
       <c r="O303" t="n">
-        <v>56858.8465217388</v>
+        <v>260238.6</v>
       </c>
       <c r="P303" t="n">
-        <v>6000</v>
+        <v>12900</v>
       </c>
       <c r="Q303" t="n">
-        <v>114000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>C7294</t>
+          <t>C7325</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>6895675680022</v>
+        <v>6974555555022</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>JUEGO DEPORTIVO HOCHEY C7294</t>
+          <t>PISTA EN BLISTER C7325</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -14050,7 +14053,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -14059,38 +14062,35 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N304" t="n">
-        <v>4337.31</v>
+        <v>3067.0906122449</v>
       </c>
       <c r="O304" t="n">
-        <v>260238.6</v>
+        <v>138019.0775510205</v>
       </c>
       <c r="P304" t="n">
-        <v>12900</v>
+        <v>7200</v>
       </c>
       <c r="Q304" t="n">
-        <v>774000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>C7325</t>
-        </is>
-      </c>
-      <c r="B305" t="n">
-        <v>6974555555022</v>
+          <t>C736</t>
+        </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>PISTA EN BLISTER C7325</t>
+          <t>GLOBO CORAZON GDE MENSAJE</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -14099,7 +14099,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -14108,35 +14108,38 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>45</v>
+        <v>2700</v>
       </c>
       <c r="N305" t="n">
-        <v>3067.0906122449</v>
+        <v>640</v>
       </c>
       <c r="O305" t="n">
-        <v>138019.0775510205</v>
+        <v>1728000</v>
       </c>
       <c r="P305" t="n">
-        <v>7200</v>
+        <v>800</v>
       </c>
       <c r="Q305" t="n">
-        <v>324000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>C736</t>
-        </is>
+          <t>C7365</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>6920240750050</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>GLOBO CORAZON GDE MENSAJE</t>
+          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -14145,7 +14148,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -14154,33 +14157,33 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>2700</v>
+        <v>19</v>
       </c>
       <c r="N306" t="n">
-        <v>640</v>
+        <v>4190.77</v>
       </c>
       <c r="O306" t="n">
-        <v>1728000</v>
+        <v>79624.63</v>
       </c>
       <c r="P306" t="n">
-        <v>800</v>
+        <v>5900</v>
       </c>
       <c r="Q306" t="n">
-        <v>2160000</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>C7365</t>
+          <t>C7366</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>6920240750050</v>
+        <v>6920240750098</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>DIDACTICO JIRAFA EN BOLSA C7365</t>
+          <t>TREN DIDACTICO EN BOLSA C7366</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -14194,7 +14197,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -14203,33 +14206,33 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="N307" t="n">
-        <v>4190.77</v>
+        <v>3499.72</v>
       </c>
       <c r="O307" t="n">
-        <v>79624.63</v>
+        <v>363970.88</v>
       </c>
       <c r="P307" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q307" t="n">
-        <v>112100</v>
+        <v>717600</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>C7366</t>
+          <t>C7368</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>6920240750098</v>
+        <v>6920240750159</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>TREN DIDACTICO EN BOLSA C7366</t>
+          <t>MOTO DIDACTICA EN BOLSA C736</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -14243,7 +14246,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -14252,38 +14255,35 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="N308" t="n">
-        <v>3499.72</v>
+        <v>4578.04</v>
       </c>
       <c r="O308" t="n">
-        <v>363970.88</v>
+        <v>723330.3199999999</v>
       </c>
       <c r="P308" t="n">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="Q308" t="n">
-        <v>717600</v>
+        <v>1185000</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>C7368</t>
-        </is>
-      </c>
-      <c r="B309" t="n">
-        <v>6920240750159</v>
+          <t>C740-IO</t>
+        </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>MOTO DIDACTICA EN BOLSA C736</t>
+          <t>GLOBO UNICORNIO MED</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -14292,7 +14292,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -14301,35 +14301,38 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>158</v>
+        <v>1876</v>
       </c>
       <c r="N309" t="n">
-        <v>4578.04</v>
+        <v>480</v>
       </c>
       <c r="O309" t="n">
-        <v>723330.3199999999</v>
+        <v>900480</v>
       </c>
       <c r="P309" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q309" t="n">
-        <v>1185000</v>
+        <v>1125600</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>C740-IO</t>
-        </is>
+          <t>C7413</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>6921202412870</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -14338,7 +14341,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -14347,38 +14350,35 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>1876</v>
+        <v>120</v>
       </c>
       <c r="N310" t="n">
-        <v>480</v>
+        <v>4159.0002996255</v>
       </c>
       <c r="O310" t="n">
-        <v>900480</v>
+        <v>499080.03595506</v>
       </c>
       <c r="P310" t="n">
-        <v>600</v>
+        <v>8900</v>
       </c>
       <c r="Q310" t="n">
-        <v>1125600</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>C7402</t>
-        </is>
-      </c>
-      <c r="B311" t="n">
-        <v>6920601877891</v>
+          <t>C744-IO</t>
+        </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>PANDERETA X 3 C7402</t>
+          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>60</v>
+        <v>478</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14396,38 +14396,38 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>60</v>
+        <v>478</v>
       </c>
       <c r="N311" t="n">
-        <v>2356.29</v>
+        <v>1554.12</v>
       </c>
       <c r="O311" t="n">
-        <v>141377.4</v>
+        <v>742869.36</v>
       </c>
       <c r="P311" t="n">
-        <v>6500</v>
+        <v>1900</v>
       </c>
       <c r="Q311" t="n">
-        <v>390000</v>
+        <v>908200</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>C7413</t>
+          <t>C7453</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>6921202412870</v>
+        <v>6920247274535</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
+          <t>JUEGO DE MESA BALONCESTO C7453</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -14445,35 +14445,35 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="N312" t="n">
-        <v>4159.0002996255</v>
+        <v>27938.1</v>
       </c>
       <c r="O312" t="n">
-        <v>499080.03595506</v>
+        <v>223504.8</v>
       </c>
       <c r="P312" t="n">
-        <v>8900</v>
+        <v>18000</v>
       </c>
       <c r="Q312" t="n">
-        <v>1068000</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>C744-IO</t>
+          <t>C7462</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>GLOBO FELIZ CUMPLEAÑOS COLORES Y PUNTOS</t>
+          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>GLOBOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -14482,7 +14482,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -14491,33 +14491,33 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="N313" t="n">
-        <v>1554.12</v>
+        <v>14751.820327869</v>
       </c>
       <c r="O313" t="n">
-        <v>742869.36</v>
+        <v>162270.023606559</v>
       </c>
       <c r="P313" t="n">
-        <v>1900</v>
+        <v>37100</v>
       </c>
       <c r="Q313" t="n">
-        <v>908200</v>
+        <v>408100</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>C7453</t>
+          <t>C7467</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>6920247274535</v>
+        <v>6920241023009</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>JUEGO DE MESA BALONCESTO C7453</t>
+          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -14531,7 +14531,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -14540,35 +14540,38 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N314" t="n">
-        <v>27938.1</v>
+        <v>15347.45</v>
       </c>
       <c r="O314" t="n">
-        <v>223504.8</v>
+        <v>230211.75</v>
       </c>
       <c r="P314" t="n">
-        <v>18000</v>
+        <v>23900</v>
       </c>
       <c r="Q314" t="n">
-        <v>144000</v>
+        <v>358500</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>C7462</t>
-        </is>
+          <t>C7488</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>6945158254520</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA ACCESORIOS PARA EL CABELLO C7462</t>
+          <t>SOPORTE CELULAR CON LUZ C7488</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -14577,7 +14580,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14586,33 +14589,33 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="N315" t="n">
-        <v>14751.820322581</v>
+        <v>8919.16</v>
       </c>
       <c r="O315" t="n">
-        <v>162270.023548391</v>
+        <v>258655.64</v>
       </c>
       <c r="P315" t="n">
-        <v>37100</v>
+        <v>10000</v>
       </c>
       <c r="Q315" t="n">
-        <v>408100</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>C7467</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>6920241023009</v>
+        <v>6905698382824</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA PARA NIÑAS C7467</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -14626,7 +14629,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14635,47 +14638,42 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N316" t="n">
-        <v>15347.45</v>
+        <v>1024.29</v>
       </c>
       <c r="O316" t="n">
-        <v>230211.75</v>
+        <v>1024.29</v>
       </c>
       <c r="P316" t="n">
-        <v>23900</v>
+        <v>2900</v>
       </c>
       <c r="Q316" t="n">
-        <v>358500</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>C7488</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>6945158254520</v>
+        <v>8596162180497</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>SOPORTE CELULAR CON LUZ C7488</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J317" t="n">
-        <v>29</v>
+        <v>1398</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -14684,47 +14682,42 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>29</v>
+        <v>1398</v>
       </c>
       <c r="N317" t="n">
-        <v>8919.16</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O317" t="n">
-        <v>258655.64</v>
+        <v>1626915.200678939</v>
       </c>
       <c r="P317" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="Q317" t="n">
-        <v>290000</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C753</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>6905698382824</v>
+        <v>8596162180503</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J318" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -14733,42 +14726,47 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="N318" t="n">
-        <v>1024.29</v>
+        <v>5113.4625508318</v>
       </c>
       <c r="O318" t="n">
-        <v>1024.29</v>
+        <v>1416429.126580409</v>
       </c>
       <c r="P318" t="n">
-        <v>2900</v>
+        <v>7000</v>
       </c>
       <c r="Q318" t="n">
-        <v>2900</v>
+        <v>1939000</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C7533</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>8596162180497</v>
+        <v>6923669699979</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>REPUESTO BIOGEL NEON C7533</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J319" t="n">
-        <v>1398</v>
+        <v>12023</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -14777,42 +14775,47 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>1398</v>
+        <v>12023</v>
       </c>
       <c r="N319" t="n">
-        <v>1163.7447787403</v>
+        <v>509.69</v>
       </c>
       <c r="O319" t="n">
-        <v>1626915.200678939</v>
+        <v>6128002.87</v>
       </c>
       <c r="P319" t="n">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="Q319" t="n">
-        <v>2097000</v>
+        <v>9017250</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>C753</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>8596162180503</v>
+        <v>6951241752002</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO GDE 4 PATAS</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J320" t="n">
-        <v>277</v>
+        <v>499</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14821,38 +14824,35 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>277</v>
+        <v>499</v>
       </c>
       <c r="N320" t="n">
-        <v>5113.4625508318</v>
+        <v>7046.939827363</v>
       </c>
       <c r="O320" t="n">
-        <v>1416429.126580409</v>
+        <v>3516422.973854137</v>
       </c>
       <c r="P320" t="n">
-        <v>7000</v>
+        <v>9900</v>
       </c>
       <c r="Q320" t="n">
-        <v>1939000</v>
+        <v>4940100</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>C7533</t>
-        </is>
-      </c>
-      <c r="B321" t="n">
-        <v>6923669699979</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>REPUESTO BIOGEL NEON C7533</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>12023</v>
+        <v>30</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14870,33 +14870,30 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>12023</v>
+        <v>30</v>
       </c>
       <c r="N321" t="n">
-        <v>509.69</v>
+        <v>24492.510949367</v>
       </c>
       <c r="O321" t="n">
-        <v>6128002.87</v>
+        <v>734775.3284810099</v>
       </c>
       <c r="P321" t="n">
-        <v>750</v>
+        <v>27900</v>
       </c>
       <c r="Q321" t="n">
-        <v>9017250</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B322" t="n">
-        <v>6951241752002</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -14910,7 +14907,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>499</v>
+        <v>188</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14919,35 +14916,38 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>499</v>
+        <v>188</v>
       </c>
       <c r="N322" t="n">
-        <v>7046.939827363</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O322" t="n">
-        <v>3516422.973854137</v>
+        <v>149706.28</v>
       </c>
       <c r="P322" t="n">
-        <v>9900</v>
+        <v>2500</v>
       </c>
       <c r="Q322" t="n">
-        <v>4940100</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>C7535</t>
-        </is>
+          <t>C7588</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>7588228020244</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
+          <t>SONAJERO LUZ PANDITA C7588</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -14956,7 +14956,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>30</v>
+        <v>1429</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14965,35 +14965,38 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>30</v>
+        <v>1429</v>
       </c>
       <c r="N323" t="n">
-        <v>24338.47</v>
+        <v>641.78</v>
       </c>
       <c r="O323" t="n">
-        <v>730154.1000000001</v>
+        <v>917103.62</v>
       </c>
       <c r="P323" t="n">
-        <v>27900</v>
+        <v>2500</v>
       </c>
       <c r="Q323" t="n">
-        <v>837000</v>
+        <v>3572500</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -15002,7 +15005,7 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -15011,30 +15014,33 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="N324" t="n">
-        <v>796.3099999999999</v>
+        <v>7811.9</v>
       </c>
       <c r="O324" t="n">
-        <v>149706.28</v>
+        <v>2156084.4</v>
       </c>
       <c r="P324" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q324" t="n">
-        <v>470000</v>
+        <v>3836400</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>C7560AC</t>
-        </is>
+          <t>C7614-F</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>6999899236130</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>TRICICLO INFANTIL OSITO C756AC</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -15048,7 +15054,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>10</v>
+        <v>382</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -15057,47 +15063,42 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>10</v>
+        <v>382</v>
       </c>
       <c r="N325" t="n">
-        <v>44113.604096386</v>
+        <v>3155</v>
       </c>
       <c r="O325" t="n">
-        <v>441136.04096386</v>
+        <v>1205210</v>
       </c>
       <c r="P325" t="n">
-        <v>71900</v>
+        <v>5900</v>
       </c>
       <c r="Q325" t="n">
-        <v>719000</v>
+        <v>2253800</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>C7588</t>
+          <t>C784</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>7588228020244</v>
+        <v>8913992935507</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ PANDITA C7588</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J326" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -15106,47 +15107,39 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="N326" t="n">
-        <v>641.78</v>
+        <v>704.8968946963899</v>
       </c>
       <c r="O326" t="n">
-        <v>917103.62</v>
+        <v>1022100.497309765</v>
       </c>
       <c r="P326" t="n">
-        <v>2500</v>
+        <v>900</v>
       </c>
       <c r="Q326" t="n">
-        <v>3572500</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>C7610</t>
-        </is>
-      </c>
-      <c r="B327" t="n">
-        <v>6999899236093</v>
+          <t>C815</t>
+        </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>SCOOTER HUMO</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J327" t="n">
-        <v>276</v>
+        <v>6</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15155,47 +15148,42 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>276</v>
+        <v>6</v>
       </c>
       <c r="N327" t="n">
-        <v>7811.9</v>
+        <v>110520.77</v>
       </c>
       <c r="O327" t="n">
-        <v>2156084.4</v>
+        <v>663124.62</v>
       </c>
       <c r="P327" t="n">
-        <v>13900</v>
+        <v>176900</v>
       </c>
       <c r="Q327" t="n">
-        <v>3836400</v>
+        <v>1061400</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>C7614-F</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>6999899236130</v>
+        <v>2087202108190</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J328" t="n">
-        <v>382</v>
+        <v>468</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15204,33 +15192,33 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>382</v>
+        <v>468</v>
       </c>
       <c r="N328" t="n">
-        <v>3155</v>
+        <v>6761.25</v>
       </c>
       <c r="O328" t="n">
-        <v>1205210</v>
+        <v>3164265</v>
       </c>
       <c r="P328" t="n">
-        <v>5900</v>
+        <v>5200</v>
       </c>
       <c r="Q328" t="n">
-        <v>2253800</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>C784</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>8913992935507</v>
+        <v>2021010563031</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -15239,7 +15227,7 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>1450</v>
+        <v>234</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -15248,30 +15236,35 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>1450</v>
+        <v>234</v>
       </c>
       <c r="N329" t="n">
-        <v>704.8968946963899</v>
+        <v>1008.8134367542</v>
       </c>
       <c r="O329" t="n">
-        <v>1022100.497309765</v>
+        <v>236062.3442004828</v>
       </c>
       <c r="P329" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="Q329" t="n">
-        <v>1305000</v>
+        <v>351000</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>C815</t>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>SCOOTER HUMO</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -15280,7 +15273,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>6</v>
+        <v>121</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -15289,42 +15282,49 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>6</v>
+        <v>121</v>
       </c>
       <c r="N330" t="n">
-        <v>110520.77</v>
+        <v>1520</v>
       </c>
       <c r="O330" t="n">
-        <v>663124.62</v>
+        <v>183920</v>
       </c>
       <c r="P330" t="n">
-        <v>176900</v>
+        <v>1900</v>
       </c>
       <c r="Q330" t="n">
-        <v>1061400</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>C819</t>
-        </is>
-      </c>
-      <c r="B331" t="n">
-        <v>2087202108190</v>
+          <t>C880</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>cg2016213</t>
+        </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J331" t="n">
-        <v>468</v>
+        <v>200</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
@@ -15333,33 +15333,30 @@
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>468</v>
+        <v>200</v>
       </c>
       <c r="N331" t="n">
-        <v>6761.25</v>
+        <v>1520</v>
       </c>
       <c r="O331" t="n">
-        <v>3164265</v>
+        <v>304000</v>
       </c>
       <c r="P331" t="n">
-        <v>5200</v>
+        <v>1900</v>
       </c>
       <c r="Q331" t="n">
-        <v>2433600</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B332" t="n">
-        <v>2021010563031</v>
+          <t>C888</t>
+        </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -15368,7 +15365,7 @@
         </is>
       </c>
       <c r="J332" t="n">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -15377,44 +15374,44 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="N332" t="n">
-        <v>1008.8134367542</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O332" t="n">
-        <v>236062.3442004828</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P332" t="n">
         <v>1500</v>
       </c>
       <c r="Q332" t="n">
-        <v>351000</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>C879</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>CG-2016-212</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>SNORKEL 66046A</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J333" t="n">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
@@ -15423,40 +15420,35 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="N333" t="n">
-        <v>1520</v>
+        <v>13493.858292683</v>
       </c>
       <c r="O333" t="n">
-        <v>183920</v>
+        <v>2415400.634390257</v>
       </c>
       <c r="P333" t="n">
-        <v>1900</v>
+        <v>16900</v>
       </c>
       <c r="Q333" t="n">
-        <v>229900</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>C880</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>cg2016213</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -15465,7 +15457,7 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>200</v>
+        <v>347</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
@@ -15474,39 +15466,49 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>200</v>
+        <v>347</v>
       </c>
       <c r="N334" t="n">
-        <v>1520</v>
+        <v>2644.9</v>
       </c>
       <c r="O334" t="n">
-        <v>304000</v>
+        <v>917780.3</v>
       </c>
       <c r="P334" t="n">
-        <v>1900</v>
+        <v>3900</v>
       </c>
       <c r="Q334" t="n">
-        <v>380000</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J335" t="n">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -15515,35 +15517,35 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="N335" t="n">
-        <v>1213.6821400778</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O335" t="n">
-        <v>205112.2816731482</v>
+        <v>33759.88</v>
       </c>
       <c r="P335" t="n">
-        <v>1500</v>
+        <v>29500</v>
       </c>
       <c r="Q335" t="n">
-        <v>253500</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -15552,7 +15554,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -15561,35 +15563,40 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="N336" t="n">
-        <v>13493.858292683</v>
+        <v>12189.831111111</v>
       </c>
       <c r="O336" t="n">
-        <v>2415400.634390257</v>
+        <v>219416.959999998</v>
       </c>
       <c r="P336" t="n">
-        <v>16900</v>
+        <v>30900</v>
       </c>
       <c r="Q336" t="n">
-        <v>3025100</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -15598,7 +15605,7 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>347</v>
+        <v>48</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -15607,40 +15614,35 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>347</v>
+        <v>48</v>
       </c>
       <c r="N337" t="n">
-        <v>2644.9</v>
+        <v>15452.21</v>
       </c>
       <c r="O337" t="n">
-        <v>917780.3</v>
+        <v>741706.08</v>
       </c>
       <c r="P337" t="n">
-        <v>3900</v>
+        <v>36500</v>
       </c>
       <c r="Q337" t="n">
-        <v>1353300</v>
+        <v>1752000</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -15649,7 +15651,7 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>4</v>
+        <v>363</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -15658,30 +15660,35 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>4</v>
+        <v>363</v>
       </c>
       <c r="N338" t="n">
-        <v>8439.969999999999</v>
+        <v>571.87</v>
       </c>
       <c r="O338" t="n">
-        <v>33759.88</v>
+        <v>207588.81</v>
       </c>
       <c r="P338" t="n">
-        <v>29500</v>
+        <v>2500</v>
       </c>
       <c r="Q338" t="n">
-        <v>118000</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -15695,7 +15702,7 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
@@ -15704,166 +15711,18 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="N339" t="n">
-        <v>12189.831111111</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O339" t="n">
-        <v>219416.959999998</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P339" t="n">
-        <v>30900</v>
+        <v>15900</v>
       </c>
       <c r="Q339" t="n">
-        <v>556200</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J340" t="n">
-        <v>48</v>
-      </c>
-      <c r="K340" t="n">
-        <v>0</v>
-      </c>
-      <c r="L340" t="n">
-        <v>0</v>
-      </c>
-      <c r="M340" t="n">
-        <v>48</v>
-      </c>
-      <c r="N340" t="n">
-        <v>15452.21</v>
-      </c>
-      <c r="O340" t="n">
-        <v>741706.08</v>
-      </c>
-      <c r="P340" t="n">
-        <v>36500</v>
-      </c>
-      <c r="Q340" t="n">
-        <v>1752000</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>MG40210</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>SONAJERO OSO MG40210</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J341" t="n">
-        <v>363</v>
-      </c>
-      <c r="K341" t="n">
-        <v>0</v>
-      </c>
-      <c r="L341" t="n">
-        <v>0</v>
-      </c>
-      <c r="M341" t="n">
-        <v>363</v>
-      </c>
-      <c r="N341" t="n">
-        <v>571.87</v>
-      </c>
-      <c r="O341" t="n">
-        <v>207588.81</v>
-      </c>
-      <c r="P341" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q341" t="n">
-        <v>907500</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J342" t="n">
-        <v>64</v>
-      </c>
-      <c r="K342" t="n">
-        <v>0</v>
-      </c>
-      <c r="L342" t="n">
-        <v>0</v>
-      </c>
-      <c r="M342" t="n">
-        <v>64</v>
-      </c>
-      <c r="N342" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O342" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P342" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q342" t="n">
         <v>1017600</v>
       </c>
     </row>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -642,10 +642,10 @@
         <v>275</v>
       </c>
       <c r="N6" t="n">
-        <v>27108.144192256</v>
+        <v>27000</v>
       </c>
       <c r="O6" t="n">
-        <v>7454739.6528704</v>
+        <v>7425000</v>
       </c>
       <c r="P6" t="n">
         <v>20000</v>
@@ -681,10 +681,10 @@
         <v>63</v>
       </c>
       <c r="N7" t="n">
-        <v>27117.391304348</v>
+        <v>27000</v>
       </c>
       <c r="O7" t="n">
-        <v>1708395.652173924</v>
+        <v>1701000</v>
       </c>
       <c r="P7" t="n">
         <v>30000</v>
@@ -1871,10 +1871,10 @@
         <v>62</v>
       </c>
       <c r="N36" t="n">
-        <v>27229.787234043</v>
+        <v>27000</v>
       </c>
       <c r="O36" t="n">
-        <v>1688246.808510666</v>
+        <v>1674000</v>
       </c>
       <c r="P36" t="n">
         <v>20000</v>
@@ -3155,10 +3155,10 @@
         <v>1232</v>
       </c>
       <c r="N66" t="n">
-        <v>5224.6087374335</v>
+        <v>5216.895993495</v>
       </c>
       <c r="O66" t="n">
-        <v>6436717.964518072</v>
+        <v>6427215.86398584</v>
       </c>
       <c r="P66" t="n">
         <v>8500</v>
@@ -3564,10 +3564,10 @@
         <v>346</v>
       </c>
       <c r="N75" t="n">
-        <v>4903.3514603175</v>
+        <v>4890.9300507937</v>
       </c>
       <c r="O75" t="n">
-        <v>1696559.605269855</v>
+        <v>1692261.79757462</v>
       </c>
       <c r="P75" t="n">
         <v>8200</v>
@@ -3884,10 +3884,10 @@
         <v>192</v>
       </c>
       <c r="N82" t="n">
-        <v>8184.2747524752</v>
+        <v>8154</v>
       </c>
       <c r="O82" t="n">
-        <v>1571380.752475238</v>
+        <v>1565568</v>
       </c>
       <c r="P82" t="n">
         <v>13500</v>
@@ -3930,10 +3930,10 @@
         <v>316</v>
       </c>
       <c r="N83" t="n">
-        <v>14831.411358927</v>
+        <v>14822.378829982</v>
       </c>
       <c r="O83" t="n">
-        <v>4686725.989420932</v>
+        <v>4683871.710274313</v>
       </c>
       <c r="P83" t="n">
         <v>24900</v>
@@ -5122,10 +5122,10 @@
         <v>432</v>
       </c>
       <c r="N109" t="n">
-        <v>11959.066350711</v>
+        <v>11921.4</v>
       </c>
       <c r="O109" t="n">
-        <v>5166316.663507152</v>
+        <v>5150044.8</v>
       </c>
       <c r="P109" t="n">
         <v>19900</v>
@@ -5879,10 +5879,10 @@
         <v>528</v>
       </c>
       <c r="N126" t="n">
-        <v>22541.90975</v>
+        <v>22485.6955</v>
       </c>
       <c r="O126" t="n">
-        <v>11902128.348</v>
+        <v>11872447.224</v>
       </c>
       <c r="P126" t="n">
         <v>36500</v>
@@ -6010,10 +6010,10 @@
         <v>180</v>
       </c>
       <c r="N129" t="n">
-        <v>24573.894298246</v>
+        <v>24538.02</v>
       </c>
       <c r="O129" t="n">
-        <v>4423300.97368428</v>
+        <v>4416843.6</v>
       </c>
       <c r="P129" t="n">
         <v>52900</v>
@@ -6591,10 +6591,10 @@
         <v>60</v>
       </c>
       <c r="N142" t="n">
-        <v>22690.398811881</v>
+        <v>21418.04</v>
       </c>
       <c r="O142" t="n">
-        <v>1361423.92871286</v>
+        <v>1285082.4</v>
       </c>
       <c r="P142" t="n">
         <v>34900</v>
@@ -6862,10 +6862,10 @@
         <v>144</v>
       </c>
       <c r="N148" t="n">
-        <v>27232.25996</v>
+        <v>27123.76488</v>
       </c>
       <c r="O148" t="n">
-        <v>3921445.43424</v>
+        <v>3905822.14272</v>
       </c>
       <c r="P148" t="n">
         <v>44500</v>
@@ -7046,10 +7046,10 @@
         <v>144</v>
       </c>
       <c r="N152" t="n">
-        <v>27011.040935673</v>
+        <v>26854</v>
       </c>
       <c r="O152" t="n">
-        <v>3889589.894736912</v>
+        <v>3866976</v>
       </c>
       <c r="P152" t="n">
         <v>43900</v>
@@ -7133,10 +7133,10 @@
         <v>31</v>
       </c>
       <c r="N154" t="n">
-        <v>13079.564264151</v>
+        <v>12981.59</v>
       </c>
       <c r="O154" t="n">
-        <v>405466.492188681</v>
+        <v>402429.29</v>
       </c>
       <c r="P154" t="n">
         <v>21900</v>
@@ -7179,10 +7179,10 @@
         <v>85</v>
       </c>
       <c r="N155" t="n">
-        <v>13974.031438356</v>
+        <v>13878.97</v>
       </c>
       <c r="O155" t="n">
-        <v>1187792.67226026</v>
+        <v>1179712.45</v>
       </c>
       <c r="P155" t="n">
         <v>21900</v>
@@ -9020,10 +9020,10 @@
         <v>216</v>
       </c>
       <c r="N195" t="n">
-        <v>9198.3277962348</v>
+        <v>9178</v>
       </c>
       <c r="O195" t="n">
-        <v>1986838.803986717</v>
+        <v>1982448</v>
       </c>
       <c r="P195" t="n">
         <v>14900</v>
@@ -9066,10 +9066,10 @@
         <v>147</v>
       </c>
       <c r="N196" t="n">
-        <v>13948.467680608</v>
+        <v>13922</v>
       </c>
       <c r="O196" t="n">
-        <v>2050424.749049376</v>
+        <v>2046534</v>
       </c>
       <c r="P196" t="n">
         <v>22900</v>
@@ -9112,10 +9112,10 @@
         <v>24</v>
       </c>
       <c r="N197" t="n">
-        <v>25260.382352941</v>
+        <v>25076</v>
       </c>
       <c r="O197" t="n">
-        <v>606249.176470584</v>
+        <v>601824</v>
       </c>
       <c r="P197" t="n">
         <v>40900</v>
@@ -9884,10 +9884,10 @@
         <v>256</v>
       </c>
       <c r="N214" t="n">
-        <v>13121.945155393</v>
+        <v>13098</v>
       </c>
       <c r="O214" t="n">
-        <v>3359217.959780608</v>
+        <v>3353088</v>
       </c>
       <c r="P214" t="n">
         <v>21200</v>
@@ -10482,10 +10482,10 @@
         <v>192</v>
       </c>
       <c r="N227" t="n">
-        <v>17123.621290098</v>
+        <v>17075.989518828</v>
       </c>
       <c r="O227" t="n">
-        <v>3287735.287698816</v>
+        <v>3278589.987614976</v>
       </c>
       <c r="P227" t="n">
         <v>27500</v>
@@ -10620,10 +10620,10 @@
         <v>67</v>
       </c>
       <c r="N230" t="n">
-        <v>21666.992481203</v>
+        <v>21346</v>
       </c>
       <c r="O230" t="n">
-        <v>1451688.496240601</v>
+        <v>1430182</v>
       </c>
       <c r="P230" t="n">
         <v>34900</v>
@@ -10807,10 +10807,10 @@
         <v>106</v>
       </c>
       <c r="N234" t="n">
-        <v>17325.987730061</v>
+        <v>17168</v>
       </c>
       <c r="O234" t="n">
-        <v>1836554.699386466</v>
+        <v>1819808</v>
       </c>
       <c r="P234" t="n">
         <v>27900</v>
@@ -10853,10 +10853,10 @@
         <v>32</v>
       </c>
       <c r="N235" t="n">
-        <v>20944.88372093</v>
+        <v>20014</v>
       </c>
       <c r="O235" t="n">
-        <v>670236.27906976</v>
+        <v>640448</v>
       </c>
       <c r="P235" t="n">
         <v>33900</v>
@@ -10899,10 +10899,10 @@
         <v>132</v>
       </c>
       <c r="N236" t="n">
-        <v>27289.075933076</v>
+        <v>27254</v>
       </c>
       <c r="O236" t="n">
-        <v>3602158.023166032</v>
+        <v>3597528</v>
       </c>
       <c r="P236" t="n">
         <v>43900</v>
@@ -11175,10 +11175,10 @@
         <v>285</v>
       </c>
       <c r="N242" t="n">
-        <v>8721.297429620599</v>
+        <v>8700</v>
       </c>
       <c r="O242" t="n">
-        <v>2485569.767441871</v>
+        <v>2479500</v>
       </c>
       <c r="P242" t="n">
         <v>14900</v>
@@ -14873,10 +14873,10 @@
         <v>30</v>
       </c>
       <c r="N321" t="n">
-        <v>24492.510949367</v>
+        <v>24338.47</v>
       </c>
       <c r="O321" t="n">
-        <v>734775.3284810099</v>
+        <v>730154.1000000001</v>
       </c>
       <c r="P321" t="n">
         <v>27900</v>

--- a/bodegas/LJ-02.xlsx
+++ b/bodegas/LJ-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q339"/>
+  <dimension ref="A1:Q338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-12</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1821,19 +1821,19 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
         <v>344599.17851064</v>
       </c>
       <c r="O35" t="n">
-        <v>2067595.07106384</v>
+        <v>1378396.71404256</v>
       </c>
       <c r="P35" t="n">
         <v>532900</v>
       </c>
       <c r="Q35" t="n">
-        <v>3197400</v>
+        <v>2131600</v>
       </c>
     </row>
     <row r="36">
@@ -3109,10 +3109,10 @@
         <v>350</v>
       </c>
       <c r="N65" t="n">
-        <v>2582.2551814224</v>
+        <v>2582.2551438323</v>
       </c>
       <c r="O65" t="n">
-        <v>903789.31349784</v>
+        <v>903789.300341305</v>
       </c>
       <c r="P65" t="n">
         <v>4500</v>
@@ -3155,10 +3155,10 @@
         <v>1232</v>
       </c>
       <c r="N66" t="n">
-        <v>5216.895993495</v>
+        <v>5216.8959816133</v>
       </c>
       <c r="O66" t="n">
-        <v>6427215.86398584</v>
+        <v>6427215.849347586</v>
       </c>
       <c r="P66" t="n">
         <v>8500</v>
@@ -3201,10 +3201,10 @@
         <v>2592</v>
       </c>
       <c r="N67" t="n">
-        <v>3158.8608347353</v>
+        <v>3158.8608348592</v>
       </c>
       <c r="O67" t="n">
-        <v>8187767.283633898</v>
+        <v>8187767.283955047</v>
       </c>
       <c r="P67" t="n">
         <v>5600</v>
@@ -3385,10 +3385,10 @@
         <v>648</v>
       </c>
       <c r="N71" t="n">
-        <v>3795.7100076132</v>
+        <v>3795.7100076147</v>
       </c>
       <c r="O71" t="n">
-        <v>2459620.084933354</v>
+        <v>2459620.084934325</v>
       </c>
       <c r="P71" t="n">
         <v>6200</v>
@@ -3564,10 +3564,10 @@
         <v>346</v>
       </c>
       <c r="N75" t="n">
-        <v>4890.9300507937</v>
+        <v>4890.9300509879</v>
       </c>
       <c r="O75" t="n">
-        <v>1692261.79757462</v>
+        <v>1692261.797641814</v>
       </c>
       <c r="P75" t="n">
         <v>8200</v>
@@ -3792,10 +3792,10 @@
         <v>240</v>
       </c>
       <c r="N80" t="n">
-        <v>3594.2534111187</v>
+        <v>3594.2533147632</v>
       </c>
       <c r="O80" t="n">
-        <v>862620.8186684881</v>
+        <v>862620.795543168</v>
       </c>
       <c r="P80" t="n">
         <v>6500</v>
@@ -3930,10 +3930,10 @@
         <v>316</v>
       </c>
       <c r="N83" t="n">
-        <v>14822.378829982</v>
+        <v>14822.378829268</v>
       </c>
       <c r="O83" t="n">
-        <v>4683871.710274313</v>
+        <v>4683871.710048688</v>
       </c>
       <c r="P83" t="n">
         <v>24900</v>
@@ -4341,10 +4341,10 @@
         <v>1356</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.171261065</v>
+        <v>4371.1712612367</v>
       </c>
       <c r="O92" t="n">
-        <v>5927308.23000414</v>
+        <v>5927308.230236965</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -5664,10 +5664,10 @@
         <v>480</v>
       </c>
       <c r="N121" t="n">
-        <v>4196.8725410978</v>
+        <v>4196.872541806</v>
       </c>
       <c r="O121" t="n">
-        <v>2014498.819726944</v>
+        <v>2014498.82006688</v>
       </c>
       <c r="P121" t="n">
         <v>5900</v>
@@ -5838,10 +5838,10 @@
         <v>432</v>
       </c>
       <c r="N125" t="n">
-        <v>2029.8740628386</v>
+        <v>2029.8740827436</v>
       </c>
       <c r="O125" t="n">
-        <v>876905.5951462751</v>
+        <v>876905.6037452351</v>
       </c>
       <c r="P125" t="n">
         <v>3600</v>
@@ -5879,10 +5879,10 @@
         <v>528</v>
       </c>
       <c r="N126" t="n">
-        <v>22485.6955</v>
+        <v>22485.695494368</v>
       </c>
       <c r="O126" t="n">
-        <v>11872447.224</v>
+        <v>11872447.2210263</v>
       </c>
       <c r="P126" t="n">
         <v>36500</v>
@@ -6235,10 +6235,10 @@
         <v>799</v>
       </c>
       <c r="N134" t="n">
-        <v>998.76126091703</v>
+        <v>998.76126229508</v>
       </c>
       <c r="O134" t="n">
-        <v>798010.2474727069</v>
+        <v>798010.2485737689</v>
       </c>
       <c r="P134" t="n">
         <v>1600</v>
@@ -6284,10 +6284,10 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>4285.1960620525</v>
+        <v>4285.1961426844</v>
       </c>
       <c r="O135" t="n">
-        <v>154267.05823389</v>
+        <v>154267.0611366384</v>
       </c>
       <c r="P135" t="n">
         <v>6900</v>
@@ -6458,10 +6458,10 @@
         <v>228</v>
       </c>
       <c r="N139" t="n">
-        <v>4814.2679276196</v>
+        <v>4814.2679275122</v>
       </c>
       <c r="O139" t="n">
-        <v>1097653.087497269</v>
+        <v>1097653.087472782</v>
       </c>
       <c r="P139" t="n">
         <v>9900</v>
@@ -6862,10 +6862,10 @@
         <v>144</v>
       </c>
       <c r="N148" t="n">
-        <v>27123.76488</v>
+        <v>27123.764869739</v>
       </c>
       <c r="O148" t="n">
-        <v>3905822.14272</v>
+        <v>3905822.141242416</v>
       </c>
       <c r="P148" t="n">
         <v>44500</v>
@@ -7821,10 +7821,10 @@
         <v>680</v>
       </c>
       <c r="N169" t="n">
-        <v>1778.4727487406</v>
+        <v>1778.4727855775</v>
       </c>
       <c r="O169" t="n">
-        <v>1209361.469143608</v>
+        <v>1209361.4941927</v>
       </c>
       <c r="P169" t="n">
         <v>4900</v>
@@ -9342,10 +9342,10 @@
         <v>280</v>
       </c>
       <c r="N202" t="n">
-        <v>3903.7386507259</v>
+        <v>3903.7388113695</v>
       </c>
       <c r="O202" t="n">
-        <v>1093046.822203252</v>
+        <v>1093046.86718346</v>
       </c>
       <c r="P202" t="n">
         <v>7500</v>
@@ -11865,10 +11865,10 @@
         <v>864</v>
       </c>
       <c r="N257" t="n">
-        <v>1516.0387603223</v>
+        <v>1516.0387548048</v>
       </c>
       <c r="O257" t="n">
-        <v>1309857.488918467</v>
+        <v>1309857.484151347</v>
       </c>
       <c r="P257" t="n">
         <v>2300</v>
@@ -13015,10 +13015,10 @@
         <v>15264</v>
       </c>
       <c r="N282" t="n">
-        <v>703.79485280542</v>
+        <v>703.79483731577</v>
       </c>
       <c r="O282" t="n">
-        <v>10742724.63322193</v>
+        <v>10742724.39678791</v>
       </c>
       <c r="P282" t="n">
         <v>900</v>
@@ -13820,10 +13820,10 @@
         <v>48</v>
       </c>
       <c r="N299" t="n">
-        <v>9746.8801980198</v>
+        <v>9746.8802</v>
       </c>
       <c r="O299" t="n">
-        <v>467850.2495049504</v>
+        <v>467850.2496</v>
       </c>
       <c r="P299" t="n">
         <v>18500</v>
@@ -13967,10 +13967,10 @@
         <v>19</v>
       </c>
       <c r="N302" t="n">
-        <v>2992.5708695652</v>
+        <v>2992.5720967742</v>
       </c>
       <c r="O302" t="n">
-        <v>56858.8465217388</v>
+        <v>56858.8698387098</v>
       </c>
       <c r="P302" t="n">
         <v>6000</v>
@@ -15125,12 +15125,15 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>C815</t>
-        </is>
+          <t>C819</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>2087202108190</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>SCOOTER HUMO</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -15139,7 +15142,7 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>6</v>
+        <v>468</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -15148,33 +15151,33 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>6</v>
+        <v>468</v>
       </c>
       <c r="N327" t="n">
-        <v>110520.77</v>
+        <v>6761.25</v>
       </c>
       <c r="O327" t="n">
-        <v>663124.62</v>
+        <v>3164265</v>
       </c>
       <c r="P327" t="n">
-        <v>176900</v>
+        <v>5200</v>
       </c>
       <c r="Q327" t="n">
-        <v>1061400</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>C819</t>
+          <t>C84</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>2087202108190</v>
+        <v>2021010563031</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -15183,7 +15186,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>468</v>
+        <v>234</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -15192,33 +15195,35 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>468</v>
+        <v>234</v>
       </c>
       <c r="N328" t="n">
-        <v>6761.25</v>
+        <v>1008.8134367542</v>
       </c>
       <c r="O328" t="n">
-        <v>3164265</v>
+        <v>236062.3442004828</v>
       </c>
       <c r="P328" t="n">
-        <v>5200</v>
+        <v>1500</v>
       </c>
       <c r="Q328" t="n">
-        <v>2433600</v>
+        <v>351000</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B329" t="n">
-        <v>2021010563031</v>
+          <t>C879</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>CG-2016-212</t>
+        </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>VELA MARIPOSA</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -15227,7 +15232,7 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>234</v>
+        <v>121</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -15236,44 +15241,49 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>234</v>
+        <v>121</v>
       </c>
       <c r="N329" t="n">
-        <v>1008.8134367542</v>
+        <v>1520</v>
       </c>
       <c r="O329" t="n">
-        <v>236062.3442004828</v>
+        <v>183920</v>
       </c>
       <c r="P329" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q329" t="n">
-        <v>351000</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>C879</t>
+          <t>C880</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>CG-2016-212</t>
+          <t>cg2016213</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>VELA MARIPOSA</t>
+          <t>VELA FLOR</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>VELA</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J330" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -15282,49 +15292,39 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="N330" t="n">
         <v>1520</v>
       </c>
       <c r="O330" t="n">
-        <v>183920</v>
+        <v>304000</v>
       </c>
       <c r="P330" t="n">
         <v>1900</v>
       </c>
       <c r="Q330" t="n">
-        <v>229900</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>C880</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>cg2016213</t>
+          <t>C888</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>VELA FLOR</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>VELA</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J331" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
@@ -15333,39 +15333,44 @@
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="N331" t="n">
-        <v>1520</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O331" t="n">
-        <v>304000</v>
+        <v>205112.2816731482</v>
       </c>
       <c r="P331" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q331" t="n">
-        <v>380000</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>C888</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>SNORKEL 66046A</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J332" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -15374,30 +15379,30 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="N332" t="n">
-        <v>1213.6821400778</v>
+        <v>13493.858292683</v>
       </c>
       <c r="O332" t="n">
-        <v>205112.2816731482</v>
+        <v>2415400.634390257</v>
       </c>
       <c r="P332" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="Q332" t="n">
-        <v>253500</v>
+        <v>3025100</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -15411,7 +15416,7 @@
         </is>
       </c>
       <c r="J333" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
@@ -15420,35 +15425,40 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="N333" t="n">
-        <v>13493.858292683</v>
+        <v>2644.9</v>
       </c>
       <c r="O333" t="n">
-        <v>2415400.634390257</v>
+        <v>917780.3</v>
       </c>
       <c r="P333" t="n">
-        <v>16900</v>
+        <v>3900</v>
       </c>
       <c r="Q333" t="n">
-        <v>3025100</v>
+        <v>1353300</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -15457,7 +15467,7 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
@@ -15466,35 +15476,30 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>347</v>
+        <v>4</v>
       </c>
       <c r="N334" t="n">
-        <v>2644.9</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O334" t="n">
-        <v>917780.3</v>
+        <v>33759.88</v>
       </c>
       <c r="P334" t="n">
-        <v>3900</v>
+        <v>29500</v>
       </c>
       <c r="Q334" t="n">
-        <v>1353300</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -15508,7 +15513,7 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -15517,35 +15522,40 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N335" t="n">
-        <v>8439.969999999999</v>
+        <v>12189.831111111</v>
       </c>
       <c r="O335" t="n">
-        <v>33759.88</v>
+        <v>219416.959999998</v>
       </c>
       <c r="P335" t="n">
-        <v>29500</v>
+        <v>30900</v>
       </c>
       <c r="Q335" t="n">
-        <v>118000</v>
+        <v>556200</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -15554,7 +15564,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -15563,35 +15573,30 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="N336" t="n">
-        <v>12189.831111111</v>
+        <v>15452.21</v>
       </c>
       <c r="O336" t="n">
-        <v>219416.959999998</v>
+        <v>741706.08</v>
       </c>
       <c r="P336" t="n">
-        <v>30900</v>
+        <v>36500</v>
       </c>
       <c r="Q336" t="n">
-        <v>556200</v>
+        <v>1752000</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>MG30151</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>MG30151</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -15605,7 +15610,7 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>48</v>
+        <v>363</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -15614,35 +15619,40 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>48</v>
+        <v>363</v>
       </c>
       <c r="N337" t="n">
-        <v>15452.21</v>
+        <v>571.87</v>
       </c>
       <c r="O337" t="n">
-        <v>741706.08</v>
+        <v>207588.81</v>
       </c>
       <c r="P337" t="n">
-        <v>36500</v>
+        <v>2500</v>
       </c>
       <c r="Q337" t="n">
-        <v>1752000</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -15651,7 +15661,7 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>363</v>
+        <v>64</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -15660,69 +15670,18 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>363</v>
+        <v>64</v>
       </c>
       <c r="N338" t="n">
-        <v>571.87</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O338" t="n">
-        <v>207588.81</v>
+        <v>634690.5600000001</v>
       </c>
       <c r="P338" t="n">
-        <v>2500</v>
+        <v>15900</v>
       </c>
       <c r="Q338" t="n">
-        <v>907500</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J339" t="n">
-        <v>64</v>
-      </c>
-      <c r="K339" t="n">
-        <v>0</v>
-      </c>
-      <c r="L339" t="n">
-        <v>0</v>
-      </c>
-      <c r="M339" t="n">
-        <v>64</v>
-      </c>
-      <c r="N339" t="n">
-        <v>9917.040000000001</v>
-      </c>
-      <c r="O339" t="n">
-        <v>634690.5600000001</v>
-      </c>
-      <c r="P339" t="n">
-        <v>15900</v>
-      </c>
-      <c r="Q339" t="n">
         <v>1017600</v>
       </c>
     </row>
